--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,67 +418,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>season_label</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>is_rerun</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>broadcast_format</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>broadcast_start</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>animation_studio</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>op_title</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>op_artist</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ed_title</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ed_artist</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>detail_url</t>
         </is>
@@ -6163,62 +6151,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>season_label</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>anime_title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>is_rerun</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>song_title</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>artist</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>youtube_url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>youtube_views</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>youtube_channel</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last_searched_at</t>
         </is>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,67 +430,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>season_label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>is_rerun</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>broadcast_format</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>broadcast_start</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>animation_studio</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>op_title</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>op_artist</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ed_title</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ed_artist</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>detail_url</t>
         </is>
@@ -6151,62 +6163,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>season_label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>anime_title</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>is_rerun</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>song_title</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>artist</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>youtube_url</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>youtube_views</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>youtube_channel</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>last_searched_at</t>
         </is>
@@ -7223,10 +7235,24 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kh1PwoEsIf8</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>6842</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>おジャ魔女どれみ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:03:45</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7263,10 +7289,24 @@
           <t>i-dle</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JCDGaA2sfi0</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1260189</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>オタクに優しいギャルはいない!?</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:03:58</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -7303,10 +7343,24 @@
           <t>三四少女</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JCDGaA2sfi0</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1260189</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>オタクに優しいギャルはいない!?</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:04:11</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -7343,10 +7397,24 @@
           <t>子ザメちゃん(CV：花澤香菜)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Laf46YXDt68</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>874040</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>アニメ『おでかけ子ザメ』チャンネル</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:04:24</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -7383,10 +7451,24 @@
           <t>オーイシマサヨシ</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8Gtb1uhjPKs</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1174964</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:04:38</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -7423,10 +7505,24 @@
           <t>おねがいかなえ隊</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=j1J45v_al9s</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>140</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>真一チャンネル</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:04:51</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -7463,10 +7559,24 @@
           <t>いぎなり東北産</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bH8Ukl9BM0s</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>41469</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>【公式】アイプリちゅ〜ぶ</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:05:05</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -7503,10 +7613,24 @@
           <t>JAM Project</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1d_YJXQZUgQ</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>487771</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ヴァンガードチャンネル【アニメ「Divinez 幻真星戦編」配信中!!】</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:05:13</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -7543,10 +7667,24 @@
           <t>JAM Project</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1d_YJXQZUgQ</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>487771</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ヴァンガードチャンネル【アニメ「Divinez 幻真星戦編」配信中!!】</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:05:20</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -7863,10 +8001,24 @@
           <t>Faulieu.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SGtyPSZqb5s</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>335542</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Faulieu.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:05:49</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -7903,10 +8055,24 @@
           <t>あおぎり高校</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mHQi_a9MjkA</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>231842</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>あおぎり高校 - Aogiri Vtuber High School</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:06:02</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -7943,10 +8109,24 @@
           <t>雨宮天</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=R7u3ISKPujU</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>96474</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>雨宮天公式YouTubeチャンネル</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:06:15</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -8103,10 +8283,24 @@
           <t>yonige</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XX90FklAWsc</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>151203</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:06:40</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -8139,10 +8333,24 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JEiHCjhKRYw</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>66168</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:06:53</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -8179,10 +8387,24 @@
           <t>HOKUTO</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yxccM_weehk</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>135172</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>HOKUTO</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:07:06</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -8219,10 +8441,24 @@
           <t>内田真礼</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Oz5EkYVJbBc</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>72088</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>アニメ『神の雫』official YouTube channel</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:07:19</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -8259,10 +8495,24 @@
           <t>入野自由</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JMqsT9cPh1c</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>189836</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:07:31</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8299,10 +8549,24 @@
           <t>JYOCHO</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aDHno6PB5pM</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>20887</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>JYOCHO</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:07:43</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8339,10 +8603,24 @@
           <t>岡村靖幸・中島健人</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JNbh6RTyOaE</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>429432</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:07:55</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8459,10 +8737,24 @@
           <t>IS:SUE</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wM3E9LXHmu0</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>2689740</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>TVアニメ「キャンディーカリエス」</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:08:09</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8499,10 +8791,24 @@
           <t>スカートとODD Foot Works</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=u5syUWK5d-8</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>58027</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ぽにきゃん-Anime PONY CANYON</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:08:22</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8539,10 +8845,24 @@
           <t>a子</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n3c6bAOhVUg</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>464180</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ぽにきゃん-Anime PONY CANYON</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:08:34</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8579,10 +8899,24 @@
           <t>aespa</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nMwSsHkjmfk</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>2326192</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>aespa</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:08:48</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8619,10 +8953,24 @@
           <t>RIIZE</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sfVO4X_xOu8</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>259210</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>RIIZE</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:09:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8659,10 +9007,24 @@
           <t>Galileo Galilei</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7ETgAcnUcro</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>51435</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Galileo Galilei Official</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:09:13</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8739,10 +9101,24 @@
           <t>reGretGirl</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2hyWBr4hceY</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>207642</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>reGretGirl</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:09:37</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8819,10 +9195,24 @@
           <t>ASCA</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ATTWunJa4yc</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>36805</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>GOOD SMILE CHANNEL</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:10:02</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8859,10 +9249,24 @@
           <t>スピラ・スピカ</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=L7t4Jsq51LE</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>24437</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spira spica Official YouTube Channel (SMEJ) </t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:10:10</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8899,10 +9303,24 @@
           <t>相葉芹亜（CV.藤寺美徳）</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uN6qJzuCFtw</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>32753</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:10:23</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8939,10 +9357,24 @@
           <t>オデッセウス（CV.寿美菜子）</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KygwMir5i_U</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>10658</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:10:33</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8979,10 +9411,24 @@
           <t>Novelbright</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SAtVrwS86pE</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>2440838</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Novelbright</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:10:46</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9019,10 +9465,24 @@
           <t>ポルカドットスティングレイ</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5ggfKnnQ-0Q</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>167421</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>TBSアニメ</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:10:59</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9099,10 +9559,24 @@
           <t>22/7</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gaPA7q3nd58</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>40260</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>22/7 OFFICIAL YouTube CHANNEL</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:11:22</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9139,10 +9613,24 @@
           <t>緑仙</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rm86UwJz8Ck</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>21883</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>NBCUniversal Anime/Music</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:11:35</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9179,10 +9667,24 @@
           <t>ファントムシータ</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WHkoz2tsc2s</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>3256</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Yamashita Gakuen Anime Song Club</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:11:46</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9219,10 +9721,24 @@
           <t>宮川愛李</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zxS6lFQHiUc</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>112725</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>アルファポリス公式</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:11:59</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9259,10 +9775,24 @@
           <t>RLOEVO</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l0FE1UDC58U</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>271591</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>RLOEVO</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:12:10</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9299,10 +9829,24 @@
           <t>ビバラッシュ</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=48pc58upFY4</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>21943</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>アニメ「自動販売機に生まれ変わった俺は迷宮を彷徨う」公式</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:12:21</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9339,10 +9883,24 @@
           <t>FUWAMOCO</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vSwxof0K8lk</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>274345</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>FUWAMOCO Ch. hololive-EN</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:12:33</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9379,10 +9937,24 @@
           <t>GLAY</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CqeuOBy-09U</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>2564203</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>GLAY</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:12:47</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9419,10 +9991,24 @@
           <t>早見沙織</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=i8xvsTsbFfM</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>13560</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>早見沙織 Official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:13:00</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9459,10 +10045,24 @@
           <t>Orangestar</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WDeVDNg6lSE</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>875036</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Orangestar</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:13:13</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9499,10 +10099,24 @@
           <t>Orangestar</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WDeVDNg6lSE</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>875036</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Orangestar</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:13:27</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9539,10 +10153,24 @@
           <t>Hey! Say! JUMP</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cZftmR93acE</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>289023</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>アニメ小3アシベQQゴマちゃん公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:13:40</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9579,10 +10207,24 @@
           <t>BOYS AND MEN</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gNZNdc5UbTE</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>4852025</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOYS AND MEN ＜ボイメン＞ </t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:13:52</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9619,10 +10261,24 @@
           <t>村上佳佑</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CGuw9xBuMVU</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>39427</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>アニメ・特撮ソング伴奏製作所</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:14:03</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9659,10 +10315,24 @@
           <t>TETSUYA</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KllomiQuM3Q</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>12495</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>アニメ・特撮ソング伴奏製作所</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:14:15</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9699,10 +10369,24 @@
           <t>SILENT SIREN</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EItnl7wcQZk</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1552645</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>SILENT_SIREN</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:14:26</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9779,10 +10463,24 @@
           <t>ベリーグッドマン</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3g-n6WbIcDA</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>8414</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>アニメ・特撮ソング伴奏製作所</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:14:49</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9899,10 +10597,24 @@
           <t>tuki.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2splxp-qwH0</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>1001886</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>tuki.(17)</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:15:03</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9939,10 +10651,24 @@
           <t>ヒグチアイ</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0vTK8SWTgws</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>422037</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:15:15</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9979,10 +10705,24 @@
           <t>亜咲花</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8XeyK9hI6WI</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>9657</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>亜咲花公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:15:28</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10019,10 +10759,24 @@
           <t>Baby Canta</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dPWuN1uP09g</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>914861</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>TVアニメ「ダイヤのA」シリーズ</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:15:41</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10059,10 +10813,24 @@
           <t>SUPER★DRAGON</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dPWuN1uP09g</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>914861</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>TVアニメ「ダイヤのA」シリーズ</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:15:53</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10099,10 +10867,24 @@
           <t>超特急</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=w8ltcHURKhc</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>190536</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>超特急</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:16:06</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10139,10 +10921,24 @@
           <t>『ユイカ』</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b92uylP2yCs</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>512594</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>『ユイカ』</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:16:19</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10179,10 +10975,24 @@
           <t>こっちのけんと</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ffxN8II-Vic</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>1572114</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>こっちのけんと</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:16:33</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10219,10 +11029,24 @@
           <t>ASH DA HERO</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=03eMtnVjiBk</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>1106840</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>isekai channel @バンダイナムコフィルムワークス</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:16:45</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10259,10 +11083,24 @@
           <t>シユイ</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Pn0c9QIiqbo</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>174604</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>isekai channel @バンダイナムコフィルムワークス</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:16:57</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10339,10 +11177,24 @@
           <t>藍井エイル</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ILfcwl8ZKDs</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>201532</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Lantis Channel</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:17:21</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10379,10 +11231,24 @@
           <t>CiON</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xdhkJtJcdEk</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>155173</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>CiON official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:17:34</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10419,10 +11285,24 @@
           <t>ALI</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sPxXiXucYcM</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>7100246</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>ALI</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:17:47</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10459,10 +11339,24 @@
           <t>KANA-BOON</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HNYp4T0kMNU</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>2456417</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:18:01</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10499,10 +11393,24 @@
           <t>ASIAN KUNG-FU GENERATION</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ycH4Twoq83I</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>807317</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:18:14</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10539,10 +11447,24 @@
           <t>BREIMEN</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5SGVXrvEK0o</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>1453819</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>BREIMEN _Channel</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:18:27</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10579,10 +11501,24 @@
           <t>音羽-otoha-</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SZhcN4jVVzA</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>1122108</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>音羽-otoha-</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:18:40</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -10619,10 +11555,24 @@
           <t>BURNOUT SYNDROMES</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HXvZ7Y7uYbo</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>629266</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:18:53</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -10659,10 +11609,24 @@
           <t>(K)NoW_NAME</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LWaqlY0Xqy0</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>911783</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>(K)NoW_NAME - Topic</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:19:05</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -10699,10 +11663,24 @@
           <t>(K)NoW_NAME</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6RnvqHkDI50</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>219181</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>(K)NoW_NAME - Topic</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:19:16</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -10739,10 +11717,24 @@
           <t>Eve</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ySpIrrCmiCU</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>2058400</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Eve</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:19:30</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -10779,10 +11771,24 @@
           <t>Nakamura Hak</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rQ0S_0CepIo</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>1305856</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>TVアニメ「とんがり帽子のアトリエ」公式</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:19:42</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -10819,10 +11825,24 @@
           <t>Aiobahn ＋81</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BnkhBwzBqlQ</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>29176895</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Aiobahn</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:19:55</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -10859,10 +11879,24 @@
           <t>キタニタツヤ</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l7hbIgnyhe0</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>579425</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>キタニタツヤ / Tatsuya Kitani</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:20:08</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -10899,10 +11933,24 @@
           <t>HoneyWorks feat.鈴木愛理</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_3aytoDQTHg</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>728377</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>MARUMOCHI from HoneyWorks</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:20:22</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -10939,10 +11987,24 @@
           <t>吉乃</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iouWS4pwX28</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>227515</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>吉乃</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:20:35</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11059,10 +12121,24 @@
           <t>キタニタツヤ</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hA_9r-3jkSg</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>1806016</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>キタニタツヤ / Tatsuya Kitani</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:20:49</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -11099,10 +12175,24 @@
           <t>Leina</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1KnySdlZHJU</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>259162</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Leina</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:21:02</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -11139,10 +12229,24 @@
           <t>DARUMA Rollin’</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mfBWkIIQE9w</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>267737</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>DARUMA Rollin'</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:21:14</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -11179,10 +12283,24 @@
           <t>高橋哲也</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=muqyayR_9ts</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>8986</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>HERO'S Web公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:21:29</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -11339,10 +12457,24 @@
           <t>前島亜美</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xuyA1jEiJ8c</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>193665</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>前島亜美</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:22:02</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -11379,10 +12511,24 @@
           <t>愛美</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ifutP5vX5TA</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>21547</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>AIMI official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:22:14</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -11419,10 +12565,24 @@
           <t>issei</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gOTNI5smH2E</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>1197894</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:22:26</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -11459,10 +12619,24 @@
           <t>神前暁</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gOTNI5smH2E</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>1197894</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:22:40</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -11539,10 +12713,24 @@
           <t>SEVENTEEN</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5A7qyhj-HjE</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>828219</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>SEVENTEEN</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:23:01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -11579,10 +12767,24 @@
           <t>レトロリロン</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4cGnQ8gFCCs</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>117523</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>MBS animation 公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:23:14</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -11619,10 +12821,24 @@
           <t>ガラクタ</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xSNhOhCEaC4</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>27686</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>MBS animation 公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:23:27</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -11659,10 +12875,24 @@
           <t>ALI</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8V9cwO1ZxGk</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>80366</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>ALI</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:23:39</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -11699,10 +12929,24 @@
           <t>紫 今</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vlbobXEQLqY</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>125026</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>ギャガ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:23:50</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -11979,10 +13223,24 @@
           <t>osage</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0XwlRpvjbmY</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>3513</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>osage official</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:24:51</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -12019,10 +13277,24 @@
           <t>ミーマイナー</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6TOl476i5Q8</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>27410</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>ミーマイナー</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:25:04</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -12059,10 +13331,24 @@
           <t>Little Glee Monster</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DNa76ODisco</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>429127</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Little Glee Monster</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:25:17</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -12099,10 +13385,24 @@
           <t>生田絵梨花</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kX0u1U7wMDk</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>705610</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>生田絵梨花 Official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:25:32</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -12139,10 +13439,24 @@
           <t>Penthouse</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=m4yCXpCiXpk</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>705610</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:25:46</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -12179,10 +13493,24 @@
           <t>CANDY TUNE</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jMhzqfi9aPw</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>630585</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>アニメ「魔入りました!入間くん」公式Anime OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:25:58</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -12299,10 +13627,24 @@
           <t>Kis-My-Ft2</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MGUp9RBrou4</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>10157104</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Kis-My-Ft2</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:26:13</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -12339,10 +13681,24 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eVfpoS0rjw0</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>1659920</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Bandai Namco Filmworks Channel</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:26:25</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -12379,10 +13735,24 @@
           <t>多次元制御機構よだか</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Z53w6cpG5GM</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>48053</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>TBSアニメ</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:26:35</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -12419,10 +13789,24 @@
           <t>リリテア（CV.若山詩音）</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZvHOYO6tfvk</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>16033</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>リリテア（CV:若山詩音） - Topic</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:26:41</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -12459,10 +13843,24 @@
           <t>ILLIT</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OZ44P4JU87E</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>1544080</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>ILLIT</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:26:55</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -12499,10 +13897,24 @@
           <t>ルルットリリィ（こんぺとリリィ（CV.橘めい）、ましゅールル（CV.小鹿なお））</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=803SES0YVcM</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>209352</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Bandai Namco Filmworks Channel</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:27:07</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -12539,10 +13951,24 @@
           <t>NEE</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0j7O1Sw62Ms</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>39536</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:27:20</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -12659,10 +14085,24 @@
           <t>平手友梨奈</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QbNwgXAXq9M</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>964216</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>平手友梨奈</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:27:50</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -12699,10 +14139,24 @@
           <t>AKASAKI</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WwI7hPXZC-Y</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>2444210</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>AKASAKI (19)</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:28:02</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -12739,10 +14193,24 @@
           <t>majiko</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VHD2269UqdM</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>37559</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>ハピネット【アニメ公式】</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:28:14</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -12779,10 +14247,24 @@
           <t>ARCANA PROJECT</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vBSo4npKK9A</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>11878</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>ハピネット【アニメ公式】</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:28:25</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -12819,10 +14301,24 @@
           <t>終活クラブ</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=suKjfBsH3UM</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>147879</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>アニメ『女神「異世界転生何になりたいですか」 俺「勇者の肋骨で」』</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:28:38</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -12859,10 +14355,24 @@
           <t>shallm</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=suKjfBsH3UM</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>147879</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>アニメ『女神「異世界転生何になりたいですか」 俺「勇者の肋骨で」』</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:28:51</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -12899,10 +14409,24 @@
           <t>藍井エイル</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l78_JpSXfxw</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>358837</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Lantis Channel</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:29:04</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -12939,10 +14463,24 @@
           <t>ZAQ</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jl7GmJBNxk4</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>89423</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>ZAQ Official Channel</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:29:16</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -13059,10 +14597,24 @@
           <t>櫻坂46</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AIspds2UVts</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>187933</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>NBCUniversal Anime/Music</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:29:28</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -13099,10 +14651,24 @@
           <t>ピラフ星人</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=X6fNe1uPs9E</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>234792</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>NBCUniversal Anime/Music</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:29:40</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -13139,10 +14705,24 @@
           <t>Vaundy</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LVCwdZoUFQ8</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>3496214</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Vaundy</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:29:53</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -13179,10 +14759,24 @@
           <t>yama</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8uRMfPTAhkU</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>373757</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>yama</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:30:06</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -13219,10 +14813,24 @@
           <t>Daoko</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0jO_isUIymg</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>129233</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>日活アニメチャンネル</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:30:19</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -13259,10 +14867,24 @@
           <t>鶸村ひより(CV：高野麻里佳)、椋林瑞希(CV：伊駒ゆりえ)、雪下祐樹(CV：篠原侑)</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LRPRccAPekk</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>132505</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>日活アニメチャンネル</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:30:33</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -13299,10 +14921,24 @@
           <t>ヨルシカ</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OHAjc-ayhus</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>6187955</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>ヨルシカ / n-buna Official</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:30:46</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -13339,10 +14975,24 @@
           <t>Lucky Kilimanjaro</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hyp8GGN7C1w</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>58183</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Lucky Kilimanjaro</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:31:00</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -13379,10 +15029,24 @@
           <t>eill</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fsgD8mLRxwo</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>208770</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>eill official</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:31:16</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -13419,10 +15083,24 @@
           <t>Sizuk</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LimcX6xNEaY</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>59739</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Sizuk / Shunryu</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:31:29</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -13459,10 +15137,24 @@
           <t>鈴木このみ feat. Ashnikko</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VDGG9zi53rQ</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>5097812</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>「Re:ゼロから始める異世界生活」チャンネル【公式】</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:31:42</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -13499,10 +15191,24 @@
           <t>MYTH &amp; ROID feat. TK（凛として時雨）</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iKLqlb_oX60</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>579546</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>「Re:ゼロから始める異世界生活」チャンネル【公式】</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:31:54</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -13539,10 +15245,24 @@
           <t>幾田りら</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JcDyAzbGA78</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>369868</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>幾田りら / Lilas Official</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:32:07</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -13579,10 +15299,24 @@
           <t>シャイトープ</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BEj-QbHC54M</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>34216</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:32:18</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -13619,10 +15353,24 @@
           <t>asmi</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ikqz8riLe1M</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>24006</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>asmi Official Channel</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:32:31</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,71 +414,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>season_label</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>is_rerun</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>broadcast_format</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>broadcast_start</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>animation_studio</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>op_title</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>op_artist</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ed_title</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ed_artist</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>detail_url</t>
         </is>
@@ -6145,6 +6133,3177 @@
       <c r="M101" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=25560</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>アズールレーン びそくぜんしんっ！にっ！！</t>
+        </is>
+      </c>
+      <c r="E102" t="b">
+        <v>0</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026年7月5日（日）～ TOKYO MX・BS11にて</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>studio CANDY BOX</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=22684</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>いびってこない義母と義姉</t>
+        </is>
+      </c>
+      <c r="E103" t="b">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26511</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>岩元先輩ノ推薦</t>
+        </is>
+      </c>
+      <c r="E104" t="b">
+        <v>0</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>スタジオディーン</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27436</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>うしろの正面カムイさん</t>
+        </is>
+      </c>
+      <c r="E105" t="b">
+        <v>0</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ゼロジー</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27661</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>うちの弟どもがすみません</t>
+        </is>
+      </c>
+      <c r="E106" t="b">
+        <v>0</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026年7月3日（金）～ TOKYO MX・BS11ほか</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27207</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>6</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ウルトラマンテオ</t>
+        </is>
+      </c>
+      <c r="E107" t="b">
+        <v>0</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>特撮</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026年7月4日（土）～ テレ東系6局ネットにて</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28241</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>7</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>乙女怪獣キャラメリゼ</t>
+        </is>
+      </c>
+      <c r="E108" t="b">
+        <v>0</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026年7月～ TBS・BS11にて</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27295</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>8</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>乙女ゲー世界はモブに厳しい世界です2</t>
+        </is>
+      </c>
+      <c r="E109" t="b">
+        <v>0</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>ENGI</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=19243</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>9</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>同じゼミの染谷さんがセクシー女優だった話。</t>
+        </is>
+      </c>
+      <c r="E110" t="b">
+        <v>0</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026年7月〜</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27886</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>10</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+        </is>
+      </c>
+      <c r="E111" t="b">
+        <v>0</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>オーラスタジオ</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>浪漫街道、お散歩中</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>PelleK</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>奇跡は起きない</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>DIALOGUE+</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25337</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>11</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になるII</t>
+        </is>
+      </c>
+      <c r="E112" t="b">
+        <v>0</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026年7月8日（水）～ テレビ朝日系全国24局ネット・BS朝日ほか</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>YAMATOWORKS</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>クレナイノハ</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>ユニコーン</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26271</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>12</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>株式会社マジルミエ 第2期</t>
+        </is>
+      </c>
+      <c r="E113" t="b">
+        <v>0</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026年7月～ 日本テレビにて</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25382</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>13</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>きみが死ぬまで恋をしたい</t>
+        </is>
+      </c>
+      <c r="E114" t="b">
+        <v>0</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>ROLL2</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25598</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>14</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>君のことが大大大大大好きな100人の彼女 第3期</t>
+        </is>
+      </c>
+      <c r="E115" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026年7月〜</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>バイブリーアニメーションスタジオ</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26982</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>15</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+        </is>
+      </c>
+      <c r="E116" t="b">
+        <v>0</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026年7月～ テレビ朝日系列・BS朝日にて</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27779</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>16</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ぐらんぶる Season 3</t>
+        </is>
+      </c>
+      <c r="E117" t="b">
+        <v>0</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026年7月～ TOKYO MX・BS11・MBSにて</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>ゼロジー</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>裸のマーメード</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>豆柴の大群</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26833</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>17</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+        </is>
+      </c>
+      <c r="E118" t="b">
+        <v>0</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Lay-duce</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Awake Anew</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>MYTH &amp; ROID</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26812</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>18</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>グロウアップショウ ～ひまわりのサーカス団～</t>
+        </is>
+      </c>
+      <c r="E119" t="b">
+        <v>0</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26410</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>19</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>攻殻機動隊 THE GHOST IN THE SHELL</t>
+        </is>
+      </c>
+      <c r="E120" t="b">
+        <v>0</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026年7月～ カンテレ・フジテレビ系全国ネット“火アニバル!!”枠にて</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>サイエンスSARU</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=24096</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>20</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>コードギアス 奪還のロゼ TV放送</t>
+        </is>
+      </c>
+      <c r="E121" t="b">
+        <v>0</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>劇場版アニメ</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>第1幕：2024年5月10日（金） 第2幕：2024年6月7日（金） 第3幕：2024年7月5日（金） 最終幕 ：2024年8月2日（金） 【TV放送】 2026年7月～ MBS／TBS系アニメイズム枠にて</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Running In My Head</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>MIYAVI</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>ロゼ (Prod.TeddyLoid)</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>満島ひかり</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=11462</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>21</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ここは俺に任せて先に行けと言ってから10年がたったら伝説になっていた。</t>
+        </is>
+      </c>
+      <c r="E122" t="b">
+        <v>0</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026年7月〜</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>月虹</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26900</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>22</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>これ描いて死ね</t>
+        </is>
+      </c>
+      <c r="E123" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026年7月～ 日本テレビ系にて</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>シンエイ動画</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26928</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>23</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>最強出涸らし皇子の暗躍帝位争い</t>
+        </is>
+      </c>
+      <c r="E124" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>MAHO FILM</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28078</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>24</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+        </is>
+      </c>
+      <c r="E125" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026年7月〜</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>ブレインズ・ベース</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27572</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>25</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>サイボーグ009 ネメシス</t>
+        </is>
+      </c>
+      <c r="E126" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>配信</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026年夏</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>アレクト</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26463</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>26</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>さよならララ</t>
+        </is>
+      </c>
+      <c r="E127" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>キネマシトラス</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>さよならララ</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>いきものがかり</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=24070</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>27</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>サンダー３</t>
+        </is>
+      </c>
+      <c r="E128" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026年7月～ フジテレビ「+Ultra」にて</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27611</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>28</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="E129" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026年7月～ TBS系にて</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Fiction</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>imase</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26460</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>29</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+        </is>
+      </c>
+      <c r="E130" t="b">
+        <v>0</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>EMTスクエアード</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27962</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>30</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>正反対な君と僕 第2期</t>
+        </is>
+      </c>
+      <c r="E131" t="b">
+        <v>0</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>第1期：2026年1月11日（日）〜2026年3月29日（日） 第2期：2026年7月5日（日）～ MBS・TBS系全国28局ネットにて</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>ラパントラック</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>メガネを外して</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>乃紫</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>ピュア feat. 橋本絵莉子</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>PAS TASTA</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25223</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>31</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
+        </is>
+      </c>
+      <c r="E132" t="b">
+        <v>0</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026年7月〜</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>MAHO FILM</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26740</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>32</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+        </is>
+      </c>
+      <c r="E133" t="b">
+        <v>0</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026年7月7日（火）～ AT-X・TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>ディオメディア</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>命短し対する乙女よ</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>花冷え。</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=11593</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>33</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>地球大好き！きっくん</t>
+        </is>
+      </c>
+      <c r="E134" t="b">
+        <v>0</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026年7月～ TOKYO MX「5時に夢中！」にて</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>勝鬨スタジオ</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28276</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>34</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="E135" t="b">
+        <v>0</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026年7月2日（木）～ MBS /TBS系28局”スーパーアニメイズムTURBO”枠にて</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>GoHands</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=24783</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>35</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>手札が多めのビクトリア</t>
+        </is>
+      </c>
+      <c r="E136" t="b">
+        <v>0</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026年7月～ テレ東系列にて</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>スタジオディーン</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>縁のつき</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>KI_EN</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26780</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>36</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+        </is>
+      </c>
+      <c r="E137" t="b">
+        <v>0</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026年7月～ TOKYO MX・BSフジほか</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>project No.9</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>夏に重ねて</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>DIALOGUE+</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=23374</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>37</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>天は赤い河のほとり</t>
+        </is>
+      </c>
+      <c r="E138" t="b">
+        <v>0</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026年夏</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>タツノコプロ</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>暁の空</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>七海ひろき</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27687</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>38</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>天幕のジャードゥーガル</t>
+        </is>
+      </c>
+      <c r="E139" t="b">
+        <v>0</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026年7月〜 テレビ朝日系にて</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>サイエンスSARU</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25815</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>39</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>盗掘王</t>
+        </is>
+      </c>
+      <c r="E140" t="b">
+        <v>0</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026年7月～ フジテレビ・関西テレビほか</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>STUDIO EEK</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>SHOW DOWN</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>QWER</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27435</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>40</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+        </is>
+      </c>
+      <c r="E141" t="b">
+        <v>0</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026年7月6日（月）～ AT-X・TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>マカリア</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>光</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>櫻井優衣</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27113</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>41</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>逃げ上手の若君 第二期</t>
+        </is>
+      </c>
+      <c r="E142" t="b">
+        <v>0</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026年7月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25034</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>42</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+        </is>
+      </c>
+      <c r="E143" t="b">
+        <v>0</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026年7月5日（日）〜 TOKYO MX・BS11ほか</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>京都アニメーション</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>ユーレカ・エヴリカ</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>五阿弥ルナ</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27014</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>43</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>猫と竜</t>
+        </is>
+      </c>
+      <c r="E144" t="b">
+        <v>0</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026年7月～ TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>OLM</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25576</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>44</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>花織さんは転生しても喧嘩がしたい</t>
+        </is>
+      </c>
+      <c r="E145" t="b">
+        <v>0</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026年7月～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>45</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>バンドリ！ ゆめ∞みた</t>
+        </is>
+      </c>
+      <c r="E146" t="b">
+        <v>0</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026年夏 TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>ニチカライン（</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>46</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+        </is>
+      </c>
+      <c r="E147" t="b">
+        <v>0</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026年7月～ TOKYO MX・BSフジほか</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>EMTスクエアード</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>47</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+        </is>
+      </c>
+      <c r="E148" t="b">
+        <v>0</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026年7月〜 テレ東・BS11ほか</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>スタジオコメット</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Q.E.D.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>小倉唯</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>グッバイ・ララバイ</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>大西亜玖璃</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>48</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+        </is>
+      </c>
+      <c r="E149" t="b">
+        <v>0</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026年7月〜 テレビ東京系列にて</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>動画工房</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>49</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>BLACK TORCH</t>
+        </is>
+      </c>
+      <c r="E150" t="b">
+        <v>0</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026年7月4日（土）～ TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>100studio</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>50</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>プラノサウルス ガチコセイブツ部</t>
+        </is>
+      </c>
+      <c r="E151" t="b">
+        <v>0</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>SMDE</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>51</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
+        </is>
+      </c>
+      <c r="E152" t="b">
+        <v>0</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026年7月～ テレ東系列ほか</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>PIERROT FILMS（</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>52</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>文豪ストレイドッグス わん！２</t>
+        </is>
+      </c>
+      <c r="E153" t="b">
+        <v>0</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026年7月〜</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>ボンズ</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>53</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+        </is>
+      </c>
+      <c r="E154" t="b">
+        <v>0</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>54</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>炎の闘球女 ドッジ弾子</t>
+        </is>
+      </c>
+      <c r="E155" t="b">
+        <v>0</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026年7月～ TOKYO MX・MBS・BS11にて</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>CUE</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>55</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+        </is>
+      </c>
+      <c r="E156" t="b">
+        <v>0</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Seven Arcs</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Ephemeral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>青木陽菜</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>56</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
+        </is>
+      </c>
+      <c r="E157" t="b">
+        <v>0</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026年7月～ TVKにて</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>57</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+        </is>
+      </c>
+      <c r="E158" t="b">
+        <v>0</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026年7月～ TOKYO MX・BS11・AT-Xにて</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>マジックバス×ピカンテサーカス</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Windmaker</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>58</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+        </is>
+      </c>
+      <c r="E159" t="b">
+        <v>0</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>決意の唄</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>大原ゆい子</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>59</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ヤニねこ</t>
+        </is>
+      </c>
+      <c r="E160" t="b">
+        <v>0</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>バイブリーアニメーションスタジオ</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>60</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>幼女戦記Ⅱ</t>
+        </is>
+      </c>
+      <c r="E161" t="b">
+        <v>0</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>NUT</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>61</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
+        </is>
+      </c>
+      <c r="E162" t="b">
+        <v>0</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>【第1クール】 2026年1月6日（火）〜2026年3月24日（火） TOKYO MXほか 【第2クール】 2026年7月～</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>サンライズ</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>YOAKE</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>blank paper</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>POWER</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>ONE OR EIGHT</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>62</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+        </is>
+      </c>
+      <c r="E163" t="b">
+        <v>0</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>EMTスクエアード</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>63</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>領民0人スタートの辺境領主様</t>
+        </is>
+      </c>
+      <c r="E164" t="b">
+        <v>0</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026年7月〜</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>animation studio42</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>64</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>令和のダラさん</t>
+        </is>
+      </c>
+      <c r="E165" t="b">
+        <v>0</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>旭プロダクション</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>ダラダラ♡ダンシング</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>65</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="E166" t="b">
+        <v>0</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026年7月～ テレ東・BSフジほか</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>ブレインズ・ベース</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>66</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ワールド イズ ダンシング</t>
+        </is>
+      </c>
+      <c r="E167" t="b">
+        <v>0</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026年7月～ TOKYO MX・BS朝日ほか</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>サイピク</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>67</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ONE PIECE HEROINES</t>
+        </is>
+      </c>
+      <c r="E168" t="b">
+        <v>0</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
         </is>
       </c>
     </row>
@@ -6159,66 +9318,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L183"/>
+  <dimension ref="A1:L214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>season_label</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>anime_title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>is_rerun</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>song_title</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>artist</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>youtube_url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>youtube_views</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>youtube_channel</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>last_searched_at</t>
         </is>
@@ -15372,6 +18531,1246 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>アズールレーン びそくぜんしんっ！にっ！！</t>
+        </is>
+      </c>
+      <c r="D184" t="b">
+        <v>0</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>主題歌</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>しゃいすまっ！</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>榊原ゆい</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>アズールレーン びそくぜんしんっ！にっ！！</t>
+        </is>
+      </c>
+      <c r="D185" t="b">
+        <v>0</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>主題歌</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Lu lu lun♪〜ウラハラ気分はオートマティック〜</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>橋本みゆき</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+        </is>
+      </c>
+      <c r="D186" t="b">
+        <v>0</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>浪漫街道、お散歩中</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>PelleK</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+        </is>
+      </c>
+      <c r="D187" t="b">
+        <v>0</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>奇跡は起きない</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>DIALOGUE+</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になるII</t>
+        </is>
+      </c>
+      <c r="D188" t="b">
+        <v>0</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>クレナイノハ</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>ユニコーン</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ぐらんぶる Season 3</t>
+        </is>
+      </c>
+      <c r="D189" t="b">
+        <v>0</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>裸のマーメード</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>豆柴の大群</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+        </is>
+      </c>
+      <c r="D190" t="b">
+        <v>0</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Awake Anew</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>MYTH &amp; ROID</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>コードギアス 奪還のロゼ TV放送</t>
+        </is>
+      </c>
+      <c r="D191" t="b">
+        <v>0</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Running In My Head</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>MIYAVI</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>コードギアス 奪還のロゼ TV放送</t>
+        </is>
+      </c>
+      <c r="D192" t="b">
+        <v>0</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>ロゼ (Prod.TeddyLoid)</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>満島ひかり</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>サイボーグ009 ネメシス</t>
+        </is>
+      </c>
+      <c r="D193" t="b">
+        <v>0</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>主題歌</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>誰がために</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>杏子</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>さよならララ</t>
+        </is>
+      </c>
+      <c r="D194" t="b">
+        <v>0</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>さよならララ</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>いきものがかり</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>スーパーの裏でヤニ吸うふたり</t>
+        </is>
+      </c>
+      <c r="D195" t="b">
+        <v>0</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Fiction</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>imase</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>正反対な君と僕 第2期</t>
+        </is>
+      </c>
+      <c r="D196" t="b">
+        <v>0</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>メガネを外して</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>乃紫</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>正反対な君と僕 第2期</t>
+        </is>
+      </c>
+      <c r="D197" t="b">
+        <v>0</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>ピュア feat. 橋本絵莉子</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>PAS TASTA</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+        </is>
+      </c>
+      <c r="D198" t="b">
+        <v>0</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>命短し対する乙女よ</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>花冷え。</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>手札が多めのビクトリア</t>
+        </is>
+      </c>
+      <c r="D199" t="b">
+        <v>0</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>縁のつき</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>KI_EN</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+        </is>
+      </c>
+      <c r="D200" t="b">
+        <v>0</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>夏に重ねて</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>DIALOGUE+</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>天は赤い河のほとり</t>
+        </is>
+      </c>
+      <c r="D201" t="b">
+        <v>0</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>暁の空</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>七海ひろき</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>盗掘王</t>
+        </is>
+      </c>
+      <c r="D202" t="b">
+        <v>0</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>SHOW DOWN</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>QWER</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+        </is>
+      </c>
+      <c r="D203" t="b">
+        <v>0</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>光</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>櫻井優衣</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+        </is>
+      </c>
+      <c r="D204" t="b">
+        <v>0</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>ユーレカ・エヴリカ</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>五阿弥ルナ</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+        </is>
+      </c>
+      <c r="D205" t="b">
+        <v>0</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Q.E.D.</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>小倉唯</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+        </is>
+      </c>
+      <c r="D206" t="b">
+        <v>0</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>グッバイ・ララバイ</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>大西亜玖璃</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>プラノサウルス ガチコセイブツ部</t>
+        </is>
+      </c>
+      <c r="D207" t="b">
+        <v>0</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>主題歌</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>ガチde古生</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>リンクルプラネット</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+        </is>
+      </c>
+      <c r="D208" t="b">
+        <v>0</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Ephemeral</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>青木陽菜</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+        </is>
+      </c>
+      <c r="D209" t="b">
+        <v>0</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Windmaker</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+        </is>
+      </c>
+      <c r="D210" t="b">
+        <v>0</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>決意の唄</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>大原ゆい子</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
+        </is>
+      </c>
+      <c r="D211" t="b">
+        <v>0</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>YOAKE</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>blank paper</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
+        </is>
+      </c>
+      <c r="D212" t="b">
+        <v>0</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>POWER</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>ONE OR EIGHT</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>令和のダラさん</t>
+        </is>
+      </c>
+      <c r="D213" t="b">
+        <v>0</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ダラダラ♡ダンシング</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="D214" t="b">
+        <v>0</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026年7月〜</t>
+          <t>2026年7月5日（日）〜 TOKYO MXほか</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026年夏 TOKYO MXほか</t>
+          <t>2026年7月2日（木）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>僕のヒーローアカデミア 特別短編アニメ「I am a hero too」</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -8660,21 +8660,17 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・MBS・BS11にて</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>CUE</t>
-        </is>
-      </c>
+          <t>2026年夏</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28292</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8688,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -8705,29 +8701,29 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
+          <t>2026年7月～ TOKYO MX・MBS・BS11にて</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Seven Arcs</t>
+          <t>CUE</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8741,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -8758,17 +8754,29 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026年7月～ TVKにて</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr"/>
+          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Seven Arcs</t>
+        </is>
+      </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Ephemeral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>青木陽菜</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8794,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -8799,29 +8807,17 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・BS11・AT-Xにて</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>マジックバス×ピカンテサーカス</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Windmaker</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
+          <t>2026年7月～ TVKにて</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8835,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="E159" t="b">
@@ -8852,25 +8848,29 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr"/>
+          <t>2026年7月～ TOKYO MX・BS11・AT-Xにて</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>マジックバス×ピカンテサーカス</t>
+        </is>
+      </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -8901,21 +8901,25 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>バイブリーアニメーションスタジオ</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>決意の唄</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>大原ゆい子</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
         </is>
       </c>
     </row>
@@ -8933,7 +8937,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -8946,12 +8950,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>NUT</t>
+          <t>バイブリーアニメーションスタジオ</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -8960,7 +8964,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
         </is>
       </c>
     </row>
@@ -8978,7 +8982,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -8991,37 +8995,21 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>【第1クール】 2026年1月6日（火）〜2026年3月24日（火） TOKYO MXほか 【第2クール】 2026年7月～</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>サンライズ</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>YOAKE</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>blank paper</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>POWER</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>ONE OR EIGHT</t>
-        </is>
-      </c>
+          <t>NUT</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9027,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -9052,21 +9040,37 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>【第1クール】 2026年1月6日（火）〜2026年3月24日（火） TOKYO MXほか 【第2クール】 2026年7月～</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>EMTスクエアード</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
+          <t>サンライズ</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>YOAKE</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>blank paper</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>POWER</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>ONE OR EIGHT</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9088,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -9097,12 +9101,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026年7月〜</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>animation studio42</t>
+          <t>EMTスクエアード</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -9111,7 +9115,7 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9133,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -9142,29 +9146,21 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月〜</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>旭プロダクション</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>ダラダラ♡ダンシング</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
-        </is>
-      </c>
+          <t>animation studio42</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9178,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -9195,29 +9191,29 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東・BSフジほか</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>ブレインズ・ベース</t>
+          <t>旭プロダクション</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9231,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -9248,21 +9244,29 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・BS朝日ほか</t>
+          <t>2026年7月～ テレ東・BSフジほか</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>サイピク</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
+          <t>ブレインズ・ベース</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9284,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ONE PIECE HEROINES</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -9293,15 +9297,60 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
+          <t>2026年7月～ TOKYO MX・BS朝日ほか</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>サイピク</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>68</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ONE PIECE HEROINES</t>
+        </is>
+      </c>
+      <c r="E169" t="b">
+        <v>0</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
         </is>
@@ -9318,7 +9367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L214"/>
+  <dimension ref="A1:L216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12438,7 +12487,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ゴーストコンサート : missing Songs</t>
+          <t>黒猫と魔女の教室</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -12446,40 +12495,26 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>業魂REQUIEMER</t>
+          <t>Twilight Magic</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>相葉芹亜（CV.藤寺美徳）</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=uN6qJzuCFtw</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>32753</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:10:23</t>
-        </is>
-      </c>
+          <t>中川翔子</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -12500,7 +12535,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -12508,21 +12543,21 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>茨の道</t>
+          <t>業魂REQUIEMER</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>オデッセウス（CV.寿美菜子）</t>
+          <t>相葉芹亜（CV.藤寺美徳）</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KygwMir5i_U</t>
+          <t>https://www.youtube.com/watch?v=uN6qJzuCFtw</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>10658</v>
+        <v>32753</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -12531,7 +12566,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-05-03T22:10:33</t>
+          <t>2026-05-03T22:10:23</t>
         </is>
       </c>
     </row>
@@ -12546,7 +12581,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>氷の城壁</t>
+          <t>ゴーストコンサート : missing Songs</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -12554,7 +12589,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -12562,30 +12597,30 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>透明</t>
+          <t>茨の道</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Novelbright</t>
+          <t>オデッセウス（CV.寿美菜子）</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SAtVrwS86pE</t>
+          <t>https://www.youtube.com/watch?v=KygwMir5i_U</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>2440838</v>
+        <v>10658</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Novelbright</t>
+          <t>KADOKAWAanime</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-05-03T22:10:46</t>
+          <t>2026-05-03T22:10:33</t>
         </is>
       </c>
     </row>
@@ -12608,7 +12643,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -12616,30 +12651,30 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>逆様</t>
+          <t>透明</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ポルカドットスティングレイ</t>
+          <t>Novelbright</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5ggfKnnQ-0Q</t>
+          <t>https://www.youtube.com/watch?v=SAtVrwS86pE</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>167421</v>
+        <v>2440838</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>TBSアニメ</t>
+          <t>Novelbright</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-05-03T22:10:59</t>
+          <t>2026-05-03T22:10:46</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12689,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>最強の王様、二度目の人生は何をする？ Season2</t>
+          <t>氷の城壁</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -12662,7 +12697,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -12670,18 +12705,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>さよならじゃない方がいい</t>
+          <t>逆様</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SIX LOUNGE</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+          <t>ポルカドットスティングレイ</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5ggfKnnQ-0Q</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>167421</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>TBSアニメ</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:10:59</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -12702,7 +12751,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -12710,32 +12759,18 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>二つの道</t>
+          <t>さよならじゃない方がいい</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>22/7</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=gaPA7q3nd58</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>40260</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>22/7 OFFICIAL YouTube CHANNEL</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:11:22</t>
-        </is>
-      </c>
+          <t>SIX LOUNGE</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -12748,7 +12783,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>最強の職業は勇者でも賢者でもなく鑑定士(仮)らしいですよ？</t>
+          <t>最強の王様、二度目の人生は何をする？ Season2</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -12756,7 +12791,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -12764,30 +12799,30 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>コンパスは透明</t>
+          <t>二つの道</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>緑仙</t>
+          <t>22/7</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rm86UwJz8Ck</t>
+          <t>https://www.youtube.com/watch?v=gaPA7q3nd58</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>21883</v>
+        <v>40260</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>NBCUniversal Anime/Music</t>
+          <t>22/7 OFFICIAL YouTube CHANNEL</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-05-03T22:11:35</t>
+          <t>2026-05-03T22:11:22</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12845,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -12818,30 +12853,30 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>もーいーかい？</t>
+          <t>コンパスは透明</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ファントムシータ</t>
+          <t>緑仙</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WHkoz2tsc2s</t>
+          <t>https://www.youtube.com/watch?v=rm86UwJz8Ck</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>3256</v>
+        <v>21883</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Yamashita Gakuen Anime Song Club</t>
+          <t>NBCUniversal Anime/Music</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-05-03T22:11:46</t>
+          <t>2026-05-03T22:11:35</t>
         </is>
       </c>
     </row>
@@ -12856,7 +12891,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>自称悪役令嬢な婚約者の観察記録。</t>
+          <t>最強の職業は勇者でも賢者でもなく鑑定士(仮)らしいですよ？</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -12864,7 +12899,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -12872,30 +12907,30 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ラフレア</t>
+          <t>もーいーかい？</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>宮川愛李</t>
+          <t>ファントムシータ</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zxS6lFQHiUc</t>
+          <t>https://www.youtube.com/watch?v=WHkoz2tsc2s</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>112725</v>
+        <v>3256</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>アルファポリス公式</t>
+          <t>Yamashita Gakuen Anime Song Club</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-05-03T22:11:59</t>
+          <t>2026-05-03T22:11:46</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12953,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -12926,30 +12961,30 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>ラフレア</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>RLOEVO</t>
+          <t>宮川愛李</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=l0FE1UDC58U</t>
+          <t>https://www.youtube.com/watch?v=zxS6lFQHiUc</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>271591</v>
+        <v>112725</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>RLOEVO</t>
+          <t>アルファポリス公式</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-05-03T22:12:10</t>
+          <t>2026-05-03T22:11:59</t>
         </is>
       </c>
     </row>
@@ -12964,7 +12999,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>自動販売機に生まれ変わった俺は迷宮を彷徨う 3rd season</t>
+          <t>自称悪役令嬢な婚約者の観察記録。</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -12972,7 +13007,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -12980,30 +13015,30 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ジハンキズム</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ビバラッシュ</t>
+          <t>RLOEVO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=48pc58upFY4</t>
+          <t>https://www.youtube.com/watch?v=l0FE1UDC58U</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>21943</v>
+        <v>271591</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>アニメ「自動販売機に生まれ変わった俺は迷宮を彷徨う」公式</t>
+          <t>RLOEVO</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-05-03T22:12:21</t>
+          <t>2026-05-03T22:12:10</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13061,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -13034,30 +13069,30 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>めくるめくランデヴー</t>
+          <t>ジハンキズム</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FUWAMOCO</t>
+          <t>ビバラッシュ</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vSwxof0K8lk</t>
+          <t>https://www.youtube.com/watch?v=48pc58upFY4</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>274345</v>
+        <v>21943</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>FUWAMOCO Ch. hololive-EN</t>
+          <t>アニメ「自動販売機に生まれ変わった俺は迷宮を彷徨う」公式</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-05-03T22:12:33</t>
+          <t>2026-05-03T22:12:21</t>
         </is>
       </c>
     </row>
@@ -13072,7 +13107,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>終末のワルキューレⅢ</t>
+          <t>自動販売機に生まれ変わった俺は迷宮を彷徨う 3rd season</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -13080,7 +13115,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -13088,30 +13123,30 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dead Or Alive</t>
+          <t>めくるめくランデヴー</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>GLAY</t>
+          <t>FUWAMOCO</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CqeuOBy-09U</t>
+          <t>https://www.youtube.com/watch?v=vSwxof0K8lk</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>2564203</v>
+        <v>274345</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>GLAY</t>
+          <t>FUWAMOCO Ch. hololive-EN</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-05-03T22:12:47</t>
+          <t>2026-05-03T22:12:33</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13169,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -13142,30 +13177,30 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Last breath, Last record</t>
+          <t>Dead Or Alive</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>早見沙織</t>
+          <t>GLAY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=i8xvsTsbFfM</t>
+          <t>https://www.youtube.com/watch?v=CqeuOBy-09U</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>13560</v>
+        <v>2564203</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>早見沙織 Official YouTube Channel</t>
+          <t>GLAY</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-05-03T22:13:00</t>
+          <t>2026-05-03T22:12:47</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13215,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>春夏秋冬代行者 春の舞</t>
+          <t>終末のワルキューレⅢ</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -13188,7 +13223,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -13196,30 +13231,30 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Petals feat. 夏背</t>
+          <t>Last breath, Last record</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Orangestar</t>
+          <t>早見沙織</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WDeVDNg6lSE</t>
+          <t>https://www.youtube.com/watch?v=i8xvsTsbFfM</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>875036</v>
+        <v>13560</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Orangestar</t>
+          <t>早見沙織 Official YouTube Channel</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-05-03T22:13:13</t>
+          <t>2026-05-03T22:13:00</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13277,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -13250,7 +13285,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>花筏 feat. 夏背</t>
+          <t>Petals feat. 夏背</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -13273,7 +13308,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-05-03T22:13:27</t>
+          <t>2026-05-03T22:13:13</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13323,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>小３アシベ QQゴマちゃん</t>
+          <t>春夏秋冬代行者 春の舞</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -13296,7 +13331,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -13304,30 +13339,30 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CUE CUE CUTE</t>
+          <t>花筏 feat. 夏背</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Hey! Say! JUMP</t>
+          <t>Orangestar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cZftmR93acE</t>
+          <t>https://www.youtube.com/watch?v=WDeVDNg6lSE</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>289023</v>
+        <v>875036</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>アニメ小3アシベQQゴマちゃん公式チャンネル</t>
+          <t>Orangestar</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-05-03T22:13:40</t>
+          <t>2026-05-03T22:13:27</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13377,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>新幹線変形ロボ シンカリオン 特別ダイヤ版</t>
+          <t>小３アシベ QQゴマちゃん</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -13350,7 +13385,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -13358,30 +13393,30 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>進化理論</t>
+          <t>CUE CUE CUTE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BOYS AND MEN</t>
+          <t>Hey! Say! JUMP</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gNZNdc5UbTE</t>
+          <t>https://www.youtube.com/watch?v=cZftmR93acE</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>4852025</v>
+        <v>289023</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOYS AND MEN ＜ボイメン＞ </t>
+          <t>アニメ小3アシベQQゴマちゃん公式チャンネル</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-05-03T22:13:52</t>
+          <t>2026-05-03T22:13:40</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13439,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -13412,30 +13447,30 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Go One Step Ahead</t>
+          <t>進化理論</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>村上佳佑</t>
+          <t>BOYS AND MEN</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CGuw9xBuMVU</t>
+          <t>https://www.youtube.com/watch?v=gNZNdc5UbTE</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>39427</v>
+        <v>4852025</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>アニメ・特撮ソング伴奏製作所</t>
+          <t xml:space="preserve">BOYS AND MEN ＜ボイメン＞ </t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-05-03T22:14:03</t>
+          <t>2026-05-03T22:13:52</t>
         </is>
       </c>
     </row>
@@ -13462,25 +13497,25 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I WANNA BE WITH YOU</t>
+          <t>Go One Step Ahead</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>TETSUYA</t>
+          <t>村上佳佑</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KllomiQuM3Q</t>
+          <t>https://www.youtube.com/watch?v=CGuw9xBuMVU</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>12495</v>
+        <v>39427</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -13489,7 +13524,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-05-03T22:14:15</t>
+          <t>2026-05-03T22:14:03</t>
         </is>
       </c>
     </row>
@@ -13516,34 +13551,34 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Go Way!</t>
+          <t>I WANNA BE WITH YOU</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>SILENT SIREN</t>
+          <t>TETSUYA</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EItnl7wcQZk</t>
+          <t>https://www.youtube.com/watch?v=KllomiQuM3Q</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>1552645</v>
+        <v>12495</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>SILENT_SIREN</t>
+          <t>アニメ・特撮ソング伴奏製作所</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-05-03T22:14:26</t>
+          <t>2026-05-03T22:14:15</t>
         </is>
       </c>
     </row>
@@ -13570,22 +13605,36 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>STARTRAiN</t>
+          <t>Go Way!</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>天月-あまつき-</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
+          <t>SILENT SIREN</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EItnl7wcQZk</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1552645</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>SILENT_SIREN</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:14:26</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -13610,36 +13659,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>スタートライン</t>
+          <t>STARTRAiN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ベリーグッドマン</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3g-n6WbIcDA</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>8414</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>アニメ・特撮ソング伴奏製作所</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:14:49</t>
-        </is>
-      </c>
+          <t>天月-あまつき-</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -13652,34 +13687,48 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>涼宮ハルヒの憂鬱</t>
+          <t>新幹線変形ロボ シンカリオン 特別ダイヤ版</t>
         </is>
       </c>
       <c r="D88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>冒険でしょでしょ?</t>
+          <t>スタートライン</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>平野綾</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+          <t>ベリーグッドマン</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3g-n6WbIcDA</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>8414</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>アニメ・特撮ソング伴奏製作所</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:14:49</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -13700,7 +13749,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -13708,12 +13757,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ハレ晴レユカイ</t>
+          <t>冒険でしょでしょ?</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>平野綾、茅原実里、後藤邑子</t>
+          <t>平野綾</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -13732,15 +13781,15 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>スノウボールアース</t>
+          <t>涼宮ハルヒの憂鬱</t>
         </is>
       </c>
       <c r="D90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -13748,32 +13797,18 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>零-zero-</t>
+          <t>ハレ晴レユカイ</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>tuki.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2splxp-qwH0</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>1001886</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>tuki.(17)</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:15:03</t>
-        </is>
-      </c>
+          <t>平野綾、茅原実里、後藤邑子</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13794,7 +13829,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -13802,30 +13837,30 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>今この胸に滾るのは</t>
+          <t>零-zero-</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ヒグチアイ</t>
+          <t>tuki.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0vTK8SWTgws</t>
+          <t>https://www.youtube.com/watch?v=2splxp-qwH0</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>422037</v>
+        <v>1001886</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>TOHO animation</t>
+          <t>tuki.(17)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-05-03T22:15:15</t>
+          <t>2026-05-03T22:15:03</t>
         </is>
       </c>
     </row>
@@ -13840,7 +13875,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>大賢者リドルの時間逆行</t>
+          <t>スノウボールアース</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -13848,7 +13883,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -13856,30 +13891,30 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>今この胸に滾るのは</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>亜咲花</t>
+          <t>ヒグチアイ</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8XeyK9hI6WI</t>
+          <t>https://www.youtube.com/watch?v=0vTK8SWTgws</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>9657</v>
+        <v>422037</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>亜咲花公式チャンネル</t>
+          <t>TOHO animation</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-05-03T22:15:28</t>
+          <t>2026-05-03T22:15:15</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13929,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ダイヤのA actⅡ Second Season</t>
+          <t>大賢者リドルの時間逆行</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -13902,7 +13937,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -13910,30 +13945,30 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Let's Go Crazy</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Baby Canta</t>
+          <t>亜咲花</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dPWuN1uP09g</t>
+          <t>https://www.youtube.com/watch?v=8XeyK9hI6WI</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>914861</v>
+        <v>9657</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>TVアニメ「ダイヤのA」シリーズ</t>
+          <t>亜咲花公式チャンネル</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-05-03T22:15:41</t>
+          <t>2026-05-03T22:15:28</t>
         </is>
       </c>
     </row>
@@ -13956,7 +13991,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -13964,12 +13999,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>Let's Go Crazy</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>SUPER★DRAGON</t>
+          <t>Baby Canta</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -13987,7 +14022,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-05-03T22:15:53</t>
+          <t>2026-05-03T22:15:41</t>
         </is>
       </c>
     </row>
@@ -14002,7 +14037,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ただいま、おじゃまされます！</t>
+          <t>ダイヤのA actⅡ Second Season</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -14010,7 +14045,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -14018,30 +14053,30 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C'est la vie</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>超特急</t>
+          <t>SUPER★DRAGON</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=w8ltcHURKhc</t>
+          <t>https://www.youtube.com/watch?v=dPWuN1uP09g</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>190536</v>
+        <v>914861</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>超特急</t>
+          <t>TVアニメ「ダイヤのA」シリーズ</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-05-03T22:16:06</t>
+          <t>2026-05-03T22:15:53</t>
         </is>
       </c>
     </row>
@@ -14064,7 +14099,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -14072,30 +14107,30 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>さんかくゲーム</t>
+          <t>C'est la vie</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>『ユイカ』</t>
+          <t>超特急</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=b92uylP2yCs</t>
+          <t>https://www.youtube.com/watch?v=w8ltcHURKhc</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>512594</v>
+        <v>190536</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>『ユイカ』</t>
+          <t>超特急</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-05-03T22:16:19</t>
+          <t>2026-05-03T22:16:06</t>
         </is>
       </c>
     </row>
@@ -14110,7 +14145,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>だんでらいおん</t>
+          <t>ただいま、おじゃまされます！</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -14118,7 +14153,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -14126,30 +14161,30 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ゴロンとドロン</t>
+          <t>さんかくゲーム</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>こっちのけんと</t>
+          <t>『ユイカ』</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ffxN8II-Vic</t>
+          <t>https://www.youtube.com/watch?v=b92uylP2yCs</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>1572114</v>
+        <v>512594</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>こっちのけんと</t>
+          <t>『ユイカ』</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-05-03T22:16:33</t>
+          <t>2026-05-03T22:16:19</t>
         </is>
       </c>
     </row>
@@ -14164,7 +14199,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>杖と剣のウィストリア シーズン2</t>
+          <t>だんでらいおん</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -14172,7 +14207,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -14180,30 +14215,30 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>BELIEVERS</t>
+          <t>ゴロンとドロン</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ASH DA HERO</t>
+          <t>こっちのけんと</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=03eMtnVjiBk</t>
+          <t>https://www.youtube.com/watch?v=ffxN8II-Vic</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>1106840</v>
+        <v>1572114</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>isekai channel @バンダイナムコフィルムワークス</t>
+          <t>こっちのけんと</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-05-03T22:16:45</t>
+          <t>2026-05-03T22:16:33</t>
         </is>
       </c>
     </row>
@@ -14226,7 +14261,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -14234,21 +14269,21 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>リーチライト</t>
+          <t>BELIEVERS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>シユイ</t>
+          <t>ASH DA HERO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Pn0c9QIiqbo</t>
+          <t>https://www.youtube.com/watch?v=03eMtnVjiBk</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>174604</v>
+        <v>1106840</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -14257,7 +14292,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-05-03T22:16:57</t>
+          <t>2026-05-03T22:16:45</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14307,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>デザート キャッチ！ティニピン</t>
+          <t>杖と剣のウィストリア シーズン2</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -14280,7 +14315,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -14288,18 +14323,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>デザート キャッチ！ティニピン</t>
+          <t>リーチライト</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Hearts2Hearts</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
+          <t>シユイ</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Pn0c9QIiqbo</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>174604</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>isekai channel @バンダイナムコフィルムワークス</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:16:57</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -14312,7 +14361,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>転生したらスライムだった件 第4期</t>
+          <t>デザート キャッチ！ティニピン</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -14328,32 +14377,18 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>絵空事</t>
+          <t>デザート キャッチ！ティニピン</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>藍井エイル</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ILfcwl8ZKDs</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>201532</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Lantis Channel</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:17:21</t>
-        </is>
-      </c>
+          <t>Hearts2Hearts</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -14374,7 +14409,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -14382,30 +14417,30 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>渇望</t>
+          <t>絵空事</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>CiON</t>
+          <t>藍井エイル</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xdhkJtJcdEk</t>
+          <t>https://www.youtube.com/watch?v=ILfcwl8ZKDs</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>155173</v>
+        <v>201532</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>CiON official YouTube Channel</t>
+          <t>Lantis Channel</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-05-03T22:17:34</t>
+          <t>2026-05-03T22:17:21</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14455,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dr.STONE SCIENCE FUTURE 第3クール</t>
+          <t>転生したらスライムだった件 第4期</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -14428,7 +14463,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -14436,30 +14471,30 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CASANOVA POSSE</t>
+          <t>渇望</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>ALI</t>
+          <t>CiON</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sPxXiXucYcM</t>
+          <t>https://www.youtube.com/watch?v=xdhkJtJcdEk</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>7100246</v>
+        <v>155173</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>ALI</t>
+          <t>CiON official YouTube Channel</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-05-03T22:17:47</t>
+          <t>2026-05-03T22:17:34</t>
         </is>
       </c>
     </row>
@@ -14486,34 +14521,34 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SUPERNOVA</t>
+          <t>CASANOVA POSSE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>KANA-BOON</t>
+          <t>ALI</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=HNYp4T0kMNU</t>
+          <t>https://www.youtube.com/watch?v=sPxXiXucYcM</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>2456417</v>
+        <v>7100246</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>TOHO animation</t>
+          <t>ALI</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-05-03T22:18:01</t>
+          <t>2026-05-03T22:17:47</t>
         </is>
       </c>
     </row>
@@ -14540,25 +14575,25 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>スキンズ</t>
+          <t>SUPERNOVA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>ASIAN KUNG-FU GENERATION</t>
+          <t>KANA-BOON</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ycH4Twoq83I</t>
+          <t>https://www.youtube.com/watch?v=HNYp4T0kMNU</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>807317</v>
+        <v>2456417</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -14567,7 +14602,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-05-03T22:18:14</t>
+          <t>2026-05-03T22:18:01</t>
         </is>
       </c>
     </row>
@@ -14590,38 +14625,38 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rolling Stone</t>
+          <t>スキンズ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>BREIMEN</t>
+          <t>ASIAN KUNG-FU GENERATION</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5SGVXrvEK0o</t>
+          <t>https://www.youtube.com/watch?v=ycH4Twoq83I</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>1453819</v>
+        <v>807317</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>BREIMEN _Channel</t>
+          <t>TOHO animation</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-05-03T22:18:27</t>
+          <t>2026-05-03T22:18:14</t>
         </is>
       </c>
     </row>
@@ -14648,34 +14683,34 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>no man's world</t>
+          <t>Rolling Stone</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>音羽-otoha-</t>
+          <t>BREIMEN</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SZhcN4jVVzA</t>
+          <t>https://www.youtube.com/watch?v=5SGVXrvEK0o</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>1122108</v>
+        <v>1453819</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>音羽-otoha-</t>
+          <t>BREIMEN _Channel</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-05-03T22:18:40</t>
+          <t>2026-05-03T22:18:27</t>
         </is>
       </c>
     </row>
@@ -14702,34 +14737,34 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ROCKET</t>
+          <t>no man's world</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>BURNOUT SYNDROMES</t>
+          <t>音羽-otoha-</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=HXvZ7Y7uYbo</t>
+          <t>https://www.youtube.com/watch?v=SZhcN4jVVzA</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>629266</v>
+        <v>1122108</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>TOHO animation</t>
+          <t>音羽-otoha-</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-05-03T22:18:53</t>
+          <t>2026-05-03T22:18:40</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14779,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ドロヘドロ Season2</t>
+          <t>Dr.STONE SCIENCE FUTURE 第3クール</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -14752,38 +14787,38 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>ゼッタイMUST断面</t>
+          <t>ROCKET</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(K)NoW_NAME</t>
+          <t>BURNOUT SYNDROMES</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=LWaqlY0Xqy0</t>
+          <t>https://www.youtube.com/watch?v=HXvZ7Y7uYbo</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>911783</v>
+        <v>629266</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>(K)NoW_NAME - Topic</t>
+          <t>TOHO animation</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-05-03T22:19:05</t>
+          <t>2026-05-03T22:18:53</t>
         </is>
       </c>
     </row>
@@ -14806,7 +14841,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -14814,7 +14849,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Return トゥ 頭（ヘッド）</t>
+          <t>ゼッタイMUST断面</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -14824,11 +14859,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6RnvqHkDI50</t>
+          <t>https://www.youtube.com/watch?v=LWaqlY0Xqy0</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>219181</v>
+        <v>911783</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -14837,7 +14872,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-05-03T22:19:16</t>
+          <t>2026-05-03T22:19:05</t>
         </is>
       </c>
     </row>
@@ -14852,7 +14887,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>とんがり帽子のアトリエ</t>
+          <t>ドロヘドロ Season2</t>
         </is>
       </c>
       <c r="D111" t="b">
@@ -14860,7 +14895,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -14868,30 +14903,30 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>風のアンセム feat. suis from ヨルシカ</t>
+          <t>Return トゥ 頭（ヘッド）</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Eve</t>
+          <t>(K)NoW_NAME</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ySpIrrCmiCU</t>
+          <t>https://www.youtube.com/watch?v=6RnvqHkDI50</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>2058400</v>
+        <v>219181</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Eve</t>
+          <t>(K)NoW_NAME - Topic</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-05-03T22:19:30</t>
+          <t>2026-05-03T22:19:16</t>
         </is>
       </c>
     </row>
@@ -14914,7 +14949,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -14922,30 +14957,30 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ただ美しい呪い</t>
+          <t>風のアンセム feat. suis from ヨルシカ</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Nakamura Hak</t>
+          <t>Eve</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rQ0S_0CepIo</t>
+          <t>https://www.youtube.com/watch?v=ySpIrrCmiCU</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>1305856</v>
+        <v>2058400</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>TVアニメ「とんがり帽子のアトリエ」公式</t>
+          <t>Eve</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-05-03T22:19:42</t>
+          <t>2026-05-03T22:19:30</t>
         </is>
       </c>
     </row>
@@ -14960,7 +14995,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NEEDY GIRL OVERDOSE</t>
+          <t>とんがり帽子のアトリエ</t>
         </is>
       </c>
       <c r="D113" t="b">
@@ -14968,7 +15003,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -14976,30 +15011,30 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>INTERNET ANGEL</t>
+          <t>ただ美しい呪い</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Aiobahn ＋81</t>
+          <t>Nakamura Hak</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BnkhBwzBqlQ</t>
+          <t>https://www.youtube.com/watch?v=rQ0S_0CepIo</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>29176895</v>
+        <v>1305856</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Aiobahn</t>
+          <t>TVアニメ「とんがり帽子のアトリエ」公式</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-05-03T22:19:55</t>
+          <t>2026-05-03T22:19:42</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15057,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -15030,30 +15065,30 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>れびてーしょん</t>
+          <t>INTERNET ANGEL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>キタニタツヤ</t>
+          <t>Aiobahn ＋81</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=l7hbIgnyhe0</t>
+          <t>https://www.youtube.com/watch?v=BnkhBwzBqlQ</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>579425</v>
+        <v>29176895</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>キタニタツヤ / Tatsuya Kitani</t>
+          <t>Aiobahn</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-05-03T22:20:08</t>
+          <t>2026-05-03T22:19:55</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15103,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>逃がした魚は大きかったが釣りあげた魚が大きすぎた件</t>
+          <t>NEEDY GIRL OVERDOSE</t>
         </is>
       </c>
       <c r="D115" t="b">
@@ -15076,7 +15111,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -15084,30 +15119,30 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>誓いはキュンと。</t>
+          <t>れびてーしょん</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>HoneyWorks feat.鈴木愛理</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_3aytoDQTHg</t>
+          <t>https://www.youtube.com/watch?v=l7hbIgnyhe0</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>728377</v>
+        <v>579425</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>MARUMOCHI from HoneyWorks</t>
+          <t>キタニタツヤ / Tatsuya Kitani</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-05-03T22:20:22</t>
+          <t>2026-05-03T22:20:08</t>
         </is>
       </c>
     </row>
@@ -15130,7 +15165,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -15138,30 +15173,30 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DEAD OR LOVE</t>
+          <t>誓いはキュンと。</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>吉乃</t>
+          <t>HoneyWorks feat.鈴木愛理</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iouWS4pwX28</t>
+          <t>https://www.youtube.com/watch?v=_3aytoDQTHg</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>227515</v>
+        <v>728377</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>吉乃</t>
+          <t>MARUMOCHI from HoneyWorks</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-05-03T22:20:35</t>
+          <t>2026-05-03T22:20:22</t>
         </is>
       </c>
     </row>
@@ -15176,15 +15211,15 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>逃げ上手の若君</t>
+          <t>逃がした魚は大きかったが釣りあげた魚が大きすぎた件</t>
         </is>
       </c>
       <c r="D117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -15192,18 +15227,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>プランA</t>
+          <t>DEAD OR LOVE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>DISH//</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
+          <t>吉乃</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iouWS4pwX28</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>227515</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>吉乃</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:20:35</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -15224,7 +15273,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -15232,12 +15281,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>鎌倉STYLE</t>
+          <t>プランA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ぼっちぼろまる</t>
+          <t>DISH//</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -15256,15 +15305,15 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>日本三國</t>
+          <t>逃げ上手の若君</t>
         </is>
       </c>
       <c r="D119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -15272,32 +15321,18 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>火種</t>
+          <t>鎌倉STYLE</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>キタニタツヤ</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=hA_9r-3jkSg</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>1806016</v>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>キタニタツヤ / Tatsuya Kitani</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:20:49</t>
-        </is>
-      </c>
+          <t>ぼっちぼろまる</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -15318,7 +15353,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -15326,30 +15361,30 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>誓い</t>
+          <t>火種</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Leina</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1KnySdlZHJU</t>
+          <t>https://www.youtube.com/watch?v=hA_9r-3jkSg</t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>259162</v>
+        <v>1806016</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Leina</t>
+          <t>キタニタツヤ / Tatsuya Kitani</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-05-03T22:21:02</t>
+          <t>2026-05-03T22:20:49</t>
         </is>
       </c>
     </row>
@@ -15364,7 +15399,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ニワトリ・ファイター</t>
+          <t>日本三國</t>
         </is>
       </c>
       <c r="D121" t="b">
@@ -15372,7 +15407,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -15380,30 +15415,30 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>What's a Hero?</t>
+          <t>誓い</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>DARUMA Rollin’</t>
+          <t>Leina</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mfBWkIIQE9w</t>
+          <t>https://www.youtube.com/watch?v=1KnySdlZHJU</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>267737</v>
+        <v>259162</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>DARUMA Rollin'</t>
+          <t>Leina</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-05-03T22:21:14</t>
+          <t>2026-05-03T22:21:02</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15461,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -15434,30 +15469,30 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>We're Loose Stars</t>
+          <t>What's a Hero?</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>高橋哲也</t>
+          <t>DARUMA Rollin’</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=muqyayR_9ts</t>
+          <t>https://www.youtube.com/watch?v=mfBWkIIQE9w</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>8986</v>
+        <v>267737</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>HERO'S Web公式チャンネル</t>
+          <t>DARUMA Rollin'</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-05-03T22:21:29</t>
+          <t>2026-05-03T22:21:14</t>
         </is>
       </c>
     </row>
@@ -15472,7 +15507,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ネコのクラちゃん～クラレ王国 大陸のLutte Amor～</t>
+          <t>ニワトリ・ファイター</t>
         </is>
       </c>
       <c r="D123" t="b">
@@ -15480,7 +15515,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -15488,18 +15523,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ネコのクラちゃん</t>
+          <t>We're Loose Stars</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ピンクスカート（宮崎寿々佳）</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
+          <t>高橋哲也</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=muqyayR_9ts</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>8986</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>HERO'S Web公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:21:29</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15520,7 +15569,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -15528,12 +15577,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>未来のシンフォニー</t>
+          <t>ネコのクラちゃん</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Baby’z Breath</t>
+          <t>ピンクスカート（宮崎寿々佳）</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15552,7 +15601,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ねずみくんのチョッキ</t>
+          <t>ネコのクラちゃん～クラレ王国 大陸のLutte Amor～</t>
         </is>
       </c>
       <c r="D125" t="b">
@@ -15560,7 +15609,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -15568,12 +15617,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>グッドラック！マイフレンド feat.ムロツヨシ &amp; さかなクン</t>
+          <t>未来のシンフォニー</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>東京スカパラダイスオーケストラ</t>
+          <t>Baby’z Breath</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15592,7 +15641,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>灰原くんの強くて青春ニューゲーム</t>
+          <t>ねずみくんのチョッキ</t>
         </is>
       </c>
       <c r="D126" t="b">
@@ -15600,7 +15649,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -15608,32 +15657,18 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fly Again!!</t>
+          <t>グッドラック！マイフレンド feat.ムロツヨシ &amp; さかなクン</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>前島亜美</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=xuyA1jEiJ8c</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>193665</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>前島亜美</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:22:02</t>
-        </is>
-      </c>
+          <t>東京スカパラダイスオーケストラ</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15654,7 +15689,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -15662,30 +15697,30 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ドラマチック逃避行</t>
+          <t>Fly Again!!</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>愛美</t>
+          <t>前島亜美</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ifutP5vX5TA</t>
+          <t>https://www.youtube.com/watch?v=xuyA1jEiJ8c</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>21547</v>
+        <v>193665</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>AIMI official YouTube Channel</t>
+          <t>前島亜美</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-05-03T22:22:14</t>
+          <t>2026-05-03T22:22:02</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15735,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BEASTARS FINAL SEASON Part2</t>
+          <t>灰原くんの強くて青春ニューゲーム</t>
         </is>
       </c>
       <c r="D128" t="b">
@@ -15708,7 +15743,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -15716,30 +15751,30 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Into the world</t>
+          <t>ドラマチック逃避行</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>issei</t>
+          <t>愛美</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gOTNI5smH2E</t>
+          <t>https://www.youtube.com/watch?v=ifutP5vX5TA</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>1197894</v>
+        <v>21547</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>TOHO animation</t>
+          <t>AIMI official YouTube Channel</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-05-03T22:22:26</t>
+          <t>2026-05-03T22:22:14</t>
         </is>
       </c>
     </row>
@@ -15766,16 +15801,16 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>LA FERALIA</t>
+          <t>Into the world</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>神前暁</t>
+          <t>issei</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -15793,7 +15828,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-05-03T22:22:40</t>
+          <t>2026-05-03T22:22:26</t>
         </is>
       </c>
     </row>
@@ -15816,26 +15851,40 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Feel Like This</t>
+          <t>LA FERALIA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>由薫</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
+          <t>神前暁</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gOTNI5smH2E</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>1197894</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:22:40</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15860,36 +15909,22 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tiny Light</t>
+          <t>Feel Like This</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>SEVENTEEN</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5A7qyhj-HjE</t>
-        </is>
-      </c>
-      <c r="J131" t="n">
-        <v>828219</v>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>SEVENTEEN</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:23:01</t>
-        </is>
-      </c>
+          <t>由薫</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15902,7 +15937,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>悲劇の元凶となる最強外道ラスボス女王は民の為に尽くします。Season２</t>
+          <t>BEASTARS FINAL SEASON Part2</t>
         </is>
       </c>
       <c r="D132" t="b">
@@ -15910,38 +15945,38 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>エゴ</t>
+          <t>Tiny Light</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>レトロリロン</t>
+          <t>SEVENTEEN</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4cGnQ8gFCCs</t>
+          <t>https://www.youtube.com/watch?v=5A7qyhj-HjE</t>
         </is>
       </c>
       <c r="J132" t="n">
-        <v>117523</v>
+        <v>828219</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>MBS animation 公式チャンネル</t>
+          <t>SEVENTEEN</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-05-03T22:23:14</t>
+          <t>2026-05-03T22:23:01</t>
         </is>
       </c>
     </row>
@@ -15964,7 +15999,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -15972,21 +16007,21 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>たられば</t>
+          <t>エゴ</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ガラクタ</t>
+          <t>レトロリロン</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xSNhOhCEaC4</t>
+          <t>https://www.youtube.com/watch?v=4cGnQ8gFCCs</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>27686</v>
+        <v>117523</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -15995,7 +16030,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-05-03T22:23:27</t>
+          <t>2026-05-03T22:23:14</t>
         </is>
       </c>
     </row>
@@ -16010,7 +16045,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>左ききのエレン</t>
+          <t>悲劇の元凶となる最強外道ラスボス女王は民の為に尽くします。Season２</t>
         </is>
       </c>
       <c r="D134" t="b">
@@ -16018,7 +16053,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -16026,30 +16061,30 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FUNKIN’ BEAUTIFUL feat. ZORN</t>
+          <t>たられば</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>ALI</t>
+          <t>ガラクタ</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8V9cwO1ZxGk</t>
+          <t>https://www.youtube.com/watch?v=xSNhOhCEaC4</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>80366</v>
+        <v>27686</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>ALI</t>
+          <t>MBS animation 公式チャンネル</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-05-03T22:23:39</t>
+          <t>2026-05-03T22:23:27</t>
         </is>
       </c>
     </row>
@@ -16072,7 +16107,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -16080,30 +16115,30 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>New Walk</t>
+          <t>FUNKIN’ BEAUTIFUL feat. ZORN</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>紫 今</t>
+          <t>ALI</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vlbobXEQLqY</t>
+          <t>https://www.youtube.com/watch?v=8V9cwO1ZxGk</t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>125026</v>
+        <v>80366</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>ギャガ公式チャンネル</t>
+          <t>ALI</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-05-03T22:23:50</t>
+          <t>2026-05-03T22:23:39</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16153,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>姫騎士は蛮族（バルバロイ）の嫁</t>
+          <t>左ききのエレン</t>
         </is>
       </c>
       <c r="D136" t="b">
@@ -16126,7 +16161,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -16134,18 +16169,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>BEAUTIFUL</t>
+          <t>New Walk</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>前島麻由</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
+          <t>紫 今</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vlbobXEQLqY</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>125026</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>ギャガ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:23:50</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16166,7 +16215,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -16174,12 +16223,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>シルベキコト</t>
+          <t>BEAUTIFUL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>sajou no hana</t>
+          <t>前島麻由</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16198,7 +16247,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>百鬼夜行抄</t>
+          <t>姫騎士は蛮族（バルバロイ）の嫁</t>
         </is>
       </c>
       <c r="D138" t="b">
@@ -16214,12 +16263,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>何にもなれない</t>
+          <t>シルベキコト</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ヤングスキニー</t>
+          <t>sajou no hana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16238,15 +16287,15 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ぷにるんず ぷに３</t>
+          <t>百鬼夜行抄</t>
         </is>
       </c>
       <c r="D139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -16254,12 +16303,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>ぷにぷにぷにるんず ぷにックスバージョン</t>
+          <t>何にもなれない</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>ななひら</t>
+          <t>ヤングスキニー</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16278,15 +16327,15 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>北斗の拳 -FIST OF THE NORTH STAR-</t>
+          <t>ぷにるんず ぷに３</t>
         </is>
       </c>
       <c r="D140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -16294,12 +16343,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hallelujah</t>
+          <t>ぷにぷにぷにるんず ぷにックスバージョン</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>[Alexandros]</t>
+          <t>ななひら</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16326,7 +16375,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -16334,12 +16383,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>愛をとりもどせ!!</t>
+          <t>Hallelujah</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Toshl</t>
+          <t>[Alexandros]</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16358,7 +16407,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ポンコツ風紀委員とスカート丈が不適切なJKの話</t>
+          <t>北斗の拳 -FIST OF THE NORTH STAR-</t>
         </is>
       </c>
       <c r="D142" t="b">
@@ -16366,7 +16415,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -16374,32 +16423,18 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ヒトリゴト</t>
+          <t>愛をとりもどせ!!</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>osage</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=0XwlRpvjbmY</t>
-        </is>
-      </c>
-      <c r="J142" t="n">
-        <v>3513</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>osage official</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:24:51</t>
-        </is>
-      </c>
+          <t>Toshl</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16420,7 +16455,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -16428,30 +16463,30 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>部屋とガラクタと私</t>
+          <t>ヒトリゴト</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ミーマイナー</t>
+          <t>osage</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6TOl476i5Q8</t>
+          <t>https://www.youtube.com/watch?v=0XwlRpvjbmY</t>
         </is>
       </c>
       <c r="J143" t="n">
-        <v>27410</v>
+        <v>3513</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>ミーマイナー</t>
+          <t>osage official</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-05-03T22:25:04</t>
+          <t>2026-05-03T22:24:51</t>
         </is>
       </c>
     </row>
@@ -16466,7 +16501,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>本好きの下剋上 領主の養女</t>
+          <t>ポンコツ風紀委員とスカート丈が不適切なJKの話</t>
         </is>
       </c>
       <c r="D144" t="b">
@@ -16474,7 +16509,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -16482,30 +16517,30 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>部屋とガラクタと私</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Little Glee Monster</t>
+          <t>ミーマイナー</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DNa76ODisco</t>
+          <t>https://www.youtube.com/watch?v=6TOl476i5Q8</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>429127</v>
+        <v>27410</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Little Glee Monster</t>
+          <t>ミーマイナー</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-05-03T22:25:17</t>
+          <t>2026-05-03T22:25:04</t>
         </is>
       </c>
     </row>
@@ -16528,7 +16563,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -16536,30 +16571,30 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>今も、ありがとう</t>
+          <t>Pages</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>生田絵梨花</t>
+          <t>Little Glee Monster</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kX0u1U7wMDk</t>
+          <t>https://www.youtube.com/watch?v=DNa76ODisco</t>
         </is>
       </c>
       <c r="J145" t="n">
-        <v>705610</v>
+        <v>429127</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>生田絵梨花 Official YouTube Channel</t>
+          <t>Little Glee Monster</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-05-03T22:25:32</t>
+          <t>2026-05-03T22:25:17</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16609,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>魔入りました！入間くん 第4シリーズ</t>
+          <t>本好きの下剋上 領主の養女</t>
         </is>
       </c>
       <c r="D146" t="b">
@@ -16582,7 +16617,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -16590,17 +16625,17 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>一二三</t>
+          <t>今も、ありがとう</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>生田絵梨花</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m4yCXpCiXpk</t>
+          <t>https://www.youtube.com/watch?v=kX0u1U7wMDk</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -16608,12 +16643,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>生田絵梨花 Official YouTube Channel</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-05-03T22:25:46</t>
+          <t>2026-05-03T22:25:32</t>
         </is>
       </c>
     </row>
@@ -16636,7 +16671,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -16644,30 +16679,30 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>すーぱー優勝ちゅーーん！</t>
+          <t>一二三</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>CANDY TUNE</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=jMhzqfi9aPw</t>
+          <t>https://www.youtube.com/watch?v=m4yCXpCiXpk</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>630585</v>
+        <v>705610</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>アニメ「魔入りました!入間くん」公式Anime OFFICIAL</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-05-03T22:25:58</t>
+          <t>2026-05-03T22:25:46</t>
         </is>
       </c>
     </row>
@@ -16682,15 +16717,15 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>前橋ウィッチーズ</t>
+          <t>魔入りました！入間くん 第4シリーズ</t>
         </is>
       </c>
       <c r="D148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -16698,18 +16733,32 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>スゴすぎ前橋ウィッチーズ！</t>
+          <t>すーぱー優勝ちゅーーん！</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>前橋ウィッチーズ</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
+          <t>CANDY TUNE</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jMhzqfi9aPw</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>630585</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>アニメ「魔入りました!入間くん」公式Anime OFFICIAL</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:25:58</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16730,7 +16779,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -16738,7 +16787,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>それぞれのドア</t>
+          <t>スゴすぎ前橋ウィッチーズ！</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -16762,15 +16811,15 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MAO</t>
+          <t>前橋ウィッチーズ</t>
         </is>
       </c>
       <c r="D150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -16778,32 +16827,18 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>HEARTLOUD</t>
+          <t>それぞれのドア</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kis-My-Ft2</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=MGUp9RBrou4</t>
-        </is>
-      </c>
-      <c r="J150" t="n">
-        <v>10157104</v>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Kis-My-Ft2</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:26:13</t>
-        </is>
-      </c>
+          <t>前橋ウィッチーズ</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16824,7 +16859,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -16832,30 +16867,30 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>呪愛</t>
+          <t>HEARTLOUD</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Kis-My-Ft2</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eVfpoS0rjw0</t>
+          <t>https://www.youtube.com/watch?v=MGUp9RBrou4</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>1659920</v>
+        <v>10157104</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Bandai Namco Filmworks Channel</t>
+          <t>Kis-My-Ft2</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-05-03T22:26:25</t>
+          <t>2026-05-03T22:26:13</t>
         </is>
       </c>
     </row>
@@ -16870,7 +16905,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>また殺されてしまったのですね、探偵様</t>
+          <t>MAO</t>
         </is>
       </c>
       <c r="D152" t="b">
@@ -16878,7 +16913,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -16886,30 +16921,30 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>スターダスト・エウレカ</t>
+          <t>呪愛</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>多次元制御機構よだか</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Z53w6cpG5GM</t>
+          <t>https://www.youtube.com/watch?v=eVfpoS0rjw0</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>48053</v>
+        <v>1659920</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>TBSアニメ</t>
+          <t>Bandai Namco Filmworks Channel</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-05-03T22:26:35</t>
+          <t>2026-05-03T22:26:25</t>
         </is>
       </c>
     </row>
@@ -16932,7 +16967,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -16940,30 +16975,30 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>リリテアの歌</t>
+          <t>スターダスト・エウレカ</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>リリテア（CV.若山詩音）</t>
+          <t>多次元制御機構よだか</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZvHOYO6tfvk</t>
+          <t>https://www.youtube.com/watch?v=Z53w6cpG5GM</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>16033</v>
+        <v>48053</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>リリテア（CV:若山詩音） - Topic</t>
+          <t>TBSアニメ</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-05-03T22:26:41</t>
+          <t>2026-05-03T22:26:35</t>
         </is>
       </c>
     </row>
@@ -16978,7 +17013,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>魔法の姉妹ルルットリリィ</t>
+          <t>また殺されてしまったのですね、探偵様</t>
         </is>
       </c>
       <c r="D154" t="b">
@@ -16986,7 +17021,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -16994,30 +17029,30 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bubee</t>
+          <t>リリテアの歌</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>ILLIT</t>
+          <t>リリテア（CV.若山詩音）</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OZ44P4JU87E</t>
+          <t>https://www.youtube.com/watch?v=ZvHOYO6tfvk</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>1544080</v>
+        <v>16033</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>ILLIT</t>
+          <t>リリテア（CV:若山詩音） - Topic</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-05-03T22:26:55</t>
+          <t>2026-05-03T22:26:41</t>
         </is>
       </c>
     </row>
@@ -17040,7 +17075,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -17048,30 +17083,30 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Calling</t>
+          <t>Bubee</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>ルルットリリィ（こんぺとリリィ（CV.橘めい）、ましゅールル（CV.小鹿なお））</t>
+          <t>ILLIT</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=803SES0YVcM</t>
+          <t>https://www.youtube.com/watch?v=OZ44P4JU87E</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>209352</v>
+        <v>1544080</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Bandai Namco Filmworks Channel</t>
+          <t>ILLIT</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-05-03T22:27:07</t>
+          <t>2026-05-03T22:26:55</t>
         </is>
       </c>
     </row>
@@ -17086,7 +17121,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>魔物喰らいの冒険者～俺だけ魔物を喰らって強くなる～</t>
+          <t>魔法の姉妹ルルットリリィ</t>
         </is>
       </c>
       <c r="D156" t="b">
@@ -17094,7 +17129,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -17102,30 +17137,30 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>正気の沙汰</t>
+          <t>Calling</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ルルットリリィ（こんぺとリリィ（CV.橘めい）、ましゅールル（CV.小鹿なお））</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0j7O1Sw62Ms</t>
+          <t>https://www.youtube.com/watch?v=803SES0YVcM</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>39536</v>
+        <v>209352</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>Bandai Namco Filmworks Channel</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-05-03T22:27:20</t>
+          <t>2026-05-03T22:27:07</t>
         </is>
       </c>
     </row>
@@ -17148,7 +17183,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -17156,18 +17191,32 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>STORY</t>
+          <t>正気の沙汰</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>niina</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0j7O1Sw62Ms</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>39536</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:27:20</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17180,7 +17229,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>茉莉花ちゃんの好感度はぶっ壊れている</t>
+          <t>魔物喰らいの冒険者～俺だけ魔物を喰らって強くなる～</t>
         </is>
       </c>
       <c r="D158" t="b">
@@ -17188,7 +17237,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -17196,12 +17245,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>はかりたい好感度</t>
+          <t>STORY</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>千歳茉莉花（CV.内田真礼）</t>
+          <t>niina</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17220,7 +17269,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>マリッジトキシン</t>
+          <t>茉莉花ちゃんの好感度はぶっ壊れている</t>
         </is>
       </c>
       <c r="D159" t="b">
@@ -17228,7 +17277,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -17236,32 +17285,18 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Kill or Kiss</t>
+          <t>はかりたい好感度</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>平手友梨奈</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=QbNwgXAXq9M</t>
-        </is>
-      </c>
-      <c r="J159" t="n">
-        <v>964216</v>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>平手友梨奈</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:27:50</t>
-        </is>
-      </c>
+          <t>千歳茉莉花（CV.内田真礼）</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17282,7 +17317,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -17290,30 +17325,30 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>シャケナベイベー</t>
+          <t>Kill or Kiss</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>AKASAKI</t>
+          <t>平手友梨奈</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WwI7hPXZC-Y</t>
+          <t>https://www.youtube.com/watch?v=QbNwgXAXq9M</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>2444210</v>
+        <v>964216</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>AKASAKI (19)</t>
+          <t>平手友梨奈</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-05-03T22:28:02</t>
+          <t>2026-05-03T22:27:50</t>
         </is>
       </c>
     </row>
@@ -17328,7 +17363,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>メイドさんは食べるだけ</t>
+          <t>マリッジトキシン</t>
         </is>
       </c>
       <c r="D161" t="b">
@@ -17336,7 +17371,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -17344,30 +17379,30 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>リボン</t>
+          <t>シャケナベイベー</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>majiko</t>
+          <t>AKASAKI</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VHD2269UqdM</t>
+          <t>https://www.youtube.com/watch?v=WwI7hPXZC-Y</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>37559</v>
+        <v>2444210</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>ハピネット【アニメ公式】</t>
+          <t>AKASAKI (19)</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-05-03T22:28:14</t>
+          <t>2026-05-03T22:28:02</t>
         </is>
       </c>
     </row>
@@ -17390,7 +17425,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -17398,21 +17433,21 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>しあわせフレーバー</t>
+          <t>リボン</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>ARCANA PROJECT</t>
+          <t>majiko</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBSo4npKK9A</t>
+          <t>https://www.youtube.com/watch?v=VHD2269UqdM</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>11878</v>
+        <v>37559</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -17421,7 +17456,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-05-03T22:28:25</t>
+          <t>2026-05-03T22:28:14</t>
         </is>
       </c>
     </row>
@@ -17436,7 +17471,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>女神「異世界転生何になりたいですか」 俺「勇者の肋骨で」</t>
+          <t>メイドさんは食べるだけ</t>
         </is>
       </c>
       <c r="D163" t="b">
@@ -17444,7 +17479,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -17452,30 +17487,30 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>転生願望</t>
+          <t>しあわせフレーバー</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>終活クラブ</t>
+          <t>ARCANA PROJECT</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=suKjfBsH3UM</t>
+          <t>https://www.youtube.com/watch?v=vBSo4npKK9A</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>147879</v>
+        <v>11878</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>アニメ『女神「異世界転生何になりたいですか」 俺「勇者の肋骨で」』</t>
+          <t>ハピネット【アニメ公式】</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-05-03T22:28:38</t>
+          <t>2026-05-03T22:28:25</t>
         </is>
       </c>
     </row>
@@ -17498,7 +17533,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -17506,12 +17541,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>何なんですか？</t>
+          <t>転生願望</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>shallm</t>
+          <t>終活クラブ</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -17529,7 +17564,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-05-03T22:28:51</t>
+          <t>2026-05-03T22:28:38</t>
         </is>
       </c>
     </row>
@@ -17544,7 +17579,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ようこそ実力至上主義の教室へ 4th Season</t>
+          <t>女神「異世界転生何になりたいですか」 俺「勇者の肋骨で」</t>
         </is>
       </c>
       <c r="D165" t="b">
@@ -17552,7 +17587,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -17560,30 +17595,30 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>MONSTER</t>
+          <t>何なんですか？</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>藍井エイル</t>
+          <t>shallm</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=l78_JpSXfxw</t>
+          <t>https://www.youtube.com/watch?v=suKjfBsH3UM</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>358837</v>
+        <v>147879</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Lantis Channel</t>
+          <t>アニメ『女神「異世界転生何になりたいですか」 俺「勇者の肋骨で」』</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-05-03T22:29:04</t>
+          <t>2026-05-03T22:28:51</t>
         </is>
       </c>
     </row>
@@ -17606,7 +17641,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -17614,30 +17649,30 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>ライアーヴェール</t>
+          <t>MONSTER</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>ZAQ</t>
+          <t>藍井エイル</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=jl7GmJBNxk4</t>
+          <t>https://www.youtube.com/watch?v=l78_JpSXfxw</t>
         </is>
       </c>
       <c r="J166" t="n">
-        <v>89423</v>
+        <v>358837</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>ZAQ Official Channel</t>
+          <t>Lantis Channel</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-05-03T22:29:16</t>
+          <t>2026-05-03T22:29:04</t>
         </is>
       </c>
     </row>
@@ -17652,15 +17687,15 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>幼女戦記</t>
+          <t>ようこそ実力至上主義の教室へ 4th Season</t>
         </is>
       </c>
       <c r="D167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -17668,18 +17703,32 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>JINGO JUNGLE</t>
+          <t>ライアーヴェール</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>MYTH ＆ROID</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
+          <t>ZAQ</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jl7GmJBNxk4</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>89423</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>ZAQ Official Channel</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:29:16</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17700,7 +17749,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -17708,12 +17757,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Los! Los! Los!</t>
+          <t>JINGO JUNGLE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ(CV.悠木碧)</t>
+          <t>MYTH ＆ROID</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17732,15 +17781,15 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>夜桜さんちの大作戦 第2期</t>
+          <t>幼女戦記</t>
         </is>
       </c>
       <c r="D169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -17748,32 +17797,18 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>What's "KAZOKU"</t>
+          <t>Los! Los! Los!</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>櫻坂46</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=AIspds2UVts</t>
-        </is>
-      </c>
-      <c r="J169" t="n">
-        <v>187933</v>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>NBCUniversal Anime/Music</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>2026-05-03T22:29:28</t>
-        </is>
-      </c>
+          <t>ターニャ・デグレチャフ(CV.悠木碧)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17794,7 +17829,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -17802,21 +17837,21 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Shalala</t>
+          <t>What's "KAZOKU"</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>ピラフ星人</t>
+          <t>櫻坂46</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=X6fNe1uPs9E</t>
+          <t>https://www.youtube.com/watch?v=AIspds2UVts</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>234792</v>
+        <v>187933</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -17825,7 +17860,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-05-03T22:29:40</t>
+          <t>2026-05-03T22:29:28</t>
         </is>
       </c>
     </row>
@@ -17840,7 +17875,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>黄泉のツガイ</t>
+          <t>夜桜さんちの大作戦 第2期</t>
         </is>
       </c>
       <c r="D171" t="b">
@@ -17848,7 +17883,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -17856,30 +17891,30 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>飛ぶ時</t>
+          <t>Shalala</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Vaundy</t>
+          <t>ピラフ星人</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=LVCwdZoUFQ8</t>
+          <t>https://www.youtube.com/watch?v=X6fNe1uPs9E</t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>3496214</v>
+        <v>234792</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Vaundy</t>
+          <t>NBCUniversal Anime/Music</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-05-03T22:29:53</t>
+          <t>2026-05-03T22:29:40</t>
         </is>
       </c>
     </row>
@@ -17902,7 +17937,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -17910,30 +17945,30 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>飛ぼうよ</t>
+          <t>飛ぶ時</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>yama</t>
+          <t>Vaundy</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8uRMfPTAhkU</t>
+          <t>https://www.youtube.com/watch?v=LVCwdZoUFQ8</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>373757</v>
+        <v>3496214</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>yama</t>
+          <t>Vaundy</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-05-03T22:30:06</t>
+          <t>2026-05-03T22:29:53</t>
         </is>
       </c>
     </row>
@@ -17948,7 +17983,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>よわよわ先生</t>
+          <t>黄泉のツガイ</t>
         </is>
       </c>
       <c r="D173" t="b">
@@ -17956,7 +17991,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -17964,30 +17999,30 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>COMIT COMET</t>
+          <t>飛ぼうよ</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Daoko</t>
+          <t>yama</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0jO_isUIymg</t>
+          <t>https://www.youtube.com/watch?v=8uRMfPTAhkU</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>129233</v>
+        <v>373757</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>日活アニメチャンネル</t>
+          <t>yama</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-05-03T22:30:19</t>
+          <t>2026-05-03T22:30:06</t>
         </is>
       </c>
     </row>
@@ -18010,7 +18045,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -18018,21 +18053,21 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>よわよわ つよつよ みにみに こわこわ</t>
+          <t>COMIT COMET</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>鶸村ひより(CV：高野麻里佳)、椋林瑞希(CV：伊駒ゆりえ)、雪下祐樹(CV：篠原侑)</t>
+          <t>Daoko</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=LRPRccAPekk</t>
+          <t>https://www.youtube.com/watch?v=0jO_isUIymg</t>
         </is>
       </c>
       <c r="J174" t="n">
-        <v>132505</v>
+        <v>129233</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -18041,7 +18076,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-05-03T22:30:33</t>
+          <t>2026-05-03T22:30:19</t>
         </is>
       </c>
     </row>
@@ -18056,7 +18091,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>LIAR GAME</t>
+          <t>よわよわ先生</t>
         </is>
       </c>
       <c r="D175" t="b">
@@ -18064,7 +18099,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -18072,30 +18107,30 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>あぶく</t>
+          <t>よわよわ つよつよ みにみに こわこわ</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>ヨルシカ</t>
+          <t>鶸村ひより(CV：高野麻里佳)、椋林瑞希(CV：伊駒ゆりえ)、雪下祐樹(CV：篠原侑)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OHAjc-ayhus</t>
+          <t>https://www.youtube.com/watch?v=LRPRccAPekk</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>6187955</v>
+        <v>132505</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>ヨルシカ / n-buna Official</t>
+          <t>日活アニメチャンネル</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-05-03T22:30:46</t>
+          <t>2026-05-03T22:30:33</t>
         </is>
       </c>
     </row>
@@ -18118,7 +18153,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -18126,30 +18161,30 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>朝日</t>
+          <t>あぶく</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Lucky Kilimanjaro</t>
+          <t>ヨルシカ</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hyp8GGN7C1w</t>
+          <t>https://www.youtube.com/watch?v=OHAjc-ayhus</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>58183</v>
+        <v>6187955</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Lucky Kilimanjaro</t>
+          <t>ヨルシカ / n-buna Official</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-05-03T22:31:00</t>
+          <t>2026-05-03T22:30:46</t>
         </is>
       </c>
     </row>
@@ -18164,7 +18199,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>リィンカーネーションの花弁</t>
+          <t>LIAR GAME</t>
         </is>
       </c>
       <c r="D177" t="b">
@@ -18172,7 +18207,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -18180,30 +18215,30 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Glitch*</t>
+          <t>朝日</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>eill</t>
+          <t>Lucky Kilimanjaro</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fsgD8mLRxwo</t>
+          <t>https://www.youtube.com/watch?v=hyp8GGN7C1w</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>208770</v>
+        <v>58183</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>eill official</t>
+          <t>Lucky Kilimanjaro</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-05-03T22:31:16</t>
+          <t>2026-05-03T22:31:00</t>
         </is>
       </c>
     </row>
@@ -18226,7 +18261,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -18234,30 +18269,30 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>零</t>
+          <t>Glitch*</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Sizuk</t>
+          <t>eill</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=LimcX6xNEaY</t>
+          <t>https://www.youtube.com/watch?v=fsgD8mLRxwo</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>59739</v>
+        <v>208770</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Sizuk / Shunryu</t>
+          <t>eill official</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-05-03T22:31:29</t>
+          <t>2026-05-03T22:31:16</t>
         </is>
       </c>
     </row>
@@ -18272,7 +18307,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Re:ゼロから始める異世界生活 4th season</t>
+          <t>リィンカーネーションの花弁</t>
         </is>
       </c>
       <c r="D179" t="b">
@@ -18280,7 +18315,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -18288,30 +18323,30 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Recollect</t>
+          <t>零</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>鈴木このみ feat. Ashnikko</t>
+          <t>Sizuk</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VDGG9zi53rQ</t>
+          <t>https://www.youtube.com/watch?v=LimcX6xNEaY</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>5097812</v>
+        <v>59739</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>「Re:ゼロから始める異世界生活」チャンネル【公式】</t>
+          <t>Sizuk / Shunryu</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-05-03T22:31:42</t>
+          <t>2026-05-03T22:31:29</t>
         </is>
       </c>
     </row>
@@ -18334,7 +18369,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -18342,21 +18377,21 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ender Ember</t>
+          <t>Recollect</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID feat. TK（凛として時雨）</t>
+          <t>鈴木このみ feat. Ashnikko</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iKLqlb_oX60</t>
+          <t>https://www.youtube.com/watch?v=VDGG9zi53rQ</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>579546</v>
+        <v>5097812</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -18365,7 +18400,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-05-03T22:31:54</t>
+          <t>2026-05-03T22:31:42</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18415,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>リラックマ</t>
+          <t>Re:ゼロから始める異世界生活 4th season</t>
         </is>
       </c>
       <c r="D181" t="b">
@@ -18388,7 +18423,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -18396,30 +18431,30 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>stay with me</t>
+          <t>Ender Ember</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>幾田りら</t>
+          <t>MYTH &amp; ROID feat. TK（凛として時雨）</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JcDyAzbGA78</t>
+          <t>https://www.youtube.com/watch?v=iKLqlb_oX60</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>369868</v>
+        <v>579546</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>幾田りら / Lilas Official</t>
+          <t>「Re:ゼロから始める異世界生活」チャンネル【公式】</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-05-03T22:32:07</t>
+          <t>2026-05-03T22:31:54</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18469,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>レプリカだって、恋をする。</t>
+          <t>リラックマ</t>
         </is>
       </c>
       <c r="D182" t="b">
@@ -18442,7 +18477,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -18450,30 +18485,30 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>リフレイン</t>
+          <t>stay with me</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>シャイトープ</t>
+          <t>幾田りら</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BEj-QbHC54M</t>
+          <t>https://www.youtube.com/watch?v=JcDyAzbGA78</t>
         </is>
       </c>
       <c r="J182" t="n">
-        <v>34216</v>
+        <v>369868</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>KADOKAWAanime</t>
+          <t>幾田りら / Lilas Official</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-05-03T22:32:18</t>
+          <t>2026-05-03T22:32:07</t>
         </is>
       </c>
     </row>
@@ -18496,7 +18531,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -18504,45 +18539,45 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>あわ</t>
+          <t>リフレイン</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>asmi</t>
+          <t>シャイトープ</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ikqz8riLe1M</t>
+          <t>https://www.youtube.com/watch?v=BEj-QbHC54M</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>24006</v>
+        <v>34216</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>asmi Official Channel</t>
+          <t>KADOKAWAanime</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-05-03T22:32:31</t>
+          <t>2026-05-03T22:32:18</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>5806</v>
+        <v>5228</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026夏アニメ</t>
+          <t>2026春アニメ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>アズールレーン びそくぜんしんっ！にっ！！</t>
+          <t>レプリカだって、恋をする。</t>
         </is>
       </c>
       <c r="D184" t="b">
@@ -18550,7 +18585,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -18558,18 +18593,32 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>しゃいすまっ！</t>
+          <t>あわ</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>榊原ゆい</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
+          <t>asmi</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ikqz8riLe1M</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>24006</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>asmi Official Channel</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-05-03T22:32:31</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18594,16 +18643,16 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lu lu lun♪〜ウラハラ気分はオートマティック〜</t>
+          <t>しゃいすまっ！</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>橋本みゆき</t>
+          <t>榊原ゆい</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18622,7 +18671,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+          <t>アズールレーン びそくぜんしんっ！にっ！！</t>
         </is>
       </c>
       <c r="D186" t="b">
@@ -18630,20 +18679,20 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>浪漫街道、お散歩中</t>
+          <t>Lu lu lun♪〜ウラハラ気分はオートマティック〜</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>PelleK</t>
+          <t>橋本みゆき</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18670,7 +18719,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -18678,12 +18727,12 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>奇跡は起きない</t>
+          <t>浪漫街道、お散歩中</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>PelleK</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18702,7 +18751,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>片田舎のおっさん、剣聖になるII</t>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
         </is>
       </c>
       <c r="D188" t="b">
@@ -18710,7 +18759,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -18718,12 +18767,12 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>クレナイノハ</t>
+          <t>奇跡は起きない</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>ユニコーン</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18742,7 +18791,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>片田舎のおっさん、剣聖になるII</t>
         </is>
       </c>
       <c r="D189" t="b">
@@ -18750,7 +18799,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -18758,12 +18807,12 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>裸のマーメード</t>
+          <t>クレナイノハ</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>豆柴の大群</t>
+          <t>ユニコーン</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18782,7 +18831,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D190" t="b">
@@ -18798,12 +18847,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Awake Anew</t>
+          <t>裸のマーメード</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>豆柴の大群</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -18822,7 +18871,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D191" t="b">
@@ -18830,7 +18879,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -18838,12 +18887,12 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Running In My Head</t>
+          <t>Awake Anew</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>MIYAVI</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -18870,7 +18919,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -18878,12 +18927,12 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>ロゼ (Prod.TeddyLoid)</t>
+          <t>Running In My Head</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>満島ひかり</t>
+          <t>MIYAVI</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -18902,7 +18951,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D193" t="b">
@@ -18910,7 +18959,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -18918,12 +18967,12 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>ロゼ (Prod.TeddyLoid)</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>杏子</t>
+          <t>満島ひかり</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -18942,7 +18991,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D194" t="b">
@@ -18950,7 +18999,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -18958,12 +19007,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -18982,7 +19031,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D195" t="b">
@@ -18990,7 +19039,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -18998,12 +19047,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>いきものがかり</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19022,7 +19071,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D196" t="b">
@@ -19030,7 +19079,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -19038,12 +19087,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -19070,7 +19119,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -19078,12 +19127,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19102,7 +19151,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D198" t="b">
@@ -19110,7 +19159,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -19118,12 +19167,12 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -19142,7 +19191,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D199" t="b">
@@ -19150,7 +19199,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -19158,12 +19207,12 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>KI_EN</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -19182,7 +19231,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D200" t="b">
@@ -19190,7 +19239,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -19198,12 +19247,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>KI_EN</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -19222,7 +19271,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D201" t="b">
@@ -19238,12 +19287,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -19262,7 +19311,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D202" t="b">
@@ -19278,12 +19327,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -19302,7 +19351,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D203" t="b">
@@ -19310,7 +19359,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -19318,12 +19367,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -19342,7 +19391,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D204" t="b">
@@ -19350,7 +19399,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -19358,12 +19407,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -19382,7 +19431,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D205" t="b">
@@ -19398,12 +19447,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -19430,7 +19479,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -19438,12 +19487,12 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -19462,7 +19511,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D207" t="b">
@@ -19470,7 +19519,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F207" t="n">
@@ -19478,12 +19527,12 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -19502,7 +19551,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D208" t="b">
@@ -19510,7 +19559,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -19518,12 +19567,12 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -19542,7 +19591,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D209" t="b">
@@ -19550,7 +19599,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -19558,12 +19607,12 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -19582,7 +19631,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D210" t="b">
@@ -19590,7 +19639,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -19598,12 +19647,12 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -19622,7 +19671,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D211" t="b">
@@ -19638,12 +19687,12 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -19662,7 +19711,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D212" t="b">
@@ -19670,7 +19719,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F212" t="n">
@@ -19678,12 +19727,12 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -19702,7 +19751,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D213" t="b">
@@ -19718,12 +19767,12 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -19742,7 +19791,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D214" t="b">
@@ -19750,7 +19799,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -19758,12 +19807,12 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -19771,6 +19820,86 @@
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
     </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>令和のダラさん</t>
+        </is>
+      </c>
+      <c r="D215" t="b">
+        <v>0</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>ダラダラ♡ダンシング</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="D216" t="b">
+        <v>0</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026年7月～ 日本テレビ系にて</t>
+          <t>2026年7月3日（金）～ 日本テレビ系にて</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7140,8 +7140,16 @@
           <t>シンエイ動画</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>遺書</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>キタニタツヤ</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
@@ -9297,7 +9305,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・BS朝日ほか</t>
+          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -9305,8 +9313,16 @@
           <t>サイピク</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
@@ -9367,7 +9383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L216"/>
+  <dimension ref="A1:L218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18991,7 +19007,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D194" t="b">
@@ -18999,7 +19015,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -19007,12 +19023,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>遺書</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>杏子</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19031,7 +19047,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D195" t="b">
@@ -19039,7 +19055,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -19047,12 +19063,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19071,7 +19087,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D196" t="b">
@@ -19079,7 +19095,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -19087,12 +19103,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>いきものがかり</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -19111,7 +19127,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D197" t="b">
@@ -19119,7 +19135,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -19127,12 +19143,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19159,7 +19175,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -19167,12 +19183,12 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -19191,7 +19207,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D199" t="b">
@@ -19199,7 +19215,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -19207,12 +19223,12 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -19231,7 +19247,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D200" t="b">
@@ -19239,7 +19255,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -19247,12 +19263,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>KI_EN</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -19271,7 +19287,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D201" t="b">
@@ -19279,7 +19295,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -19287,12 +19303,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>KI_EN</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -19311,7 +19327,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D202" t="b">
@@ -19327,12 +19343,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -19351,7 +19367,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D203" t="b">
@@ -19367,12 +19383,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -19391,7 +19407,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D204" t="b">
@@ -19399,7 +19415,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -19407,12 +19423,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -19431,7 +19447,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D205" t="b">
@@ -19439,7 +19455,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -19447,12 +19463,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -19471,7 +19487,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D206" t="b">
@@ -19487,12 +19503,12 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -19519,7 +19535,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F207" t="n">
@@ -19527,12 +19543,12 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -19551,7 +19567,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D208" t="b">
@@ -19559,7 +19575,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -19567,12 +19583,12 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -19591,7 +19607,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D209" t="b">
@@ -19599,7 +19615,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -19607,12 +19623,12 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -19631,7 +19647,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D210" t="b">
@@ -19647,12 +19663,12 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -19671,7 +19687,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D211" t="b">
@@ -19679,7 +19695,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F211" t="n">
@@ -19687,12 +19703,12 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -19711,7 +19727,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D212" t="b">
@@ -19727,12 +19743,12 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -19751,7 +19767,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D213" t="b">
@@ -19767,12 +19783,12 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -19799,7 +19815,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -19807,12 +19823,12 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -19831,7 +19847,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D215" t="b">
@@ -19839,7 +19855,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F215" t="n">
@@ -19847,12 +19863,12 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -19871,7 +19887,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D216" t="b">
@@ -19887,12 +19903,12 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -19900,6 +19916,86 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
     </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="D217" t="b">
+        <v>0</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ワールド イズ ダンシング</t>
+        </is>
+      </c>
+      <c r="D218" t="b">
+        <v>0</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -9483,24 +9483,10 @@
           <t>CHiCO with HoneyWorks</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2tqTCYjznf0</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>46621</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>日活アニメチャンネル</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-05-03T10:26:09</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -9537,24 +9523,10 @@
           <t>PompadollS</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Idz-Bcjh95c</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>41037</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>PompadollS</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-05-03T10:26:18</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9751,24 +9723,10 @@
           <t>桑田佳祐</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=lBOmiR_1CGQ</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>2034617</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>桑田佳祐</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2026-05-03T10:26:27</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9805,24 +9763,10 @@
           <t>桑田佳祐</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=lBOmiR_1CGQ</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>2034617</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>桑田佳祐</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2026-05-03T10:26:37</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9939,24 +9883,10 @@
           <t>HanaHope</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=eTeTEuwu_8c</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>115354</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2026-05-03T10:26:46</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9993,24 +9923,10 @@
           <t>中島美嘉</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=BNXqkwbfakg</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>44161</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>中島美嘉 Official YouTube Channel</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2026-05-03T10:26:55</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10127,24 +10043,10 @@
           <t>ルールーシー＝ルー（CV.下地紫野）＆ティア（CV.洲崎綾)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=EMhgPcxCz9I</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>135897</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>ぽにきゃん-Anime PONY CANYON</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2026-05-03T10:27:20</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10181,24 +10083,10 @@
           <t>緋月ゆい</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=40K8d9oveiY</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>49858</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>ぽにきゃん-Anime PONY CANYON</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2026-05-03T10:27:29</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10235,24 +10123,10 @@
           <t>Sophià la Mode</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3Psx5SclWFI</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>18119</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>NBCUniversal Anime/Music</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-05-03T10:27:38</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10289,24 +10163,10 @@
           <t>夢限大みゅーたいぷ</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=1ApeGKiI-FQ</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>6419</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>夢限大みゅーたいぷ</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-05-03T10:27:45</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -2813,37 +2813,21 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 2026年～</t>
+          <t>2026年6月4日（木）～ お口の恋人ロッテ【LOTTE】公式チャンネルにて</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>フルボコ</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>WANIMA</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Mountain Top</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Novel Core</t>
-        </is>
-      </c>
+          <t>TOHO animation STUDIO</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23828</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28459</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2845,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>花織さんは転生しても喧嘩がしたい</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -2869,26 +2853,42 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026年7月～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
+          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 2026年～</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+          <t>トムス・エンタテインメント</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>フルボコ</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>WANIMA</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Mountain Top</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Novel Core</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23828</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>花織さんは転生しても喧嘩がしたい</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -2919,37 +2919,21 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MX・BS11ほか</t>
+          <t>2026年7月～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>シグナル・エムディ（</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>FLASHBULB</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>花束</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27990</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2951,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>バンドリ！ ゆめ∞みた</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -2980,21 +2964,37 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MXほか</t>
+          <t>2026年7月1日（水）～ TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ニチカライン（</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+          <t>シグナル・エムディ（</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>FLASHBULB</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>花束</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27990</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>パンの赤ちゃん</t>
+          <t>バンドリ！ ゆめ∞みた</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -3025,17 +3025,21 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ カンテレ・フジテレビ系列「土曜はナニする！？」にて</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>2026年7月2日（木）～ TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ニチカライン（</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25145</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3057,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>パンの赤ちゃん</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -3066,37 +3070,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MX・BSフジほか</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>EMTスクエアード</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>マデュアル↔ハート</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>ハンドメイド</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>仲村宗悟</t>
-        </is>
-      </c>
+          <t>2026年7月4日（土）～ カンテレ・フジテレビ系列「土曜はナニする！？」にて</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25145</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3098,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3127,37 +3111,37 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026年7月〜 テレ東・BS11ほか</t>
+          <t>2026年7月1日（水）～ TOKYO MX・BSフジほか</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>スタジオコメット</t>
+          <t>EMTスクエアード</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3159,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -3188,21 +3172,37 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026年7月12日（日）〜 テレビ東京系列にて</t>
+          <t>2026年7月〜 テレ東・BS11ほか</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>動画工房</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>スタジオコメット</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Q.E.D.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>小倉唯</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>グッバイ・ララバイ</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>大西亜玖璃</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MXほか</t>
+          <t>2026年7月12日（日）〜 テレビ東京系列にて</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>100studio</t>
+          <t>動画工房</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -3247,7 +3247,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
+          <t>2026年7月4日（土）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SMDE</t>
+          <t>100studio</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3292,7 +3292,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BLEACH 千年血戦篇-禍進譚-</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列ほか</t>
+          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>PIERROT FILMS（</t>
+          <t>SMDE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3337,7 +3337,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>文豪ストレイドッグス わん！２</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026年7月〜</t>
+          <t>2026年7月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ボンズ</t>
+          <t>PIERROT FILMS（</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3382,7 +3382,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>文豪ストレイドッグス わん！２</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -3413,17 +3413,21 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・MBS・BS日テレにて</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>2026年7月〜</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ボンズ</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3445,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -3454,29 +3458,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・MBS・BS11にて</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>CUE</t>
-        </is>
-      </c>
+          <t>2026年7月～ TOKYO MX・MBS・BS日テレにて</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Welcome to あざとさワールド</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>i☆Ris</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3486,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -3507,37 +3499,37 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
+          <t>2026年7月6日（月）～ TOKYO MX・MBS・BS11にて</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Seven Arcs</t>
+          <t>CUE</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3547,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -3568,21 +3560,37 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026年7月～ TVKにて</t>
+          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+          <t>Seven Arcs</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>CRIMSON BULLET</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>水樹奈々</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Ephemeral</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>青木陽菜</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3608,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -3613,37 +3621,21 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・BS11・AT-Xにて</t>
+          <t>2026年7月～ TVKにて</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>マジックバス×ピカンテサーカス</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Windmaker</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>アンノウンミー</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
-        </is>
-      </c>
+          <t>Imagica Infos</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3653,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -3674,25 +3666,37 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>2026年7月～ TOKYO MX・BS11・AT-Xにて</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>マジックバス×ピカンテサーカス</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>アンノウンミー</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3714,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -3723,29 +3727,25 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>動画工房</t>
-        </is>
-      </c>
+          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28016</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -3776,29 +3776,29 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>バイブリーアニメーションスタジオ</t>
+          <t>動画工房</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28016</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -3829,21 +3829,29 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>NUT</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>バイブリーアニメーションスタジオ</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>なんもねえ</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>忘れらんねえよ</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3869,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="E69" t="b">
@@ -3874,37 +3882,21 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>【第1クール】 2026年1月6日（火）〜2026年3月24日（火） TOKYO MXほか 【第2クール】 2026年7月～</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>サンライズ</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>YOAKE</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>blank paper</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>POWER</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>ONE OR EIGHT</t>
-        </is>
-      </c>
+          <t>NUT</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3914,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -3935,29 +3927,37 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>第1クール：2026年1月6日（火）〜2026年3月24日（火） 第2クール：2026年7月7日（火）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>EMTスクエアード</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>サンライズ</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>YOAKE</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>blank paper</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -3988,37 +3988,29 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026年7月10日（金）～ TOKYO MXほか</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>animation studio42</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Wonder</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>CROWN HEAD</t>
-        </is>
-      </c>
+          <t>EMTスクエアード</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4028,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -4049,29 +4041,37 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月10日（金）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>旭プロダクション</t>
+          <t>animation studio42</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+          <t>CROWN HEAD</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>星降る夜の約束</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>レッツゴー怪奇組</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="E73" t="b">
@@ -4102,21 +4102,29 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TBS系全国28局ネットにて</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>C-Station</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>旭プロダクション</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>ダラダラ♡ダンシング</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28373</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4142,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>レッツゴー怪奇組</t>
         </is>
       </c>
       <c r="E74" t="b">
@@ -4147,29 +4155,21 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東・BSフジほか</t>
+          <t>2026年7月5日（日）〜 TBS系全国28局ネットにて</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ブレインズ・ベース</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Not a Hero</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>藍月なくる&amp;棗いつき</t>
-        </is>
-      </c>
+          <t>C-Station</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28373</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4200,29 +4200,29 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
+          <t>2026年7月～ テレ東・BSフジほか</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>サイピク</t>
+          <t>ブレインズ・ベース</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ONE PIECE HEROINES</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -4253,35 +4253,47 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>サイピク</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>アオアシ Season2</t>
+          <t>ONE PIECE HEROINES</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -4294,21 +4306,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ NHK Eテレにて</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
+          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
         </is>
       </c>
     </row>
@@ -4322,11 +4330,11 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>アオのハコ 第2期</t>
+          <t>アオアシ Season2</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -4339,12 +4347,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ TBS系にて</t>
+          <t>2026年10月4日（日）～ NHK Eテレにて</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>エレクトリックサーカス</t>
+          <t>トムス・エンタテインメント</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4353,7 +4361,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
         </is>
       </c>
     </row>
@@ -4367,11 +4375,11 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>傷だらけ聖女より報復をこめて Season2</t>
+          <t>アオのハコ 第2期</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -4384,12 +4392,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月4日（日）～ TBS系にて</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
+          <t>エレクトリックサーカス</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -4398,7 +4406,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
         </is>
       </c>
     </row>
@@ -4412,11 +4420,11 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>恐怖コレクター</t>
+          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -4429,17 +4437,21 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK総合にて</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>キネマシトラス</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
         </is>
       </c>
     </row>
@@ -4453,11 +4465,11 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
+          <t>傷だらけ聖女より報復をこめて Season2</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -4470,12 +4482,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>KONAMI animation</t>
+          <t>Imagica Infos</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4484,7 +4496,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
         </is>
       </c>
     </row>
@@ -4498,11 +4510,11 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>薬屋のひとりごと 第3期</t>
+          <t>恐怖コレクター</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -4515,7 +4527,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
+          <t>2026年10月～ NHK総合にて</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -4525,7 +4537,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
         </is>
       </c>
     </row>
@@ -4539,11 +4551,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ケロロ軍曹☆</t>
+          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -4556,17 +4568,21 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>KONAMI animation</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
         </is>
       </c>
     </row>
@@ -4580,11 +4596,11 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>幻想水滸伝</t>
+          <t>薬屋のひとりごと 第3期</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -4597,7 +4613,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -4607,7 +4623,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
         </is>
       </c>
     </row>
@@ -4621,11 +4637,11 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PSYREN -サイレン-</t>
+          <t>ケロロ軍曹☆</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -4638,21 +4654,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>サテライト</t>
-        </is>
-      </c>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
         </is>
       </c>
     </row>
@@ -4666,11 +4678,11 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ジャンケットバンク</t>
+          <t>幻想水滸伝</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -4686,18 +4698,14 @@
           <t>2026年10月～</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>CUE</t>
-        </is>
-      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
         </is>
       </c>
     </row>
@@ -4711,11 +4719,11 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>朱色の仮面</t>
+          <t>PSYREN -サイレン-</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -4728,17 +4736,21 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>サテライト</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
         </is>
       </c>
     </row>
@@ -4752,11 +4764,11 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>しろたん</t>
+          <t>ジャンケットバンク</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -4769,12 +4781,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>レスプリ</t>
+          <t>CUE</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -4783,7 +4795,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
         </is>
       </c>
     </row>
@@ -4797,11 +4809,11 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
+          <t>朱色の仮面</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -4814,7 +4826,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -4824,7 +4836,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
         </is>
       </c>
     </row>
@@ -4838,11 +4850,11 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>世界最強の魔女、始めました</t>
+          <t>しろたん</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -4855,12 +4867,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ブリッジ</t>
+          <t>レスプリ</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -4869,7 +4881,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
         </is>
       </c>
     </row>
@@ -4883,11 +4895,11 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>#ゾンビさがしてます</t>
+          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -4900,7 +4912,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026年10月〜 テレビ朝日系にて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -4910,7 +4922,7 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
         </is>
       </c>
     </row>
@@ -4924,11 +4936,11 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>タヌキとキツネ</t>
+          <t>世界最強の魔女、始めました</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -4944,14 +4956,18 @@
           <t>2026年10月～</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ブリッジ</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
         </is>
       </c>
     </row>
@@ -4965,11 +4981,11 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>TANK CHAIR-戦車椅子-</t>
+          <t>#ゾンビさがしてます</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -4982,21 +4998,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>ポリゴン・ピクチュアズ</t>
-        </is>
-      </c>
+          <t>2026年10月〜 テレビ朝日系にて</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
         </is>
       </c>
     </row>
@@ -5010,11 +5022,11 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>探偵はもう、死んでいる。Season2</t>
+          <t>タヌキとキツネ</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -5027,21 +5039,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>ENGI</t>
-        </is>
-      </c>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
         </is>
       </c>
     </row>
@@ -5055,11 +5063,11 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>超巡！超条先輩</t>
+          <t>TANK CHAIR-戦車椅子-</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -5072,12 +5080,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>アルボアニメーション</t>
+          <t>ポリゴン・ピクチュアズ</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5086,7 +5094,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
         </is>
       </c>
     </row>
@@ -5100,11 +5108,11 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>てつりょー！meet with 鉄道むすめ</t>
+          <t>探偵はもう、死んでいる。Season2</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -5117,12 +5125,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>イーストフィッシュスタジオ</t>
+          <t>ENGI</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5131,7 +5139,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
         </is>
       </c>
     </row>
@@ -5145,11 +5153,11 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
+          <t>超巡！超条先輩</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -5162,12 +5170,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>studio MOTHER</t>
+          <t>アルボアニメーション</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5176,7 +5184,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
         </is>
       </c>
     </row>
@@ -5190,11 +5198,11 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>転生ゴブリンだけど質問ある？</t>
+          <t>てつりょー！meet with 鉄道むすめ</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -5207,12 +5215,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>BAKKKA</t>
+          <t>イーストフィッシュスタジオ</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5221,7 +5229,7 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
         </is>
       </c>
     </row>
@@ -5235,11 +5243,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -5252,37 +5260,21 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>FelixFilm</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Flare of Soul</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>STELLAR</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>ウタヒメドリーム オールスターズ</t>
-        </is>
-      </c>
+          <t>studio MOTHER</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
         </is>
       </c>
     </row>
@@ -5296,11 +5288,11 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>転生したら剣でした 第2期</t>
+          <t>転生ゴブリンだけど質問ある？</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -5318,7 +5310,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>C2C</t>
+          <t>BAKKKA</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5327,7 +5319,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
         </is>
       </c>
     </row>
@@ -5341,11 +5333,11 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>とある暗部の少女共棲</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -5358,21 +5350,37 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+          <t>FelixFilm</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
         </is>
       </c>
     </row>
@@ -5386,11 +5394,11 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>東京リベンジャーズ 三天戦争編</t>
+          <t>転生したら剣でした 第2期</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -5408,7 +5416,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
+          <t>C2C</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5417,7 +5425,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
         </is>
       </c>
     </row>
@@ -5431,11 +5439,11 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
+          <t>とある暗部の少女共棲</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -5448,17 +5456,21 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
         </is>
       </c>
     </row>
@@ -5472,11 +5484,11 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ドラゴンボール超 ビルス</t>
+          <t>東京リベンジャーズ 三天戦争編</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -5489,17 +5501,21 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026年秋 フジテレビにて</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
         </is>
       </c>
     </row>
@@ -5513,11 +5529,11 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>バーテックスフォース</t>
+          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -5530,21 +5546,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>SMDE</t>
-        </is>
-      </c>
+          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
         </is>
       </c>
     </row>
@@ -5558,11 +5570,11 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Battle Spirits [Re] 絶界の空</t>
+          <t>ドラゴンボール超 ビルス</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -5575,7 +5587,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年秋 フジテレビにて</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -5585,7 +5597,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
         </is>
       </c>
     </row>
@@ -5599,11 +5611,11 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>パンどろぼう</t>
+          <t>バーテックスフォース</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -5616,17 +5628,21 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026年10月〜 NHK Eテレにて</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>SMDE</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
         </is>
       </c>
     </row>
@@ -5640,11 +5656,11 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>百妖譜 京師篇</t>
+          <t>Battle Spirits [Re] 絶界の空</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -5657,7 +5673,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -5667,7 +5683,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
         </is>
       </c>
     </row>
@@ -5681,11 +5697,11 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>冰剣の魔術師が世界を統べるⅡ</t>
+          <t>パンどろぼう</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -5698,21 +5714,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>ゼロジー</t>
-        </is>
-      </c>
+          <t>2026年10月〜 NHK Eテレにて</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
         </is>
       </c>
     </row>
@@ -5726,11 +5738,11 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ホタルの嫁入り</t>
+          <t>百妖譜 京師篇</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -5743,21 +5755,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>david production</t>
-        </is>
-      </c>
+          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
         </is>
       </c>
     </row>
@@ -5771,11 +5779,11 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ポップパップポルターズ</t>
+          <t>冰剣の魔術師が世界を統べるⅡ</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -5788,12 +5796,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026年秋 テレビ朝日にて</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>MOZU STUDIOS</t>
+          <t>ゼロジー</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -5802,7 +5810,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
         </is>
       </c>
     </row>
@@ -5816,11 +5824,11 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ホテル・インヒューマンズ 第2期</t>
+          <t>ホタルの嫁入り</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -5833,12 +5841,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列ほか</t>
+          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ブリッジ</t>
+          <t>david production</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -5847,7 +5855,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
         </is>
       </c>
     </row>
@@ -5861,11 +5869,11 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>マジカル★エクスプローラー</t>
+          <t>ポップパップポルターズ</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -5878,12 +5886,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年秋 テレビ朝日にて</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>WHITE FOX</t>
+          <t>MOZU STUDIOS</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5892,7 +5900,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
         </is>
       </c>
     </row>
@@ -5906,11 +5914,11 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>魔法騎士レイアース</t>
+          <t>ホテル・インヒューマンズ 第2期</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -5923,12 +5931,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日系列にて</t>
+          <t>2026年10月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>E&amp;H production</t>
+          <t>ブリッジ</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -5937,7 +5945,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
         </is>
       </c>
     </row>
@@ -5951,11 +5959,11 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>マジカル★エクスプローラー</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -5973,24 +5981,16 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>SynergySP</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>No tears here</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
+          <t>WHITE FOX</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
         </is>
       </c>
     </row>
@@ -6004,11 +6004,11 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
+          <t>魔法騎士レイアース</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月～ テレビ朝日系列にて</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>studio A-CAT</t>
+          <t>E&amp;H production</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6035,7 +6035,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
         </is>
       </c>
     </row>
@@ -6049,11 +6049,11 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+          <t>魔法少女育成計画restart</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -6066,21 +6066,29 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>寿門堂</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>SynergySP</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
         </is>
       </c>
     </row>
@@ -6094,11 +6102,11 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>らんま1/2 第3期</t>
+          <t>マロニエ王国の七人の騎士</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -6111,17 +6119,21 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>2026年10月～ NHK Eテレにて</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
         </is>
       </c>
     </row>
@@ -6135,11 +6147,11 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LEGO® ONE PIECE</t>
+          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -6147,20 +6159,151 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026年9月29日（火） Netflixにて</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>studio A-CAT</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>43</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+        </is>
+      </c>
+      <c r="E120" t="b">
+        <v>0</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>寿門堂</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>44</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>らんま1/2 第3期</t>
+        </is>
+      </c>
+      <c r="E121" t="b">
+        <v>0</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026年10月～ 日本テレビ系にて</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>45</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LEGO® ONE PIECE</t>
+        </is>
+      </c>
+      <c r="E122" t="b">
+        <v>0</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>配信</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026年9月29日（火） Netflixにて</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28168</t>
         </is>
@@ -6177,7 +6320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7813,7 +7956,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -7821,7 +7964,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -7829,12 +7972,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>安保心結</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -7861,7 +8004,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -7869,12 +8012,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -7893,7 +8036,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -7901,7 +8044,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -7909,12 +8052,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -7941,7 +8084,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -7949,7 +8092,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7973,7 +8116,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -7981,7 +8124,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -7989,12 +8132,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -8021,7 +8164,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -8029,12 +8172,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -8053,7 +8196,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -8061,7 +8204,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -8069,12 +8212,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -8101,7 +8244,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -8109,12 +8252,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -8133,7 +8276,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -8141,7 +8284,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -8149,12 +8292,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -8173,7 +8316,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -8181,7 +8324,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -8189,12 +8332,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -8213,7 +8356,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -8229,12 +8372,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -8253,7 +8396,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -8269,12 +8412,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -8293,7 +8436,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -8309,12 +8452,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -8333,7 +8476,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -8349,12 +8492,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -8373,7 +8516,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -8389,12 +8532,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -8413,7 +8556,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -8421,7 +8564,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -8429,12 +8572,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8453,7 +8596,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -8469,12 +8612,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8493,7 +8636,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -8509,12 +8652,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8533,7 +8676,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -8541,7 +8684,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -8549,12 +8692,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8573,7 +8716,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -8581,7 +8724,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -8589,12 +8732,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8613,7 +8756,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -8625,16 +8768,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8653,7 +8796,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -8669,12 +8812,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8693,7 +8836,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -8701,20 +8844,20 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8733,7 +8876,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -8741,7 +8884,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -8749,12 +8892,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8773,7 +8916,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -8789,12 +8932,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8804,16 +8947,16 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -8821,7 +8964,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8829,7 +8972,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8844,16 +8987,16 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -8861,7 +9004,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8869,12 +9012,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8884,16 +9027,16 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -8909,12 +9052,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8922,6 +9065,166 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ワールド イズ ダンシング</t>
+        </is>
+      </c>
+      <c r="D69" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1246,14 +1246,30 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026年7月～ テレビ朝日系列・BS朝日にて</t>
+          <t>2026年7月4日（土）～ テレビ朝日系列・BS朝日にて</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>いつかちゃんと。</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>りりあ。</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>最終回</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>sorato</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=27779</t>
@@ -5615,7 +5631,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>バーテックスフォース</t>
+          <t>鳴海の平日</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -5623,17 +5639,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>SMDE</t>
+          <t>Production I.G</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -5642,7 +5658,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5676,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Battle Spirits [Re] 絶界の空</t>
+          <t>バーテックスフォース</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -5673,17 +5689,21 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>SMDE</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5721,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>パンどろぼう</t>
+          <t>Battle Spirits [Re] 絶界の空</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -5714,7 +5734,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026年10月〜 NHK Eテレにて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -5724,7 +5744,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5762,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>百妖譜 京師篇</t>
+          <t>パンどろぼう</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -5755,7 +5775,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+          <t>2026年10月〜 NHK Eテレにて</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -5765,7 +5785,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5803,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>冰剣の魔術師が世界を統べるⅡ</t>
+          <t>百妖譜 京師篇</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -5796,21 +5816,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>ゼロジー</t>
-        </is>
-      </c>
+          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5844,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ホタルの嫁入り</t>
+          <t>冰剣の魔術師が世界を統べるⅡ</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -5841,12 +5857,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>david production</t>
+          <t>ゼロジー</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -5855,7 +5871,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5889,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ポップパップポルターズ</t>
+          <t>ホタルの嫁入り</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -5886,12 +5902,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026年秋 テレビ朝日にて</t>
+          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>MOZU STUDIOS</t>
+          <t>david production</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5900,7 +5916,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5934,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ホテル・インヒューマンズ 第2期</t>
+          <t>ポップパップポルターズ</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -5931,12 +5947,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列ほか</t>
+          <t>2026年秋 テレビ朝日にて</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ブリッジ</t>
+          <t>MOZU STUDIOS</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -5945,7 +5961,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5979,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>マジカル★エクスプローラー</t>
+          <t>ホテル・インヒューマンズ 第2期</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -5976,12 +5992,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>WHITE FOX</t>
+          <t>ブリッジ</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -5990,7 +6006,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6024,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>魔法騎士レイアース</t>
+          <t>マジカル★エクスプローラー</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -6021,12 +6037,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日系列にて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>E&amp;H production</t>
+          <t>WHITE FOX</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6035,7 +6051,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6069,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>魔法騎士レイアース</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -6066,29 +6082,21 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレビ朝日系列にて</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>SynergySP</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>No tears here</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
+          <t>E&amp;H production</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6114,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>マロニエ王国の七人の騎士</t>
+          <t>魔法少女育成計画restart</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -6119,21 +6127,29 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK Eテレにて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+          <t>SynergySP</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6167,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
+          <t>マロニエ王国の七人の騎士</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -6164,12 +6180,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月～ NHK Eテレにて</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>studio A-CAT</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6178,7 +6194,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6212,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -6209,12 +6225,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>寿門堂</t>
+          <t>studio A-CAT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6223,7 +6239,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6257,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>らんま1/2 第3期</t>
+          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -6254,17 +6270,21 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>寿門堂</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6302,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LEGO® ONE PIECE</t>
+          <t>らんま1/2 第3期</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -6290,12 +6310,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026年9月29日（火） Netflixにて</t>
+          <t>2026年10月～ 日本テレビ系にて</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -6304,6 +6324,47 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>46</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LEGO® ONE PIECE</t>
+        </is>
+      </c>
+      <c r="E123" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>配信</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026年9月29日（火） Netflixにて</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28168</t>
         </is>
@@ -6320,7 +6381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6916,7 +6977,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -6932,12 +6993,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>夏子</t>
+          <t>いつかちゃんと。</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>FUNKY MONKEY BΛBY'S</t>
+          <t>りりあ。</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -6956,7 +7017,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -6972,12 +7033,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>裸のマーメード</t>
+          <t>最終回</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>豆柴の大群</t>
+          <t>sorato</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -6996,7 +7057,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -7004,7 +7065,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -7012,12 +7073,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Awake Anew</t>
+          <t>夏子</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>FUNKY MONKEY BΛBY'S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -7036,7 +7097,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -7044,7 +7105,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -7052,12 +7113,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Running In My Head</t>
+          <t>裸のマーメード</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MIYAVI</t>
+          <t>豆柴の大群</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -7076,7 +7137,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -7092,12 +7153,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ロゼ (Prod.TeddyLoid)</t>
+          <t>Awake Anew</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>満島ひかり</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -7116,7 +7177,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -7132,12 +7193,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>遺書</t>
+          <t>Running In My Head</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>キタニタツヤ</t>
+          <t>MIYAVI</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -7156,7 +7217,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -7164,7 +7225,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -7172,12 +7233,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>最最最高級のお世話して</t>
+          <t>ロゼ (Prod.TeddyLoid)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>angela</t>
+          <t>満島ひかり</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -7196,7 +7257,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -7212,12 +7273,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>遺書</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>杏子</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -7236,7 +7297,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -7252,12 +7313,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>最最最高級のお世話して</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>angela</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -7276,7 +7337,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -7292,12 +7353,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>イチジク煙</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ずっと真夜中でいいのに。</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -7316,7 +7377,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -7324,7 +7385,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -7332,12 +7393,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>いきものがかり</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -7356,7 +7417,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -7372,12 +7433,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>INUWASI</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -7396,7 +7457,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -7412,12 +7473,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -7436,7 +7497,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -7452,12 +7513,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -7476,7 +7537,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -7484,20 +7545,20 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>猫じゃらし</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7co</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -7524,7 +7585,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -7532,12 +7593,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -7556,7 +7617,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -7568,16 +7629,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>猫じゃらし</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>7co</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -7596,7 +7657,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -7604,7 +7665,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -7612,12 +7673,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -7636,7 +7697,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -7652,12 +7713,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -7676,7 +7737,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -7684,7 +7745,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -7692,12 +7753,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KI_EN</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -7716,7 +7777,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -7732,12 +7793,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>原因は自分にある。</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -7756,7 +7817,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -7764,7 +7825,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -7772,12 +7833,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>KI_EN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -7796,7 +7857,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -7812,12 +7873,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -7836,7 +7897,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -7852,12 +7913,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -7876,7 +7937,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -7884,7 +7945,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -7892,12 +7953,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>SEKAI NO OWARI</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -7916,7 +7977,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -7932,12 +7993,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -7956,7 +8017,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -7964,7 +8025,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -7972,12 +8033,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -7996,7 +8057,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -8012,12 +8073,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -8036,7 +8097,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -8044,7 +8105,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -8052,12 +8113,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>安保心結</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -8076,7 +8137,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -8092,12 +8153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -8116,7 +8177,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -8132,12 +8193,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -8156,7 +8217,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -8172,12 +8233,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -8196,7 +8257,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -8212,12 +8273,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -8236,7 +8297,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -8252,12 +8313,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -8276,7 +8337,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -8292,12 +8353,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -8316,7 +8377,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -8324,7 +8385,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -8332,12 +8393,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -8356,7 +8417,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -8364,7 +8425,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -8372,12 +8433,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -8396,7 +8457,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -8404,7 +8465,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -8412,12 +8473,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -8436,7 +8497,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -8452,12 +8513,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -8476,7 +8537,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -8492,12 +8553,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -8516,7 +8577,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -8532,12 +8593,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -8556,7 +8617,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -8572,12 +8633,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8596,7 +8657,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -8612,12 +8673,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8636,7 +8697,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -8644,7 +8705,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -8652,12 +8713,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8676,7 +8737,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -8692,12 +8753,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8716,7 +8777,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -8732,12 +8793,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8756,7 +8817,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -8768,16 +8829,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8804,7 +8865,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -8812,12 +8873,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8844,7 +8905,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -8852,12 +8913,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8876,7 +8937,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -8892,12 +8953,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8916,7 +8977,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -8924,20 +8985,20 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8956,7 +9017,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -8972,12 +9033,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8996,7 +9057,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -9012,12 +9073,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9036,7 +9097,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -9044,7 +9105,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -9052,12 +9113,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9076,7 +9137,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -9092,12 +9153,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9107,16 +9168,16 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -9132,12 +9193,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9147,16 +9208,16 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -9164,7 +9225,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -9172,12 +9233,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>終宵</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>マカロニえんぴつ</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9196,7 +9257,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -9212,12 +9273,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>Flare of Soul</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9225,6 +9286,86 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D74" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,7 +862,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月8日（水）～ AT-X・TOKYO MXほか</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月6日（月）～ AT-X・TOKYO MXほか</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2145,8 +2145,16 @@
           <t>花冷え。</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NEW GAME</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>halca</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=11593</t>
@@ -2861,7 +2869,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -2874,7 +2882,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 2026年～</t>
+          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 第1クール：2026年7月5日（日）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2922,7 +2930,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>花織さんは転生しても喧嘩がしたい</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -2930,26 +2938,42 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026年7月～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
+          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 第1クール：2026年7月5日（日）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+          <t>トムス・エンタテインメント</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>フルボコ</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>WANIMA</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Mountain Top</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Novel Core</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23828</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2991,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>花織さんは転生しても喧嘩がしたい</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -2980,37 +3004,21 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MX・BS11ほか</t>
+          <t>2026年7月～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>シグナル・エムディ（</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>FLASHBULB</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>花束</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27990</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3036,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>バンドリ！ ゆめ∞みた</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -3041,21 +3049,37 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MXほか</t>
+          <t>2026年7月1日（水）～ TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ニチカライン（</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+          <t>シグナル・エムディ（</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>FLASHBULB</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>花束</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27990</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3097,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>パンの赤ちゃん</t>
+          <t>バンドリ！ ゆめ∞みた</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -3086,17 +3110,21 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ カンテレ・フジテレビ系列「土曜はナニする！？」にて</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>2026年7月2日（木）～ TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ニチカライン（</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25145</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3142,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>パンの赤ちゃん</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3127,37 +3155,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MX・BSフジほか</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>EMTスクエアード</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>マデュアル↔ハート</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>ハンドメイド</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>仲村宗悟</t>
-        </is>
-      </c>
+          <t>2026年7月4日（土）～ カンテレ・フジテレビ系列「土曜はナニする！？」にて</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25145</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3183,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -3188,37 +3196,37 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026年7月〜 テレ東・BS11ほか</t>
+          <t>2026年7月1日（水）～ TOKYO MX・BSフジほか</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>スタジオコメット</t>
+          <t>EMTスクエアード</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3244,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -3249,21 +3257,37 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026年7月12日（日）〜 テレビ東京系列にて</t>
+          <t>2026年7月〜 テレ東・BS11ほか</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>動画工房</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+          <t>スタジオコメット</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Q.E.D.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>小倉唯</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>グッバイ・ララバイ</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>大西亜玖璃</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3305,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -3294,12 +3318,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MXほか</t>
+          <t>2026年7月12日（日）〜 テレビ東京系列にて</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>100studio</t>
+          <t>動画工房</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3308,7 +3332,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3350,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -3339,12 +3363,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
+          <t>2026年7月4日（土）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SMDE</t>
+          <t>100studio</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3353,7 +3377,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3395,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BLEACH 千年血戦篇-禍進譚-</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -3384,12 +3408,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列ほか</t>
+          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>PIERROT FILMS（</t>
+          <t>SMDE</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3398,7 +3422,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3440,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>文豪ストレイドッグス わん！２</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -3429,12 +3453,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026年7月〜</t>
+          <t>2026年7月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ボンズ</t>
+          <t>PIERROT FILMS（</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -3443,7 +3467,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3485,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>文豪ストレイドッグス わん！２</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -3474,17 +3498,21 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・MBS・BS日テレにて</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>2026年7月〜</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ボンズ</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3530,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -3515,37 +3543,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026年7月6日（月）～ TOKYO MX・MBS・BS11にて</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>CUE</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>会心の一劇</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>ももいろクローバーZ</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Welcome to あざとさワールド</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>i☆Ris</t>
-        </is>
-      </c>
+          <t>2026年7月～ TOKYO MX・MBS・BS日テレにて</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3571,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -3576,37 +3584,37 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
+          <t>2026年7月6日（月）～ TOKYO MX・MBS・BS11にて</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Seven Arcs</t>
+          <t>CUE</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3632,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -3637,21 +3645,37 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026年7月～ TVKにて</t>
+          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+          <t>Seven Arcs</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>CRIMSON BULLET</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>水樹奈々</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Ephemeral</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>青木陽菜</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3693,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -3682,37 +3706,21 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・BS11・AT-Xにて</t>
+          <t>2026年7月～ TVKにて</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>マジックバス×ピカンテサーカス</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Windmaker</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>アンノウンミー</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
-        </is>
-      </c>
+          <t>Imagica Infos</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3738,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -3743,25 +3751,37 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>2026年7月～ TOKYO MX・BS11・AT-Xにて</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>マジックバス×ピカンテサーカス</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>アンノウンミー</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3799,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -3792,29 +3812,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>動画工房</t>
-        </is>
-      </c>
+          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28016</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3848,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -3845,29 +3861,29 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>バイブリーアニメーションスタジオ</t>
+          <t>動画工房</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28016</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3901,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="E69" t="b">
@@ -3898,21 +3914,29 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>NUT</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>バイブリーアニメーションスタジオ</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>なんもねえ</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>忘れらんねえよ</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3954,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -3943,37 +3967,21 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>第1クール：2026年1月6日（火）〜2026年3月24日（火） 第2クール：2026年7月7日（火）～ TOKYO MXほか</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>サンライズ</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>YOAKE</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>blank paper</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>POWER</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>ONE OR EIGHT</t>
-        </is>
-      </c>
+          <t>NUT</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3999,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -4004,29 +4012,37 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>第1クール：2026年1月6日（火）〜2026年3月24日（火） 第2クール：2026年7月7日（火）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>EMTスクエアード</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>サンライズ</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>YOAKE</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>blank paper</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4060,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -4057,37 +4073,29 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026年7月10日（金）～ TOKYO MXほか</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>animation studio42</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Wonder</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>CROWN HEAD</t>
-        </is>
-      </c>
+          <t>EMTスクエアード</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4113,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="E73" t="b">
@@ -4118,29 +4126,37 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月10日（金）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>旭プロダクション</t>
+          <t>animation studio42</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+          <t>CROWN HEAD</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>星降る夜の約束</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4174,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>レッツゴー怪奇組</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="E74" t="b">
@@ -4171,21 +4187,29 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TBS系全国28局ネットにて</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>C-Station</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>旭プロダクション</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ダラダラ♡ダンシング</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28373</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4227,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>レッツゴー怪奇組</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4216,29 +4240,21 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東・BSフジほか</t>
+          <t>2026年7月5日（日）〜 TBS系全国28局ネットにて</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ブレインズ・ベース</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Not a Hero</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>藍月なくる&amp;棗いつき</t>
-        </is>
-      </c>
+          <t>C-Station</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28373</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4272,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -4269,29 +4285,29 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
+          <t>2026年7月～ テレ東・BSフジほか</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>サイピク</t>
+          <t>ブレインズ・ベース</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4325,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ONE PIECE HEROINES</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -4322,35 +4338,47 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>サイピク</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>アオアシ Season2</t>
+          <t>ONE PIECE HEROINES</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -4363,21 +4391,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ NHK Eテレにて</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
+          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
         </is>
       </c>
     </row>
@@ -4391,11 +4415,11 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>アオのハコ 第2期</t>
+          <t>アオアシ Season2</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -4408,12 +4432,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ TBS系にて</t>
+          <t>2026年10月4日（日）～ NHK Eテレにて</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>エレクトリックサーカス</t>
+          <t>トムス・エンタテインメント</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -4422,7 +4446,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
         </is>
       </c>
     </row>
@@ -4436,11 +4460,11 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
+          <t>アオのハコ 第2期</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -4453,12 +4477,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
+          <t>2026年10月4日（日）～ TBS系にて</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>キネマシトラス</t>
+          <t>エレクトリックサーカス</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4467,7 +4491,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
         </is>
       </c>
     </row>
@@ -4481,11 +4505,11 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>傷だらけ聖女より報復をこめて Season2</t>
+          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -4498,12 +4522,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
+          <t>キネマシトラス</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4512,7 +4536,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
         </is>
       </c>
     </row>
@@ -4526,11 +4550,11 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>恐怖コレクター</t>
+          <t>傷だらけ聖女より報復をこめて Season2</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -4543,17 +4567,21 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK総合にて</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Imagica Infos</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
         </is>
       </c>
     </row>
@@ -4567,11 +4595,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
+          <t>恐怖コレクター</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -4584,21 +4612,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>KONAMI animation</t>
-        </is>
-      </c>
+          <t>2026年10月～ NHK総合にて</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
         </is>
       </c>
     </row>
@@ -4612,11 +4636,11 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>薬屋のひとりごと 第3期</t>
+          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -4629,17 +4653,21 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>KONAMI animation</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
         </is>
       </c>
     </row>
@@ -4653,11 +4681,11 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ケロロ軍曹☆</t>
+          <t>薬屋のひとりごと 第3期</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -4670,7 +4698,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -4680,7 +4708,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
         </is>
       </c>
     </row>
@@ -4694,11 +4722,11 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>幻想水滸伝</t>
+          <t>ケロロ軍曹☆</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -4711,7 +4739,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -4721,7 +4749,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
         </is>
       </c>
     </row>
@@ -4735,11 +4763,11 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PSYREN -サイレン-</t>
+          <t>幻想水滸伝</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -4755,18 +4783,14 @@
           <t>2026年10月～</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>サテライト</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
         </is>
       </c>
     </row>
@@ -4780,11 +4804,11 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ジャンケットバンク</t>
+          <t>PSYREN -サイレン-</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -4802,7 +4826,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>CUE</t>
+          <t>サテライト</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -4811,7 +4835,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
         </is>
       </c>
     </row>
@@ -4825,11 +4849,11 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>朱色の仮面</t>
+          <t>ジャンケットバンク</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -4842,17 +4866,21 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>CUE</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
         </is>
       </c>
     </row>
@@ -4866,11 +4894,11 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>しろたん</t>
+          <t>朱色の仮面</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -4883,21 +4911,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>レスプリ</t>
-        </is>
-      </c>
+          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
         </is>
       </c>
     </row>
@@ -4911,11 +4935,11 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
+          <t>獣王武神ダンデヴァイン</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -4928,17 +4952,29 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28479</t>
         </is>
       </c>
     </row>
@@ -4952,11 +4988,11 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>世界最強の魔女、始めました</t>
+          <t>しろたん</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -4969,12 +5005,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ブリッジ</t>
+          <t>レスプリ</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4983,7 +5019,7 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
         </is>
       </c>
     </row>
@@ -4997,11 +5033,11 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>#ゾンビさがしてます</t>
+          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -5014,7 +5050,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026年10月〜 テレビ朝日系にて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -5024,7 +5060,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
         </is>
       </c>
     </row>
@@ -5038,11 +5074,11 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>タヌキとキツネ</t>
+          <t>世界最強の魔女、始めました</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -5058,14 +5094,18 @@
           <t>2026年10月～</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ブリッジ</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
         </is>
       </c>
     </row>
@@ -5079,11 +5119,11 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TANK CHAIR-戦車椅子-</t>
+          <t>#ゾンビさがしてます</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -5096,21 +5136,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>ポリゴン・ピクチュアズ</t>
-        </is>
-      </c>
+          <t>2026年10月〜 テレビ朝日系にて</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
         </is>
       </c>
     </row>
@@ -5124,11 +5160,11 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>探偵はもう、死んでいる。Season2</t>
+          <t>タヌキとキツネ</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -5141,21 +5177,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>ENGI</t>
-        </is>
-      </c>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
         </is>
       </c>
     </row>
@@ -5169,11 +5201,11 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>超巡！超条先輩</t>
+          <t>TANK CHAIR-戦車椅子-</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -5186,12 +5218,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>アルボアニメーション</t>
+          <t>ポリゴン・ピクチュアズ</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5200,7 +5232,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
         </is>
       </c>
     </row>
@@ -5214,11 +5246,11 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>てつりょー！meet with 鉄道むすめ</t>
+          <t>探偵はもう、死んでいる。Season2</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -5231,12 +5263,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>イーストフィッシュスタジオ</t>
+          <t>ENGI</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5245,7 +5277,7 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
         </is>
       </c>
     </row>
@@ -5259,11 +5291,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
+          <t>超巡！超条先輩</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -5276,12 +5308,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>studio MOTHER</t>
+          <t>アルボアニメーション</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5290,7 +5322,7 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
         </is>
       </c>
     </row>
@@ -5304,11 +5336,11 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>転生ゴブリンだけど質問ある？</t>
+          <t>てつりょー！meet with 鉄道むすめ</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -5321,12 +5353,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>BAKKKA</t>
+          <t>イーストフィッシュスタジオ</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5335,7 +5367,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
         </is>
       </c>
     </row>
@@ -5349,11 +5381,11 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>テムパル～アイテムの力～</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -5371,32 +5403,16 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>FelixFilm</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Flare of Soul</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>STELLAR</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>ウタヒメドリーム オールスターズ</t>
-        </is>
-      </c>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
         </is>
       </c>
     </row>
@@ -5410,11 +5426,11 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>転生したら剣でした 第2期</t>
+          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -5427,12 +5443,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>C2C</t>
+          <t>studio MOTHER</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5441,7 +5457,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
         </is>
       </c>
     </row>
@@ -5455,11 +5471,11 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>とある暗部の少女共棲</t>
+          <t>転生ゴブリンだけど質問ある？</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -5472,12 +5488,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>BAKKKA</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5486,7 +5502,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
         </is>
       </c>
     </row>
@@ -5500,11 +5516,11 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>東京リベンジャーズ 三天戦争編</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -5522,16 +5538,32 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
+          <t>FelixFilm</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
         </is>
       </c>
     </row>
@@ -5545,11 +5577,11 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
+          <t>転生したら剣でした 第2期</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -5562,17 +5594,21 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>C2C</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
         </is>
       </c>
     </row>
@@ -5586,11 +5622,11 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ドラゴンボール超 ビルス</t>
+          <t>とある暗部の少女共棲</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -5603,17 +5639,21 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026年秋 フジテレビにて</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
         </is>
       </c>
     </row>
@@ -5627,11 +5667,11 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>鳴海の平日</t>
+          <t>東京リベンジャーズ 三天戦争編</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -5639,17 +5679,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Production I.G</t>
+          <t>ライデンフィルム</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -5658,7 +5698,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
         </is>
       </c>
     </row>
@@ -5672,11 +5712,11 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>バーテックスフォース</t>
+          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -5689,21 +5729,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>SMDE</t>
-        </is>
-      </c>
+          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
         </is>
       </c>
     </row>
@@ -5717,11 +5753,11 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Battle Spirits [Re] 絶界の空</t>
+          <t>ドラゴンボール超 ビルス</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -5734,7 +5770,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年秋 フジテレビにて</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -5744,7 +5780,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
         </is>
       </c>
     </row>
@@ -5758,11 +5794,11 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>パンどろぼう</t>
+          <t>鳴海の平日</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -5770,22 +5806,26 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026年10月〜 NHK Eテレにて</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Production I.G</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
         </is>
       </c>
     </row>
@@ -5799,11 +5839,11 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>百妖譜 京師篇</t>
+          <t>バーテックスフォース</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -5816,17 +5856,21 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「B8station」にて</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>SMDE</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
         </is>
       </c>
     </row>
@@ -5840,11 +5884,11 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>冰剣の魔術師が世界を統べるⅡ</t>
+          <t>Battle Spirits [Re] 絶界の空</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -5857,21 +5901,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>ゼロジー</t>
-        </is>
-      </c>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
         </is>
       </c>
     </row>
@@ -5885,11 +5925,11 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ホタルの嫁入り</t>
+          <t>パンどろぼう</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -5902,21 +5942,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>david production</t>
-        </is>
-      </c>
+          <t>2026年10月〜 NHK Eテレにて</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
         </is>
       </c>
     </row>
@@ -5930,11 +5966,11 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ポップパップポルターズ</t>
+          <t>百妖譜 京師篇</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -5947,21 +5983,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026年秋 テレビ朝日にて</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>MOZU STUDIOS</t>
-        </is>
-      </c>
+          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
         </is>
       </c>
     </row>
@@ -5975,11 +6007,11 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ホテル・インヒューマンズ 第2期</t>
+          <t>冰剣の魔術師が世界を統べるⅡ</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -5992,12 +6024,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列ほか</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ブリッジ</t>
+          <t>ゼロジー</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -6006,7 +6038,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
         </is>
       </c>
     </row>
@@ -6020,11 +6052,11 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>マジカル★エクスプローラー</t>
+          <t>ホタルの嫁入り</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -6037,12 +6069,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>WHITE FOX</t>
+          <t>david production</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6051,7 +6083,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
         </is>
       </c>
     </row>
@@ -6065,11 +6097,11 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>魔法騎士レイアース</t>
+          <t>ポップパップポルターズ</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -6082,12 +6114,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日系列にて</t>
+          <t>2026年秋 テレビ朝日にて</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>E&amp;H production</t>
+          <t>MOZU STUDIOS</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -6096,7 +6128,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
         </is>
       </c>
     </row>
@@ -6110,11 +6142,11 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>ホテル・インヒューマンズ 第2期</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -6127,29 +6159,21 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>SynergySP</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>No tears here</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
+          <t>ブリッジ</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
         </is>
       </c>
     </row>
@@ -6163,11 +6187,11 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>マロニエ王国の七人の騎士</t>
+          <t>マジカル★エクスプローラー</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -6180,12 +6204,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK Eテレにて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>WHITE FOX</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6194,7 +6218,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
         </is>
       </c>
     </row>
@@ -6208,11 +6232,11 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
+          <t>魔法騎士レイアース</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -6225,12 +6249,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月～ テレビ朝日系列にて</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>studio A-CAT</t>
+          <t>E&amp;H production</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6239,7 +6263,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
         </is>
       </c>
     </row>
@@ -6253,11 +6277,11 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+          <t>魔法少女育成計画restart</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -6270,21 +6294,29 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>寿門堂</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
+          <t>SynergySP</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
         </is>
       </c>
     </row>
@@ -6298,11 +6330,11 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>らんま1/2 第3期</t>
+          <t>マロニエ王国の七人の騎士</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -6315,17 +6347,21 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>2026年10月～ NHK Eテレにて</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
         </is>
       </c>
     </row>
@@ -6339,11 +6375,11 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LEGO® ONE PIECE</t>
+          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -6351,20 +6387,151 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026年9月29日（火） Netflixにて</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>studio A-CAT</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>46</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+        </is>
+      </c>
+      <c r="E124" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>寿門堂</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>47</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>らんま1/2 第3期</t>
+        </is>
+      </c>
+      <c r="E125" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026年10月～ 日本テレビ系にて</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>48</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LEGO® ONE PIECE</t>
+        </is>
+      </c>
+      <c r="E126" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>配信</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026年9月29日（火） Netflixにて</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28168</t>
         </is>
@@ -6381,7 +6548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7737,7 +7904,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -7745,7 +7912,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -7753,12 +7920,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>NEW GAME</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>halca</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -7777,7 +7944,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -7793,12 +7960,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -7817,7 +7984,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -7825,7 +7992,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -7833,12 +8000,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KI_EN</t>
+          <t>原因は自分にある。</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -7857,7 +8024,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -7865,7 +8032,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -7873,18 +8040,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+          <t>KI_EN</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>107892</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-06-04T19:29:01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -7897,7 +8078,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -7913,12 +8094,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -7937,7 +8118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -7953,12 +8134,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -7977,7 +8158,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -7993,12 +8174,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>SEKAI NO OWARI</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -8017,7 +8198,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -8025,7 +8206,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -8033,12 +8214,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -8057,7 +8238,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -8065,7 +8246,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -8073,12 +8254,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -8097,7 +8278,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -8105,7 +8286,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -8113,12 +8294,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -8137,7 +8318,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -8145,7 +8326,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -8153,12 +8334,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>安保心結</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -8177,7 +8358,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -8185,7 +8366,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -8193,12 +8374,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -8217,7 +8398,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -8229,16 +8410,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -8257,7 +8438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -8273,12 +8454,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -8297,7 +8478,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -8305,20 +8486,20 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -8337,7 +8518,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -8345,7 +8526,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -8353,12 +8534,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -8377,7 +8558,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -8389,16 +8570,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -8417,7 +8598,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -8433,12 +8614,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -8457,7 +8638,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -8465,20 +8646,20 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -8497,7 +8678,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -8513,12 +8694,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -8537,7 +8718,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -8553,12 +8734,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -8577,7 +8758,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -8593,12 +8774,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -8617,7 +8798,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -8633,12 +8814,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8657,7 +8838,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -8673,12 +8854,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8697,7 +8878,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -8713,12 +8894,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8737,7 +8918,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -8745,7 +8926,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -8753,12 +8934,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8777,7 +8958,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -8793,12 +8974,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8817,7 +8998,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -8825,7 +9006,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -8833,12 +9014,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8857,7 +9038,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -8873,12 +9054,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8897,7 +9078,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -8905,20 +9086,20 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8937,7 +9118,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -8945,7 +9126,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -8953,12 +9134,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8977,7 +9158,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -8989,16 +9170,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9017,7 +9198,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -9025,7 +9206,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -9033,12 +9214,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9057,7 +9238,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -9073,12 +9254,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9097,7 +9278,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -9105,7 +9286,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -9113,12 +9294,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9137,7 +9318,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -9153,12 +9334,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9177,7 +9358,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -9189,16 +9370,16 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9217,7 +9398,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -9225,7 +9406,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -9233,12 +9414,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9248,16 +9429,16 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -9265,20 +9446,20 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9288,16 +9469,16 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -9313,12 +9494,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9328,16 +9509,16 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -9353,12 +9534,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9366,6 +9547,326 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>領民0人スタートの辺境領主様</t>
+        </is>
+      </c>
+      <c r="D75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>星降る夜の約束</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>令和のダラさん</t>
+        </is>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ダラダラ♡ダンシング</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="D77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ワールド イズ ダンシング</t>
+        </is>
+      </c>
+      <c r="D78" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>獣王武神ダンデヴァイン</t>
+        </is>
+      </c>
+      <c r="D79" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D80" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D81" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D82" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -2751,7 +2751,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MXほか</t>
+          <t>2026年7月4日（土）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3826,8 +3826,16 @@
           <t>大原ゆい子</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>祈り、終われば</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>中島美嘉</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
@@ -3861,7 +3869,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月9日（木）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3879,8 +3887,16 @@
           <t>家入レオ</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ジレンマ</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>冨岡愛</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28016</t>
@@ -6548,7 +6564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7368,10 +7384,24 @@
           <t>MIYAVI</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HSakQbaQifs</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>19423</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>コードギアスチャンネル CODEGEASS Channel</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-06-05T19:01:45</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9238,7 +9268,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -9246,7 +9276,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -9254,12 +9284,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>中島美嘉</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9278,7 +9308,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -9294,12 +9324,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9318,7 +9348,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -9326,7 +9356,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -9334,12 +9364,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>冨岡愛</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9358,7 +9388,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -9370,16 +9400,16 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9406,7 +9436,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -9414,12 +9444,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9446,7 +9476,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -9454,12 +9484,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9478,7 +9508,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -9494,12 +9524,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9518,7 +9548,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -9526,20 +9556,20 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9558,7 +9588,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -9574,12 +9604,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9598,7 +9628,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -9614,12 +9644,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9638,7 +9668,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -9646,7 +9676,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -9654,12 +9684,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9678,7 +9708,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -9694,12 +9724,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9709,16 +9739,16 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -9734,12 +9764,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>西川貴教</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9749,16 +9779,16 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -9774,12 +9804,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>終宵</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>マカロニえんぴつ</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9798,7 +9828,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>獣王武神ダンデヴァイン</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -9806,7 +9836,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -9814,12 +9844,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>曲名未発表</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>西川貴教</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9838,7 +9868,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -9854,12 +9884,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>Flare of Soul</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9867,6 +9897,86 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D83" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D84" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,7 +658,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月3日（金）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026年7月〜</t>
+          <t>2026年7月5日（日）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1143,11 +1143,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>きみが死ぬまで恋をしたい</t>
+          <t>帰還者の魔法は特別です</t>
         </is>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1156,21 +1156,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2023年10月7日（土）〜2023年12月23日（土） TOKYO MXほか 【再放送】 2026年7月2日（木）〜 フジテレビほか</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ROLL2</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>アルボアニメーション</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>GET BACK</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6を撫でる</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ももすももす</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25598</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=20416</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1204,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>君のことが大大大大大好きな100人の彼女 第3期</t>
+          <t>きみが死ぬまで恋をしたい</t>
         </is>
       </c>
       <c r="E16" t="b">
@@ -1201,12 +1217,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TOKYO MXほか</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>バイブリーアニメーションスタジオ</t>
+          <t>ROLL2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1215,7 +1231,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26982</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25598</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1249,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>君のことが大大大大大好きな100人の彼女 第3期</t>
         </is>
       </c>
       <c r="E17" t="b">
@@ -1246,33 +1262,21 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ テレビ朝日系列・BS朝日にて</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>いつかちゃんと。</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>りりあ。</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>最終回</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>sorato</t>
-        </is>
-      </c>
+          <t>2026年7月5日（日）〜 TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>バイブリーアニメーションスタジオ</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27779</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26982</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1294,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="E18" t="b">
@@ -1303,37 +1307,33 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・BS11・MBSにて</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ゼロジー</t>
-        </is>
-      </c>
+          <t>2026年7月4日（土）～ テレビ朝日系列・BS朝日にて</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>夏子</t>
+          <t>いつかちゃんと。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FUNKY MONKEY BΛBY'S</t>
+          <t>りりあ。</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>裸のマーメード</t>
+          <t>最終回</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>豆柴の大群</t>
+          <t>sorato</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26833</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27779</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -1364,29 +1364,37 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月～ TOKYO MX・BS11・MBSにて</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lay-duce</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>ゼロジー</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>夏子</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>FUNKY MONKEY BΛBY'S</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Awake Anew</t>
+          <t>裸のマーメード</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>豆柴の大群</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26812</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26833</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1412,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>グロウアップショウ ～ひまわりのサーカス団～</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -1420,14 +1428,26 @@
           <t>2026年7月～</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Lay-duce</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Awake Anew</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>MYTH &amp; ROID</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26410</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26812</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1465,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>攻殻機動隊 THE GHOST IN THE SHELL</t>
+          <t>グロウアップショウ ～ひまわりのサーカス団～</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1458,21 +1478,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026年7月7日（火）～ カンテレ・フジテレビ系全国ネット“火アニバル!!”枠にて</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>サイエンスSARU</t>
-        </is>
-      </c>
+          <t>2026年7月～</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24096</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26410</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1506,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>攻殻機動隊 THE GHOST IN THE SHELL</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -1498,38 +1514,26 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>劇場版アニメ</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>第1幕：2024年5月10日（金） 第2幕：2024年6月7日（金） 第3幕：2024年7月5日（金） 最終幕 ：2024年8月2日（金） 【TV放送】 2026年7月10日（金）～ MBS／TBS系アニメイズム枠にて</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Running In My Head</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>MIYAVI</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>ロゼ (Prod.TeddyLoid)</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>満島ひかり</t>
-        </is>
-      </c>
+          <t>2026年7月7日（火）～ カンテレ・フジテレビ系全国ネット“火アニバル!!”枠にて</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>サイエンスSARU</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=11462</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24096</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1551,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ここは俺に任せて先に行けと言ってから10年がたったら伝説になっていた。</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -1555,26 +1559,38 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>劇場版アニメ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026年7月6日（月）～</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>月虹</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>第1幕：2024年5月10日（金） 第2幕：2024年6月7日（金） 第3幕：2024年7月5日（金） 最終幕 ：2024年8月2日（金） 【TV放送】 2026年7月10日（金）～ MBS／TBS系アニメイズム枠にて</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Running In My Head</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MIYAVI</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ロゼ (Prod.TeddyLoid)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>満島ひかり</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26900</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=11462</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1608,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>ここは俺に任せて先に行けと言ってから10年がたったら伝説になっていた。</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -1605,29 +1621,21 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026年7月3日（金）～ 日本テレビ系にて</t>
+          <t>2026年7月6日（月）～</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>シンエイ動画</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>遺書</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>キタニタツヤ</t>
-        </is>
-      </c>
+          <t>月虹</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26928</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26900</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1653,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>最強出涸らし皇子の暗躍帝位争い</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="E25" t="b">
@@ -1658,21 +1666,29 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月3日（金）～ 日本テレビ系にて</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MAHO FILM</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>シンエイ動画</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>遺書</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>キタニタツヤ</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28078</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26928</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1706,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>最強出涸らし皇子の暗躍帝位争い</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -1703,29 +1719,21 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）〜 MBSほか</t>
+          <t>2026年7月～</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ブレインズ・ベース</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>最最最高級のお世話して</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>angela</t>
-        </is>
-      </c>
+          <t>MAHO FILM</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27572</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28078</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1751,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -1751,34 +1759,42 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026年夏</t>
+          <t>2026年7月4日（土）〜 MBSほか</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>アレクト</t>
+          <t>ブレインズ・ベース</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>最最最高級のお世話して</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>杏子</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>angela</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>完璧じゃないわたし</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>前島亜美</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26463</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27572</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1812,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -1804,34 +1820,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TOKYO MXほか</t>
+          <t>2026年夏</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>キネマシトラス</t>
+          <t>アレクト</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24070</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26463</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1865,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>サンダー３</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -1862,17 +1878,29 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026年7月～ フジテレビ「+Ultra」にて</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>2026年7月5日（日）〜 TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>キネマシトラス</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>さよならララ</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>いきものがかり</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27611</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24070</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1918,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>サンダー３</t>
         </is>
       </c>
       <c r="E30" t="b">
@@ -1903,33 +1931,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026年7月～ TBS系にて</t>
+          <t>2026年7月～ フジテレビ「+Ultra」にて</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>イチジク煙</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>ずっと真夜中でいいのに。</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Fiction</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>imase</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26460</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27611</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1959,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="E31" t="b">
@@ -1960,37 +1972,33 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・ＢＳ日テレほか</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>EMTスクエアード</t>
-        </is>
-      </c>
+          <t>2026年7月～ TBS系にて</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>INUWASI</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27962</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26460</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2016,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -2021,37 +2029,37 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>第1期：2026年1月11日（日）〜2026年3月29日（日） 第2期：2026年7月5日（日）～ MBS・TBS系全国28局ネットにて</t>
+          <t>2026年7月～ TOKYO MX・ＢＳ日テレほか</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ラパントラック</t>
+          <t>EMTスクエアード</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25223</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27962</t>
         </is>
       </c>
     </row>
@@ -2069,11 +2077,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="E33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2082,21 +2090,33 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TOKYO MX・サンテレビ ほか</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>MAHO FILM</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+          <t>2025年7月5日（土）～2025年9月27日（土） TOKYO MX・BS11ほか 【再放送】 2026年7月5日（日）〜 TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>スノウドロップ</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Conton Candy</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>水平線は僕の古傷</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26740</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23173</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2134,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="E34" t="b">
@@ -2127,37 +2147,37 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026年7月7日（火）～ AT-X・TOKYO MXほか</t>
+          <t>第1期：2026年1月11日（日）〜2026年3月29日（日） 第2期：2026年7月5日（日）～ MBS・TBS系全国28局ネットにて</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ディオメディア</t>
+          <t>ラパントラック</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>NEW GAME</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>halca</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=11593</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25223</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2195,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>地球大好き！きっくん</t>
+          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
         </is>
       </c>
       <c r="E35" t="b">
@@ -2188,12 +2208,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX「5時に夢中！」にて</t>
+          <t>2026年7月5日（日）〜 TOKYO MX・サンテレビ ほか</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>勝鬨スタジオ</t>
+          <t>MAHO FILM</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2202,7 +2222,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28276</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26740</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2240,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -2233,29 +2253,37 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ MBS /TBS系28局”スーパーアニメイズムTURBO”枠にて</t>
+          <t>2026年7月7日（火）～ AT-X・TOKYO MXほか</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>GoHands</t>
+          <t>ディオメディア</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+          <t>花冷え。</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NEW GAME</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>halca</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24783</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=11593</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2301,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>地球大好き！きっくん</t>
         </is>
       </c>
       <c r="E37" t="b">
@@ -2286,29 +2314,21 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）～ テレ東系列6局ネットにて</t>
+          <t>2026年7月～ TOKYO MX「5時に夢中！」にて</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>TROYCA</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>火宴</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>原因は自分にある。</t>
-        </is>
-      </c>
+          <t>勝鬨スタジオ</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27260</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28276</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2346,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -2339,29 +2359,29 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列にて</t>
+          <t>2026年7月2日（木）～ MBS /TBS系28局”スーパーアニメイズムTURBO”枠にて</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>スタジオディーン</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>縁のつき</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>KI_EN</t>
-        </is>
-      </c>
+          <t>GoHands</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Awake</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>SPYAIR</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26780</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24783</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2399,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="E39" t="b">
@@ -2392,29 +2412,29 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・BSフジほか</t>
+          <t>2026年7月5日（日）～ テレ東系列6局ネットにて</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>project No.9</t>
+          <t>TROYCA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>原因は自分にある。</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23374</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27260</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2452,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -2445,29 +2465,29 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026年7月7日（火）～ 日本テレビほか</t>
+          <t>2026年7月7日（火）～ テレ東系列にて</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>タツノコプロ</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>暁の空</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>七海ひろき</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+          <t>スタジオディーン</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>縁のつき</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>KI_EN</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27687</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26780</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2505,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -2498,29 +2518,29 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）〜 テレビ朝日系にて</t>
+          <t>2026年7月～ TOKYO MX・BSフジほか</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>サイエンスSARU</t>
+          <t>project No.9</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25815</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23374</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2558,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -2551,29 +2571,29 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026年7月8日（水）～ フジテレビ・関西テレビほか</t>
+          <t>2026年7月7日（火）～ 日本テレビほか</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>STUDIO EEK</t>
+          <t>タツノコプロ</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27435</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27687</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2611,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -2604,29 +2624,29 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026年7月6日（月）～ AT-X・TOKYO MXほか</t>
+          <t>2026年7月4日（土）〜 テレビ朝日系にて</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>マカリア</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>光</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>櫻井優衣</t>
-        </is>
-      </c>
+          <t>サイエンスSARU</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Stella</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>SEKAI NO OWARI</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27113</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25815</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2664,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>逃げ上手の若君 第二期</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -2657,17 +2677,29 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026年7月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>2026年7月8日（水）～ フジテレビ・関西テレビほか</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>STUDIO EEK</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>SHOW DOWN</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>QWER</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25034</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27435</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2717,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -2698,29 +2730,29 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TOKYO MX・BS11ほか</t>
+          <t>2026年7月6日（月）～ AT-X・TOKYO MXほか</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>京都アニメーション</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>ユーレカ・エヴリカ</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>五阿弥ルナ</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+          <t>マカリア</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>光</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>櫻井優衣</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27014</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27113</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2770,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>猫と竜</t>
+          <t>逃げ上手の若君 第二期</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -2751,21 +2783,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MXほか</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>OLM</t>
-        </is>
-      </c>
+          <t>2026年7月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25576</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25034</t>
         </is>
       </c>
     </row>
@@ -2783,30 +2811,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>パーフェクトアディクション</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026年7月～ tvk（テレビ神奈川）にて</t>
+          <t>2026年7月5日（日）〜 TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>京都アニメーション</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ユーレカ・エヴリカ</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>五阿弥ルナ</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27780</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27014</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2864,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>猫と竜</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -2832,17 +2872,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026年6月4日（木）～ お口の恋人ロッテ【LOTTE】公式チャンネルにて</t>
+          <t>2026年7月4日（土）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>TOHO animation STUDIO</t>
+          <t>OLM</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2851,7 +2891,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28459</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25576</t>
         </is>
       </c>
     </row>
@@ -2869,50 +2909,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>パーフェクトアディクション</t>
         </is>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>配信</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 第1クール：2026年7月5日（日）～ TOKYO MXほか</t>
+          <t>2026年7月～ tvk（テレビ神奈川）にて</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>フルボコ</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>WANIMA</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Mountain Top</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Novel Core</t>
-        </is>
-      </c>
+          <t>Imagica Infos</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23828</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27780</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2950,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -2943,37 +2963,21 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 第1クール：2026年7月5日（日）～ TOKYO MXほか</t>
+          <t>2026年6月4日（木）～ お口の恋人ロッテ【LOTTE】公式チャンネルにて</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>フルボコ</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>WANIMA</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Mountain Top</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Novel Core</t>
-        </is>
-      </c>
+          <t>TOHO animation STUDIO</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23828</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28459</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2995,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>花織さんは転生しても喧嘩がしたい</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -2999,26 +3003,42 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026年7月～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
+          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 第1クール：2026年7月5日（日）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+          <t>トムス・エンタテインメント</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>フルボコ</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>WANIMA</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Mountain Top</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Novel Core</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23828</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3056,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -3044,42 +3064,42 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MX・BS11ほか</t>
+          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 第1クール：2026年7月5日（日）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>シグナル・エムディ（</t>
+          <t>トムス・エンタテインメント</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27990</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23828</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3117,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>バンドリ！ ゆめ∞みた</t>
+          <t>花織さんは転生しても喧嘩がしたい</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -3110,12 +3130,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MXほか</t>
+          <t>2026年7月～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ニチカライン（</t>
+          <t>ライデンフィルム</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3124,7 +3144,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3162,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>パンの赤ちゃん</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3155,17 +3175,37 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ カンテレ・フジテレビ系列「土曜はナニする！？」にて</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+          <t>2026年7月1日（水）～ TOKYO MX・BS11ほか</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>シグナル・エムディ（</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>FLASHBULB</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>花束</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25145</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27990</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3223,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>バンドリ！ ゆめ∞みた</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -3196,37 +3236,21 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MX・BSフジほか</t>
+          <t>2026年7月2日（木）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>EMTスクエアード</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>マデュアル↔ハート</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>ハンドメイド</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>仲村宗悟</t>
-        </is>
-      </c>
+          <t>ニチカライン（</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3268,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>パンの赤ちゃん</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -3257,37 +3281,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026年7月〜 テレ東・BS11ほか</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>スタジオコメット</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Q.E.D.</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>小倉唯</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>グッバイ・ララバイ</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>大西亜玖璃</t>
-        </is>
-      </c>
+          <t>2026年7月4日（土）～ カンテレ・フジテレビ系列「土曜はナニする！？」にて</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25145</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3309,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -3318,21 +3322,37 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026年7月12日（日）〜 テレビ東京系列にて</t>
+          <t>2026年7月1日（水）～ TOKYO MX・BSフジほか</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>動画工房</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+          <t>EMTスクエアード</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>マデュアル↔ハート</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ハンドメイド</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>仲村宗悟</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3370,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -3363,21 +3383,37 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MXほか</t>
+          <t>2026年7月6日（月）〜 テレ東・BS11ほか</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>100studio</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+          <t>スタジオコメット</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Q.E.D.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>小倉唯</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>グッバイ・ララバイ</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>大西亜玖璃</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3431,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -3408,12 +3444,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
+          <t>2026年7月12日（日）〜 テレビ東京系列にて</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SMDE</t>
+          <t>動画工房</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3422,7 +3458,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3476,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BLEACH 千年血戦篇-禍進譚-</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -3453,21 +3489,37 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列ほか</t>
+          <t>2026年7月4日（土）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>PIERROT FILMS（</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+          <t>100studio</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>FREEZE ME UP</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>SiM</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Groooovy</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>I Don't Like Mondays.</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3537,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>文豪ストレイドッグス わん！２</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -3498,12 +3550,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026年7月〜</t>
+          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ボンズ</t>
+          <t>SMDE</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -3512,7 +3564,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3582,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -3543,17 +3595,21 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・MBS・BS日テレにて</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>2026年7月～ テレ東系列ほか</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>PIERROT FILMS（</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3627,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>文豪ストレイドッグス わん！２</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -3584,37 +3640,21 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026年7月6日（月）～ TOKYO MX・MBS・BS11にて</t>
+          <t>2026年7月〜</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>CUE</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>会心の一劇</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>ももいろクローバーZ</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Welcome to あざとさワールド</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>i☆Ris</t>
-        </is>
-      </c>
+          <t>ボンズ</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3672,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -3645,37 +3685,29 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
+          <t>2026年7月3日（金）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Seven Arcs</t>
+          <t>横浜アニメーションラボ</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Ephemeral</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>青木陽菜</t>
-        </is>
-      </c>
+          <t>浪漫派マシュマロ</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3725,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -3706,21 +3738,37 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026年7月～ TVKにて</t>
+          <t>2026年7月6日（月）～ TOKYO MX・MBS・BS11にて</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+          <t>CUE</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>会心の一劇</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>ももいろクローバーZ</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Welcome to あざとさワールド</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>i☆Ris</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3786,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -3751,37 +3799,37 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・BS11・AT-Xにて</t>
+          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>マジックバス×ピカンテサーカス</t>
+          <t>Seven Arcs</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3847,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -3812,33 +3860,21 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>決意の唄</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>大原ゆい子</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>祈り、終われば</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>中島美嘉</t>
-        </is>
-      </c>
+          <t>2026年7月～ TVKにて</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Imagica Infos</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3892,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -3869,37 +3905,37 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026年7月9日（木）～ TOKYO MXほか</t>
+          <t>2026年6月30日（火）～ AT-Xほか</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>動画工房</t>
+          <t>マジックバス×ピカンテサーカス</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28016</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3953,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="E69" t="b">
@@ -3930,29 +3966,33 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>バイブリーアニメーションスタジオ</t>
-        </is>
-      </c>
+          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+          <t>大原ゆい子</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>祈り、終われば</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>中島美嘉</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
         </is>
       </c>
     </row>
@@ -3970,7 +4010,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -3983,21 +4023,37 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月9日（木）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>NUT</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+          <t>動画工房</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>メビウス</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>家入レオ</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ジレンマ</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>冨岡愛</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28016</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4071,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -4028,37 +4084,29 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>第1クール：2026年1月6日（火）〜2026年3月24日（火） 第2クール：2026年7月7日（火）～ TOKYO MXほか</t>
+          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>サンライズ</t>
+          <t>バイブリーアニメーションスタジオ</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>blank paper</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>POWER</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>ONE OR EIGHT</t>
-        </is>
-      </c>
+          <t>忘れらんねえよ</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4124,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -4089,29 +4137,37 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月8日（水）～ AT-X・TOKYO MXほか</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>EMTスクエアード</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>NUT</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Why? RED induction</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>MYTH &amp; ROID</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4185,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="E73" t="b">
@@ -4142,37 +4198,37 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026年7月10日（金）～ TOKYO MXほか</t>
+          <t>第1クール：2026年1月6日（火）〜2026年3月24日（火） 第2クール：2026年7月7日（火）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>animation studio42</t>
+          <t>サンライズ</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4246,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="E74" t="b">
@@ -4203,29 +4259,37 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月1日（水）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>旭プロダクション</t>
+          <t>EMTスクエアード</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>憧憬</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>TrySail</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4307,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>レッツゴー怪奇組</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4256,21 +4320,37 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TBS系全国28局ネットにて</t>
+          <t>2026年7月10日（金）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>C-Station</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+          <t>animation studio42</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Wonder</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>CROWN HEAD</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>星降る夜の約束</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28373</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4368,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -4301,29 +4381,37 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東・BSフジほか</t>
+          <t>2026年7月2日（木）～ AT-X・TOKYO MXほか</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ブレインズ・ベース</t>
+          <t>旭プロダクション</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ひなたぼっこ</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>REIRIE</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4429,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>レッツゴー怪奇組</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -4354,29 +4442,21 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
+          <t>2026年7月5日（日）〜 TBS系全国28局ネットにて</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>サイピク</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>終宵</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>マカロニえんぴつ</t>
-        </is>
-      </c>
+          <t>C-Station</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28373</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4474,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ONE PIECE HEROINES</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -4407,35 +4487,55 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
+          <t>2026年7月1日（水）～ テレ東ほか</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ブレインズ・ベース</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>ゆきむら。</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>アオアシ Season2</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -4448,39 +4548,47 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ NHK Eテレにて</t>
+          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>サイピク</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>アオのハコ 第2期</t>
+          <t>ONE PIECE HEROINES</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -4493,21 +4601,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ TBS系にて</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>エレクトリックサーカス</t>
-        </is>
-      </c>
+          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
         </is>
       </c>
     </row>
@@ -4521,11 +4625,11 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
+          <t>アオアシ Season2</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -4538,12 +4642,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
+          <t>2026年10月4日（日）～ NHK Eテレにて</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>キネマシトラス</t>
+          <t>トムス・エンタテインメント</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4552,7 +4656,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
         </is>
       </c>
     </row>
@@ -4566,11 +4670,11 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>傷だらけ聖女より報復をこめて Season2</t>
+          <t>アオのハコ 第2期</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -4583,12 +4687,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月4日（日）～ TBS系にて</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
+          <t>エレクトリックサーカス</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4597,7 +4701,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
         </is>
       </c>
     </row>
@@ -4611,11 +4715,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>恐怖コレクター</t>
+          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -4628,17 +4732,21 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK総合にて</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>キネマシトラス</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
         </is>
       </c>
     </row>
@@ -4652,11 +4760,11 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
+          <t>帰還者の魔法は特別です 第2期</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -4669,21 +4777,29 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜 フジテレビ「＋Ultra」ほか</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>KONAMI animation</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>アルボアニメーション</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sorrow</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23327</t>
         </is>
       </c>
     </row>
@@ -4697,11 +4813,11 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>薬屋のひとりごと 第3期</t>
+          <t>傷だらけ聖女より報復をこめて Season2</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -4714,17 +4830,21 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Imagica Infos</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
         </is>
       </c>
     </row>
@@ -4738,11 +4858,11 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ケロロ軍曹☆</t>
+          <t>恐怖コレクター</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -4755,7 +4875,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ NHK総合にて</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -4765,7 +4885,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
         </is>
       </c>
     </row>
@@ -4779,11 +4899,11 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>幻想水滸伝</t>
+          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -4799,14 +4919,18 @@
           <t>2026年10月～</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>KONAMI animation</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
         </is>
       </c>
     </row>
@@ -4820,11 +4944,11 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PSYREN -サイレン-</t>
+          <t>薬屋のひとりごと 第3期</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -4837,21 +4961,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>サテライト</t>
-        </is>
-      </c>
+          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
         </is>
       </c>
     </row>
@@ -4865,11 +4985,11 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ジャンケットバンク</t>
+          <t>ケロロ軍曹☆</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -4882,21 +5002,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>CUE</t>
-        </is>
-      </c>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
         </is>
       </c>
     </row>
@@ -4910,11 +5026,11 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>朱色の仮面</t>
+          <t>幻想水滸伝</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -4927,7 +5043,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -4937,7 +5053,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
         </is>
       </c>
     </row>
@@ -4951,11 +5067,11 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>PSYREN -サイレン-</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -4973,24 +5089,16 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>曲名未発表</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>西川貴教</t>
-        </is>
-      </c>
+          <t>サテライト</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28479</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
         </is>
       </c>
     </row>
@@ -5004,11 +5112,11 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>しろたん</t>
+          <t>ジャンケットバンク</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -5021,12 +5129,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>レスプリ</t>
+          <t>CUE</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -5035,7 +5143,7 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
         </is>
       </c>
     </row>
@@ -5049,11 +5157,11 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
+          <t>朱色の仮面</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -5066,7 +5174,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -5076,7 +5184,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
         </is>
       </c>
     </row>
@@ -5090,11 +5198,11 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>世界最強の魔女、始めました</t>
+          <t>獣王武神ダンデヴァイン</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -5112,16 +5220,24 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ブリッジ</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28479</t>
         </is>
       </c>
     </row>
@@ -5135,11 +5251,11 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>#ゾンビさがしてます</t>
+          <t>しろたん</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -5152,17 +5268,21 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026年10月〜 テレビ朝日系にて</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>レスプリ</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
         </is>
       </c>
     </row>
@@ -5176,11 +5296,11 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>タヌキとキツネ</t>
+          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -5193,7 +5313,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -5203,7 +5323,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
         </is>
       </c>
     </row>
@@ -5217,11 +5337,11 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TANK CHAIR-戦車椅子-</t>
+          <t>世界最強の魔女、始めました</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -5234,12 +5354,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ポリゴン・ピクチュアズ</t>
+          <t>ブリッジ</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5248,7 +5368,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
         </is>
       </c>
     </row>
@@ -5262,11 +5382,11 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>探偵はもう、死んでいる。Season2</t>
+          <t>#ゾンビさがしてます</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -5279,21 +5399,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>ENGI</t>
-        </is>
-      </c>
+          <t>2026年10月〜 テレビ朝日系にて</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
         </is>
       </c>
     </row>
@@ -5307,11 +5423,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>超巡！超条先輩</t>
+          <t>タヌキとキツネ</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -5327,18 +5443,14 @@
           <t>2026年10月～</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>アルボアニメーション</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
         </is>
       </c>
     </row>
@@ -5352,11 +5464,11 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>てつりょー！meet with 鉄道むすめ</t>
+          <t>TANK CHAIR-戦車椅子-</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -5374,7 +5486,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>イーストフィッシュスタジオ</t>
+          <t>ポリゴン・ピクチュアズ</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5383,7 +5495,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
         </is>
       </c>
     </row>
@@ -5397,11 +5509,11 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>テムパル～アイテムの力～</t>
+          <t>探偵はもう、死んでいる。Season2</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -5414,12 +5526,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>ENGI</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5428,7 +5540,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
         </is>
       </c>
     </row>
@@ -5442,11 +5554,11 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
+          <t>超巡！超条先輩</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -5459,12 +5571,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>studio MOTHER</t>
+          <t>アルボアニメーション</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5473,7 +5585,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
         </is>
       </c>
     </row>
@@ -5487,11 +5599,11 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>転生ゴブリンだけど質問ある？</t>
+          <t>てつりょー！meet with 鉄道むすめ</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -5504,12 +5616,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>BAKKKA</t>
+          <t>イーストフィッシュスタジオ</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5518,7 +5630,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
         </is>
       </c>
     </row>
@@ -5532,11 +5644,11 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>テムパル～アイテムの力～</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -5554,32 +5666,16 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>FelixFilm</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Flare of Soul</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>STELLAR</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>ウタヒメドリーム オールスターズ</t>
-        </is>
-      </c>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
         </is>
       </c>
     </row>
@@ -5593,11 +5689,11 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>転生したら剣でした 第2期</t>
+          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -5610,12 +5706,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>C2C</t>
+          <t>studio MOTHER</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -5624,7 +5720,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
         </is>
       </c>
     </row>
@@ -5638,11 +5734,11 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>とある暗部の少女共棲</t>
+          <t>転生ゴブリンだけど質問ある？</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -5655,12 +5751,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>BAKKKA</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -5669,7 +5765,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
         </is>
       </c>
     </row>
@@ -5683,11 +5779,11 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>東京リベンジャーズ 三天戦争編</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -5705,16 +5801,32 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+          <t>FelixFilm</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
         </is>
       </c>
     </row>
@@ -5728,11 +5840,11 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
+          <t>転生したら剣でした 第2期</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -5745,17 +5857,21 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>C2C</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
         </is>
       </c>
     </row>
@@ -5769,11 +5885,11 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ドラゴンボール超 ビルス</t>
+          <t>とある暗部の少女共棲</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -5786,17 +5902,21 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026年秋 フジテレビにて</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
         </is>
       </c>
     </row>
@@ -5810,11 +5930,11 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>鳴海の平日</t>
+          <t>東京リベンジャーズ 三天戦争編</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -5822,17 +5942,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Production I.G</t>
+          <t>ライデンフィルム</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -5841,7 +5961,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
         </is>
       </c>
     </row>
@@ -5855,11 +5975,11 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>バーテックスフォース</t>
+          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -5872,21 +5992,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>SMDE</t>
-        </is>
-      </c>
+          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
         </is>
       </c>
     </row>
@@ -5900,11 +6016,11 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Battle Spirits [Re] 絶界の空</t>
+          <t>ドラゴンボール超 ビルス</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -5917,7 +6033,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年秋 フジテレビにて</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -5927,7 +6043,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
         </is>
       </c>
     </row>
@@ -5941,11 +6057,11 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>パンどろぼう</t>
+          <t>鳴海の平日</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -5953,22 +6069,26 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026年10月〜 NHK Eテレにて</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Production I.G</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
         </is>
       </c>
     </row>
@@ -5982,11 +6102,11 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>百妖譜 京師篇</t>
+          <t>バーテックスフォース</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -5999,17 +6119,21 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「B8station」にて</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>SMDE</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
         </is>
       </c>
     </row>
@@ -6023,11 +6147,11 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>冰剣の魔術師が世界を統べるⅡ</t>
+          <t>Battle Spirits [Re] 絶界の空</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -6040,21 +6164,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>ゼロジー</t>
-        </is>
-      </c>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
         </is>
       </c>
     </row>
@@ -6068,11 +6188,11 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ホタルの嫁入り</t>
+          <t>パンどろぼう</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -6085,21 +6205,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>david production</t>
-        </is>
-      </c>
+          <t>2026年10月〜 NHK Eテレにて</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
         </is>
       </c>
     </row>
@@ -6113,11 +6229,11 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ポップパップポルターズ</t>
+          <t>百妖譜 京師篇</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -6130,21 +6246,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026年秋 テレビ朝日にて</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>MOZU STUDIOS</t>
-        </is>
-      </c>
+          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
         </is>
       </c>
     </row>
@@ -6158,11 +6270,11 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ホテル・インヒューマンズ 第2期</t>
+          <t>冰剣の魔術師が世界を統べるⅡ</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -6175,12 +6287,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列ほか</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ブリッジ</t>
+          <t>ゼロジー</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -6189,7 +6301,7 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
         </is>
       </c>
     </row>
@@ -6203,11 +6315,11 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>マジカル★エクスプローラー</t>
+          <t>ホタルの嫁入り</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -6220,12 +6332,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>WHITE FOX</t>
+          <t>david production</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6234,7 +6346,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
         </is>
       </c>
     </row>
@@ -6248,11 +6360,11 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>魔法騎士レイアース</t>
+          <t>ポップパップポルターズ</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -6265,12 +6377,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日系列にて</t>
+          <t>2026年秋 テレビ朝日にて</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>E&amp;H production</t>
+          <t>MOZU STUDIOS</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6279,7 +6391,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6405,11 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>ホテル・インヒューマンズ 第2期</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -6310,29 +6422,21 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>SynergySP</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>No tears here</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
+          <t>ブリッジ</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
         </is>
       </c>
     </row>
@@ -6346,11 +6450,11 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>マロニエ王国の七人の騎士</t>
+          <t>マジカル★エクスプローラー</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -6363,12 +6467,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK Eテレにて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>WHITE FOX</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6377,7 +6481,7 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
         </is>
       </c>
     </row>
@@ -6391,11 +6495,11 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
+          <t>魔法騎士レイアース</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -6408,12 +6512,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月～ テレビ朝日系列にて</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>studio A-CAT</t>
+          <t>E&amp;H production</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -6422,7 +6526,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
         </is>
       </c>
     </row>
@@ -6436,11 +6540,11 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+          <t>魔法少女育成計画restart</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -6453,21 +6557,29 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>寿門堂</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+          <t>SynergySP</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
         </is>
       </c>
     </row>
@@ -6481,11 +6593,11 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>らんま1/2 第3期</t>
+          <t>マロニエ王国の七人の騎士</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -6498,17 +6610,21 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+          <t>2026年10月～ NHK Eテレにて</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
         </is>
       </c>
     </row>
@@ -6522,11 +6638,11 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LEGO® ONE PIECE</t>
+          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -6534,20 +6650,151 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026年9月29日（火） Netflixにて</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>studio A-CAT</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>47</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+        </is>
+      </c>
+      <c r="E127" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>寿門堂</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>48</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>らんま1/2 第3期</t>
+        </is>
+      </c>
+      <c r="E128" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026年10月～ 日本テレビ系にて</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>49</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LEGO® ONE PIECE</t>
+        </is>
+      </c>
+      <c r="E129" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>配信</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026年9月29日（火） Netflixにて</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28168</t>
         </is>
@@ -6564,7 +6811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7000,7 +7247,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+          <t>同じゼミの染谷さんがセクシー女優だった話。</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -7008,7 +7255,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -7016,12 +7263,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>浪漫街道、お散歩中</t>
+          <t>未来コントレール</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PelleK</t>
+          <t>桜空もも</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -7048,7 +7295,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -7056,12 +7303,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>奇跡は起きない</t>
+          <t>浪漫街道、お散歩中</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>PelleK</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -7080,7 +7327,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>片田舎のおっさん、剣聖になるII</t>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -7088,7 +7335,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -7096,12 +7343,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>クレナイノハ</t>
+          <t>奇跡は起きない</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ユニコーン</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -7120,7 +7367,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>株式会社マジルミエ 第2期</t>
+          <t>片田舎のおっさん、剣聖になるII</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -7128,7 +7375,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -7136,12 +7383,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BooooM!!!</t>
+          <t>クレナイノハ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>宝鐘マリン</t>
+          <t>ユニコーン</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -7160,7 +7407,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>株式会社マジルミエ 第2期</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -7168,7 +7415,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -7176,12 +7423,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>いつかちゃんと。</t>
+          <t>BooooM!!!</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>りりあ。</t>
+          <t>宝鐘マリン</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -7200,15 +7447,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>帰還者の魔法は特別です</t>
         </is>
       </c>
       <c r="D16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -7216,12 +7463,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>最終回</t>
+          <t>GET BACK</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>sorato</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -7240,15 +7487,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>帰還者の魔法は特別です</t>
         </is>
       </c>
       <c r="D17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -7256,12 +7503,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>夏子</t>
+          <t>6を撫でる</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FUNKY MONKEY BΛBY'S</t>
+          <t>ももすももす</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -7280,7 +7527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -7288,7 +7535,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -7296,12 +7543,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>裸のマーメード</t>
+          <t>いつかちゃんと。</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>豆柴の大群</t>
+          <t>りりあ。</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -7320,7 +7567,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -7336,12 +7583,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Awake Anew</t>
+          <t>最終回</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>sorato</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -7360,7 +7607,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -7376,32 +7623,18 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Running In My Head</t>
+          <t>夏子</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MIYAVI</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=HSakQbaQifs</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>19423</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>コードギアスチャンネル CODEGEASS Channel</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-06-05T19:01:45</t>
-        </is>
-      </c>
+          <t>FUNKY MONKEY BΛBY'S</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7414,7 +7647,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -7430,12 +7663,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ロゼ (Prod.TeddyLoid)</t>
+          <t>裸のマーメード</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>満島ひかり</t>
+          <t>豆柴の大群</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -7454,7 +7687,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -7462,7 +7695,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -7470,12 +7703,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>遺書</t>
+          <t>Awake Anew</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>キタニタツヤ</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -7494,7 +7727,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -7510,18 +7743,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>最最最高級のお世話して</t>
+          <t>Running In My Head</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>angela</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>MIYAVI</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HSakQbaQifs</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>19423</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>コードギアスチャンネル CODEGEASS Channel</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-06-05T19:01:45</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7534,7 +7781,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -7542,7 +7789,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -7550,12 +7797,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>ロゼ (Prod.TeddyLoid)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>杏子</t>
+          <t>満島ひかり</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -7574,7 +7821,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -7590,12 +7837,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>遺書</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -7614,7 +7861,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -7630,12 +7877,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>イチジク煙</t>
+          <t>最最最高級のお世話して</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ずっと真夜中でいいのに。</t>
+          <t>angela</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -7654,7 +7901,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -7670,12 +7917,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>完璧じゃないわたし</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>前島亜美</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -7694,7 +7941,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -7710,12 +7957,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>INUWASI</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -7734,7 +7981,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -7742,7 +7989,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -7750,12 +7997,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>いきものがかり</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -7774,7 +8021,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -7790,12 +8037,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -7814,7 +8061,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -7822,20 +8069,20 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>猫じゃらし</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7co</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -7854,7 +8101,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -7862,7 +8109,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -7870,12 +8117,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -7894,7 +8141,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -7902,7 +8149,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -7910,12 +8157,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -7934,15 +8181,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -7950,12 +8197,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NEW GAME</t>
+          <t>スノウドロップ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>halca</t>
+          <t>Conton Candy</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -7974,15 +8221,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -7990,12 +8237,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>水平線は僕の古傷</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -8014,7 +8261,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -8030,12 +8277,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -8054,7 +8301,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -8062,40 +8309,26 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>猫じゃらし</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KI_EN</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>107892</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>2026-06-04T19:29:01</t>
-        </is>
-      </c>
+          <t>7co</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -8108,7 +8341,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -8116,7 +8349,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -8124,12 +8357,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -8148,7 +8381,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -8164,12 +8397,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -8188,7 +8421,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -8196,7 +8429,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -8204,12 +8437,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>NEW GAME</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
+          <t>halca</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -8228,7 +8461,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -8244,12 +8477,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -8268,7 +8501,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -8276,7 +8509,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -8284,12 +8517,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>原因は自分にある。</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -8308,7 +8541,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -8316,7 +8549,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -8324,18 +8557,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+          <t>KI_EN</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>107892</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-06-04T19:29:01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -8348,7 +8595,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -8356,7 +8603,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -8364,12 +8611,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -8388,7 +8635,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -8404,12 +8651,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -8428,7 +8675,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -8440,16 +8687,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>SEKAI NO OWARI</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -8468,7 +8715,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -8476,7 +8723,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -8484,12 +8731,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -8508,7 +8755,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -8520,16 +8767,16 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -8548,7 +8795,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -8564,12 +8811,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -8588,7 +8835,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -8596,20 +8843,20 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>安保心結</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -8628,7 +8875,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -8636,7 +8883,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -8644,12 +8891,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -8668,7 +8915,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -8676,7 +8923,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -8684,12 +8931,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -8708,7 +8955,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -8716,7 +8963,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -8724,12 +8971,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -8748,7 +8995,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -8760,16 +9007,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -8788,7 +9035,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -8804,12 +9051,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -8828,7 +9075,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -8836,20 +9083,20 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8868,7 +9115,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -8876,7 +9123,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -8884,12 +9131,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8908,7 +9155,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -8920,16 +9167,16 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8948,7 +9195,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -8956,7 +9203,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -8964,12 +9211,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8988,7 +9235,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -8996,7 +9243,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -9004,12 +9251,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -9028,7 +9275,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -9036,7 +9283,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -9044,12 +9291,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -9068,7 +9315,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -9076,7 +9323,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -9084,12 +9331,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -9108,7 +9355,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -9116,7 +9363,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -9124,12 +9371,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -9148,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -9156,7 +9403,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -9164,12 +9411,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9188,7 +9435,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -9196,7 +9443,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -9204,12 +9451,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>SiM</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9228,7 +9475,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -9236,7 +9483,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -9244,12 +9491,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Groooovy</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>I Don't Like Mondays.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9268,7 +9515,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -9276,7 +9523,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -9284,12 +9531,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9308,7 +9555,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -9324,12 +9571,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>浪漫派マシュマロ</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9348,7 +9595,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -9356,7 +9603,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -9364,12 +9611,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9388,7 +9635,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -9396,7 +9643,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -9404,12 +9651,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9428,7 +9675,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -9444,12 +9691,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9468,7 +9715,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -9476,20 +9723,20 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9508,7 +9755,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -9516,7 +9763,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -9524,12 +9771,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9548,7 +9795,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -9560,16 +9807,16 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9588,7 +9835,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -9596,7 +9843,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -9604,12 +9851,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9628,7 +9875,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -9636,7 +9883,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -9644,12 +9891,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>中島美嘉</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9668,7 +9915,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -9676,7 +9923,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -9684,12 +9931,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9708,7 +9955,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -9716,7 +9963,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -9724,12 +9971,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>冨岡愛</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9748,7 +9995,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -9764,12 +10011,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9788,7 +10035,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -9804,12 +10051,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9819,16 +10066,16 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -9836,7 +10083,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -9844,12 +10091,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>西川貴教</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9859,16 +10106,16 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -9884,12 +10131,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9899,16 +10146,16 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -9916,20 +10163,20 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9939,16 +10186,16 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D84" t="b">
@@ -9956,7 +10203,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -9964,12 +10211,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9977,6 +10224,606 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
+        </is>
+      </c>
+      <c r="D85" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ばけもん</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>カラノア</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+        </is>
+      </c>
+      <c r="D86" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>＋ENCOUNT</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+        </is>
+      </c>
+      <c r="D87" t="b">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>憧憬</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>TrySail</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>領民0人スタートの辺境領主様</t>
+        </is>
+      </c>
+      <c r="D88" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Wonder</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CROWN HEAD</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>領民0人スタートの辺境領主様</t>
+        </is>
+      </c>
+      <c r="D89" t="b">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>星降る夜の約束</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>令和のダラさん</t>
+        </is>
+      </c>
+      <c r="D90" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ダラダラ♡ダンシング</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>令和のダラさん</t>
+        </is>
+      </c>
+      <c r="D91" t="b">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ひなたぼっこ</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>REIRIE</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="D92" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="D93" t="b">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ゆきむら。</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ワールド イズ ダンシング</t>
+        </is>
+      </c>
+      <c r="D94" t="b">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>帰還者の魔法は特別です 第2期</t>
+        </is>
+      </c>
+      <c r="D95" t="b">
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Sorrow</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>獣王武神ダンデヴァイン</t>
+        </is>
+      </c>
+      <c r="D96" t="b">
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D97" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D98" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D99" t="b">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,7 +817,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026年7月～ TBS・BS11にて</t>
+          <t>2026年7月2日（木）～ TBS・BS11にて</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -825,10 +825,26 @@
           <t>ライデンフィルム</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>乙女怪獣</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>METANICK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>オトメノホンキ</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>HoneyWorks feat.ハコニワリリィ</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=27295</t>
@@ -1684,8 +1700,16 @@
           <t>キタニタツヤ</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>コニファー</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>リーガルリリー</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=26928</t>
@@ -2770,7 +2794,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>逃げ上手の若君 第二期</t>
+          <t>トミカとトム</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -2783,7 +2807,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026年7月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
+          <t>シーズン1：2025年7月20日（日）～2026年3月15日（日） シーズン2：2026年7月5日（日）～ テレ東系列「トミプラワールド のりのりタイムズ！！」にて</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2793,7 +2817,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25034</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28504</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2835,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>逃げ上手の若君 第二期</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -2824,29 +2848,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TOKYO MX・BS11ほか</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>京都アニメーション</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>ユーレカ・エヴリカ</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>五阿弥ルナ</t>
-        </is>
-      </c>
+          <t>2026年7月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27014</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25034</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2876,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>猫と竜</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -2877,21 +2889,29 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MXほか</t>
+          <t>2026年7月5日（日）〜 TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>OLM</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>京都アニメーション</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ユーレカ・エヴリカ</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>五阿弥ルナ</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25576</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27014</t>
         </is>
       </c>
     </row>
@@ -2909,21 +2929,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>パーフェクトアディクション</t>
+          <t>猫と竜</t>
         </is>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026年7月～ tvk（テレビ神奈川）にて</t>
+          <t>2026年7月4日（土）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
+          <t>OLM</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2932,7 +2956,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27780</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25576</t>
         </is>
       </c>
     </row>
@@ -2950,25 +2974,21 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>パーフェクトアディクション</t>
         </is>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>配信</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026年6月4日（木）～ お口の恋人ロッテ【LOTTE】公式チャンネルにて</t>
+          <t>2026年7月～ tvk（テレビ神奈川）にて</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>TOHO animation STUDIO</t>
+          <t>Imagica Infos</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2977,7 +2997,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28459</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27780</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3015,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -3008,37 +3028,21 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 第1クール：2026年7月5日（日）～ TOKYO MXほか</t>
+          <t>2026年6月4日（木）～ お口の恋人ロッテ【LOTTE】公式チャンネルにて</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>フルボコ</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>WANIMA</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Mountain Top</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Novel Core</t>
-        </is>
-      </c>
+          <t>TOHO animation STUDIO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23828</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28459</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3060,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -3117,7 +3121,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>花織さんは転生しても喧嘩がしたい</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -3125,26 +3129,42 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026年7月～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
+          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 第1クール：2026年7月5日（日）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+          <t>トムス・エンタテインメント</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>フルボコ</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>WANIMA</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Mountain Top</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Novel Core</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23828</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3182,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>花織さんは転生しても喧嘩がしたい</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3175,37 +3195,21 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MX・BS11ほか</t>
+          <t>2026年7月～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>シグナル・エムディ（</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>FLASHBULB</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>花束</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27990</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3227,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>バンドリ！ ゆめ∞みた</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -3236,21 +3240,37 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MXほか</t>
+          <t>2026年7月1日（水）～ TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ニチカライン（</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>シグナル・エムディ（</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>FLASHBULB</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>花束</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27990</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3288,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>パンの赤ちゃん</t>
+          <t>バンドリ！ ゆめ∞みた</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -3281,17 +3301,21 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ カンテレ・フジテレビ系列「土曜はナニする！？」にて</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>2026年7月2日（木）～ TOKYO MXほか</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ニチカライン（</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25145</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3333,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>パンの赤ちゃん</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -3322,37 +3346,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MX・BSフジほか</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>EMTスクエアード</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>マデュアル↔ハート</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>ハンドメイド</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>仲村宗悟</t>
-        </is>
-      </c>
+          <t>2026年7月4日（土）～ カンテレ・フジテレビ系列「土曜はナニする！？」にて</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25145</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3374,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -3383,37 +3387,37 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026年7月6日（月）〜 テレ東・BS11ほか</t>
+          <t>2026年7月1日（水）～ TOKYO MX・BSフジほか</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>スタジオコメット</t>
+          <t>EMTスクエアード</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3435,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -3444,21 +3448,37 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026年7月12日（日）〜 テレビ東京系列にて</t>
+          <t>2026年7月6日（月）〜 テレ東・BS11ほか</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>動画工房</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+          <t>スタジオコメット</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Q.E.D.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>小倉唯</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>グッバイ・ララバイ</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>大西亜玖璃</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3496,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -3489,37 +3509,21 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MXほか</t>
+          <t>2026年7月12日（日）〜 テレビ東京系列にて</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>100studio</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>FREEZE ME UP</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>SiM</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Groooovy</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>I Don't Like Mondays.</t>
-        </is>
-      </c>
+          <t>動画工房</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3541,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -3550,21 +3554,37 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
+          <t>2026年7月4日（土）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SMDE</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+          <t>100studio</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>FREEZE ME UP</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>SiM</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Groooovy</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>I Don't Like Mondays.</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3602,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BLEACH 千年血戦篇-禍進譚-</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -3595,12 +3615,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列ほか</t>
+          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>PIERROT FILMS（</t>
+          <t>SMDE</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -3609,7 +3629,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3647,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>文豪ストレイドッグス わん！２</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -3640,12 +3660,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026年7月〜</t>
+          <t>2026年7月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ボンズ</t>
+          <t>PIERROT FILMS（</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3654,7 +3674,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3692,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>文豪ストレイドッグス わん！２</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -3685,29 +3705,21 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026年7月3日（金）～ TOKYO MXほか</t>
+          <t>2026年7月〜</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>横浜アニメーションラボ</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>○✕△□</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>浪漫派マシュマロ</t>
-        </is>
-      </c>
+          <t>ボンズ</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3737,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -3738,37 +3750,29 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026年7月6日（月）～ TOKYO MX・MBS・BS11にて</t>
+          <t>2026年7月3日（金）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CUE</t>
+          <t>横浜アニメーションラボ</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Welcome to あざとさワールド</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>i☆Ris</t>
-        </is>
-      </c>
+          <t>浪漫派マシュマロ</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3790,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -3799,37 +3803,37 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
+          <t>2026年7月6日（月）～ TOKYO MX・MBS・BS11にて</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Seven Arcs</t>
+          <t>CUE</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26401</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3851,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -3860,21 +3864,37 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026年7月～ TVKにて</t>
+          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+          <t>Seven Arcs</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>CRIMSON BULLET</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>水樹奈々</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Ephemeral</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>青木陽菜</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25418</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3912,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -3905,37 +3925,21 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026年6月30日（火）～ AT-Xほか</t>
+          <t>2026年7月～ TVKにて</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>マジックバス×ピカンテサーカス</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Windmaker</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>アンノウンミー</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
-        </is>
-      </c>
+          <t>Imagica Infos</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28112</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3957,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="E69" t="b">
@@ -3966,33 +3970,37 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>2026年6月30日（火）～ AT-Xほか</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>マジックバス×ピカンテサーカス</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26462</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4018,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -4023,37 +4031,33 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026年7月9日（木）～ TOKYO MXほか</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>動画工房</t>
-        </is>
-      </c>
+          <t>2026年7月5日（日）～ TOKYO MX・BS11ほか</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
+          <t>中島美嘉</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28016</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24285</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4075,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -4084,29 +4088,37 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
+          <t>2026年7月9日（木）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>バイブリーアニメーションスタジオ</t>
+          <t>動画工房</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+          <t>家入レオ</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ジレンマ</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>冨岡愛</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28016</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4136,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -4137,37 +4149,29 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026年7月8日（水）～ AT-X・TOKYO MXほか</t>
+          <t>2026年7月2日（木）～ TOKYO MX・BS11にて</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>NUT</t>
+          <t>バイブリーアニメーションスタジオ</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Why? RED induction</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Weiter! Weiter!</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
-        </is>
-      </c>
+          <t>忘れらんねえよ</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4189,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="E73" t="b">
@@ -4198,37 +4202,37 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>第1クール：2026年1月6日（火）〜2026年3月24日（火） 第2クール：2026年7月7日（火）～ TOKYO MXほか</t>
+          <t>2026年7月8日（水）～ AT-X・TOKYO MXほか</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>サンライズ</t>
+          <t>NUT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4250,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="E74" t="b">
@@ -4259,37 +4263,37 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MXほか</t>
+          <t>第1クール：2026年1月6日（火）〜2026年3月24日（火） 第2クール：2026年7月7日（火）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>EMTスクエアード</t>
+          <t>サンライズ</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4311,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4320,37 +4324,37 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026年7月10日（金）～ TOKYO MXほか</t>
+          <t>2026年7月1日（水）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>animation studio42</t>
+          <t>EMTスクエアード</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4372,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -4381,37 +4385,37 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ AT-X・TOKYO MXほか</t>
+          <t>2026年7月10日（金）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>旭プロダクション</t>
+          <t>animation studio42</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>REIRIE</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4433,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>レッツゴー怪奇組</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="E77" t="b">
@@ -4442,21 +4446,37 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TBS系全国28局ネットにて</t>
+          <t>2026年7月2日（木）～ AT-X・TOKYO MXほか</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>C-Station</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+          <t>旭プロダクション</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ダラダラ♡ダンシング</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>ひなたぼっこ</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>REIRIE</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28373</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4494,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>レッツゴー怪奇組</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -4487,37 +4507,21 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ テレ東ほか</t>
+          <t>2026年7月5日（日）〜 TBS系全国28局ネットにて</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ブレインズ・ベース</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Not a Hero</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>藍月なくる&amp;棗いつき</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>ゆきむら。</t>
-        </is>
-      </c>
+          <t>C-Station</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28373</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4539,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -4548,29 +4552,37 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
+          <t>2026年7月1日（水）～ テレ東ほか</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>サイピク</t>
+          <t>ブレインズ・ベース</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>ゆきむら。</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4600,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ONE PIECE HEROINES</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -4601,35 +4613,47 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>サイピク</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>アオアシ Season2</t>
+          <t>ONE PIECE HEROINES</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -4642,21 +4666,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ NHK Eテレにて</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
+          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
         </is>
       </c>
     </row>
@@ -4670,11 +4690,11 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>アオのハコ 第2期</t>
+          <t>アオアシ Season2</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -4687,12 +4707,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ TBS系にて</t>
+          <t>2026年10月4日（日）～ NHK Eテレにて</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>エレクトリックサーカス</t>
+          <t>トムス・エンタテインメント</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4701,7 +4721,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
         </is>
       </c>
     </row>
@@ -4715,11 +4735,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
+          <t>アオのハコ 第2期</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -4732,12 +4752,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
+          <t>2026年10月4日（日）～ TBS系にて</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>キネマシトラス</t>
+          <t>エレクトリックサーカス</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4746,7 +4766,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
         </is>
       </c>
     </row>
@@ -4760,11 +4780,11 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -4777,29 +4797,21 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「＋Ultra」ほか</t>
+          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>アルボアニメーション</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Sorrow</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>FLOW</t>
-        </is>
-      </c>
+          <t>キネマシトラス</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23327</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
         </is>
       </c>
     </row>
@@ -4813,11 +4825,11 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>傷だらけ聖女より報復をこめて Season2</t>
+          <t>帰還者の魔法は特別です 第2期</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -4830,21 +4842,29 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月〜 フジテレビ「＋Ultra」ほか</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+          <t>アルボアニメーション</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sorrow</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23327</t>
         </is>
       </c>
     </row>
@@ -4858,11 +4878,11 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>恐怖コレクター</t>
+          <t>傷だらけ聖女より報復をこめて Season2</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -4875,17 +4895,21 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK総合にて</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Imagica Infos</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
         </is>
       </c>
     </row>
@@ -4899,11 +4923,11 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
+          <t>恐怖コレクター</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -4916,21 +4940,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>KONAMI animation</t>
-        </is>
-      </c>
+          <t>2026年10月～ NHK総合にて</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
         </is>
       </c>
     </row>
@@ -4944,11 +4964,11 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>薬屋のひとりごと 第3期</t>
+          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -4961,17 +4981,21 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>KONAMI animation</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
         </is>
       </c>
     </row>
@@ -4985,11 +5009,11 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ケロロ軍曹☆</t>
+          <t>薬屋のひとりごと 第3期</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -5002,7 +5026,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -5012,7 +5036,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
         </is>
       </c>
     </row>
@@ -5026,11 +5050,11 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>幻想水滸伝</t>
+          <t>ケロロ軍曹☆</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -5043,7 +5067,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -5053,7 +5077,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
         </is>
       </c>
     </row>
@@ -5067,11 +5091,11 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PSYREN -サイレン-</t>
+          <t>幻想水滸伝</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -5087,18 +5111,14 @@
           <t>2026年10月～</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>サテライト</t>
-        </is>
-      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
         </is>
       </c>
     </row>
@@ -5112,11 +5132,11 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ジャンケットバンク</t>
+          <t>PSYREN -サイレン-</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -5134,7 +5154,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CUE</t>
+          <t>サテライト</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -5143,7 +5163,7 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
         </is>
       </c>
     </row>
@@ -5157,11 +5177,11 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>朱色の仮面</t>
+          <t>ジャンケットバンク</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -5174,17 +5194,21 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>CUE</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
         </is>
       </c>
     </row>
@@ -5198,11 +5222,11 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>朱色の仮面</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -5215,29 +5239,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>曲名未発表</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>西川貴教</t>
-        </is>
-      </c>
+          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28479</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
         </is>
       </c>
     </row>
@@ -5251,11 +5263,11 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>しろたん</t>
+          <t>獣王武神ダンデヴァイン</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -5268,21 +5280,29 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>レスプリ</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28479</t>
         </is>
       </c>
     </row>
@@ -5296,11 +5316,11 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
+          <t>しろたん</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -5316,14 +5336,18 @@
           <t>2026年秋</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>レスプリ</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
         </is>
       </c>
     </row>
@@ -5337,11 +5361,11 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>世界最強の魔女、始めました</t>
+          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -5354,21 +5378,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>ブリッジ</t>
-        </is>
-      </c>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
         </is>
       </c>
     </row>
@@ -5382,11 +5402,11 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>#ゾンビさがしてます</t>
+          <t>世界最強の魔女、始めました</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -5399,17 +5419,21 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026年10月〜 テレビ朝日系にて</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ブリッジ</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
         </is>
       </c>
     </row>
@@ -5423,11 +5447,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>タヌキとキツネ</t>
+          <t>#ゾンビさがしてます</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -5440,7 +5464,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜 テレビ朝日系にて</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -5450,7 +5474,7 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
         </is>
       </c>
     </row>
@@ -5464,11 +5488,11 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>TANK CHAIR-戦車椅子-</t>
+          <t>タヌキとキツネ</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -5481,21 +5505,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>ポリゴン・ピクチュアズ</t>
-        </is>
-      </c>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
         </is>
       </c>
     </row>
@@ -5509,11 +5529,11 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>探偵はもう、死んでいる。Season2</t>
+          <t>TANK CHAIR-戦車椅子-</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -5526,12 +5546,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ENGI</t>
+          <t>ポリゴン・ピクチュアズ</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5540,7 +5560,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
         </is>
       </c>
     </row>
@@ -5554,11 +5574,11 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>超巡！超条先輩</t>
+          <t>探偵はもう、死んでいる。Season2</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -5571,12 +5591,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>アルボアニメーション</t>
+          <t>ENGI</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5585,7 +5605,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
         </is>
       </c>
     </row>
@@ -5599,11 +5619,11 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>てつりょー！meet with 鉄道むすめ</t>
+          <t>超巡！超条先輩</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -5616,12 +5636,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>イーストフィッシュスタジオ</t>
+          <t>アルボアニメーション</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5630,7 +5650,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
         </is>
       </c>
     </row>
@@ -5644,11 +5664,11 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>テムパル～アイテムの力～</t>
+          <t>てつりょー！meet with 鉄道むすめ</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -5661,12 +5681,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>イーストフィッシュスタジオ</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -5675,7 +5695,7 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
         </is>
       </c>
     </row>
@@ -5689,11 +5709,11 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
+          <t>テムパル～アイテムの力～</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -5706,12 +5726,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>studio MOTHER</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -5720,7 +5740,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
         </is>
       </c>
     </row>
@@ -5734,11 +5754,11 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>転生ゴブリンだけど質問ある？</t>
+          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -5751,12 +5771,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>BAKKKA</t>
+          <t>studio MOTHER</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -5765,7 +5785,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
         </is>
       </c>
     </row>
@@ -5779,11 +5799,11 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>転生ゴブリンだけど質問ある？</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -5801,32 +5821,16 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>FelixFilm</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Flare of Soul</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>STELLAR</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>ウタヒメドリーム オールスターズ</t>
-        </is>
-      </c>
+          <t>BAKKKA</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
         </is>
       </c>
     </row>
@@ -5840,11 +5844,11 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>転生したら剣でした 第2期</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -5862,16 +5866,32 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>C2C</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
+          <t>FelixFilm</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
         </is>
       </c>
     </row>
@@ -5885,11 +5905,11 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>とある暗部の少女共棲</t>
+          <t>転生したら剣でした 第2期</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -5902,12 +5922,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>C2C</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -5916,7 +5936,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
         </is>
       </c>
     </row>
@@ -5930,11 +5950,11 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>東京リベンジャーズ 三天戦争編</t>
+          <t>とある暗部の少女共棲</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -5947,12 +5967,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -5961,7 +5981,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
         </is>
       </c>
     </row>
@@ -5975,11 +5995,11 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
+          <t>東京リベンジャーズ 三天戦争編</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -5992,17 +6012,21 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
         </is>
       </c>
     </row>
@@ -6016,11 +6040,11 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ドラゴンボール超 ビルス</t>
+          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -6033,7 +6057,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026年秋 フジテレビにて</t>
+          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -6043,7 +6067,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
         </is>
       </c>
     </row>
@@ -6057,11 +6081,11 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>鳴海の平日</t>
+          <t>ドラゴンボール超 ビルス</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -6069,26 +6093,22 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Production I.G</t>
-        </is>
-      </c>
+          <t>2026年秋 フジテレビにて</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
         </is>
       </c>
     </row>
@@ -6102,11 +6122,11 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>バーテックスフォース</t>
+          <t>鳴海の平日</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -6114,17 +6134,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>SMDE</t>
+          <t>Production I.G</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -6133,7 +6153,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
         </is>
       </c>
     </row>
@@ -6147,11 +6167,11 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Battle Spirits [Re] 絶界の空</t>
+          <t>バーテックスフォース</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -6164,17 +6184,21 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>SMDE</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
         </is>
       </c>
     </row>
@@ -6188,11 +6212,11 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>パンどろぼう</t>
+          <t>Battle Spirits [Re] 絶界の空</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -6205,7 +6229,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026年10月〜 NHK Eテレにて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -6215,7 +6239,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
         </is>
       </c>
     </row>
@@ -6229,11 +6253,11 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>百妖譜 京師篇</t>
+          <t>パンどろぼう</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -6246,7 +6270,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+          <t>2026年10月〜 NHK Eテレにて</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -6256,7 +6280,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
         </is>
       </c>
     </row>
@@ -6270,11 +6294,11 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>冰剣の魔術師が世界を統べるⅡ</t>
+          <t>百妖譜 京師篇</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -6287,21 +6311,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>ゼロジー</t>
-        </is>
-      </c>
+          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
         </is>
       </c>
     </row>
@@ -6315,11 +6335,11 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ホタルの嫁入り</t>
+          <t>冰剣の魔術師が世界を統べるⅡ</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -6332,12 +6352,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>david production</t>
+          <t>ゼロジー</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6346,7 +6366,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
         </is>
       </c>
     </row>
@@ -6360,11 +6380,11 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ポップパップポルターズ</t>
+          <t>ホタルの嫁入り</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -6377,12 +6397,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026年秋 テレビ朝日にて</t>
+          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>MOZU STUDIOS</t>
+          <t>david production</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6391,7 +6411,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
         </is>
       </c>
     </row>
@@ -6405,11 +6425,11 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ホテル・インヒューマンズ 第2期</t>
+          <t>ポップパップポルターズ</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -6422,12 +6442,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列ほか</t>
+          <t>2026年秋 テレビ朝日にて</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ブリッジ</t>
+          <t>MOZU STUDIOS</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -6436,7 +6456,7 @@
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
         </is>
       </c>
     </row>
@@ -6450,11 +6470,11 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>マジカル★エクスプローラー</t>
+          <t>ホテル・インヒューマンズ 第2期</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -6467,12 +6487,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>WHITE FOX</t>
+          <t>ブリッジ</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6481,7 +6501,7 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
         </is>
       </c>
     </row>
@@ -6495,11 +6515,11 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>魔法騎士レイアース</t>
+          <t>マジカル★エクスプローラー</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -6512,12 +6532,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日系列にて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>E&amp;H production</t>
+          <t>WHITE FOX</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -6526,7 +6546,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
         </is>
       </c>
     </row>
@@ -6540,11 +6560,11 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>魔法騎士レイアース</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -6557,29 +6577,21 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレビ朝日系列にて</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>SynergySP</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>No tears here</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
+          <t>E&amp;H production</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
         </is>
       </c>
     </row>
@@ -6593,11 +6605,11 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>マロニエ王国の七人の騎士</t>
+          <t>魔法少女育成計画restart</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -6610,21 +6622,29 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK Eテレにて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
+          <t>SynergySP</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
         </is>
       </c>
     </row>
@@ -6638,11 +6658,11 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
+          <t>マロニエ王国の七人の騎士</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -6655,12 +6675,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月～ NHK Eテレにて</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>studio A-CAT</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -6669,7 +6689,7 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
         </is>
       </c>
     </row>
@@ -6683,11 +6703,11 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -6700,12 +6720,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>寿門堂</t>
+          <t>studio A-CAT</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -6714,7 +6734,7 @@
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
         </is>
       </c>
     </row>
@@ -6728,11 +6748,11 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>らんま1/2 第3期</t>
+          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -6745,17 +6765,21 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>寿門堂</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
         </is>
       </c>
     </row>
@@ -6769,11 +6793,11 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LEGO® ONE PIECE</t>
+          <t>らんま1/2 第3期</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -6781,12 +6805,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026年9月29日（火） Netflixにて</t>
+          <t>2026年10月～ 日本テレビ系にて</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -6795,6 +6819,47 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>49</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LEGO® ONE PIECE</t>
+        </is>
+      </c>
+      <c r="E130" t="b">
+        <v>0</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>配信</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026年9月29日（火） Netflixにて</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28168</t>
         </is>
@@ -6811,7 +6876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7247,7 +7312,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>同じゼミの染谷さんがセクシー女優だった話。</t>
+          <t>乙女怪獣キャラメリゼ</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -7255,7 +7320,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -7263,12 +7328,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>未来コントレール</t>
+          <t>乙女怪獣</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>桜空もも</t>
+          <t>METANICK</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -7287,7 +7352,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+          <t>乙女怪獣キャラメリゼ</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -7295,7 +7360,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -7303,12 +7368,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>浪漫街道、お散歩中</t>
+          <t>オトメノホンキ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PelleK</t>
+          <t>HoneyWorks feat.ハコニワリリィ</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -7327,7 +7392,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+          <t>同じゼミの染谷さんがセクシー女優だった話。</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -7335,7 +7400,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -7343,12 +7408,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>奇跡は起きない</t>
+          <t>未来コントレール</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>桜空もも</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -7367,7 +7432,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>片田舎のおっさん、剣聖になるII</t>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -7383,12 +7448,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>クレナイノハ</t>
+          <t>浪漫街道、お散歩中</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ユニコーン</t>
+          <t>PelleK</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -7407,7 +7472,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>株式会社マジルミエ 第2期</t>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -7423,12 +7488,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BooooM!!!</t>
+          <t>奇跡は起きない</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>宝鐘マリン</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -7447,11 +7512,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です</t>
+          <t>片田舎のおっさん、剣聖になるII</t>
         </is>
       </c>
       <c r="D16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -7463,12 +7528,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>GET BACK</t>
+          <t>クレナイノハ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>ユニコーン</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -7487,11 +7552,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です</t>
+          <t>株式会社マジルミエ 第2期</t>
         </is>
       </c>
       <c r="D17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -7503,12 +7568,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6を撫でる</t>
+          <t>BooooM!!!</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ももすももす</t>
+          <t>宝鐘マリン</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -7527,11 +7592,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>帰還者の魔法は特別です</t>
         </is>
       </c>
       <c r="D18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -7543,12 +7608,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>いつかちゃんと。</t>
+          <t>GET BACK</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>りりあ。</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -7567,11 +7632,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>帰還者の魔法は特別です</t>
         </is>
       </c>
       <c r="D19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -7583,12 +7648,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>最終回</t>
+          <t>6を撫でる</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>sorato</t>
+          <t>ももすももす</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -7607,7 +7672,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -7623,12 +7688,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>夏子</t>
+          <t>いつかちゃんと。</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FUNKY MONKEY BΛBY'S</t>
+          <t>りりあ。</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -7647,7 +7712,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -7663,12 +7728,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>裸のマーメード</t>
+          <t>最終回</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>豆柴の大群</t>
+          <t>sorato</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -7687,7 +7752,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -7695,7 +7760,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -7703,12 +7768,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Awake Anew</t>
+          <t>夏子</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>FUNKY MONKEY BΛBY'S</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -7727,7 +7792,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -7735,7 +7800,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -7743,32 +7808,18 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Running In My Head</t>
+          <t>裸のマーメード</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>MIYAVI</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=HSakQbaQifs</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>19423</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>コードギアスチャンネル CODEGEASS Channel</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2026-06-05T19:01:45</t>
-        </is>
-      </c>
+          <t>豆柴の大群</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7781,7 +7832,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -7797,12 +7848,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ロゼ (Prod.TeddyLoid)</t>
+          <t>Awake Anew</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>満島ひかり</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -7821,7 +7872,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -7837,18 +7888,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>遺書</t>
+          <t>Running In My Head</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>キタニタツヤ</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>MIYAVI</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HSakQbaQifs</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>19423</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>コードギアスチャンネル CODEGEASS Channel</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-06-05T19:01:45</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -7861,7 +7926,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -7869,7 +7934,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -7877,12 +7942,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>最最最高級のお世話して</t>
+          <t>ロゼ (Prod.TeddyLoid)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>angela</t>
+          <t>満島ひかり</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -7901,7 +7966,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -7909,7 +7974,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -7917,12 +7982,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>完璧じゃないわたし</t>
+          <t>遺書</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>前島亜美</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -7941,7 +8006,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -7949,7 +8014,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -7957,12 +8022,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>コニファー</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>杏子</t>
+          <t>リーガルリリー</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -7981,7 +8046,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -7997,12 +8062,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>最最最高級のお世話して</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>angela</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -8021,7 +8086,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -8029,7 +8094,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -8037,12 +8102,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>イチジク煙</t>
+          <t>完璧じゃないわたし</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ずっと真夜中でいいのに。</t>
+          <t>前島亜美</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -8061,7 +8126,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -8069,7 +8134,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -8077,12 +8142,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -8101,7 +8166,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -8117,12 +8182,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>INUWASI</t>
+          <t>いきものがかり</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -8141,7 +8206,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -8149,7 +8214,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -8157,12 +8222,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -8181,15 +8246,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -8197,12 +8262,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>スノウドロップ</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Conton Candy</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -8221,15 +8286,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -8237,12 +8302,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>水平線は僕の古傷</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -8261,7 +8326,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -8269,7 +8334,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -8277,12 +8342,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -8301,11 +8366,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -8313,16 +8378,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>猫じゃらし</t>
+          <t>スノウドロップ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7co</t>
+          <t>Conton Candy</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -8341,11 +8406,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -8357,12 +8422,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>水平線は僕の古傷</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -8381,7 +8446,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -8397,12 +8462,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -8421,7 +8486,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -8429,20 +8494,20 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>NEW GAME</t>
+          <t>猫じゃらし</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>halca</t>
+          <t>7co</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -8461,7 +8526,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -8469,7 +8534,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -8477,12 +8542,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -8501,7 +8566,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -8517,12 +8582,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -8541,7 +8606,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -8557,32 +8622,18 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>NEW GAME</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KI_EN</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>107892</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>2026-06-04T19:29:01</t>
-        </is>
-      </c>
+          <t>halca</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -8595,7 +8646,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -8611,12 +8662,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -8635,7 +8686,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -8651,12 +8702,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>原因は自分にある。</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -8675,7 +8726,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -8683,7 +8734,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -8691,18 +8742,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+          <t>KI_EN</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>107892</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-06-04T19:29:01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -8715,7 +8780,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -8731,12 +8796,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -8755,7 +8820,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -8763,7 +8828,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -8771,12 +8836,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -8795,7 +8860,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -8811,12 +8876,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>SEKAI NO OWARI</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -8835,7 +8900,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -8843,7 +8908,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -8851,12 +8916,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -8875,7 +8940,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -8883,7 +8948,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -8891,12 +8956,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -8915,7 +8980,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>トミカとトム</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -8923,20 +8988,20 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>きみのたからもの</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>May J.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -8955,7 +9020,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -8963,7 +9028,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -8971,12 +9036,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -8995,7 +9060,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -9003,20 +9068,20 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>安保心結</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -9035,7 +9100,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -9075,7 +9140,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -9115,7 +9180,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -9155,7 +9220,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -9195,7 +9260,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -9211,12 +9276,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -9235,7 +9300,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -9243,20 +9308,20 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -9275,7 +9340,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -9283,7 +9348,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -9291,12 +9356,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -9315,7 +9380,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -9327,16 +9392,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -9355,7 +9420,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -9371,12 +9436,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -9395,7 +9460,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -9411,12 +9476,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9435,7 +9500,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -9451,12 +9516,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>FREEZE ME UP</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SiM</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9475,7 +9540,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -9491,12 +9556,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Groooovy</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>I Don't Like Mondays.</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9515,7 +9580,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -9523,7 +9588,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -9531,12 +9596,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9555,7 +9620,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -9563,7 +9628,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -9571,12 +9636,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>○✕△□</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>浪漫派マシュマロ</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9595,7 +9660,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -9611,12 +9676,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>SiM</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9635,7 +9700,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -9651,12 +9716,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>Groooovy</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>I Don't Like Mondays.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9675,7 +9740,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -9683,7 +9748,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -9691,12 +9756,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9715,7 +9780,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -9723,7 +9788,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -9731,12 +9796,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>浪漫派マシュマロ</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9755,7 +9820,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -9771,12 +9836,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9795,7 +9860,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -9811,12 +9876,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9835,7 +9900,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -9851,12 +9916,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9875,7 +9940,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -9891,12 +9956,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9915,7 +9980,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -9931,12 +9996,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9955,7 +10020,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -9971,12 +10036,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9995,7 +10060,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -10011,12 +10076,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10035,7 +10100,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -10043,7 +10108,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -10051,12 +10116,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Why? RED induction</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>中島美嘉</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10075,7 +10140,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -10083,7 +10148,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -10091,12 +10156,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Weiter! Weiter!</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10115,7 +10180,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -10123,7 +10188,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -10131,12 +10196,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>冨岡愛</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10155,7 +10220,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -10167,16 +10232,16 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10195,7 +10260,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D84" t="b">
@@ -10203,7 +10268,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -10211,12 +10276,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10235,7 +10300,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -10247,16 +10312,16 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10275,7 +10340,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -10291,12 +10356,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10315,7 +10380,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -10323,20 +10388,20 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10355,7 +10420,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -10363,7 +10428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -10371,12 +10436,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10395,7 +10460,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -10407,16 +10472,16 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10435,7 +10500,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -10451,12 +10516,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10475,7 +10540,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -10491,12 +10556,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>REIRIE</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10515,7 +10580,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -10531,12 +10596,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10555,7 +10620,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -10571,12 +10636,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ゆきむら。</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10595,7 +10660,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D94" t="b">
@@ -10611,12 +10676,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10626,16 +10691,16 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -10643,7 +10708,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -10651,12 +10716,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sorrow</t>
+          <t>ひなたぼっこ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>REIRIE</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10666,16 +10731,16 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -10691,12 +10756,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>西川貴教</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10706,16 +10771,16 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -10723,7 +10788,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -10731,12 +10796,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>ゆきむら。</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10746,16 +10811,16 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -10763,7 +10828,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -10771,12 +10836,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>終宵</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>マカロニえんぴつ</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10795,7 +10860,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>帰還者の魔法は特別です 第2期</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -10811,12 +10876,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>Sorrow</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10824,6 +10889,166 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
     </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>獣王武神ダンデヴァイン</t>
+        </is>
+      </c>
+      <c r="D100" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D101" t="b">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D102" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D103" t="b">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -1233,7 +1233,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月7日（火）～ TOKYO MX ほか</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1241,10 +1241,26 @@
           <t>ROLL2</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Amore</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ReoNa</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>エテルネル</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>sajou no hana</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=25598</t>
@@ -1441,7 +1457,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月8日（水）～ TOKYO MX ほか</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1449,8 +1465,16 @@
           <t>Lay-duce</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Foreshadow</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>前島麻由</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Awake Anew</t>
@@ -3195,7 +3219,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026年7月～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
+          <t>2026年7月11日（土）～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3517,8 +3541,16 @@
           <t>動画工房</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sunny</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>milet</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
@@ -6876,7 +6908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7672,7 +7704,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>きみが死ぬまで恋をしたい</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -7688,12 +7720,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>いつかちゃんと。</t>
+          <t>Amore</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>りりあ。</t>
+          <t>ReoNa</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -7712,7 +7744,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>きみが死ぬまで恋をしたい</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -7728,12 +7760,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>最終回</t>
+          <t>エテルネル</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>sorato</t>
+          <t>sajou no hana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -7752,7 +7784,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -7768,12 +7800,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>夏子</t>
+          <t>いつかちゃんと。</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FUNKY MONKEY BΛBY'S</t>
+          <t>りりあ。</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -7792,7 +7824,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -7808,12 +7840,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>裸のマーメード</t>
+          <t>最終回</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>豆柴の大群</t>
+          <t>sorato</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -7832,7 +7864,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -7840,7 +7872,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -7848,12 +7880,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Awake Anew</t>
+          <t>夏子</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>FUNKY MONKEY BΛBY'S</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -7872,7 +7904,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -7880,7 +7912,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -7888,32 +7920,18 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Running In My Head</t>
+          <t>裸のマーメード</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MIYAVI</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=HSakQbaQifs</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>19423</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>コードギアスチャンネル CODEGEASS Channel</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2026-06-05T19:01:45</t>
-        </is>
-      </c>
+          <t>豆柴の大群</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -7926,7 +7944,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -7934,7 +7952,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -7942,12 +7960,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ロゼ (Prod.TeddyLoid)</t>
+          <t>Foreshadow</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>満島ひかり</t>
+          <t>前島麻由</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -7966,7 +7984,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -7974,7 +7992,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -7982,12 +8000,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>遺書</t>
+          <t>Awake Anew</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>キタニタツヤ</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -8006,7 +8024,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -8014,7 +8032,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -8022,18 +8040,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>コニファー</t>
+          <t>Running In My Head</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>リーガルリリー</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>MIYAVI</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HSakQbaQifs</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>19423</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>コードギアスチャンネル CODEGEASS Channel</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-06-05T19:01:45</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -8046,7 +8078,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -8054,7 +8086,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -8062,12 +8094,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>最最最高級のお世話して</t>
+          <t>ロゼ (Prod.TeddyLoid)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>angela</t>
+          <t>満島ひかり</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -8086,7 +8118,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -8094,7 +8126,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -8102,12 +8134,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>完璧じゃないわたし</t>
+          <t>遺書</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>前島亜美</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -8126,7 +8158,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -8134,7 +8166,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -8142,12 +8174,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>コニファー</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>杏子</t>
+          <t>リーガルリリー</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -8166,7 +8198,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -8182,12 +8214,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>最最最高級のお世話して</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>angela</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -8206,7 +8238,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -8214,7 +8246,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -8222,12 +8254,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>イチジク煙</t>
+          <t>完璧じゃないわたし</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ずっと真夜中でいいのに。</t>
+          <t>前島亜美</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -8246,7 +8278,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -8254,7 +8286,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -8262,12 +8294,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -8286,7 +8318,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -8302,12 +8334,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>INUWASI</t>
+          <t>いきものがかり</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -8326,7 +8358,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -8334,7 +8366,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -8342,12 +8374,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -8366,15 +8398,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -8382,12 +8414,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>スノウドロップ</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Conton Candy</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -8406,15 +8438,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -8422,12 +8454,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>水平線は僕の古傷</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -8446,7 +8478,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -8454,7 +8486,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -8462,12 +8494,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -8486,11 +8518,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -8498,16 +8530,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>猫じゃらし</t>
+          <t>スノウドロップ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7co</t>
+          <t>Conton Candy</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -8526,11 +8558,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -8542,12 +8574,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>水平線は僕の古傷</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -8566,7 +8598,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -8582,12 +8614,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -8606,7 +8638,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -8614,20 +8646,20 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NEW GAME</t>
+          <t>猫じゃらし</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>halca</t>
+          <t>7co</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -8646,7 +8678,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -8654,7 +8686,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -8662,12 +8694,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -8686,7 +8718,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -8702,12 +8734,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -8726,7 +8758,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -8742,32 +8774,18 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>NEW GAME</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KI_EN</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>107892</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>2026-06-04T19:29:01</t>
-        </is>
-      </c>
+          <t>halca</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -8780,7 +8798,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -8796,12 +8814,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -8820,7 +8838,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -8836,12 +8854,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>原因は自分にある。</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -8860,7 +8878,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -8868,7 +8886,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -8876,18 +8894,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+          <t>KI_EN</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>107892</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-06-04T19:29:01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8900,7 +8932,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -8916,12 +8948,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -8940,7 +8972,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -8948,7 +8980,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -8956,12 +8988,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -8980,7 +9012,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>トミカとトム</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -8988,7 +9020,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -8996,12 +9028,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>きみのたからもの</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>May J.</t>
+          <t>SEKAI NO OWARI</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -9020,7 +9052,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -9036,12 +9068,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -9060,7 +9092,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -9068,7 +9100,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -9076,12 +9108,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -9100,7 +9132,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>トミカとトム</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -9108,7 +9140,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -9116,12 +9148,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>きみのたからもの</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>May J.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -9140,7 +9172,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -9152,16 +9184,16 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -9180,7 +9212,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -9188,7 +9220,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -9196,12 +9228,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>安保心結</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -9228,20 +9260,20 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -9260,7 +9292,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -9272,16 +9304,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -9300,7 +9332,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -9308,20 +9340,20 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -9340,7 +9372,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>刃牙道 第1クール（TV放送）</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -9352,16 +9384,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -9388,20 +9420,20 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -9420,7 +9452,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -9432,16 +9464,16 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -9460,7 +9492,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -9476,12 +9508,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9500,7 +9532,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -9508,20 +9540,20 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9540,7 +9572,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -9548,7 +9580,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -9556,12 +9588,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9580,7 +9612,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -9588,7 +9620,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -9596,12 +9628,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9620,7 +9652,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -9628,7 +9660,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -9636,12 +9668,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9660,7 +9692,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -9668,7 +9700,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -9676,12 +9708,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>FREEZE ME UP</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SiM</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9700,7 +9732,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -9708,7 +9740,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -9716,12 +9748,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Groooovy</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>I Don't Like Mondays.</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9740,7 +9772,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -9748,7 +9780,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -9756,12 +9788,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9780,7 +9812,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -9796,12 +9828,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>○✕△□</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>浪漫派マシュマロ</t>
+          <t>milet</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9820,7 +9852,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -9836,12 +9868,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>SiM</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9860,7 +9892,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -9876,12 +9908,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>Groooovy</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>I Don't Like Mondays.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9900,7 +9932,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -9908,7 +9940,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -9916,12 +9948,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9940,7 +9972,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -9948,7 +9980,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -9956,12 +9988,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>浪漫派マシュマロ</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9980,7 +10012,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -9996,12 +10028,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10020,7 +10052,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -10036,12 +10068,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10060,7 +10092,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -10076,12 +10108,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10100,7 +10132,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -10116,12 +10148,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10140,7 +10172,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -10156,12 +10188,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10180,7 +10212,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -10196,12 +10228,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10220,7 +10252,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -10236,12 +10268,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10260,7 +10292,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D84" t="b">
@@ -10268,7 +10300,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -10276,12 +10308,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Why? RED induction</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>中島美嘉</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10300,7 +10332,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -10308,7 +10340,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -10316,12 +10348,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Weiter! Weiter!</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10340,7 +10372,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -10348,7 +10380,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -10356,12 +10388,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>冨岡愛</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10380,7 +10412,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -10392,16 +10424,16 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10420,7 +10452,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -10428,7 +10460,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -10436,12 +10468,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10460,7 +10492,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -10472,16 +10504,16 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10500,7 +10532,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -10516,12 +10548,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10540,7 +10572,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -10548,20 +10580,20 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10580,7 +10612,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -10588,7 +10620,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -10596,12 +10628,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10620,7 +10652,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -10632,16 +10664,16 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10660,7 +10692,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D94" t="b">
@@ -10676,12 +10708,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10700,7 +10732,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -10716,12 +10748,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>REIRIE</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10740,7 +10772,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -10756,12 +10788,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10780,7 +10812,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -10796,12 +10828,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ゆきむら。</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10820,7 +10852,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -10836,12 +10868,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10851,16 +10883,16 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -10868,7 +10900,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -10876,12 +10908,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sorrow</t>
+          <t>ひなたぼっこ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>REIRIE</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10891,16 +10923,16 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -10916,12 +10948,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>西川貴教</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10931,16 +10963,16 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -10948,7 +10980,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -10956,12 +10988,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>ゆきむら。</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10971,16 +11003,16 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -10988,7 +11020,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -10996,12 +11028,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>終宵</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>マカロニえんぴつ</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11020,7 +11052,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>帰還者の魔法は特別です 第2期</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -11036,12 +11068,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>Sorrow</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11049,6 +11081,166 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>獣王武神ダンデヴァイン</t>
+        </is>
+      </c>
+      <c r="D104" t="b">
+        <v>0</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D105" t="b">
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D106" t="b">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D107" t="b">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1084,8 +1084,16 @@
           <t>ユニコーン</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BLUE ENCOUNT</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=26271</t>
@@ -2786,8 +2794,16 @@
           <t>マカリア</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ひとひら</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>秦基博</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>光</t>
@@ -3080,11 +3096,11 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -3141,11 +3157,11 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>花織さんは転生しても喧嘩がしたい</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -3153,42 +3169,26 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>第1クール：2026年2月26日（木）〜 第2クール：2026年6月18日（木）～ Netflixにて 【TV放送】 第1クール：2026年7月5日（日）～ TOKYO MXほか</t>
+          <t>2026年7月11日（土）～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>フルボコ</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>WANIMA</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Mountain Top</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Novel Core</t>
-        </is>
-      </c>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23828</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
         </is>
       </c>
     </row>
@@ -3202,11 +3202,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>花織さんは転生しても喧嘩がしたい</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -3219,21 +3219,37 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026年7月11日（土）～ ABCテレビ・テレビ朝日系・BS日テレにて</t>
+          <t>2026年7月1日（水）～ TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+          <t>シグナル・エムディ（</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>FLASHBULB</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>花束</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27990</t>
         </is>
       </c>
     </row>
@@ -3247,11 +3263,11 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>バンドリ！ ゆめ∞みた</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -3264,37 +3280,21 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MX・BS11ほか</t>
+          <t>2026年7月2日（木）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>シグナル・エムディ（</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>FLASHBULB</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>花束</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
+          <t>ニチカライン（</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27990</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
         </is>
       </c>
     </row>
@@ -3308,11 +3308,11 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>バンドリ！ ゆめ∞みた</t>
+          <t>パンの赤ちゃん</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -3325,21 +3325,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MXほか</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>ニチカライン（</t>
-        </is>
-      </c>
+          <t>2026年7月4日（土）～ カンテレ・フジテレビ系列「土曜はナニする！？」にて</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26737</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25145</t>
         </is>
       </c>
     </row>
@@ -3353,11 +3349,11 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>パンの赤ちゃん</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -3370,17 +3366,37 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ カンテレ・フジテレビ系列「土曜はナニする！？」にて</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+          <t>2026年7月1日（水）～ TOKYO MX・BSフジほか</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>EMTスクエアード</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>マデュアル↔ハート</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ハンドメイド</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>仲村宗悟</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25145</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
         </is>
       </c>
     </row>
@@ -3394,11 +3410,11 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -3411,37 +3427,37 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MX・BSフジほか</t>
+          <t>2026年7月6日（月）〜 テレ東・BS11ほか</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>EMTスクエアード</t>
+          <t>スタジオコメット</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25936</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
         </is>
       </c>
     </row>
@@ -3455,11 +3471,11 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -3472,37 +3488,29 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026年7月6日（月）〜 テレ東・BS11ほか</t>
+          <t>2026年7月12日（日）〜 テレビ東京系列にて</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>スタジオコメット</t>
+          <t>動画工房</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>小倉唯</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>グッバイ・ララバイ</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>大西亜玖璃</t>
-        </is>
-      </c>
+          <t>milet</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27366</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
         </is>
       </c>
     </row>
@@ -3516,11 +3524,11 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -3533,29 +3541,37 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026年7月12日（日）〜 テレビ東京系列にて</t>
+          <t>2026年7月4日（土）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>動画工房</t>
+          <t>100studio</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>milet</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+          <t>SiM</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Groooovy</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>I Don't Like Mondays.</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25702</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
         </is>
       </c>
     </row>
@@ -3569,11 +3585,11 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -3586,37 +3602,21 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MXほか</t>
+          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>100studio</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>FREEZE ME UP</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>SiM</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Groooovy</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>I Don't Like Mondays.</t>
-        </is>
-      </c>
+          <t>SMDE</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25641</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
         </is>
       </c>
     </row>
@@ -3630,11 +3630,11 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列6局ネット「アニもり！」内にて</t>
+          <t>2026年7月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SMDE</t>
+          <t>PIERROT FILMS（</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -3661,7 +3661,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BLEACH 千年血戦篇-禍進譚-</t>
+          <t>文豪ストレイドッグス わん！２</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列ほか</t>
+          <t>2026年7月〜</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>PIERROT FILMS（</t>
+          <t>ボンズ</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
         </is>
       </c>
     </row>
@@ -3720,11 +3720,11 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>文豪ストレイドッグス わん！２</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -3737,21 +3737,29 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026年7月〜</t>
+          <t>2026年7月3日（金）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ボンズ</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>横浜アニメーションラボ</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>○✕△□</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>浪漫派マシュマロ</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
         </is>
       </c>
     </row>
@@ -3765,11 +3773,11 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -3782,29 +3790,37 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026年7月3日（金）～ TOKYO MXほか</t>
+          <t>第1クール：2026年1月5日（月）～2026年3月23日（月） 第2クール：2026年7月6日（月）～ AT-X・TOKYO MXにて</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>横浜アニメーションラボ</t>
+          <t>動楽</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>○✕△□</t>
+          <t>Blacker Co., Ltd.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>浪漫派マシュマロ</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+          <t>イツカ▶</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Elegy of the Enemies</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>The Canbellz</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28020</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26775</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3834,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3879,7 +3895,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3940,7 +3956,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3985,7 +4001,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4046,7 +4062,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4103,7 +4119,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4164,7 +4180,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4217,7 +4233,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4278,7 +4294,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4339,7 +4355,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4400,7 +4416,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4461,7 +4477,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4522,7 +4538,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4567,7 +4583,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4628,7 +4644,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4681,7 +4697,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5700,7 +5716,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>てつりょー！meet with 鉄道むすめ</t>
+          <t>追放されたチート付与魔術師は気ままなセカンドライフを謳歌する。</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -5713,12 +5729,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレ東系列にて</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>イーストフィッシュスタジオ</t>
+          <t>P.A.WORKS</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -5727,7 +5743,7 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27631</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5761,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>テムパル～アイテムの力～</t>
+          <t>てつりょー！meet with 鉄道むすめ</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -5758,12 +5774,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>イーストフィッシュスタジオ</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -5772,7 +5788,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5806,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
+          <t>テムパル～アイテムの力～</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -5803,12 +5819,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>studio MOTHER</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -5817,7 +5833,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5851,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>転生ゴブリンだけど質問ある？</t>
+          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -5848,12 +5864,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>BAKKKA</t>
+          <t>studio MOTHER</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -5862,7 +5878,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5896,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>転生ゴブリンだけど質問ある？</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -5898,32 +5914,16 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>FelixFilm</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Flare of Soul</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>STELLAR</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>ウタヒメドリーム オールスターズ</t>
-        </is>
-      </c>
+          <t>BAKKKA</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>転生したら剣でした 第2期</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -5959,16 +5959,32 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>C2C</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
+          <t>FelixFilm</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
         </is>
       </c>
     </row>
@@ -5986,7 +6002,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>とある暗部の少女共棲</t>
+          <t>転生したら剣でした 第2期</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -5999,12 +6015,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>C2C</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -6013,7 +6029,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6047,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>東京リベンジャーズ 三天戦争編</t>
+          <t>とある暗部の少女共棲</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -6044,12 +6060,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -6058,7 +6074,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6092,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
+          <t>東京リベンジャーズ 三天戦争編</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -6089,17 +6105,21 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6137,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ドラゴンボール超 ビルス</t>
+          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -6130,7 +6150,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026年秋 フジテレビにて</t>
+          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -6140,7 +6160,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6178,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>鳴海の平日</t>
+          <t>ドラゴンボール超 ビルス</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -6166,26 +6186,22 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Production I.G</t>
-        </is>
-      </c>
+          <t>2026年秋 フジテレビにて</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6219,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>バーテックスフォース</t>
+          <t>鳴海の平日</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -6211,17 +6227,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>SMDE</t>
+          <t>Production I.G</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -6230,7 +6246,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6264,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Battle Spirits [Re] 絶界の空</t>
+          <t>バーテックスフォース</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -6261,17 +6277,21 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>SMDE</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6309,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>パンどろぼう</t>
+          <t>Battle Spirits [Re] 絶界の空</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -6302,7 +6322,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026年10月〜 NHK Eテレにて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -6312,7 +6332,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6350,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>百妖譜 京師篇</t>
+          <t>パンどろぼう</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -6343,7 +6363,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+          <t>2026年10月〜 NHK Eテレにて</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -6353,7 +6373,7 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
         </is>
       </c>
     </row>
@@ -6371,7 +6391,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>冰剣の魔術師が世界を統べるⅡ</t>
+          <t>百妖譜 京師篇</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -6384,21 +6404,17 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>ゼロジー</t>
-        </is>
-      </c>
+          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6432,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ホタルの嫁入り</t>
+          <t>冰剣の魔術師が世界を統べるⅡ</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -6429,12 +6445,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>david production</t>
+          <t>ゼロジー</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6443,7 +6459,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6477,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ポップパップポルターズ</t>
+          <t>ホタルの嫁入り</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -6474,12 +6490,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026年秋 テレビ朝日にて</t>
+          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>MOZU STUDIOS</t>
+          <t>david production</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -6488,7 +6504,7 @@
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6522,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ホテル・インヒューマンズ 第2期</t>
+          <t>ポップパップポルターズ</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -6519,12 +6535,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列ほか</t>
+          <t>2026年秋 テレビ朝日にて</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ブリッジ</t>
+          <t>MOZU STUDIOS</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6533,7 +6549,7 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6567,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>マジカル★エクスプローラー</t>
+          <t>ホテル・インヒューマンズ 第2期</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -6564,12 +6580,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>WHITE FOX</t>
+          <t>ブリッジ</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -6578,7 +6594,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6612,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>魔法騎士レイアース</t>
+          <t>マジカル★エクスプローラー</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -6609,12 +6625,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日系列にて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>E&amp;H production</t>
+          <t>WHITE FOX</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -6623,7 +6639,7 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6657,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>魔法騎士レイアース</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -6654,29 +6670,21 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレビ朝日系列にて</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>SynergySP</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>No tears here</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
+          <t>E&amp;H production</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6702,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>マロニエ王国の七人の騎士</t>
+          <t>魔法少女育成計画restart</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -6707,21 +6715,29 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK Eテレにて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
+          <t>SynergySP</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6755,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
+          <t>マロニエ王国の七人の騎士</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -6752,12 +6768,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月～ NHK Eテレにて</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>studio A-CAT</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -6766,7 +6782,7 @@
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6800,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -6797,12 +6813,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>寿門堂</t>
+          <t>studio A-CAT</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6811,7 +6827,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6845,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>らんま1/2 第3期</t>
+          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -6842,17 +6858,21 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>寿門堂</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6890,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LEGO® ONE PIECE</t>
+          <t>らんま1/2 第3期</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -6878,12 +6898,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026年9月29日（火） Netflixにて</t>
+          <t>2026年10月～ 日本テレビ系にて</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -6892,6 +6912,47 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>50</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LEGO® ONE PIECE</t>
+        </is>
+      </c>
+      <c r="E131" t="b">
+        <v>0</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>配信</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026年9月29日（火） Netflixにて</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28168</t>
         </is>
@@ -6908,7 +6969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7584,7 +7645,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>株式会社マジルミエ 第2期</t>
+          <t>片田舎のおっさん、剣聖になるII</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -7600,12 +7661,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BooooM!!!</t>
+          <t>未完成</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>宝鐘マリン</t>
+          <t>BLUE ENCOUNT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -7624,15 +7685,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です</t>
+          <t>株式会社マジルミエ 第2期</t>
         </is>
       </c>
       <c r="D18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -7640,12 +7701,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GET BACK</t>
+          <t>BooooM!!!</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>宝鐘マリン</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -7672,7 +7733,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -7680,12 +7741,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6を撫でる</t>
+          <t>GET BACK</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ももすももす</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -7704,15 +7765,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>きみが死ぬまで恋をしたい</t>
+          <t>帰還者の魔法は特別です</t>
         </is>
       </c>
       <c r="D20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -7720,12 +7781,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Amore</t>
+          <t>6を撫でる</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ReoNa</t>
+          <t>ももすももす</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -7752,7 +7813,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -7760,12 +7821,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>エテルネル</t>
+          <t>Amore</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>sajou no hana</t>
+          <t>ReoNa</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -7784,7 +7845,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>きみが死ぬまで恋をしたい</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -7792,7 +7853,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -7800,12 +7861,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>いつかちゃんと。</t>
+          <t>エテルネル</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>りりあ。</t>
+          <t>sajou no hana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -7832,7 +7893,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -7840,12 +7901,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>最終回</t>
+          <t>いつかちゃんと。</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>sorato</t>
+          <t>りりあ。</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -7864,7 +7925,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -7872,7 +7933,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -7880,12 +7941,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>夏子</t>
+          <t>最終回</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FUNKY MONKEY BΛBY'S</t>
+          <t>sorato</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -7912,7 +7973,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -7920,12 +7981,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>裸のマーメード</t>
+          <t>夏子</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>豆柴の大群</t>
+          <t>FUNKY MONKEY BΛBY'S</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -7944,7 +8005,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -7952,7 +8013,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -7960,12 +8021,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Foreshadow</t>
+          <t>裸のマーメード</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>前島麻由</t>
+          <t>豆柴の大群</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -7992,7 +8053,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -8000,12 +8061,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Awake Anew</t>
+          <t>Foreshadow</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>前島麻由</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -8024,7 +8085,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -8032,7 +8093,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -8040,32 +8101,18 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Running In My Head</t>
+          <t>Awake Anew</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MIYAVI</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=HSakQbaQifs</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>19423</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>コードギアスチャンネル CODEGEASS Channel</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2026-06-05T19:01:45</t>
-        </is>
-      </c>
+          <t>MYTH &amp; ROID</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -8086,7 +8133,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -8094,18 +8141,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ロゼ (Prod.TeddyLoid)</t>
+          <t>Running In My Head</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>満島ひかり</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>MIYAVI</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HSakQbaQifs</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>19423</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>コードギアスチャンネル CODEGEASS Channel</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-06-05T19:01:45</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -8118,7 +8179,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -8126,7 +8187,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -8134,12 +8195,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>遺書</t>
+          <t>ロゼ (Prod.TeddyLoid)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>キタニタツヤ</t>
+          <t>満島ひかり</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -8166,7 +8227,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -8174,12 +8235,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>コニファー</t>
+          <t>遺書</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>リーガルリリー</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -8198,7 +8259,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -8206,7 +8267,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -8214,12 +8275,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>最最最高級のお世話して</t>
+          <t>コニファー</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>angela</t>
+          <t>リーガルリリー</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -8246,7 +8307,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -8254,12 +8315,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>完璧じゃないわたし</t>
+          <t>最最最高級のお世話して</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>前島亜美</t>
+          <t>angela</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -8278,7 +8339,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -8286,7 +8347,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -8294,12 +8355,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>完璧じゃないわたし</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>杏子</t>
+          <t>前島亜美</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -8318,7 +8379,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -8334,12 +8395,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -8358,7 +8419,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -8374,12 +8435,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>イチジク煙</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ずっと真夜中でいいのに。</t>
+          <t>いきものがかり</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -8406,7 +8467,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -8414,12 +8475,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -8438,7 +8499,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -8446,7 +8507,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -8454,12 +8515,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>INUWASI</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -8486,7 +8547,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -8494,12 +8555,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -8518,15 +8579,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -8534,12 +8595,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>スノウドロップ</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Conton Candy</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -8566,7 +8627,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -8574,12 +8635,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>水平線は僕の古傷</t>
+          <t>スノウドロップ</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+          <t>Conton Candy</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -8598,15 +8659,15 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -8614,12 +8675,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>水平線は僕の古傷</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -8650,16 +8711,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>猫じゃらし</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>7co</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -8686,20 +8747,20 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>猫じゃらし</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>7co</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -8718,7 +8779,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -8726,7 +8787,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -8734,12 +8795,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -8766,7 +8827,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -8774,12 +8835,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>NEW GAME</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>halca</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -8798,7 +8859,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -8806,7 +8867,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -8814,12 +8875,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>NEW GAME</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>halca</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -8838,7 +8899,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -8854,12 +8915,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -8878,7 +8939,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -8886,7 +8947,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -8894,32 +8955,18 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KI_EN</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>107892</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>2026-06-04T19:29:01</t>
-        </is>
-      </c>
+          <t>原因は自分にある。</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8932,7 +8979,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -8940,7 +8987,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -8948,12 +8995,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>KI_EN</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -8972,7 +9019,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -8988,12 +9035,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -9012,7 +9059,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -9028,12 +9075,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -9052,7 +9099,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -9068,12 +9115,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>SEKAI NO OWARI</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -9092,7 +9139,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -9100,7 +9147,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -9108,12 +9155,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -9132,7 +9179,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>トミカとトム</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -9140,7 +9187,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -9148,12 +9195,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>きみのたからもの</t>
+          <t>ひとひら</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>May J.</t>
+          <t>秦基博</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -9172,7 +9219,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -9180,7 +9227,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -9188,12 +9235,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -9212,7 +9259,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>トミカとトム</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -9228,12 +9275,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>きみのたからもの</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>May J.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -9252,7 +9299,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -9268,12 +9315,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -9292,7 +9339,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -9300,20 +9347,20 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>安保心結</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -9332,7 +9379,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -9340,7 +9387,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -9348,12 +9395,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -9372,7 +9419,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>刃牙道 第1クール（TV放送）</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -9380,7 +9427,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -9388,12 +9435,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -9420,7 +9467,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -9428,12 +9475,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -9460,7 +9507,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -9468,12 +9515,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -9492,7 +9539,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -9500,7 +9547,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -9508,12 +9555,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9532,7 +9579,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -9544,16 +9591,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9572,7 +9619,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -9588,12 +9635,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9612,7 +9659,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -9628,12 +9675,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9652,7 +9699,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -9668,12 +9715,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9692,7 +9739,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -9708,12 +9755,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9732,7 +9779,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -9748,12 +9795,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>milet</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9772,7 +9819,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -9780,7 +9827,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -9788,12 +9835,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>SiM</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9812,7 +9859,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -9820,7 +9867,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -9828,12 +9875,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Groooovy</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>milet</t>
+          <t>I Don't Like Mondays.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9852,7 +9899,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -9860,7 +9907,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -9868,12 +9915,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FREEZE ME UP</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SiM</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9892,7 +9939,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -9900,7 +9947,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -9908,12 +9955,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Groooovy</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>I Don't Like Mondays.</t>
+          <t>浪漫派マシュマロ</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9932,7 +9979,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -9940,7 +9987,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -9948,12 +9995,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>Blacker Co., Ltd.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>イツカ▶</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9972,7 +10019,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -9980,7 +10027,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -9988,12 +10035,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>○✕△□</t>
+          <t>Elegy of the Enemies</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>浪漫派マシュマロ</t>
+          <t>The Canbellz</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10012,7 +10059,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -10020,20 +10067,20 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>白い蝶が飛んだら</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10060,7 +10107,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -10068,12 +10115,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10092,7 +10139,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -10100,7 +10147,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -10108,12 +10155,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10140,7 +10187,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -10148,12 +10195,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10172,7 +10219,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -10180,7 +10227,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -10188,12 +10235,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10220,7 +10267,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -10228,12 +10275,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10252,7 +10299,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -10260,7 +10307,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -10268,12 +10315,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10300,7 +10347,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -10308,12 +10355,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10332,7 +10379,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -10340,7 +10387,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -10348,12 +10395,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>中島美嘉</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10380,7 +10427,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -10388,12 +10435,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10412,7 +10459,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -10420,7 +10467,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -10428,12 +10475,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>冨岡愛</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10452,7 +10499,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -10468,12 +10515,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Why? RED induction</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10500,7 +10547,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -10508,12 +10555,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Weiter! Weiter!</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10532,7 +10579,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -10540,7 +10587,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -10548,12 +10595,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10584,16 +10631,16 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10620,20 +10667,20 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10664,16 +10711,16 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10692,7 +10739,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D94" t="b">
@@ -10700,20 +10747,20 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10740,7 +10787,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -10748,12 +10795,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10772,7 +10819,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -10780,7 +10827,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -10788,12 +10835,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10820,7 +10867,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -10828,12 +10875,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10852,7 +10899,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -10860,7 +10907,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -10868,12 +10915,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10900,7 +10947,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -10908,12 +10955,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>REIRIE</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10932,7 +10979,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -10940,7 +10987,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -10948,12 +10995,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>ひなたぼっこ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>REIRIE</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10980,7 +11027,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -10988,12 +11035,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ゆきむら。</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11012,7 +11059,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -11020,7 +11067,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -11028,12 +11075,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>ゆきむら。</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11043,16 +11090,16 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -11068,12 +11115,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sorrow</t>
+          <t>終宵</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>マカロニえんぴつ</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11092,7 +11139,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>帰還者の魔法は特別です 第2期</t>
         </is>
       </c>
       <c r="D104" t="b">
@@ -11108,12 +11155,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>Sorrow</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>西川貴教</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11132,7 +11179,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>獣王武神ダンデヴァイン</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -11148,12 +11195,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>曲名未発表</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>西川貴教</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11180,7 +11227,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -11188,12 +11235,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>Flare of Soul</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11212,7 +11259,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -11220,7 +11267,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -11228,12 +11275,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>STELLAR</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>ウタヒメドリーム オールスターズ</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11241,6 +11288,46 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
     </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D108" t="b">
+        <v>0</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・BS11・MBSにて</t>
+          <t>2026年7月6日（月）～ TOKYO MX・BS11・MBSにて</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1577,8 +1577,16 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MILLENNIUM PARADE feat. Saya Gray, Daniel Caesar</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=24096</t>
@@ -1987,14 +1995,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026年7月～ フジテレビ「+Ultra」にて</t>
+          <t>2026年7月8日（水）～ フジテレビ「+Ultra」にて</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>しゅるれりら</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>音羽-otoha-</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=27611</t>
@@ -2028,7 +2044,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026年7月～ TBS系にて</t>
+          <t>2026年7月9日（木）～ TBS系にて</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2085,7 +2101,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・ＢＳ日テレほか</t>
+          <t>2026年7月6日（月）～ TOKYO MX・ＢＳ日テレほか</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6969,7 +6985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8125,7 +8141,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>攻殻機動隊 THE GHOST IN THE SHELL</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -8133,7 +8149,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -8141,32 +8157,18 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Running In My Head</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MIYAVI</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=HSakQbaQifs</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>19423</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>コードギアスチャンネル CODEGEASS Channel</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2026-06-05T19:01:45</t>
-        </is>
-      </c>
+          <t>MILLENNIUM PARADE feat. Saya Gray, Daniel Caesar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -8187,7 +8189,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -8195,12 +8197,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ロゼ (Prod.TeddyLoid)</t>
+          <t>Running In My Head</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>満島ひかり</t>
+          <t>MIYAVI</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -8219,7 +8221,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -8227,7 +8229,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -8235,12 +8237,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>遺書</t>
+          <t>ロゼ (Prod.TeddyLoid)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>キタニタツヤ</t>
+          <t>満島ひかり</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -8267,7 +8269,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -8275,12 +8277,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>コニファー</t>
+          <t>遺書</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>リーガルリリー</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -8299,7 +8301,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -8307,7 +8309,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -8315,12 +8317,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>最最最高級のお世話して</t>
+          <t>コニファー</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>angela</t>
+          <t>リーガルリリー</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -8347,7 +8349,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -8355,12 +8357,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>完璧じゃないわたし</t>
+          <t>最最最高級のお世話して</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>前島亜美</t>
+          <t>angela</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -8379,7 +8381,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -8387,7 +8389,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -8395,12 +8397,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>完璧じゃないわたし</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>杏子</t>
+          <t>前島亜美</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -8419,7 +8421,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -8435,12 +8437,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -8459,7 +8461,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -8475,12 +8477,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>イチジク煙</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ずっと真夜中でいいのに。</t>
+          <t>いきものがかり</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -8499,7 +8501,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>サンダー３</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -8515,12 +8517,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>しゅるれりら</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>音羽-otoha-</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -8539,7 +8541,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -8555,12 +8557,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>INUWASI</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -8579,7 +8581,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -8595,12 +8597,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -8619,11 +8621,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -8635,12 +8637,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>スノウドロップ</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Conton Candy</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -8659,11 +8661,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -8675,12 +8677,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>水平線は僕の古傷</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -8699,11 +8701,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -8715,12 +8717,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>スノウドロップ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>Conton Candy</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -8739,28 +8741,28 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>猫じゃらし</t>
+          <t>水平線は僕の古傷</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>7co</t>
+          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -8787,7 +8789,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -8795,12 +8797,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -8819,7 +8821,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -8831,16 +8833,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>猫じゃらし</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>7co</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -8859,7 +8861,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -8875,12 +8877,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NEW GAME</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>halca</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -8899,7 +8901,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -8915,12 +8917,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -8939,7 +8941,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -8947,7 +8949,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -8955,12 +8957,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>NEW GAME</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>halca</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -8979,7 +8981,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -8987,7 +8989,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -8995,12 +8997,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KI_EN</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -9019,7 +9021,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -9035,12 +9037,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>原因は自分にある。</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -9059,7 +9061,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -9067,7 +9069,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -9075,12 +9077,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>KI_EN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -9099,7 +9101,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -9115,12 +9117,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -9139,7 +9141,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -9155,12 +9157,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -9179,7 +9181,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -9195,12 +9197,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ひとひら</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>秦基博</t>
+          <t>SEKAI NO OWARI</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -9219,7 +9221,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -9227,7 +9229,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -9235,12 +9237,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -9259,7 +9261,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>トミカとトム</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -9267,7 +9269,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -9275,12 +9277,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>きみのたからもの</t>
+          <t>ひとひら</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>May J.</t>
+          <t>秦基博</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -9299,7 +9301,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -9307,7 +9309,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -9315,12 +9317,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -9339,7 +9341,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>トミカとトム</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -9355,12 +9357,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>きみのたからもの</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>May J.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -9379,7 +9381,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -9395,12 +9397,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -9419,7 +9421,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -9427,20 +9429,20 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>安保心結</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -9467,7 +9469,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -9475,12 +9477,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -9507,7 +9509,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -9515,12 +9517,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -9539,7 +9541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -9547,7 +9549,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -9555,12 +9557,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9579,7 +9581,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -9591,16 +9593,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9619,7 +9621,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -9635,12 +9637,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9659,7 +9661,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -9675,12 +9677,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9699,7 +9701,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -9715,12 +9717,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9739,7 +9741,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -9755,12 +9757,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9779,7 +9781,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -9795,12 +9797,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>milet</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9819,7 +9821,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -9827,7 +9829,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -9835,12 +9837,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FREEZE ME UP</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SiM</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9859,7 +9861,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -9867,7 +9869,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -9875,12 +9877,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Groooovy</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>I Don't Like Mondays.</t>
+          <t>milet</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9899,7 +9901,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -9907,7 +9909,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -9915,12 +9917,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>SiM</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9939,7 +9941,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -9947,7 +9949,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -9955,12 +9957,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>○✕△□</t>
+          <t>Groooovy</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>浪漫派マシュマロ</t>
+          <t>I Don't Like Mondays.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9979,7 +9981,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -9987,7 +9989,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -9995,12 +9997,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Blacker Co., Ltd.</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>イツカ▶</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10019,7 +10021,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -10027,7 +10029,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -10035,12 +10037,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Elegy of the Enemies</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>The Canbellz</t>
+          <t>浪漫派マシュマロ</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10067,20 +10069,20 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>白い蝶が飛んだら</t>
+          <t>Blacker Co., Ltd.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
+          <t>イツカ▶</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10099,7 +10101,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -10107,7 +10109,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -10115,12 +10117,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>Elegy of the Enemies</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>The Canbellz</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10139,7 +10141,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -10151,16 +10153,16 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>白い蝶が飛んだら</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10179,7 +10181,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -10195,12 +10197,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10219,7 +10221,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -10235,12 +10237,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10259,7 +10261,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -10275,12 +10277,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10299,7 +10301,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -10315,12 +10317,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10339,7 +10341,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D84" t="b">
@@ -10355,12 +10357,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10379,7 +10381,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -10395,12 +10397,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10419,7 +10421,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -10435,12 +10437,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10459,7 +10461,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -10475,12 +10477,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
+          <t>中島美嘉</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10499,7 +10501,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -10515,12 +10517,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10539,7 +10541,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -10547,7 +10549,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -10555,12 +10557,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Why? RED induction</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>冨岡愛</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10579,7 +10581,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -10587,7 +10589,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -10595,12 +10597,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Weiter! Weiter!</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10619,7 +10621,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -10635,12 +10637,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10659,7 +10661,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -10667,20 +10669,20 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10707,7 +10709,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -10715,12 +10717,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10747,7 +10749,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -10755,12 +10757,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10779,7 +10781,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -10787,7 +10789,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -10795,12 +10797,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10819,7 +10821,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -10831,16 +10833,16 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10859,7 +10861,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -10875,12 +10877,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10899,7 +10901,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -10915,12 +10917,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10939,7 +10941,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -10955,12 +10957,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10979,7 +10981,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -10995,12 +10997,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>REIRIE</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11019,7 +11021,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -11035,12 +11037,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11059,7 +11061,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -11075,12 +11077,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ひなたぼっこ</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ゆきむら。</t>
+          <t>REIRIE</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11099,7 +11101,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -11115,12 +11117,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11130,16 +11132,16 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D104" t="b">
@@ -11147,7 +11149,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -11155,12 +11157,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sorrow</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>ゆきむら。</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11170,16 +11172,16 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -11195,12 +11197,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>終宵</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>西川貴教</t>
+          <t>マカロニえんぴつ</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11219,7 +11221,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>帰還者の魔法は特別です 第2期</t>
         </is>
       </c>
       <c r="D106" t="b">
@@ -11235,12 +11237,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>Sorrow</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11259,7 +11261,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>獣王武神ダンデヴァイン</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -11267,7 +11269,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -11275,12 +11277,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>曲名未発表</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>西川貴教</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11299,7 +11301,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="D108" t="b">
@@ -11315,12 +11317,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>Flare of Soul</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11328,6 +11330,86 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D109" t="b">
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D110" t="b">
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -6985,7 +6985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7046,6 +7046,21 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>anime_youtube_url</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>anime_youtube_views</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>anime_youtube_channel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>last_searched_at</t>
         </is>
       </c>
@@ -7089,6 +7104,9 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -7129,6 +7147,9 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7169,6 +7190,9 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -7209,6 +7233,9 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7249,6 +7276,9 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7289,6 +7319,9 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7329,6 +7362,9 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7369,6 +7405,9 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7409,6 +7448,9 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7449,6 +7491,9 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7489,6 +7534,9 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7529,6 +7577,9 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7569,6 +7620,9 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7609,6 +7663,9 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7649,6 +7706,9 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7689,6 +7749,9 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7729,6 +7792,9 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7769,6 +7835,9 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7809,6 +7878,9 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7849,6 +7921,9 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7889,6 +7964,9 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7929,6 +8007,9 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7969,6 +8050,9 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -8009,6 +8093,9 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -8049,6 +8136,9 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -8089,6 +8179,9 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -8129,6 +8222,9 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -8169,6 +8265,9 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -8209,6 +8308,9 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -8249,6 +8351,9 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -8289,6 +8394,9 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -8329,6 +8437,9 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -8369,6 +8480,9 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -8409,6 +8523,9 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -8449,6 +8566,9 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -8489,6 +8609,9 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -8529,6 +8652,9 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -8569,6 +8695,9 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -8609,6 +8738,9 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -8649,6 +8781,9 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -8689,6 +8824,9 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -8729,6 +8867,9 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -8769,6 +8910,9 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -8809,6 +8953,9 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -8849,6 +8996,9 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -8889,6 +9039,9 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -8929,6 +9082,9 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -8969,6 +9125,9 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -9009,6 +9168,9 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -9049,6 +9211,9 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -9089,6 +9254,9 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -9129,6 +9297,9 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -9169,6 +9340,9 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -9209,6 +9383,9 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -9249,6 +9426,9 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -9289,6 +9469,9 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -9329,6 +9512,9 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -9369,6 +9555,9 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9409,6 +9598,9 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9449,6 +9641,9 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9489,6 +9684,9 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9529,6 +9727,9 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9569,6 +9770,9 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9609,6 +9813,9 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9649,6 +9856,9 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9689,6 +9899,9 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9729,6 +9942,9 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9769,6 +9985,9 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9809,6 +10028,9 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9849,6 +10071,9 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9889,6 +10114,9 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9929,6 +10157,9 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9969,6 +10200,9 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10009,6 +10243,9 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10049,6 +10286,9 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10089,6 +10329,9 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10129,6 +10372,9 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10169,6 +10415,9 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10209,6 +10458,9 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10249,6 +10501,9 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10289,6 +10544,9 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10329,6 +10587,9 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10369,6 +10630,9 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10409,6 +10673,9 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10449,6 +10716,9 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10489,6 +10759,9 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10529,6 +10802,9 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10569,6 +10845,9 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10609,6 +10888,9 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10649,6 +10931,9 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10689,6 +10974,9 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10729,6 +11017,9 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10769,6 +11060,9 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10809,6 +11103,9 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10849,6 +11146,9 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10889,6 +11189,9 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10929,6 +11232,9 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10969,6 +11275,9 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11009,6 +11318,9 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11049,6 +11361,9 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11089,6 +11404,9 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11129,6 +11447,9 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11169,6 +11490,9 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11209,6 +11533,9 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11249,6 +11576,9 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11289,6 +11619,9 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11329,6 +11662,9 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11369,6 +11705,9 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11409,6 +11748,9 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -7960,13 +7960,27 @@
           <t>sajou no hana</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1qcDcvE9lWc</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1654</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>sajou no hana Official Channel</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-06-14T18:14:57</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,14 +556,30 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月8日（水）～ tvkテレビ神奈川・テレ玉ほか</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>雨宿りの憧憬</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Lia</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>クレール</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AVAM</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=26511</t>
@@ -597,7 +613,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MX・サンテレビにて</t>
+          <t>2026年7月4日（土）～ TOKYO MX・サンテレビほか</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,14 +980,30 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月4日（土）～ TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ヒトコト</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ClariS</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>心星</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>山崎育三郎</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=26164</t>
@@ -1526,14 +1558,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月4日（土）～ TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ユラリユレル</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NOMELON NOLEMON</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>DAYS!</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Aooo</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=26410</t>
@@ -2749,7 +2797,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026年7月8日（水）～ フジテレビ・関西テレビほか</t>
+          <t>2026年7月8日（水）～ フジテレビほか</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2767,8 +2815,16 @@
           <t>QWER</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>To Be Continued</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>QWER</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=27435</t>
@@ -2963,8 +3019,16 @@
           <t>五阿弥ルナ</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Soarin’</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Ginger Root</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=27014</t>
@@ -3708,7 +3772,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026年7月〜</t>
+          <t>2026年7月2日（木）～ TOKYO MX1・サンテレビほか</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3718,8 +3782,16 @@
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>僕ら～芥川龍之介Ver.～</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>芥川龍之介（CV.小野賢章）</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=27057</t>
@@ -6121,7 +6193,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月2日（金）～ MBS・TBS・CBC”アニメイズム”枠ほか</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -6906,11 +6978,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>らんま1/2 第3期</t>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会 第2期</t>
         </is>
       </c>
       <c r="E130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6919,17 +6991,21 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>2022年4月2日（土）～2022年6月25日（土） TOKYO MXほか 【再放送】 2026年9月30日（水）〜 BS日テレにて</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>サンライズ</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=14120</t>
         </is>
       </c>
     </row>
@@ -6947,7 +7023,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LEGO® ONE PIECE</t>
+          <t>らんま1/2 第3期</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -6955,12 +7031,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026年9月29日（火） Netflixにて</t>
+          <t>2026年10月～ 日本テレビ系にて</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -6969,6 +7045,47 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>51</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LEGO® ONE PIECE</t>
+        </is>
+      </c>
+      <c r="E132" t="b">
+        <v>0</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>配信</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026年9月29日（火） Netflixにて</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28168</t>
         </is>
@@ -6985,7 +7102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7162,7 +7279,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>岩元先輩ノ推薦</t>
+          <t>いびってこない義母と義姉</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -7178,12 +7295,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BUDDING</t>
+          <t>雨宿りの憧憬</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>THE JET BOY BANGERZ</t>
+          <t>Lia</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -7205,7 +7322,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>岩元先輩ノ推薦</t>
+          <t>いびってこない義母と義姉</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -7221,12 +7338,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ココニイル</t>
+          <t>クレール</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WOLF HOWL HARMONY</t>
+          <t>AVAM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -7248,7 +7365,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>うしろの正面カムイさん</t>
+          <t>岩元先輩ノ推薦</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -7264,12 +7381,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>成仏Come true</t>
+          <t>BUDDING</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ORCALAND</t>
+          <t>THE JET BOY BANGERZ</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -7291,7 +7408,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>うしろの正面カムイさん</t>
+          <t>岩元先輩ノ推薦</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -7307,12 +7424,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SAY-BYE!!</t>
+          <t>ココニイル</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KOTOKO</t>
+          <t>WOLF HOWL HARMONY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -7334,7 +7451,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>うちの弟どもがすみません</t>
+          <t>うしろの正面カムイさん</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -7350,12 +7467,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>アイコトバ</t>
+          <t>成仏Come true</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DISH//</t>
+          <t>ORCALAND</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -7377,7 +7494,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>うちの弟どもがすみません</t>
+          <t>うしろの正面カムイさん</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -7393,12 +7510,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Clover</t>
+          <t>SAY-BYE!!</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>汐れいら</t>
+          <t>KOTOKO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -7420,7 +7537,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ウルトラマンテオ</t>
+          <t>うちの弟どもがすみません</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -7428,7 +7545,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -7436,12 +7553,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LINK HEARTS</t>
+          <t>アイコトバ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ASTRO DONUTS</t>
+          <t>DISH//</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -7463,7 +7580,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>乙女怪獣キャラメリゼ</t>
+          <t>うちの弟どもがすみません</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -7471,7 +7588,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -7479,12 +7596,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>乙女怪獣</t>
+          <t>Clover</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>METANICK</t>
+          <t>汐れいら</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -7506,7 +7623,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>乙女怪獣キャラメリゼ</t>
+          <t>ウルトラマンテオ</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -7514,7 +7631,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -7522,12 +7639,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>オトメノホンキ</t>
+          <t>LINK HEARTS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>HoneyWorks feat.ハコニワリリィ</t>
+          <t>ASTRO DONUTS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -7549,7 +7666,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>同じゼミの染谷さんがセクシー女優だった話。</t>
+          <t>乙女怪獣キャラメリゼ</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -7557,7 +7674,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -7565,12 +7682,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>未来コントレール</t>
+          <t>乙女怪獣</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>桜空もも</t>
+          <t>METANICK</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -7592,7 +7709,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+          <t>乙女怪獣キャラメリゼ</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -7600,7 +7717,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -7608,12 +7725,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>浪漫街道、お散歩中</t>
+          <t>オトメノホンキ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PelleK</t>
+          <t>HoneyWorks feat.ハコニワリリィ</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -7635,7 +7752,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+          <t>同じゼミの染谷さんがセクシー女優だった話。</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -7643,7 +7760,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -7651,12 +7768,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>奇跡は起きない</t>
+          <t>未来コントレール</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>桜空もも</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -7678,7 +7795,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>片田舎のおっさん、剣聖になるII</t>
+          <t>鬼の花嫁</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -7694,12 +7811,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>クレナイノハ</t>
+          <t>ヒトコト</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ユニコーン</t>
+          <t>ClariS</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -7721,7 +7838,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>片田舎のおっさん、剣聖になるII</t>
+          <t>鬼の花嫁</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -7737,12 +7854,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>未完成</t>
+          <t>心星</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BLUE ENCOUNT</t>
+          <t>山崎育三郎</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -7764,7 +7881,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>株式会社マジルミエ 第2期</t>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -7772,7 +7889,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -7780,12 +7897,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BooooM!!!</t>
+          <t>浪漫街道、お散歩中</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>宝鐘マリン</t>
+          <t>PelleK</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -7807,15 +7924,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です</t>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
         </is>
       </c>
       <c r="D19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -7823,12 +7940,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GET BACK</t>
+          <t>奇跡は起きない</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -7850,15 +7967,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です</t>
+          <t>片田舎のおっさん、剣聖になるII</t>
         </is>
       </c>
       <c r="D20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -7866,12 +7983,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6を撫でる</t>
+          <t>クレナイノハ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ももすももす</t>
+          <t>ユニコーン</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -7893,7 +8010,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>きみが死ぬまで恋をしたい</t>
+          <t>片田舎のおっさん、剣聖になるII</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -7901,7 +8018,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -7909,12 +8026,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Amore</t>
+          <t>未完成</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ReoNa</t>
+          <t>BLUE ENCOUNT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -7936,7 +8053,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>きみが死ぬまで恋をしたい</t>
+          <t>株式会社マジルミエ 第2期</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -7952,35 +8069,21 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>エテルネル</t>
+          <t>BooooM!!!</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>sajou no hana</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=1qcDcvE9lWc</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>1654</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>sajou no hana Official Channel</t>
-        </is>
-      </c>
+          <t>宝鐘マリン</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2026-06-14T18:14:57</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7993,11 +8096,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>帰還者の魔法は特別です</t>
         </is>
       </c>
       <c r="D23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -8009,12 +8112,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>いつかちゃんと。</t>
+          <t>GET BACK</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>りりあ。</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -8036,11 +8139,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>帰還者の魔法は特別です</t>
         </is>
       </c>
       <c r="D24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -8052,12 +8155,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>最終回</t>
+          <t>6を撫でる</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>sorato</t>
+          <t>ももすももす</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -8079,7 +8182,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>きみが死ぬまで恋をしたい</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -8095,12 +8198,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>夏子</t>
+          <t>Amore</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FUNKY MONKEY BΛBY'S</t>
+          <t>ReoNa</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -8122,7 +8225,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>きみが死ぬまで恋をしたい</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -8138,21 +8241,35 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>裸のマーメード</t>
+          <t>エテルネル</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>豆柴の大群</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>sajou no hana</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1qcDcvE9lWc</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1654</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>sajou no hana Official Channel</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-06-14T18:14:57</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -8165,7 +8282,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -8181,12 +8298,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Foreshadow</t>
+          <t>いつかちゃんと。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>前島麻由</t>
+          <t>りりあ。</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -8208,7 +8325,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -8224,12 +8341,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Awake Anew</t>
+          <t>最終回</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>sorato</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -8251,7 +8368,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>攻殻機動隊 THE GHOST IN THE SHELL</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -8259,7 +8376,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -8267,12 +8384,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>夏子</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MILLENNIUM PARADE feat. Saya Gray, Daniel Caesar</t>
+          <t>FUNKY MONKEY BΛBY'S</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -8294,7 +8411,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -8302,7 +8419,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -8310,12 +8427,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Running In My Head</t>
+          <t>裸のマーメード</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MIYAVI</t>
+          <t>豆柴の大群</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -8337,7 +8454,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -8345,7 +8462,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -8353,12 +8470,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ロゼ (Prod.TeddyLoid)</t>
+          <t>Foreshadow</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>満島ひかり</t>
+          <t>前島麻由</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -8380,7 +8497,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -8388,7 +8505,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -8396,12 +8513,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>遺書</t>
+          <t>Awake Anew</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>キタニタツヤ</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -8423,7 +8540,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>グロウアップショウ ～ひまわりのサーカス団～</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -8431,7 +8548,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -8439,12 +8556,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>コニファー</t>
+          <t>ユラリユレル</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>リーガルリリー</t>
+          <t>NOMELON NOLEMON</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -8466,7 +8583,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>グロウアップショウ ～ひまわりのサーカス団～</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -8474,7 +8591,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -8482,12 +8599,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>最最最高級のお世話して</t>
+          <t>DAYS!</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>angela</t>
+          <t>Aooo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -8509,7 +8626,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>攻殻機動隊 THE GHOST IN THE SHELL</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -8525,12 +8642,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>完璧じゃないわたし</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>前島亜美</t>
+          <t>MILLENNIUM PARADE feat. Saya Gray, Daniel Caesar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -8552,7 +8669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -8568,12 +8685,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>Running In My Head</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>杏子</t>
+          <t>MIYAVI</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -8595,7 +8712,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -8603,7 +8720,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -8611,12 +8728,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>ロゼ (Prod.TeddyLoid)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>満島ひかり</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -8638,7 +8755,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>サンダー３</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -8646,7 +8763,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -8654,12 +8771,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>しゅるれりら</t>
+          <t>遺書</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>音羽-otoha-</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -8681,7 +8798,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -8689,7 +8806,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -8697,12 +8814,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>イチジク煙</t>
+          <t>コニファー</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ずっと真夜中でいいのに。</t>
+          <t>リーガルリリー</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -8724,7 +8841,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -8732,7 +8849,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -8740,12 +8857,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>最最最高級のお世話して</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>angela</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -8767,7 +8884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -8775,7 +8892,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -8783,12 +8900,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>完璧じゃないわたし</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>INUWASI</t>
+          <t>前島亜美</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -8810,7 +8927,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -8818,7 +8935,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -8826,12 +8943,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -8853,11 +8970,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -8869,12 +8986,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>スノウドロップ</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Conton Candy</t>
+          <t>いきものがかり</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -8896,11 +9013,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>サンダー３</t>
         </is>
       </c>
       <c r="D44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -8912,12 +9029,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>水平線は僕の古傷</t>
+          <t>しゅるれりら</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+          <t>音羽-otoha-</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -8939,7 +9056,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -8955,12 +9072,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -8982,7 +9099,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -8990,20 +9107,20 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>猫じゃらし</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7co</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -9025,7 +9142,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -9033,7 +9150,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -9041,12 +9158,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -9068,7 +9185,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -9076,7 +9193,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -9084,12 +9201,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -9111,15 +9228,15 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -9127,12 +9244,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NEW GAME</t>
+          <t>スノウドロップ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>halca</t>
+          <t>Conton Candy</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -9154,15 +9271,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -9170,12 +9287,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>水平線は僕の古傷</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -9197,7 +9314,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -9213,12 +9330,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -9240,7 +9357,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -9248,20 +9365,20 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>猫じゃらし</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KI_EN</t>
+          <t>7co</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -9283,7 +9400,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -9291,7 +9408,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -9299,12 +9416,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -9326,7 +9443,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -9342,12 +9459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -9369,7 +9486,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -9377,7 +9494,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -9385,12 +9502,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>NEW GAME</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
+          <t>halca</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -9412,7 +9529,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -9428,12 +9545,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -9455,7 +9572,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -9471,12 +9588,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ひとひら</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>秦基博</t>
+          <t>原因は自分にある。</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -9498,7 +9615,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -9514,12 +9631,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>KI_EN</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -9541,7 +9658,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>トミカとトム</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -9549,7 +9666,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -9557,12 +9674,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>きみのたからもの</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>May J.</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -9584,7 +9701,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -9600,12 +9717,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -9627,7 +9744,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -9635,7 +9752,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -9643,12 +9760,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>SEKAI NO OWARI</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -9670,7 +9787,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -9686,12 +9803,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -9713,7 +9830,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -9721,20 +9838,20 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>To Be Continued</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -9756,7 +9873,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -9764,7 +9881,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -9772,12 +9889,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>ひとひら</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>秦基博</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9799,7 +9916,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -9811,16 +9928,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9842,7 +9959,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>トミカとトム</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -9850,7 +9967,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -9858,12 +9975,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>きみのたからもの</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>May J.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9885,7 +10002,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -9893,7 +10010,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -9901,12 +10018,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9928,7 +10045,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -9936,7 +10053,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -9944,12 +10061,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>Soarin’</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>Ginger Root</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9971,7 +10088,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -9979,7 +10096,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -9987,12 +10104,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>安保心結</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -10014,7 +10131,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -10030,12 +10147,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -10057,7 +10174,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -10065,20 +10182,20 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10100,7 +10217,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -10108,7 +10225,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -10116,12 +10233,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>milet</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10143,7 +10260,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -10151,20 +10268,20 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FREEZE ME UP</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SiM</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10186,7 +10303,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -10194,7 +10311,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -10202,12 +10319,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Groooovy</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>I Don't Like Mondays.</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10229,7 +10346,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -10237,7 +10354,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -10245,12 +10362,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10272,7 +10389,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -10288,12 +10405,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>○✕△□</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>浪漫派マシュマロ</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10315,7 +10432,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -10323,7 +10440,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -10331,12 +10448,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Blacker Co., Ltd.</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>イツカ▶</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10358,7 +10475,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -10366,7 +10483,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -10374,12 +10491,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Elegy of the Enemies</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>The Canbellz</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10401,7 +10518,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -10413,16 +10530,16 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>白い蝶が飛んだら</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10444,7 +10561,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -10460,12 +10577,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>milet</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10487,7 +10604,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -10495,7 +10612,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -10503,12 +10620,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>SiM</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10530,7 +10647,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -10538,7 +10655,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -10546,12 +10663,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>Groooovy</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>I Don't Like Mondays.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10573,7 +10690,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -10581,7 +10698,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -10589,12 +10706,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10616,7 +10733,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>文豪ストレイドッグス わん！２</t>
         </is>
       </c>
       <c r="D84" t="b">
@@ -10624,7 +10741,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -10632,12 +10749,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>僕ら～芥川龍之介Ver.～</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>芥川龍之介（CV.小野賢章）</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10659,7 +10776,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -10667,7 +10784,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -10675,12 +10792,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>浪漫派マシュマロ</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10702,7 +10819,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -10718,12 +10835,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Blacker Co., Ltd.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>イツカ▶</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10745,7 +10862,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -10761,12 +10878,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>Elegy of the Enemies</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
+          <t>The Canbellz</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10788,7 +10905,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -10796,20 +10913,20 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>白い蝶が飛んだら</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10831,7 +10948,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -10839,7 +10956,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -10847,12 +10964,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10874,7 +10991,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -10882,7 +10999,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -10890,12 +11007,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10917,7 +11034,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -10933,12 +11050,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Why? RED induction</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10960,7 +11077,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -10976,12 +11093,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Weiter! Weiter!</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11003,7 +11120,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -11019,12 +11136,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11046,7 +11163,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D94" t="b">
@@ -11054,20 +11171,20 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11089,7 +11206,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -11097,7 +11214,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -11105,12 +11222,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11132,7 +11249,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -11144,16 +11261,16 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>中島美嘉</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11175,7 +11292,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -11191,12 +11308,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11218,7 +11335,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -11234,12 +11351,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>冨岡愛</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11261,7 +11378,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -11277,12 +11394,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11304,7 +11421,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -11312,7 +11429,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -11320,12 +11437,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11347,7 +11464,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -11355,7 +11472,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -11363,12 +11480,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11390,7 +11507,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -11398,7 +11515,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -11406,12 +11523,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>REIRIE</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11433,7 +11550,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -11445,16 +11562,16 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11476,7 +11593,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D104" t="b">
@@ -11492,12 +11609,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ゆきむら。</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11519,7 +11636,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -11527,20 +11644,20 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11553,16 +11670,16 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D106" t="b">
@@ -11578,7 +11695,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sorrow</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11596,16 +11713,16 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -11613,7 +11730,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -11621,12 +11738,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>西川貴教</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11639,16 +11756,16 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D108" t="b">
@@ -11664,12 +11781,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11682,16 +11799,16 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -11707,12 +11824,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11725,16 +11842,16 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D110" t="b">
@@ -11750,12 +11867,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11766,6 +11883,436 @@
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>令和のダラさん</t>
+        </is>
+      </c>
+      <c r="D111" t="b">
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ひなたぼっこ</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>REIRIE</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="D112" t="b">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="D113" t="b">
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>ゆきむら。</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ワールド イズ ダンシング</t>
+        </is>
+      </c>
+      <c r="D114" t="b">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ONE PIECE HEROINES</t>
+        </is>
+      </c>
+      <c r="D115" t="b">
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>主題歌</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>ONE PIECE（モノクロ版）</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>電子書籍（コミック）</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>帰還者の魔法は特別です 第2期</t>
+        </is>
+      </c>
+      <c r="D116" t="b">
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Sorrow</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>獣王武神ダンデヴァイン</t>
+        </is>
+      </c>
+      <c r="D117" t="b">
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D118" t="b">
+        <v>0</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D119" t="b">
+        <v>0</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D120" t="b">
+        <v>0</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M132"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,10 +902,26 @@
           <t>ENGI</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>人生エンドロール</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ando</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>あしたはあしたのけせらせら！</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>名称非公開</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=19243</t>
@@ -1167,8 +1183,16 @@
           <t>J.C.STAFF</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ラテマジック</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>syudou×八木勇征(FANTASTICS)</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>BooooM!!!</t>
@@ -1725,7 +1749,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026年7月6日（月）～</t>
+          <t>2026年7月6日（月）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1733,10 +1757,26 @@
           <t>月虹</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>それでも曇天を越えてゆく</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>sajou no hana</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>在り来たりな日常と幸運な日々へ</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>名称非公開</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=26900</t>
@@ -1831,7 +1871,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026年7月～</t>
+          <t>2026年7月6日（月）～ TOKYO MX・BSフジにて</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1839,10 +1879,26 @@
           <t>MAHO FILM</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>BUDDiiS</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>素敵なかんちがい</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>くらわん</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28078</t>
@@ -1937,7 +1993,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026年夏</t>
+          <t>2026年7月19日（日）～ ABEMAプレミアム・dアニメストア・U-NEXTほか</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2336,10 +2392,26 @@
           <t>MAHO FILM</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>license</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Redhair Rosy</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>終わらない夜の守り方</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>インナージャーニー</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=26740</t>
@@ -2434,7 +2506,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX「5時に夢中！」にて</t>
+          <t>2026年7月1日（水）～ TOKYO MX「5時に夢中！」にて</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2497,8 +2569,16 @@
           <t>SPYAIR</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Lv.1 職業：⼈間</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ReoNa</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=24783</t>
@@ -3176,7 +3256,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3237,7 +3317,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3282,7 +3362,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3343,7 +3423,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3388,7 +3468,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3429,7 +3509,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3490,7 +3570,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3551,7 +3631,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3604,7 +3684,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3665,7 +3745,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3710,7 +3790,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3755,7 +3835,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3808,7 +3888,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3861,7 +3941,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3922,7 +4002,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3983,7 +4063,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4044,7 +4124,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4089,7 +4169,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4111,7 +4191,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>マジックバス×ピカンテサーカス</t>
+          <t>マジックバス</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4150,7 +4230,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4207,7 +4287,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4268,7 +4348,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4303,8 +4383,16 @@
           <t>忘れらんねえよ</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>煙とブルー</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>ネクライトーキー</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=27571</t>
@@ -4321,7 +4409,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4382,7 +4470,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4443,7 +4531,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4504,7 +4592,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4565,7 +4653,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4626,7 +4714,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4671,7 +4759,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4732,7 +4820,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4785,7 +4873,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -4818,23 +4906,23 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>アオアシ Season2</t>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="E82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4843,21 +4931,37 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ NHK Eテレにて</t>
+          <t>2020年10月3日（土）～2020年12月26日（土） TOKYO MXほか 【再放送】 2026年7月1日（水）〜 BS日テレにて</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
+          <t>サンライズ</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>虹色Passions！</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NEO SKY, NEO MAP!</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=9267</t>
         </is>
       </c>
     </row>
@@ -4871,11 +4975,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>アオのハコ 第2期</t>
+          <t>アオアシ Season2</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -4888,12 +4992,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ TBS系にて</t>
+          <t>2026年10月4日（日）～ NHK Eテレにて</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>エレクトリックサーカス</t>
+          <t>トムス・エンタテインメント</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4902,7 +5006,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
         </is>
       </c>
     </row>
@@ -4916,11 +5020,11 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
+          <t>アオのハコ 第2期</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -4933,12 +5037,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
+          <t>2026年10月4日（日）～ TBS系にて</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>キネマシトラス</t>
+          <t>エレクトリックサーカス</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4947,7 +5051,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
         </is>
       </c>
     </row>
@@ -4961,11 +5065,11 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>おじさんはカワイイものがお好き。</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -4978,29 +5082,21 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「＋Ultra」ほか</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>アルボアニメーション</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Sorrow</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>FLOW</t>
-        </is>
-      </c>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23327</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27078</t>
         </is>
       </c>
     </row>
@@ -5014,11 +5110,11 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>傷だらけ聖女より報復をこめて Season2</t>
+          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -5031,12 +5127,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
+          <t>キネマシトラス</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -5045,7 +5141,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
         </is>
       </c>
     </row>
@@ -5059,11 +5155,11 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>恐怖コレクター</t>
+          <t>貸した魔力は【リボ払い】で強制徴収</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -5076,17 +5172,21 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK総合にて</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>2026年10月～ テレビ朝日系ほか</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>SynergySP</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27102</t>
         </is>
       </c>
     </row>
@@ -5100,11 +5200,11 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
+          <t>帰還者の魔法は特別です 第2期</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -5117,21 +5217,29 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜 フジテレビ「＋Ultra」ほか</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>KONAMI animation</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+          <t>アルボアニメーション</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Sorrow</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23327</t>
         </is>
       </c>
     </row>
@@ -5145,11 +5253,11 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>薬屋のひとりごと 第3期</t>
+          <t>傷だらけ聖女より報復をこめて Season2</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -5162,17 +5270,21 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Imagica Infos</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
         </is>
       </c>
     </row>
@@ -5186,11 +5298,11 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ケロロ軍曹☆</t>
+          <t>恐怖コレクター</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -5203,7 +5315,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ NHK総合にて</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -5213,7 +5325,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
         </is>
       </c>
     </row>
@@ -5227,11 +5339,11 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>幻想水滸伝</t>
+          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -5247,14 +5359,18 @@
           <t>2026年10月～</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>KONAMI animation</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
         </is>
       </c>
     </row>
@@ -5268,11 +5384,11 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PSYREN -サイレン-</t>
+          <t>薬屋のひとりごと 第3期</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -5285,21 +5401,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>サテライト</t>
-        </is>
-      </c>
+          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
         </is>
       </c>
     </row>
@@ -5313,11 +5425,11 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ジャンケットバンク</t>
+          <t>ケロロ軍曹☆</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -5330,21 +5442,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>CUE</t>
-        </is>
-      </c>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
         </is>
       </c>
     </row>
@@ -5358,11 +5466,11 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>朱色の仮面</t>
+          <t>幻想水滸伝</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -5375,7 +5483,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -5385,7 +5493,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
         </is>
       </c>
     </row>
@@ -5399,11 +5507,11 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>PSYREN -サイレン-</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -5416,29 +5524,21 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月～ TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>曲名未発表</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>西川貴教</t>
-        </is>
-      </c>
+          <t>サテライト</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28479</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
         </is>
       </c>
     </row>
@@ -5452,11 +5552,11 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>しろたん</t>
+          <t>佐々木とピーちゃん シーズン２</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -5469,12 +5569,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>レスプリ</t>
+          <t>SILVER LINK.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5483,7 +5583,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23804</t>
         </is>
       </c>
     </row>
@@ -5497,11 +5597,11 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
+          <t>ジャンケットバンク</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -5514,17 +5614,21 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CUE</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
         </is>
       </c>
     </row>
@@ -5538,11 +5642,11 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>世界最強の魔女、始めました</t>
+          <t>朱色の仮面</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -5555,21 +5659,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>ブリッジ</t>
-        </is>
-      </c>
+          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
         </is>
       </c>
     </row>
@@ -5583,11 +5683,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>#ゾンビさがしてます</t>
+          <t>獣王武神ダンデヴァイン</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -5600,17 +5700,29 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026年10月〜 テレビ朝日系にて</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28479</t>
         </is>
       </c>
     </row>
@@ -5624,11 +5736,11 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>タヌキとキツネ</t>
+          <t>しろたん</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -5641,17 +5753,21 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>2026年10月～ テレビ朝日にて</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>レスプリ</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
         </is>
       </c>
     </row>
@@ -5665,11 +5781,11 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>TANK CHAIR-戦車椅子-</t>
+          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -5685,18 +5801,14 @@
           <t>2026年秋</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>ポリゴン・ピクチュアズ</t>
-        </is>
-      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
         </is>
       </c>
     </row>
@@ -5710,11 +5822,11 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>探偵はもう、死んでいる。Season2</t>
+          <t>世界最強の魔女、始めました</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -5727,12 +5839,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ENGI</t>
+          <t>ブリッジ</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5741,7 +5853,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
         </is>
       </c>
     </row>
@@ -5755,11 +5867,11 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>超巡！超条先輩</t>
+          <t>#ゾンビさがしてます</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -5772,21 +5884,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>アルボアニメーション</t>
-        </is>
-      </c>
+          <t>2026年10月〜 テレビ朝日系にて</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
         </is>
       </c>
     </row>
@@ -5800,11 +5908,11 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>追放されたチート付与魔術師は気ままなセカンドライフを謳歌する。</t>
+          <t>タヌキとキツネ</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -5817,21 +5925,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列にて</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>P.A.WORKS</t>
-        </is>
-      </c>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27631</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
         </is>
       </c>
     </row>
@@ -5845,11 +5949,11 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>てつりょー！meet with 鉄道むすめ</t>
+          <t>TANK CHAIR-戦車椅子-</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -5867,7 +5971,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>イーストフィッシュスタジオ</t>
+          <t>ポリゴン・ピクチュアズ</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -5876,7 +5980,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
         </is>
       </c>
     </row>
@@ -5890,11 +5994,11 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>テムパル～アイテムの力～</t>
+          <t>探偵はもう、死んでいる。Season2</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -5907,12 +6011,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>ENGI</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -5921,7 +6025,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
         </is>
       </c>
     </row>
@@ -5935,11 +6039,11 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
+          <t>超巡！超条先輩</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -5952,12 +6056,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
+          <t>2026年10月～ カンテレ・フジテレビ系全国ネットにて</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>studio MOTHER</t>
+          <t>アルボアニメーション</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -5966,7 +6070,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
         </is>
       </c>
     </row>
@@ -5980,11 +6084,11 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>転生ゴブリンだけど質問ある？</t>
+          <t>追放されたチート付与魔術師は気ままなセカンドライフを謳歌する。</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -5997,12 +6101,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月～ テレ東系列にて</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>BAKKKA</t>
+          <t>P.A.WORKS</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -6011,7 +6115,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27631</t>
         </is>
       </c>
     </row>
@@ -6025,11 +6129,11 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>てつりょー！meet with 鉄道むすめ</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -6042,37 +6146,21 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>FelixFilm</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Flare of Soul</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>STELLAR</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>ウタヒメドリーム オールスターズ</t>
-        </is>
-      </c>
+          <t>イーストフィッシュスタジオ</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
         </is>
       </c>
     </row>
@@ -6086,11 +6174,11 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>転生したら剣でした 第2期</t>
+          <t>テムパル～アイテムの力～</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -6108,7 +6196,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>C2C</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -6117,7 +6205,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
         </is>
       </c>
     </row>
@@ -6131,11 +6219,11 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>とある暗部の少女共棲</t>
+          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -6148,12 +6236,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>studio MOTHER</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -6162,7 +6250,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
         </is>
       </c>
     </row>
@@ -6176,11 +6264,11 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>東京リベンジャーズ 三天戦争編</t>
+          <t>転生ゴブリンだけど質問ある？</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -6193,12 +6281,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026年10月2日（金）～ MBS・TBS・CBC”アニメイズム”枠ほか</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
+          <t>BAKKKA</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -6207,7 +6295,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
         </is>
       </c>
     </row>
@@ -6221,11 +6309,11 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -6238,17 +6326,37 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>FelixFilm</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
         </is>
       </c>
     </row>
@@ -6262,11 +6370,11 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ドラゴンボール超 ビルス</t>
+          <t>転生したら剣でした 第2期</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -6279,17 +6387,21 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026年秋 フジテレビにて</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>C2C</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
         </is>
       </c>
     </row>
@@ -6303,11 +6415,11 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>鳴海の平日</t>
+          <t>とある暗部の少女共棲</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -6315,7 +6427,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6325,7 +6437,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Production I.G</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -6334,7 +6446,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
         </is>
       </c>
     </row>
@@ -6348,11 +6460,11 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>バーテックスフォース</t>
+          <t>東京リベンジャーズ 三天戦争編</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -6365,12 +6477,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月2日（金）～ MBS・TBS・CBC”アニメイズム”枠ほか</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>SMDE</t>
+          <t>ライデンフィルム</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6379,7 +6491,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
         </is>
       </c>
     </row>
@@ -6393,11 +6505,11 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Battle Spirits [Re] 絶界の空</t>
+          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -6410,7 +6522,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -6420,7 +6532,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
         </is>
       </c>
     </row>
@@ -6434,11 +6546,11 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>パンどろぼう</t>
+          <t>ドラゴンボール超 ビルス</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -6451,7 +6563,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026年10月〜 NHK Eテレにて</t>
+          <t>2026年秋 フジテレビにて</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -6461,7 +6573,7 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
         </is>
       </c>
     </row>
@@ -6475,11 +6587,11 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>百妖譜 京師篇</t>
+          <t>鳴海の平日</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -6487,22 +6599,26 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「B8station」にて</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Production I.G</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
         </is>
       </c>
     </row>
@@ -6516,11 +6632,11 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>冰剣の魔術師が世界を統べるⅡ</t>
+          <t>バーテックスフォース</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -6538,7 +6654,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>ゼロジー</t>
+          <t>SMDE</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6547,7 +6663,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
         </is>
       </c>
     </row>
@@ -6561,11 +6677,11 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ホタルの嫁入り</t>
+          <t>Battle Spirits [Re] 絶界の空</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -6578,21 +6694,17 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>david production</t>
-        </is>
-      </c>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
         </is>
       </c>
     </row>
@@ -6606,11 +6718,11 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ポップパップポルターズ</t>
+          <t>パンどろぼう</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -6623,21 +6735,17 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026年秋 テレビ朝日にて</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>MOZU STUDIOS</t>
-        </is>
-      </c>
+          <t>2026年10月〜 NHK Eテレにて</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
         </is>
       </c>
     </row>
@@ -6651,11 +6759,11 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ホテル・インヒューマンズ 第2期</t>
+          <t>百妖譜 京師篇</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -6668,21 +6776,17 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列ほか</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>ブリッジ</t>
-        </is>
-      </c>
+          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
         </is>
       </c>
     </row>
@@ -6696,11 +6800,11 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>マジカル★エクスプローラー</t>
+          <t>冰剣の魔術師が世界を統べるⅡ</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -6713,12 +6817,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>WHITE FOX</t>
+          <t>ゼロジー</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -6727,7 +6831,7 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
         </is>
       </c>
     </row>
@@ -6741,11 +6845,11 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>魔法騎士レイアース</t>
+          <t>ブラッククローバー 2nd Season</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -6758,12 +6862,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日系列にて</t>
+          <t>2026年10月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>E&amp;H production</t>
+          <t>スタジオぴえろ</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -6772,7 +6876,7 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26361</t>
         </is>
       </c>
     </row>
@@ -6786,11 +6890,11 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>ホタルの嫁入り</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -6803,29 +6907,21 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>SynergySP</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>No tears here</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
+          <t>david production</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
         </is>
       </c>
     </row>
@@ -6839,11 +6935,11 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>マロニエ王国の七人の騎士</t>
+          <t>ポップパップポルターズ</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -6856,12 +6952,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK Eテレにて</t>
+          <t>2026年10月～ テレビ朝日「PicoAniTime」にて</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>MOZU STUDIOS</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -6870,7 +6966,7 @@
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
         </is>
       </c>
     </row>
@@ -6884,11 +6980,11 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
+          <t>ホテル・インヒューマンズ 第2期</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -6901,12 +6997,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>studio A-CAT</t>
+          <t>ブリッジ</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6915,7 +7011,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
         </is>
       </c>
     </row>
@@ -6929,11 +7025,11 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+          <t>マジカル★エクスプローラー</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -6946,12 +7042,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>寿門堂</t>
+          <t>WHITE FOX</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -6960,7 +7056,7 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
         </is>
       </c>
     </row>
@@ -6974,15 +7070,15 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会 第2期</t>
+          <t>魔法騎士レイアース</t>
         </is>
       </c>
       <c r="E130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -6991,12 +7087,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2022年4月2日（土）～2022年6月25日（土） TOKYO MXほか 【再放送】 2026年9月30日（水）〜 BS日テレにて</t>
+          <t>2026年10月～ テレビ朝日系列にて</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>サンライズ</t>
+          <t>E&amp;H production</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -7005,7 +7101,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=14120</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
         </is>
       </c>
     </row>
@@ -7019,11 +7115,11 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>らんま1/2 第3期</t>
+          <t>魔法少女育成計画restart</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -7036,17 +7132,29 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>SynergySP</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
         </is>
       </c>
     </row>
@@ -7060,11 +7168,11 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LEGO® ONE PIECE</t>
+          <t>マロニエ王国の七人の騎士</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -7072,20 +7180,282 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026年9月29日（火） Netflixにて</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
+          <t>2026年10月～ NHK Eテレにて</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>51</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
+        </is>
+      </c>
+      <c r="E133" t="b">
+        <v>0</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>studio A-CAT</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>52</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ゆるゆる図鑑</t>
+        </is>
+      </c>
+      <c r="E134" t="b">
+        <v>0</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026年10月～ テレ東系列6局ネット「アニもり！」内にて</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28579</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>53</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+        </is>
+      </c>
+      <c r="E135" t="b">
+        <v>0</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>寿門堂</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>54</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会 第2期</t>
+        </is>
+      </c>
+      <c r="E136" t="b">
+        <v>1</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2022年4月2日（土）～2022年6月25日（土） TOKYO MXほか 【再放送】 2026年9月30日（水）〜 BS日テレにて</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>サンライズ</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=14120</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>55</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>らんま1/2 第3期</t>
+        </is>
+      </c>
+      <c r="E137" t="b">
+        <v>0</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026年10月～ 日本テレビ系にて</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>56</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LEGO® ONE PIECE</t>
+        </is>
+      </c>
+      <c r="E138" t="b">
+        <v>0</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>配信</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026年9月29日（火） Netflixにて</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28168</t>
         </is>
@@ -7102,7 +7472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7752,7 +8122,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>同じゼミの染谷さんがセクシー女優だった話。</t>
+          <t>乙女ゲー世界はモブに厳しい世界です2</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -7760,7 +8130,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -7768,12 +8138,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>未来コントレール</t>
+          <t>人生エンドロール</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>桜空もも</t>
+          <t>Ando</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -7795,7 +8165,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>鬼の花嫁</t>
+          <t>乙女ゲー世界はモブに厳しい世界です2</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -7803,7 +8173,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -7811,12 +8181,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ヒトコト</t>
+          <t>あしたはあしたのけせらせら！</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ClariS</t>
+          <t>名称非公開</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -7838,7 +8208,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>鬼の花嫁</t>
+          <t>同じゼミの染谷さんがセクシー女優だった話。</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -7846,7 +8216,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -7854,12 +8224,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>心星</t>
+          <t>未来コントレール</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>山崎育三郎</t>
+          <t>桜空もも</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -7881,7 +8251,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+          <t>鬼の花嫁</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -7897,12 +8267,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>浪漫街道、お散歩中</t>
+          <t>ヒトコト</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PelleK</t>
+          <t>ClariS</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -7924,7 +8294,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
+          <t>鬼の花嫁</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -7940,12 +8310,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>奇跡は起きない</t>
+          <t>心星</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>山崎育三郎</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -7967,7 +8337,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>片田舎のおっさん、剣聖になるII</t>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -7983,12 +8353,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>クレナイノハ</t>
+          <t>浪漫街道、お散歩中</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ユニコーン</t>
+          <t>PelleK</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -8010,7 +8380,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>片田舎のおっさん、剣聖になるII</t>
+          <t>骸骨騎士様、只今異世界へお出掛け中Ⅱ</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -8026,12 +8396,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未完成</t>
+          <t>奇跡は起きない</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BLUE ENCOUNT</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -8053,7 +8423,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>株式会社マジルミエ 第2期</t>
+          <t>片田舎のおっさん、剣聖になるII</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -8061,7 +8431,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -8069,12 +8439,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BooooM!!!</t>
+          <t>クレナイノハ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>宝鐘マリン</t>
+          <t>ユニコーン</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -8096,15 +8466,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です</t>
+          <t>片田舎のおっさん、剣聖になるII</t>
         </is>
       </c>
       <c r="D23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -8112,12 +8482,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>GET BACK</t>
+          <t>未完成</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>BLUE ENCOUNT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -8139,15 +8509,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です</t>
+          <t>株式会社マジルミエ 第2期</t>
         </is>
       </c>
       <c r="D24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -8155,12 +8525,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6を撫でる</t>
+          <t>ラテマジック</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ももすももす</t>
+          <t>syudou×八木勇征(FANTASTICS)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -8182,7 +8552,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>きみが死ぬまで恋をしたい</t>
+          <t>株式会社マジルミエ 第2期</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -8190,7 +8560,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -8198,12 +8568,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Amore</t>
+          <t>BooooM!!!</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ReoNa</t>
+          <t>宝鐘マリン</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -8225,15 +8595,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>きみが死ぬまで恋をしたい</t>
+          <t>帰還者の魔法は特別です</t>
         </is>
       </c>
       <c r="D26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -8241,35 +8611,21 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>エテルネル</t>
+          <t>GET BACK</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>sajou no hana</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=1qcDcvE9lWc</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>1654</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>sajou no hana Official Channel</t>
-        </is>
-      </c>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2026-06-14T18:14:57</t>
-        </is>
-      </c>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -8282,15 +8638,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>帰還者の魔法は特別です</t>
         </is>
       </c>
       <c r="D27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -8298,12 +8654,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>いつかちゃんと。</t>
+          <t>6を撫でる</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>りりあ。</t>
+          <t>ももすももす</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -8325,7 +8681,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
+          <t>きみが死ぬまで恋をしたい</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -8333,7 +8689,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -8341,12 +8697,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>最終回</t>
+          <t>Amore</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>sorato</t>
+          <t>ReoNa</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -8368,7 +8724,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>きみが死ぬまで恋をしたい</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -8376,7 +8732,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -8384,21 +8740,35 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>夏子</t>
+          <t>エテルネル</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>FUNKY MONKEY BΛBY'S</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>sajou no hana</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1qcDcvE9lWc</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1654</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>sajou no hana Official Channel</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-06-14T18:14:57</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -8411,7 +8781,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ぐらんぶる Season 3</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -8419,7 +8789,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -8427,12 +8797,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>裸のマーメード</t>
+          <t>いつかちゃんと。</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>豆柴の大群</t>
+          <t>りりあ。</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -8454,7 +8824,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>「きみを愛する気はない」と言った次期公爵様がなぜか溺愛してきます</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -8462,7 +8832,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -8470,12 +8840,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Foreshadow</t>
+          <t>最終回</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>前島麻由</t>
+          <t>sorato</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -8497,7 +8867,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -8505,7 +8875,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -8513,12 +8883,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Awake Anew</t>
+          <t>夏子</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>FUNKY MONKEY BΛBY'S</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -8540,7 +8910,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>グロウアップショウ ～ひまわりのサーカス団～</t>
+          <t>ぐらんぶる Season 3</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -8548,7 +8918,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -8556,12 +8926,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ユラリユレル</t>
+          <t>裸のマーメード</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NOMELON NOLEMON</t>
+          <t>豆柴の大群</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -8583,7 +8953,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>グロウアップショウ ～ひまわりのサーカス団～</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -8591,7 +8961,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -8599,12 +8969,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DAYS!</t>
+          <t>Foreshadow</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Aooo</t>
+          <t>前島麻由</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -8626,7 +8996,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>攻殻機動隊 THE GHOST IN THE SHELL</t>
+          <t>クレバテスII-魔獣の王と偽りの勇者伝承-</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -8642,12 +9012,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Awake Anew</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MILLENNIUM PARADE feat. Saya Gray, Daniel Caesar</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -8669,7 +9039,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>グロウアップショウ ～ひまわりのサーカス団～</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -8685,12 +9055,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Running In My Head</t>
+          <t>ユラリユレル</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MIYAVI</t>
+          <t>NOMELON NOLEMON</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -8712,7 +9082,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>コードギアス 奪還のロゼ TV放送</t>
+          <t>グロウアップショウ ～ひまわりのサーカス団～</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -8728,12 +9098,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ロゼ (Prod.TeddyLoid)</t>
+          <t>DAYS!</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>満島ひかり</t>
+          <t>Aooo</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -8755,7 +9125,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>攻殻機動隊 THE GHOST IN THE SHELL</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -8763,7 +9133,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -8771,12 +9141,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>遺書</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>キタニタツヤ</t>
+          <t>MILLENNIUM PARADE feat. Saya Gray, Daniel Caesar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -8798,7 +9168,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>これ描いて死ね</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -8806,7 +9176,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -8814,12 +9184,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>コニファー</t>
+          <t>Running In My Head</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>リーガルリリー</t>
+          <t>MIYAVI</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -8841,7 +9211,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>コードギアス 奪還のロゼ TV放送</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -8849,7 +9219,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -8857,12 +9227,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>最最最高級のお世話して</t>
+          <t>ロゼ (Prod.TeddyLoid)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>angela</t>
+          <t>満島ひかり</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -8884,7 +9254,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
+          <t>ここは俺に任せて先に行けと言ってから10年がたったら伝説になっていた。</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -8892,7 +9262,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -8900,12 +9270,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>完璧じゃないわたし</t>
+          <t>それでも曇天を越えてゆく</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>前島亜美</t>
+          <t>sajou no hana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -8927,7 +9297,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>サイボーグ009 ネメシス</t>
+          <t>ここは俺に任せて先に行けと言ってから10年がたったら伝説になっていた。</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -8935,7 +9305,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -8943,12 +9313,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>誰がために</t>
+          <t>在り来たりな日常と幸運な日々へ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>杏子</t>
+          <t>名称非公開</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -8970,7 +9340,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -8986,12 +9356,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>遺書</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
+          <t>キタニタツヤ</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -9013,7 +9383,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>サンダー３</t>
+          <t>これ描いて死ね</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -9029,12 +9399,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>しゅるれりら</t>
+          <t>コニファー</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>音羽-otoha-</t>
+          <t>リーガルリリー</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -9056,7 +9426,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>最強出涸らし皇子の暗躍帝位争い</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -9072,12 +9442,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>イチジク煙</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ずっと真夜中でいいのに。</t>
+          <t>BUDDiiS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -9099,7 +9469,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>最強出涸らし皇子の暗躍帝位争い</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -9115,12 +9485,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>素敵なかんちがい</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>くらわん</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -9142,7 +9512,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -9158,12 +9528,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>最最最高級のお世話して</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>INUWASI</t>
+          <t>angela</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -9185,7 +9555,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>才女のお世話 高嶺の花だらけな名門校で、学院一のお嬢様(生活能力皆無)を陰ながらお世話することになりました</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -9201,12 +9571,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>完璧じゃないわたし</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>前島亜美</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -9228,11 +9598,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -9244,12 +9614,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>スノウドロップ</t>
+          <t>誰がために</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Conton Candy</t>
+          <t>杏子</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -9271,15 +9641,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -9287,12 +9657,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>水平線は僕の古傷</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+          <t>いきものがかり</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -9314,7 +9684,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>サンダー３</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -9322,7 +9692,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -9330,12 +9700,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>しゅるれりら</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>乃紫</t>
+          <t>音羽-otoha-</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -9357,7 +9727,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -9369,16 +9739,16 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>猫じゃらし</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7co</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -9400,7 +9770,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -9416,12 +9786,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -9443,7 +9813,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -9459,12 +9829,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -9486,7 +9856,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -9502,12 +9872,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>NEW GAME</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>halca</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -9529,11 +9899,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -9545,12 +9915,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>スノウドロップ</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>Conton Candy</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -9572,15 +9942,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -9588,12 +9958,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>水平線は僕の古傷</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -9615,7 +9985,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -9623,7 +9993,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -9631,12 +10001,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>KI_EN</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -9658,7 +10028,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -9670,16 +10040,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>猫じゃらし</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>7co</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -9701,7 +10071,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -9709,7 +10079,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -9717,12 +10087,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>PAS TASTA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -9744,7 +10114,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -9760,12 +10130,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>license</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
+          <t>Redhair Rosy</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -9787,7 +10157,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -9795,7 +10165,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -9803,12 +10173,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>終わらない夜の守り方</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>インナージャーニー</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -9830,7 +10200,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -9838,7 +10208,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -9846,12 +10216,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>To Be Continued</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -9873,7 +10243,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -9881,7 +10251,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -9889,12 +10259,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ひとひら</t>
+          <t>NEW GAME</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>秦基博</t>
+          <t>halca</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9916,7 +10286,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -9924,7 +10294,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -9932,12 +10302,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9959,7 +10329,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>トミカとトム</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -9967,7 +10337,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -9975,12 +10345,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>きみのたからもの</t>
+          <t>Lv.1 職業：⼈間</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>May J.</t>
+          <t>ReoNa</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -10002,7 +10372,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -10018,12 +10388,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>原因は自分にある。</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -10045,7 +10415,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -10061,12 +10431,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Soarin’</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Ginger Root</t>
+          <t>KI_EN</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -10088,7 +10458,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -10096,7 +10466,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -10104,12 +10474,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -10131,7 +10501,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -10147,12 +10517,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>WANIMA</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -10174,7 +10544,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -10186,16 +10556,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>SEKAI NO OWARI</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10217,7 +10587,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -10225,7 +10595,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -10233,12 +10603,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10260,7 +10630,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -10272,16 +10642,16 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>To Be Continued</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10303,7 +10673,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -10319,12 +10689,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>ひとひら</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>秦基博</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10346,7 +10716,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -10362,12 +10732,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10389,7 +10759,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>トミカとトム</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -10397,7 +10767,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -10405,12 +10775,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>きみのたからもの</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+          <t>May J.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10432,7 +10802,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -10440,7 +10810,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -10448,12 +10818,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>五阿弥ルナ</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10475,7 +10845,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -10483,7 +10853,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -10491,12 +10861,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>Soarin’</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>Ginger Root</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10518,7 +10888,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -10526,7 +10896,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -10534,12 +10904,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
+          <t>安保心結</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10561,7 +10931,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -10577,12 +10947,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>milet</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10604,7 +10974,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -10616,16 +10986,16 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FREEZE ME UP</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>SiM</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10647,7 +11017,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -10663,12 +11033,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Groooovy</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>I Don't Like Mondays.</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10690,7 +11060,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -10698,20 +11068,20 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10733,7 +11103,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>文豪ストレイドッグス わん！２</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D84" t="b">
@@ -10741,7 +11111,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -10749,12 +11119,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>僕ら～芥川龍之介Ver.～</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>芥川龍之介（CV.小野賢章）</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10776,7 +11146,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -10784,7 +11154,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -10792,12 +11162,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>○✕△□</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>浪漫派マシュマロ</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10819,7 +11189,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -10835,12 +11205,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Blacker Co., Ltd.</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>イツカ▶</t>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10862,7 +11232,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -10878,12 +11248,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Elegy of the Enemies</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>The Canbellz</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10905,7 +11275,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -10913,20 +11283,20 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>白い蝶が飛んだら</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10948,7 +11318,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -10956,7 +11326,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -10964,12 +11334,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>大西亜玖璃</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10991,7 +11361,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -10999,7 +11369,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -11007,12 +11377,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>milet</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11034,7 +11404,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -11050,12 +11420,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
+          <t>SiM</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11077,7 +11447,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -11093,12 +11463,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Groooovy</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
+          <t>I Don't Like Mondays.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11120,7 +11490,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -11128,7 +11498,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -11136,12 +11506,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11163,7 +11533,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>文豪ストレイドッグス わん！２</t>
         </is>
       </c>
       <c r="D94" t="b">
@@ -11179,12 +11549,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>僕ら～芥川龍之介Ver.～</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>芥川龍之介（CV.小野賢章）</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11206,7 +11576,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -11222,12 +11592,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
+          <t>浪漫派マシュマロ</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11249,7 +11619,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -11257,7 +11627,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -11265,12 +11635,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>Blacker Co., Ltd.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
+          <t>イツカ▶</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11292,7 +11662,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -11300,7 +11670,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -11308,12 +11678,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>Elegy of the Enemies</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>The Canbellz</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11335,7 +11705,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -11347,16 +11717,16 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>白い蝶が飛んだら</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
+          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11378,7 +11748,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -11394,12 +11764,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>ももいろクローバーZ</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11421,7 +11791,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -11429,7 +11799,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -11437,12 +11807,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Why? RED induction</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11464,7 +11834,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -11472,7 +11842,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -11480,12 +11850,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Weiter! Weiter!</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11507,7 +11877,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -11515,7 +11885,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -11523,12 +11893,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>青木陽菜</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11550,7 +11920,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -11562,16 +11932,16 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11593,7 +11963,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D104" t="b">
@@ -11609,12 +11979,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11636,7 +12006,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -11644,20 +12014,20 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11679,7 +12049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D106" t="b">
@@ -11687,7 +12057,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -11695,12 +12065,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>中島美嘉</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11722,7 +12092,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -11730,7 +12100,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -11738,12 +12108,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11765,7 +12135,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D108" t="b">
@@ -11773,7 +12143,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -11781,12 +12151,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>冨岡愛</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11808,7 +12178,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -11816,7 +12186,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -11824,12 +12194,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11851,7 +12221,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D110" t="b">
@@ -11859,7 +12229,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -11867,12 +12237,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>煙とブルー</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>ネクライトーキー</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11894,7 +12264,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D111" t="b">
@@ -11902,7 +12272,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -11910,12 +12280,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>REIRIE</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11937,7 +12307,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D112" t="b">
@@ -11945,7 +12315,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -11953,12 +12323,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11980,7 +12350,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D113" t="b">
@@ -11988,7 +12358,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -11996,12 +12366,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>ゆきむら。</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12023,7 +12393,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D114" t="b">
@@ -12035,16 +12405,16 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12066,7 +12436,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ONE PIECE HEROINES</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D115" t="b">
@@ -12074,7 +12444,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -12082,12 +12452,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ONE PIECE（モノクロ版）</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>電子書籍（コミック）</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12100,16 +12470,16 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D116" t="b">
@@ -12117,20 +12487,20 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sorrow</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12143,16 +12513,16 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D117" t="b">
@@ -12168,12 +12538,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>西川貴教</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12186,16 +12556,16 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D118" t="b">
@@ -12203,7 +12573,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -12211,12 +12581,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12229,16 +12599,16 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D119" t="b">
@@ -12246,7 +12616,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -12254,12 +12624,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12272,16 +12642,16 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D120" t="b">
@@ -12289,7 +12659,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -12297,12 +12667,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>茅原実里</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12313,6 +12683,565 @@
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>令和のダラさん</t>
+        </is>
+      </c>
+      <c r="D121" t="b">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ダラダラ♡ダンシング</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>令和のダラさん</t>
+        </is>
+      </c>
+      <c r="D122" t="b">
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ひなたぼっこ</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>REIRIE</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="D123" t="b">
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>LV999の村人</t>
+        </is>
+      </c>
+      <c r="D124" t="b">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>ゆきむら。</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ワールド イズ ダンシング</t>
+        </is>
+      </c>
+      <c r="D125" t="b">
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ONE PIECE HEROINES</t>
+        </is>
+      </c>
+      <c r="D126" t="b">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>主題歌</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ONE PIECE（モノクロ版）</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>電子書籍（コミック）</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
+        </is>
+      </c>
+      <c r="D127" t="b">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>虹色Passions！</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
+        </is>
+      </c>
+      <c r="D128" t="b">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>NEO SKY, NEO MAP!</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>帰還者の魔法は特別です 第2期</t>
+        </is>
+      </c>
+      <c r="D129" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Sorrow</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>獣王武神ダンデヴァイン</t>
+        </is>
+      </c>
+      <c r="D130" t="b">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D131" t="b">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D132" t="b">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D133" t="b">
+        <v>0</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,67 +430,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>season_label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>is_rerun</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>broadcast_format</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>broadcast_start</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>animation_studio</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>op_title</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>op_artist</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ed_title</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ed_artist</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>detail_url</t>
         </is>
@@ -7476,77 +7488,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>season_label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>anime_title</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>is_rerun</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>song_title</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>artist</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>youtube_url</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>youtube_views</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>youtube_channel</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>anime_youtube_url</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>anime_youtube_views</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>anime_youtube_channel</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>last_searched_at</t>
         </is>
@@ -7587,13 +7599,37 @@
           <t>榊原ゆい</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KJkoRG38MXo</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>52344</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>アズールレーン</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bFCBwBCTCBU</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>26101</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:13:31</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -7845,13 +7881,37 @@
           <t>ORCALAND</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fI6BUhMXqKQ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>22060</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>デレギュラ【新アニメレーベル】</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fI6BUhMXqKQ</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>22060</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>デレギュラ【新アニメレーベル】</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:14:06</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7888,13 +7948,37 @@
           <t>KOTOKO</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mcFFaGYC9JU</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>20903</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>デレギュラ【新アニメレーベル】</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mcFFaGYC9JU</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>20903</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>デレギュラ【新アニメレーベル】</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:14:12</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7931,13 +8015,37 @@
           <t>DISH//</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8So8zgJAYMI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>6811</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8So8zgJAYMI</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>6811</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:14:24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7974,13 +8082,37 @@
           <t>汐れいら</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6fUdDUk-FZQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3487</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6fUdDUk-FZQ</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>3487</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:14:33</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8404,13 +8536,27 @@
           <t>DIALOGUE+</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YCCI6qrDhow</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>362547</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>DIALOGUE＋Official Channel</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:16:17</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8533,13 +8679,27 @@
           <t>syudou×八木勇征(FANTASTICS)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=46w2OsPayB4</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>13154</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>TVアニメ『株式会社マジルミエ』公式チャンネル</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:16:54</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -8576,13 +8736,37 @@
           <t>宝鐘マリン</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2_opjVlYhi4</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>16610711</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Marine Ch. 宝鐘マリン</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=R6oIaWuN0lk</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>223037</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>TVアニメ『株式会社マジルミエ』公式チャンネル</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:17:17</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -8754,7 +8938,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1654</v>
+        <v>1851</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -8766,7 +8950,7 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-06-14T18:14:57</t>
+          <t>2026-06-21T18:17:42</t>
         </is>
       </c>
     </row>
@@ -8934,13 +9118,37 @@
           <t>豆柴の大群</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_gLM5qjn5Hk</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>466412</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>NBCUniversal Anime/Music</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_gLM5qjn5Hk</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>466412</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>NBCUniversal Anime/Music</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:18:12</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -9063,13 +9271,37 @@
           <t>NOMELON NOLEMON</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IYW8Mfdzwfo</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>11744</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IYW8Mfdzwfo</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>11744</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:18:28</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -9106,13 +9338,37 @@
           <t>Aooo</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_HJ9d-6oNt4</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>13489</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_HJ9d-6oNt4</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>13489</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>アニプレックス チャンネル</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:18:33</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -9149,13 +9405,27 @@
           <t>MILLENNIUM PARADE feat. Saya Gray, Daniel Caesar</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fuXZMQAD9vU</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>12852008</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>MILLENNIUM PARADE Official YouTube Channel</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:19:08</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -9192,13 +9462,27 @@
           <t>MIYAVI</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0ym3Zj4kJyo</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>295392</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>コードギアスチャンネル CODEGEASS Channel</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:19:26</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -9235,13 +9519,27 @@
           <t>満島ひかり</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0ym3Zj4kJyo</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>295392</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>コードギアスチャンネル CODEGEASS Channel</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:19:43</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -9364,13 +9662,27 @@
           <t>キタニタツヤ</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MQhd0ne_uYo</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>6682341</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>キタニタツヤ / Tatsuya Kitani</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:20:22</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -9407,13 +9719,37 @@
           <t>リーガルリリー</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jI61NtGuxV4</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>42562</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>VAP Official</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GVgOmS-7xBg</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>145</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Anime Pulse Japan ⚡</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:20:33</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -9579,13 +9915,27 @@
           <t>前島亜美</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BnQf97HkufE</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>4032</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>前島亜美</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:21:04</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -9622,13 +9972,27 @@
           <t>杏子</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wc1Npu2_IFs</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>13236</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>杏子</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:21:26</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -9665,13 +10029,37 @@
           <t>いきものがかり</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c4-6PwVRRj8</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>305568</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c4-6PwVRRj8</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>305568</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:21:38</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -9751,13 +10139,37 @@
           <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ut889MZ9yNo</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>6309471</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ずっと真夜中でいいのに。 ZUTOMAYO</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OUmtsSroxns</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>594902</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Asmik Ace</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:21:56</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -9794,13 +10206,37 @@
           <t>imase</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9eo3M7-wAtU</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>867945</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Asmik Ace</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9eo3M7-wAtU</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>867945</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Asmik Ace</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:09</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -10009,13 +10445,37 @@
           <t>乃紫</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XOKQluw_YLU</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>3803168</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>乃紫</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>1711081</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:34</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -10052,13 +10512,37 @@
           <t>7co</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1711081</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>1711081</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:43</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -10095,13 +10579,37 @@
           <t>PAS TASTA</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A6aH9jPW8ZY</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>273328</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A6aH9jPW8ZY</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>273328</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:55</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -10439,13 +10947,37 @@
           <t>KI_EN</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>140125</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>140125</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:23:55</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10525,13 +11057,27 @@
           <t>七海ひろき</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qpFcQ1Bek08</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>69452</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>VAP Official</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:24:32</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10869,13 +11415,37 @@
           <t>Ginger Root</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>3207</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Lantis Channel</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>3207</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Lantis Channel</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:26:16</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10955,13 +11525,37 @@
           <t>WANIMA</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>402991</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>402991</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:26:31</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10998,13 +11592,37 @@
           <t>Chevon</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>174316</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>174316</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:26:42</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11041,13 +11659,37 @@
           <t>Novel Core</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>294329</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>294329</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:26:53</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11084,13 +11726,37 @@
           <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>25824</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>25824</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:27:05</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11299,13 +11965,27 @@
           <t>小倉唯</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LFS_qg2JrPI</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>11323</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Yui Ogura YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:27:45</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11342,13 +12022,27 @@
           <t>大西亜玖璃</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MzjYjMBpQ6g</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>4603</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>大西亜玖璃 - Aguri Onishi</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:27:58</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11385,13 +12079,27 @@
           <t>milet</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nR_vqhD2rGM</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>451401</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:28:12</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11858,13 +12566,27 @@
           <t>水樹奈々</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>590624</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:29:37</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11901,13 +12623,27 @@
           <t>青木陽菜</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>590624</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:29:56</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12030,13 +12766,37 @@
           <t>大原ゆい子</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hZ6TnKvB2rc</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>12105753</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>大原ゆい子Official YouTube</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PINgF6rCuME</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>2457533</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:30:35</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12073,13 +12833,27 @@
           <t>中島美嘉</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ODxfIvSgWuo</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>1140774</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:31:08</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12116,13 +12890,37 @@
           <t>家入レオ</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vJzWWkigrU8</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>32222</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>家入レオ</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5QGZX_Kky4I</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>27576</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>leafstamp</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:31:32</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12202,13 +13000,27 @@
           <t>忘れらんねえよ</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>480871</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:32:14</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12245,13 +13057,27 @@
           <t>ネクライトーキー</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>480871</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:32:32</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12288,13 +13114,27 @@
           <t>MYTH &amp; ROID</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RMaOR0Pyfts</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>50838</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>MYTH &amp; ROID Official Channel</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12374,13 +13214,37 @@
           <t>blank paper</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>603666</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>603666</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:22</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12417,13 +13281,27 @@
           <t>Dannie May</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>66350</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:34</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12460,13 +13338,37 @@
           <t>ONE OR EIGHT</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aw45Q_mr0_M</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>9441868</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>ONE OR EIGHT</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VJflo-z7e7A</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>151043</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:47</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12503,13 +13405,27 @@
           <t>カラノア</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>66350</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:34:00</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12804,13 +13720,27 @@
           <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9-RVzXLF53U</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>78910</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Itsuki Natsume / 棗いつき</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:35:08</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12890,13 +13820,37 @@
           <t>マカロニえんぴつ</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>262519</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
+        <v>262519</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:35:26</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12933,13 +13887,37 @@
           <t>電子書籍（コミック）</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6hRjsvdINgg</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>17920416</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>ONE PIECE Official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YFbno_aPm0w</t>
+        </is>
+      </c>
+      <c r="M126" t="n">
+        <v>27924515</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>ONE PIECE Official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:35:55</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13234,13 +14212,27 @@
           <t>茅原実里</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-PX7FqZ55tE</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>105042</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>TVアニメ「魔法少女育成計画restart」公式チャンネル</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:36:51</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TOKYO MXほか</t>
+          <t>2026年7月5日（日）〜 TOKYO MX・BS朝日ほか</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2076,8 +2076,16 @@
           <t>いきものがかり</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Hearts Glow</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Hana Hope</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=24070</t>
@@ -2730,7 +2738,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026年7月～ TOKYO MX・BSフジほか</t>
+          <t>2026年7月6日（月）～ TOKYO MX・BSフジほか</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2748,8 +2756,16 @@
           <t>DIALOGUE+</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Tilt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>harmoe</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=23374</t>
@@ -3460,8 +3476,16 @@
           <t>ニチカライン（</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>これはぼくたちの生存のあらすじ</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>夢限大みゅーたいぷ</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
@@ -3819,7 +3843,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026年7月～ テレ東系列ほか</t>
+          <t>2026年7月25日（土）～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3827,10 +3851,26 @@
           <t>PIERROT FILMS（</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>I-BULL</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>jo0ji</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>螺旋</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>9Lana</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=25417</t>
@@ -4031,7 +4071,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026年7月6日（月）～ TOKYO MX・MBS・BS11にて</t>
+          <t>2026年7月6日（月）～ TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4425,7 +4465,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>闇芝居 十七期</t>
         </is>
       </c>
       <c r="E73" t="b">
@@ -4438,37 +4478,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026年7月8日（水）～ AT-X・TOKYO MXほか</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>NUT</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Why? RED induction</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>MYTH &amp; ROID</t>
-        </is>
-      </c>
+          <t>2026年7月12日（日）～ テレ東にて</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Weiter! Weiter!</t>
+          <t>闇芝居のブルース</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
+          <t>風輪（徳間ジャパンコミュニケーションズ）</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28592</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4514,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="E74" t="b">
@@ -4499,37 +4527,37 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>第1クール：2026年1月6日（火）〜2026年3月24日（火） 第2クール：2026年7月7日（火）～ TOKYO MXほか</t>
+          <t>2026年7月8日（水）～ AT-X・TOKYO MXほか</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>サンライズ</t>
+          <t>NUT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=14369</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4575,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -4560,37 +4588,37 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ TOKYO MXほか</t>
+          <t>第1クール：2026年1月6日（火）〜2026年3月24日（火） 第2クール：2026年7月7日（火）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>EMTスクエアード</t>
+          <t>サンライズ</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>TrySail</t>
+          <t>ONE OR EIGHT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26202</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4636,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -4621,37 +4649,37 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026年7月10日（金）～ TOKYO MXほか</t>
+          <t>2026年7月1日（水）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>animation studio42</t>
+          <t>EMTスクエアード</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27769</t>
         </is>
       </c>
     </row>
@@ -4669,11 +4697,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="E77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4682,37 +4710,37 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ AT-X・TOKYO MXほか</t>
+          <t>2020年10月3日（土）～2020年12月26日（土） TOKYO MXほか 【再放送】 2026年7月1日（水）〜 BS日テレにて</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>旭プロダクション</t>
+          <t>サンライズ</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>虹色Passions！</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>NEO SKY, NEO MAP!</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>REIRIE</t>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=9267</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4758,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>レッツゴー怪奇組</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -4743,21 +4771,37 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026年7月5日（日）〜 TBS系全国28局ネットにて</t>
+          <t>2026年7月10日（金）～ TOKYO MXほか</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>C-Station</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
+          <t>animation studio42</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Wonder</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>CROWN HEAD</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>星降る夜の約束</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28373</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26472</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4819,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -4788,37 +4832,37 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026年7月1日（水）～ テレ東ほか</t>
+          <t>2026年7月2日（木）～ AT-X・TOKYO MXほか</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ブレインズ・ベース</t>
+          <t>旭プロダクション</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ひなたぼっこ</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>ゆきむら。</t>
+          <t>REIRIE</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27242</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4880,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>レッツゴー怪奇組</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -4849,29 +4893,21 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
+          <t>2026年7月5日（日）〜 TBS系全国28局ネットにて</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>サイピク</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>終宵</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>マカロニえんぴつ</t>
-        </is>
-      </c>
+          <t>C-Station</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28373</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4925,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ONE PIECE HEROINES</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -4902,17 +4938,37 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+          <t>2026年7月1日（水）～ テレ東ほか</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ブレインズ・ベース</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Not a Hero</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>ゆきむら。</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26648</t>
         </is>
       </c>
     </row>
@@ -4930,11 +4986,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="E82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4943,55 +4999,47 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2020年10月3日（土）～2020年12月26日（土） TOKYO MXほか 【再放送】 2026年7月1日（水）〜 BS日テレにて</t>
+          <t>2026年7月2日（木）～ TOKYO MX・BS朝日ほか</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>サンライズ</t>
+          <t>サイピク</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>虹色Passions！</t>
+          <t>終宵</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>虹ヶ咲学園スクールアイドル同好会</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>NEO SKY, NEO MAP!</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>虹ヶ咲学園スクールアイドル同好会</t>
-        </is>
-      </c>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=9267</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27472</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>アオアシ Season2</t>
+          <t>ONE PIECE HEROINES</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -5004,21 +5052,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ NHK Eテレにて</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>トムス・エンタテインメント</t>
-        </is>
-      </c>
+          <t>2026年7月5日（日） 全国フジテレビ系にて</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26606</t>
         </is>
       </c>
     </row>
@@ -5032,11 +5076,11 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>アオのハコ 第2期</t>
+          <t>アオアシ Season2</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -5049,12 +5093,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026年10月4日（日）～ TBS系にて</t>
+          <t>2026年10月4日（日）～ NHK Eテレにて</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>エレクトリックサーカス</t>
+          <t>トムス・エンタテインメント</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -5063,7 +5107,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25889</t>
         </is>
       </c>
     </row>
@@ -5077,11 +5121,11 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>おじさんはカワイイものがお好き。</t>
+          <t>アオのハコ 第2期</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -5094,12 +5138,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月4日（日）～ TBS系にて</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
+          <t>エレクトリックサーカス</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -5108,7 +5152,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27078</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25746</t>
         </is>
       </c>
     </row>
@@ -5122,11 +5166,11 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
+          <t>おじさんはカワイイものがお好き。</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -5139,12 +5183,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>キネマシトラス</t>
+          <t>ライデンフィルム</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -5153,7 +5197,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27078</t>
         </is>
       </c>
     </row>
@@ -5167,11 +5211,11 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>貸した魔力は【リボ払い】で強制徴収</t>
+          <t>カードファイト!! ヴァンガード Divinez 運命星戦編</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -5184,12 +5228,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日系ほか</t>
+          <t>2026年11月7日（土）～2026年11月21日（土） テレビ愛知・テレ東系列6局ネットほか 【劇場先行】 2026年10月2日（金）</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SynergySP</t>
+          <t>キネマシトラス</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -5198,7 +5242,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27102</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28214</t>
         </is>
       </c>
     </row>
@@ -5212,11 +5256,11 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>貸した魔力は【リボ払い】で強制徴収</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -5229,29 +5273,21 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「＋Ultra」ほか</t>
+          <t>2026年10月～ テレビ朝日系ほか</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>アルボアニメーション</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Sorrow</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>FLOW</t>
-        </is>
-      </c>
+          <t>SynergySP</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23327</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27102</t>
         </is>
       </c>
     </row>
@@ -5265,11 +5301,11 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>傷だらけ聖女より報復をこめて Season2</t>
+          <t>帰還者の魔法は特別です 第2期</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -5282,21 +5318,29 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月〜 フジテレビ「＋Ultra」ほか</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Imagica Infos</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>アルボアニメーション</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sorrow</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23327</t>
         </is>
       </c>
     </row>
@@ -5310,11 +5354,11 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>恐怖コレクター</t>
+          <t>傷だらけ聖女より報復をこめて Season2</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -5327,17 +5371,21 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK総合にて</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Imagica Infos</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25118</t>
         </is>
       </c>
     </row>
@@ -5351,11 +5399,11 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
+          <t>恐怖コレクター</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -5368,21 +5416,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>KONAMI animation</t>
-        </is>
-      </c>
+          <t>2026年10月～ NHK総合にて</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27214</t>
         </is>
       </c>
     </row>
@@ -5396,11 +5440,11 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>薬屋のひとりごと 第3期</t>
+          <t>凶乱令嬢ニア・リストン 病弱令嬢に転生した神殺しの武人の華麗なる無双録</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -5413,17 +5457,21 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>KONAMI animation</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27537</t>
         </is>
       </c>
     </row>
@@ -5437,11 +5485,11 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ケロロ軍曹☆</t>
+          <t>薬屋のひとりごと 第3期</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -5454,7 +5502,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>第1クール：2026年10月～ 第2クール：2027年4月～ 日本テレビ系にて</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -5464,7 +5512,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26369</t>
         </is>
       </c>
     </row>
@@ -5478,11 +5526,11 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>幻想水滸伝</t>
+          <t>ケロロ軍曹☆</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -5495,7 +5543,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -5505,7 +5553,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27337</t>
         </is>
       </c>
     </row>
@@ -5519,11 +5567,11 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PSYREN -サイレン-</t>
+          <t>幻想水滸伝</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -5536,21 +5584,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026年10月～ TOKYO MX・BS11ほか</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>サテライト</t>
-        </is>
-      </c>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25616</t>
         </is>
       </c>
     </row>
@@ -5564,11 +5608,11 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>佐々木とピーちゃん シーズン２</t>
+          <t>PSYREN -サイレン-</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -5581,12 +5625,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月～ TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>SILVER LINK.</t>
+          <t>サテライト</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5595,7 +5639,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23804</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27257</t>
         </is>
       </c>
     </row>
@@ -5609,11 +5653,11 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ジャンケットバンク</t>
+          <t>佐々木とピーちゃん シーズン２</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -5631,7 +5675,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CUE</t>
+          <t>SILVER LINK.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5640,7 +5684,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23804</t>
         </is>
       </c>
     </row>
@@ -5654,11 +5698,11 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>朱色の仮面</t>
+          <t>ジャンケットバンク</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -5671,17 +5715,21 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>CUE</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27908</t>
         </is>
       </c>
     </row>
@@ -5695,11 +5743,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>朱色の仮面</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -5712,29 +5760,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>ライデンフィルム</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>曲名未発表</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>西川貴教</t>
-        </is>
-      </c>
+          <t>2026年10月～ 読売テレビ・日本テレビ系全国ネットにて</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28479</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26362</t>
         </is>
       </c>
     </row>
@@ -5748,11 +5784,11 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>しろたん</t>
+          <t>獣王武神ダンデヴァイン</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -5765,21 +5801,29 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日にて</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>レスプリ</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28479</t>
         </is>
       </c>
     </row>
@@ -5793,11 +5837,11 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
+          <t>しろたん</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -5810,17 +5854,21 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>2026年10月～ テレビ朝日にて</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>レスプリ</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27989</t>
         </is>
       </c>
     </row>
@@ -5834,11 +5882,11 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>世界最強の魔女、始めました</t>
+          <t>新テニスの王子様 U-17 WORLD CUP 決勝メンバー決定戦</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -5851,21 +5899,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>ブリッジ</t>
-        </is>
-      </c>
+          <t>2026年秋</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26829</t>
         </is>
       </c>
     </row>
@@ -5879,11 +5923,11 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>#ゾンビさがしてます</t>
+          <t>世界最強の魔女、始めました</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -5896,17 +5940,21 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026年10月〜 テレビ朝日系にて</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>ブリッジ</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28288</t>
         </is>
       </c>
     </row>
@@ -5920,11 +5968,11 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>タヌキとキツネ</t>
+          <t>#ゾンビさがしてます</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -5937,7 +5985,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜 テレビ朝日系にて</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -5947,7 +5995,7 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26825</t>
         </is>
       </c>
     </row>
@@ -5961,11 +6009,11 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>TANK CHAIR-戦車椅子-</t>
+          <t>タヌキとキツネ</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -5978,21 +6026,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026年秋</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>ポリゴン・ピクチュアズ</t>
-        </is>
-      </c>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=6380</t>
         </is>
       </c>
     </row>
@@ -6006,11 +6050,11 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>探偵はもう、死んでいる。Season2</t>
+          <t>TANK CHAIR-戦車椅子-</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -6023,12 +6067,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ENGI</t>
+          <t>ポリゴン・ピクチュアズ</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -6037,7 +6081,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27965</t>
         </is>
       </c>
     </row>
@@ -6051,11 +6095,11 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>超巡！超条先輩</t>
+          <t>探偵はもう、死んでいる。Season2</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -6068,12 +6112,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026年10月～ カンテレ・フジテレビ系全国ネットにて</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>アルボアニメーション</t>
+          <t>ENGI</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -6082,7 +6126,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=16348</t>
         </is>
       </c>
     </row>
@@ -6096,11 +6140,11 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>追放されたチート付与魔術師は気ままなセカンドライフを謳歌する。</t>
+          <t>超巡！超条先輩</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -6113,12 +6157,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列にて</t>
+          <t>2026年10月～ カンテレ・フジテレビ系全国ネットにて</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>P.A.WORKS</t>
+          <t>アルボアニメーション</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -6127,7 +6171,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27631</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26933</t>
         </is>
       </c>
     </row>
@@ -6141,11 +6185,11 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>てつりょー！meet with 鉄道むすめ</t>
+          <t>追放されたチート付与魔術師は気ままなセカンドライフを謳歌する。</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -6158,12 +6202,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレ東系列にて</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>イーストフィッシュスタジオ</t>
+          <t>P.A.WORKS</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -6172,7 +6216,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27631</t>
         </is>
       </c>
     </row>
@@ -6186,11 +6230,11 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>テムパル～アイテムの力～</t>
+          <t>てつりょー！meet with 鉄道むすめ</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -6203,12 +6247,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>イーストフィッシュスタジオ</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -6217,7 +6261,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26895</t>
         </is>
       </c>
     </row>
@@ -6231,11 +6275,11 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
+          <t>テムパル～アイテムの力～</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -6248,12 +6292,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>studio MOTHER</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -6262,7 +6306,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28478</t>
         </is>
       </c>
     </row>
@@ -6276,11 +6320,11 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>転生ゴブリンだけど質問ある？</t>
+          <t>転生貴族、鑑定スキルで成り上がる 第3期</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -6293,12 +6337,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年秋 CBC/TBS系全国28局ネット「アガルアニメ」にて</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>BAKKKA</t>
+          <t>studio MOTHER</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -6307,7 +6351,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25385</t>
         </is>
       </c>
     </row>
@@ -6321,11 +6365,11 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>転生ゴブリンだけど質問ある？</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -6343,32 +6387,16 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>FelixFilm</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Flare of Soul</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>STELLAR</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>ウタヒメドリーム オールスターズ</t>
-        </is>
-      </c>
+          <t>BAKKKA</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27909</t>
         </is>
       </c>
     </row>
@@ -6382,11 +6410,11 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>転生したら剣でした 第2期</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -6404,16 +6432,32 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>C2C</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
+          <t>FelixFilm</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25630</t>
         </is>
       </c>
     </row>
@@ -6427,11 +6471,11 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>とある暗部の少女共棲</t>
+          <t>転生したら剣でした 第2期</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -6444,12 +6488,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>C2C</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -6458,7 +6502,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=19149</t>
         </is>
       </c>
     </row>
@@ -6472,11 +6516,11 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>東京リベンジャーズ 三天戦争編</t>
+          <t>とある暗部の少女共棲</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -6489,12 +6533,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026年10月2日（金）～ MBS・TBS・CBC”アニメイズム”枠ほか</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ライデンフィルム</t>
+          <t>J.C.STAFF</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -6503,7 +6547,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25552</t>
         </is>
       </c>
     </row>
@@ -6517,11 +6561,11 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
+          <t>東京リベンジャーズ 三天戦争編</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -6534,17 +6578,21 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>2026年10月2日（金）～ MBS・TBS・CBC”アニメイズム”枠ほか</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>ライデンフィルム</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24207</t>
         </is>
       </c>
     </row>
@@ -6558,11 +6606,11 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ドラゴンボール超 ビルス</t>
+          <t>桃源暗鬼 ～日光・華厳の滝編～</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -6575,7 +6623,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026年秋 フジテレビにて</t>
+          <t>2026年10月～ 日本テレビ系「FRIDAY ANIME NIGHT（フラアニ）」枠にて</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -6585,7 +6633,7 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27376</t>
         </is>
       </c>
     </row>
@@ -6599,11 +6647,11 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>鳴海の平日</t>
+          <t>どうも、好きな人に惚れ薬を依頼された魔女です。</t>
         </is>
       </c>
       <c r="E119" t="b">
@@ -6611,17 +6659,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Production I.G</t>
+          <t>ディオメディア</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -6630,7 +6678,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27581</t>
         </is>
       </c>
     </row>
@@ -6644,11 +6692,11 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>バーテックスフォース</t>
+          <t>ドラゴンボール超 ビルス</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -6661,21 +6709,17 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>SMDE</t>
-        </is>
-      </c>
+          <t>2026年秋 フジテレビにて</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27491</t>
         </is>
       </c>
     </row>
@@ -6689,11 +6733,11 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Battle Spirits [Re] 絶界の空</t>
+          <t>鳴海の平日</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -6701,7 +6745,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>TVアニメ</t>
+          <t>配信</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -6709,14 +6753,18 @@
           <t>2026年秋</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Production I.G</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28465</t>
         </is>
       </c>
     </row>
@@ -6730,11 +6778,11 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>パンどろぼう</t>
+          <t>バーテックスフォース</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -6747,17 +6795,21 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026年10月〜 NHK Eテレにて</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>2026年10月〜</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>SMDE</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27988</t>
         </is>
       </c>
     </row>
@@ -6771,11 +6823,11 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>百妖譜 京師篇</t>
+          <t>Battle Spirits [Re] 絶界の空</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -6788,7 +6840,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -6798,7 +6850,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27954</t>
         </is>
       </c>
     </row>
@@ -6812,11 +6864,11 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>冰剣の魔術師が世界を統べるⅡ</t>
+          <t>パンどろぼう</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -6829,21 +6881,17 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>ゼロジー</t>
-        </is>
-      </c>
+          <t>2026年10月〜 NHK Eテレにて</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26163</t>
         </is>
       </c>
     </row>
@@ -6857,11 +6905,11 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ブラッククローバー 2nd Season</t>
+          <t>百妖譜 京師篇</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -6874,21 +6922,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列ほか</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>スタジオぴえろ</t>
-        </is>
-      </c>
+          <t>2026年10月〜 フジテレビ「B8station」にて</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26361</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27781</t>
         </is>
       </c>
     </row>
@@ -6902,11 +6946,11 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ホタルの嫁入り</t>
+          <t>冰剣の魔術師が世界を統べるⅡ</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -6919,12 +6963,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>david production</t>
+          <t>ゼロジー</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -6933,7 +6977,7 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28403</t>
         </is>
       </c>
     </row>
@@ -6947,11 +6991,11 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ポップパップポルターズ</t>
+          <t>ブラッククローバー 2nd Season</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -6964,12 +7008,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日「PicoAniTime」にて</t>
+          <t>2026年10月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>MOZU STUDIOS</t>
+          <t>スタジオぴえろ</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -6978,7 +7022,7 @@
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26361</t>
         </is>
       </c>
     </row>
@@ -6992,11 +7036,11 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ホテル・インヒューマンズ 第2期</t>
+          <t>ホタルの嫁入り</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -7009,12 +7053,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列ほか</t>
+          <t>2026年10月～ 全国フジテレビ系“ ノイタミナ ”にて</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ブリッジ</t>
+          <t>david production</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -7023,7 +7067,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27415</t>
         </is>
       </c>
     </row>
@@ -7037,11 +7081,11 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>マジカル★エクスプローラー</t>
+          <t>ポップパップポルターズ</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -7054,12 +7098,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026年秋</t>
+          <t>2026年10月～ テレビ朝日「PicoAniTime」にて</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>WHITE FOX</t>
+          <t>MOZU STUDIOS</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -7068,7 +7112,7 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=27823</t>
         </is>
       </c>
     </row>
@@ -7082,11 +7126,11 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>魔法騎士レイアース</t>
+          <t>ホテル・インヒューマンズ 第2期</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -7099,12 +7143,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026年10月～ テレビ朝日系列にて</t>
+          <t>2026年10月～ テレ東系列ほか</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>E&amp;H production</t>
+          <t>ブリッジ</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -7113,7 +7157,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26870</t>
         </is>
       </c>
     </row>
@@ -7127,11 +7171,11 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>マジカル★エクスプローラー</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -7149,24 +7193,16 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>SynergySP</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>No tears here</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
+          <t>WHITE FOX</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=23375</t>
         </is>
       </c>
     </row>
@@ -7180,11 +7216,11 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>マロニエ王国の七人の騎士</t>
+          <t>魔法騎士レイアース</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -7197,12 +7233,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026年10月～ NHK Eテレにて</t>
+          <t>2026年10月～ テレビ朝日系列にて</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>J.C.STAFF</t>
+          <t>E&amp;H production</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -7211,7 +7247,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=24301</t>
         </is>
       </c>
     </row>
@@ -7225,11 +7261,11 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
+          <t>魔法少女育成計画restart</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -7242,21 +7278,29 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年秋</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>studio A-CAT</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
+          <t>SynergySP</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26693</t>
         </is>
       </c>
     </row>
@@ -7270,11 +7314,11 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ゆるゆる図鑑</t>
+          <t>マロニエ王国の七人の騎士</t>
         </is>
       </c>
       <c r="E134" t="b">
@@ -7287,17 +7331,21 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026年10月～ テレ東系列6局ネット「アニもり！」内にて</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>2026年10月～ NHK Eテレにて</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>J.C.STAFF</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28579</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28456</t>
         </is>
       </c>
     </row>
@@ -7311,11 +7359,11 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
+          <t>目覚めたら最強装備と宇宙船持ちだったので、一戸建て目指して傭兵として自由に生きたい</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -7328,12 +7376,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026年10月～</t>
+          <t>2026年10月〜</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>寿門堂</t>
+          <t>studio A-CAT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -7342,7 +7390,7 @@
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=25525</t>
         </is>
       </c>
     </row>
@@ -7356,15 +7404,15 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会 第2期</t>
+          <t>ゆるゆる図鑑</t>
         </is>
       </c>
       <c r="E136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -7373,21 +7421,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2022年4月2日（土）～2022年6月25日（土） TOKYO MXほか 【再放送】 2026年9月30日（水）〜 BS日テレにて</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>サンライズ</t>
-        </is>
-      </c>
+          <t>2026年10月～ テレ東系列6局ネット「アニもり！」内にて</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=14120</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=28579</t>
         </is>
       </c>
     </row>
@@ -7401,11 +7445,11 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>らんま1/2 第3期</t>
+          <t>弱気MAX令嬢なのに、辣腕婚約者様の賭けに乗ってしまった</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -7418,17 +7462,21 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026年10月～ 日本テレビ系にて</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
+          <t>2026年10月～</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>寿門堂</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+          <t>https://www.animatetimes.com/tag/details.php?id=26947</t>
         </is>
       </c>
     </row>
@@ -7442,32 +7490,118 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LEGO® ONE PIECE</t>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会 第2期</t>
         </is>
       </c>
       <c r="E138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>配信</t>
+          <t>TVアニメ</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026年9月29日（火） Netflixにて</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr"/>
+          <t>2022年4月2日（土）～2022年6月25日（土） TOKYO MXほか 【再放送】 2026年9月30日（水）〜 BS日テレにて</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>サンライズ</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=14120</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>56</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>らんま1/2 第3期</t>
+        </is>
+      </c>
+      <c r="E139" t="b">
+        <v>0</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>TVアニメ</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026年10月～ 日本テレビ系にて</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>https://www.animatetimes.com/tag/details.php?id=28013</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>57</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LEGO® ONE PIECE</t>
+        </is>
+      </c>
+      <c r="E140" t="b">
+        <v>0</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>配信</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026年9月29日（火） Netflixにて</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=28168</t>
         </is>
@@ -7484,7 +7618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O133"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10072,7 +10206,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>サンダー３</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -10088,12 +10222,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>しゅるれりら</t>
+          <t>Hearts Glow</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>音羽-otoha-</t>
+          <t>Hana Hope</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -10115,7 +10249,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>サンダー３</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -10123,7 +10257,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -10131,45 +10265,21 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>イチジク煙</t>
+          <t>しゅるれりら</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ずっと真夜中でいいのに。</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ut889MZ9yNo</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>6309471</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>ずっと真夜中でいいのに。 ZUTOMAYO</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=OUmtsSroxns</t>
-        </is>
-      </c>
-      <c r="M52" t="n">
-        <v>594902</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Asmik Ace</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:21:56</t>
-        </is>
-      </c>
+          <t>音羽-otoha-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -10190,7 +10300,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -10198,43 +10308,43 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9eo3M7-wAtU</t>
+          <t>https://www.youtube.com/watch?v=ut889MZ9yNo</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>867945</v>
+        <v>6309471</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t>ずっと真夜中でいいのに。 ZUTOMAYO</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OUmtsSroxns</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>594902</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>Asmik Ace</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9eo3M7-wAtU</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
-        <v>867945</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Asmik Ace</t>
-        </is>
-      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-06-21T18:22:09</t>
+          <t>2026-06-21T18:21:56</t>
         </is>
       </c>
     </row>
@@ -10249,7 +10359,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -10257,7 +10367,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -10265,21 +10375,45 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>INUWASI</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+          <t>imase</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9eo3M7-wAtU</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>867945</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Asmik Ace</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9eo3M7-wAtU</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>867945</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Asmik Ace</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:09</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -10300,7 +10434,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -10308,12 +10442,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -10335,15 +10469,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -10351,12 +10485,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>スノウドロップ</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Conton Candy</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -10386,7 +10520,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -10394,12 +10528,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>水平線は僕の古傷</t>
+          <t>スノウドロップ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+          <t>Conton Candy</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -10421,15 +10555,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -10437,45 +10571,21 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>水平線は僕の古傷</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>乃紫</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=XOKQluw_YLU</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>3803168</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>乃紫</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
-        </is>
-      </c>
-      <c r="M58" t="n">
-        <v>1711081</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>SHOCHIKU anime Channel</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:22:34</t>
-        </is>
-      </c>
+          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -10500,29 +10610,29 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>猫じゃらし</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>7co</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
+          <t>https://www.youtube.com/watch?v=XOKQluw_YLU</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1711081</v>
+        <v>3803168</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>SHOCHIKU anime Channel</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -10540,7 +10650,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-06-21T18:22:43</t>
+          <t>2026-06-21T18:22:34</t>
         </is>
       </c>
     </row>
@@ -10563,29 +10673,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>猫じゃらし</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>7co</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A6aH9jPW8ZY</t>
+          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>273328</v>
+        <v>1711081</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -10594,11 +10704,11 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A6aH9jPW8ZY</t>
+          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>273328</v>
+        <v>1711081</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -10607,7 +10717,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-06-21T18:22:55</t>
+          <t>2026-06-21T18:22:43</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10732,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -10630,7 +10740,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -10638,21 +10748,45 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>license</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Redhair Rosy</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+          <t>PAS TASTA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A6aH9jPW8ZY</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>273328</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A6aH9jPW8ZY</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>273328</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:55</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -10665,7 +10799,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -10677,16 +10811,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>終わらない夜の守り方</t>
+          <t>運命の君</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>インナージャーニー</t>
+          <t>Mega Shinnosuke</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -10708,7 +10842,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -10724,12 +10858,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>license</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>Redhair Rosy</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -10751,7 +10885,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -10767,12 +10901,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>NEW GAME</t>
+          <t>終わらない夜の守り方</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>halca</t>
+          <t>インナージャーニー</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -10794,7 +10928,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -10810,12 +10944,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -10837,7 +10971,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -10853,12 +10987,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lv.1 職業：⼈間</t>
+          <t>NEW GAME</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ReoNa</t>
+          <t>halca</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -10880,7 +11014,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -10896,12 +11030,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -10923,7 +11057,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -10939,45 +11073,21 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>Lv.1 職業：⼈間</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>KI_EN</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>140125</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
-        </is>
-      </c>
-      <c r="M68" t="n">
-        <v>140125</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:23:55</t>
-        </is>
-      </c>
+          <t>ReoNa</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10990,7 +11100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -11006,12 +11116,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>原因は自分にある。</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -11033,7 +11143,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -11041,7 +11151,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -11049,33 +11159,43 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
+          <t>KI_EN</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qpFcQ1Bek08</t>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>69452</v>
+        <v>140125</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>VAP Official</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>140125</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-06-21T18:24:32</t>
+          <t>2026-06-21T18:23:55</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11210,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -11106,12 +11226,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -11133,7 +11253,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -11141,7 +11261,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -11149,12 +11269,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>Tilt</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>harmoe</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -11176,7 +11296,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -11184,7 +11304,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -11192,21 +11312,35 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>To Be Continued</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>QWER</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+          <t>七海ひろき</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qpFcQ1Bek08</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>69452</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>VAP Official</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:24:32</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -11219,7 +11353,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -11235,12 +11369,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ひとひら</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>秦基博</t>
+          <t>SEKAI NO OWARI</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -11262,7 +11396,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -11270,7 +11404,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -11278,12 +11412,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -11305,7 +11439,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>トミカとトム</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -11313,7 +11447,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -11321,12 +11455,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>きみのたからもの</t>
+          <t>To Be Continued</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>May J.</t>
+          <t>QWER</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -11348,7 +11482,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -11364,12 +11498,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>ひとひら</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>秦基博</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -11391,7 +11525,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -11407,45 +11541,21 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Soarin’</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Ginger Root</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>3207</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Lantis Channel</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
-        </is>
-      </c>
-      <c r="M78" t="n">
-        <v>3207</v>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Lantis Channel</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:26:16</t>
-        </is>
-      </c>
+          <t>櫻井優衣</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11458,7 +11568,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>トミカとトム</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -11474,12 +11584,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>きみのたからもの</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>May J.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11501,7 +11611,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -11517,45 +11627,21 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>WANIMA</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>402991</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>TMSアニメ公式チャンネル</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>402991</v>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>TMSアニメ公式チャンネル</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:26:31</t>
-        </is>
-      </c>
+          <t>五阿弥ルナ</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11568,7 +11654,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -11576,51 +11662,51 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>Soarin’</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>Ginger Root</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
+          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>174316</v>
+        <v>3207</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>TMSアニメ公式チャンネル</t>
+          <t>Lantis Channel</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
+          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>174316</v>
+        <v>3207</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>TMSアニメ公式チャンネル</t>
+          <t>Lantis Channel</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-06-21T18:26:42</t>
+          <t>2026-06-21T18:26:16</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11721,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -11643,7 +11729,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -11651,45 +11737,21 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Novel Core</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>294329</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>TMSアニメ公式チャンネル</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
-        </is>
-      </c>
-      <c r="M82" t="n">
-        <v>294329</v>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>TMSアニメ公式チャンネル</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:26:53</t>
-        </is>
-      </c>
+          <t>安保心結</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11710,29 +11772,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>25824</v>
+        <v>402991</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -11741,11 +11803,11 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>25824</v>
+        <v>402991</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -11754,7 +11816,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-06-21T18:27:05</t>
+          <t>2026-06-21T18:26:31</t>
         </is>
       </c>
     </row>
@@ -11769,7 +11831,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D84" t="b">
@@ -11781,25 +11843,49 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+          <t>Chevon</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>174316</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>174316</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:26:42</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11812,7 +11898,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -11828,21 +11914,45 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
+          <t>Novel Core</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>294329</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>294329</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:26:53</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11855,7 +11965,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -11863,29 +11973,53 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+          <t>三代目 J SOUL BROTHERS</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>25824</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>25824</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:27:05</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11898,7 +12032,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -11906,7 +12040,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -11914,12 +12048,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11941,7 +12075,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -11949,7 +12083,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -11957,35 +12091,21 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>小倉唯</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=LFS_qg2JrPI</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>11323</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Yui Ogura YouTube OFFICIAL CHANNEL</t>
-        </is>
-      </c>
+          <t>Omoinotake</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:27:45</t>
-        </is>
-      </c>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11998,7 +12118,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>バンドリ！ ゆめ∞みた</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -12006,7 +12126,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -12014,35 +12134,21 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>これはぼくたちの生存のあらすじ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=MzjYjMBpQ6g</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>4603</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>大西亜玖璃 - Aguri Onishi</t>
-        </is>
-      </c>
+          <t>夢限大みゅーたいぷ</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:27:58</t>
-        </is>
-      </c>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12055,7 +12161,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -12071,35 +12177,21 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>milet</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nR_vqhD2rGM</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>451401</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>TOHO animation</t>
-        </is>
-      </c>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:28:12</t>
-        </is>
-      </c>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12112,7 +12204,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -12120,7 +12212,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -12128,12 +12220,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>FREEZE ME UP</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>SiM</t>
+          <t>仲村宗悟</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12155,7 +12247,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -12163,7 +12255,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -12171,21 +12263,35 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Groooovy</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>I Don't Like Mondays.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+          <t>小倉唯</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LFS_qg2JrPI</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>11323</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Yui Ogura YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:27:45</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12198,7 +12304,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -12206,7 +12312,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -12214,21 +12320,35 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+          <t>大西亜玖璃</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MzjYjMBpQ6g</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>4603</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>大西亜玖璃 - Aguri Onishi</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:27:58</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12241,7 +12361,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>文豪ストレイドッグス わん！２</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="D94" t="b">
@@ -12249,7 +12369,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -12257,21 +12377,35 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>僕ら～芥川龍之介Ver.～</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>芥川龍之介（CV.小野賢章）</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+          <t>milet</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nR_vqhD2rGM</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>451401</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:28:12</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12284,7 +12418,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -12300,12 +12434,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>○✕△□</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>浪漫派マシュマロ</t>
+          <t>SiM</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12327,7 +12461,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -12335,7 +12469,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -12343,12 +12477,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Blacker Co., Ltd.</t>
+          <t>Groooovy</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>イツカ▶</t>
+          <t>I Don't Like Mondays.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -12370,7 +12504,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -12378,7 +12512,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -12386,12 +12520,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Elegy of the Enemies</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>The Canbellz</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12413,7 +12547,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -12421,20 +12555,20 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>白い蝶が飛んだら</t>
+          <t>I-BULL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
+          <t>jo0ji</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12456,7 +12590,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -12464,7 +12598,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -12472,12 +12606,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>螺旋</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>9Lana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12499,7 +12633,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>文豪ストレイドッグス わん！２</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -12515,12 +12649,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>僕ら～芥川龍之介Ver.～</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>芥川龍之介（CV.小野賢章）</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12542,7 +12676,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -12558,35 +12692,21 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>590624</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
-        </is>
-      </c>
+          <t>浪漫派マシュマロ</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:29:37</t>
-        </is>
-      </c>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12599,7 +12719,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -12607,7 +12727,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -12615,35 +12735,21 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Blacker Co., Ltd.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>590624</v>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
-        </is>
-      </c>
+          <t>イツカ▶</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:29:56</t>
-        </is>
-      </c>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12656,7 +12762,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -12664,7 +12770,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -12672,12 +12778,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>Elegy of the Enemies</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>The Canbellz</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12699,7 +12805,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D104" t="b">
@@ -12711,16 +12817,16 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>白い蝶が飛んだら</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12742,7 +12848,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -12758,45 +12864,21 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=hZ6TnKvB2rc</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
-        <v>12105753</v>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>大原ゆい子Official YouTube</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=PINgF6rCuME</t>
-        </is>
-      </c>
-      <c r="M105" t="n">
-        <v>2457533</v>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>TOHO animation</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:30:35</t>
-        </is>
-      </c>
+          <t>ももいろクローバーZ</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12809,7 +12891,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D106" t="b">
@@ -12825,35 +12907,21 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ODxfIvSgWuo</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>1140774</v>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>TOHO animation</t>
-        </is>
-      </c>
+          <t>i☆Ris</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:31:08</t>
-        </is>
-      </c>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12866,7 +12934,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -12882,43 +12950,33 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>水樹奈々</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vJzWWkigrU8</t>
+          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>32222</v>
+        <v>590624</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>家入レオ</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5QGZX_Kky4I</t>
-        </is>
-      </c>
-      <c r="M107" t="n">
-        <v>27576</v>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>leafstamp</t>
-        </is>
-      </c>
+          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-06-21T18:31:32</t>
+          <t>2026-06-21T18:29:37</t>
         </is>
       </c>
     </row>
@@ -12933,7 +12991,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D108" t="b">
@@ -12949,21 +13007,35 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+          <t>青木陽菜</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>590624</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:29:56</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12976,7 +13048,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -12992,35 +13064,21 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>480871</v>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
-        </is>
-      </c>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:32:14</t>
-        </is>
-      </c>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13033,7 +13091,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D110" t="b">
@@ -13049,35 +13107,21 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>煙とブルー</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ネクライトーキー</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>480871</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
-        </is>
-      </c>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:32:32</t>
-        </is>
-      </c>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13090,7 +13134,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D111" t="b">
@@ -13106,33 +13150,43 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Why? RED induction</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RMaOR0Pyfts</t>
+          <t>https://www.youtube.com/watch?v=hZ6TnKvB2rc</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>50838</v>
+        <v>12105753</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID Official Channel</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+          <t>大原ゆい子Official YouTube</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PINgF6rCuME</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>2457533</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-06-21T18:33:01</t>
+          <t>2026-06-21T18:30:35</t>
         </is>
       </c>
     </row>
@@ -13147,7 +13201,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D112" t="b">
@@ -13163,21 +13217,35 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Weiter! Weiter!</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+          <t>中島美嘉</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ODxfIvSgWuo</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>1140774</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:31:08</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13190,7 +13258,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D113" t="b">
@@ -13206,43 +13274,43 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
+          <t>https://www.youtube.com/watch?v=vJzWWkigrU8</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>603666</v>
+        <v>32222</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
+          <t>https://www.youtube.com/watch?v=5QGZX_Kky4I</t>
         </is>
       </c>
       <c r="M113" t="n">
-        <v>603666</v>
+        <v>27576</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+          <t>leafstamp</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-06-21T18:33:22</t>
+          <t>2026-06-21T18:31:32</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13325,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D114" t="b">
@@ -13265,43 +13333,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Dannie May</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>66350</v>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
-        </is>
-      </c>
+          <t>冨岡愛</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:33:34</t>
-        </is>
-      </c>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13314,7 +13368,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D115" t="b">
@@ -13322,7 +13376,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -13330,43 +13384,33 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aw45Q_mr0_M</t>
+          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>9441868</v>
+        <v>480871</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=VJflo-z7e7A</t>
-        </is>
-      </c>
-      <c r="M115" t="n">
-        <v>151043</v>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
-        </is>
-      </c>
+          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-06-21T18:33:47</t>
+          <t>2026-06-21T18:32:14</t>
         </is>
       </c>
     </row>
@@ -13381,7 +13425,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D116" t="b">
@@ -13393,29 +13437,29 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>煙とブルー</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>ネクライトーキー</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
+          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>66350</v>
+        <v>480871</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -13423,7 +13467,7 @@
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>2026-06-21T18:34:00</t>
+          <t>2026-06-21T18:32:32</t>
         </is>
       </c>
     </row>
@@ -13438,7 +13482,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>闇芝居 十七期</t>
         </is>
       </c>
       <c r="D117" t="b">
@@ -13446,7 +13490,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -13454,12 +13498,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>闇芝居のブルース</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>風輪（徳間ジャパンコミュニケーションズ）</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13481,7 +13525,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D118" t="b">
@@ -13489,7 +13533,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -13497,21 +13541,35 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>TrySail</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+          <t>MYTH &amp; ROID</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RMaOR0Pyfts</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>50838</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>MYTH &amp; ROID Official Channel</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:01</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13524,7 +13582,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D119" t="b">
@@ -13532,7 +13590,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -13540,12 +13598,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13567,7 +13625,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D120" t="b">
@@ -13575,7 +13633,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -13583,21 +13641,45 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+          <t>blank paper</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>603666</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
+        </is>
+      </c>
+      <c r="M120" t="n">
+        <v>603666</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:22</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13610,7 +13692,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D121" t="b">
@@ -13622,25 +13704,39 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+          <t>Dannie May</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>66350</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:34</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13653,7 +13749,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D122" t="b">
@@ -13669,21 +13765,45 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>REIRIE</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
+          <t>ONE OR EIGHT</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aw45Q_mr0_M</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>9441868</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>ONE OR EIGHT</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VJflo-z7e7A</t>
+        </is>
+      </c>
+      <c r="M122" t="n">
+        <v>151043</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:47</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13696,7 +13816,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D123" t="b">
@@ -13704,33 +13824,33 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
+          <t>カラノア</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9-RVzXLF53U</t>
+          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>78910</v>
+        <v>66350</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Itsuki Natsume / 棗いつき</t>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -13738,7 +13858,7 @@
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
-          <t>2026-06-21T18:35:08</t>
+          <t>2026-06-21T18:34:00</t>
         </is>
       </c>
     </row>
@@ -13753,7 +13873,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D124" t="b">
@@ -13761,7 +13881,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -13769,12 +13889,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ゆきむら。</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13796,7 +13916,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D125" t="b">
@@ -13804,7 +13924,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -13812,45 +13932,21 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>262519</v>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>SHOCHIKU anime Channel</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
-        </is>
-      </c>
-      <c r="M125" t="n">
-        <v>262519</v>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>SHOCHIKU anime Channel</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:35:26</t>
-        </is>
-      </c>
+          <t>TrySail</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13863,15 +13959,15 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ONE PIECE HEROINES</t>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="D126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -13879,45 +13975,21 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ONE PIECE（モノクロ版）</t>
+          <t>虹色Passions！</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>電子書籍（コミック）</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=6hRjsvdINgg</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>17920416</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>ONE PIECE Official YouTube Channel</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=YFbno_aPm0w</t>
-        </is>
-      </c>
-      <c r="M126" t="n">
-        <v>27924515</v>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>ONE PIECE Official YouTube Channel</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:35:55</t>
-        </is>
-      </c>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13938,7 +14010,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -13946,7 +14018,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>虹色Passions！</t>
+          <t>NEO SKY, NEO MAP!</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -13973,15 +14045,15 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -13989,12 +14061,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>NEO SKY, NEO MAP!</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>虹ヶ咲学園スクールアイドル同好会</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14007,16 +14079,16 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D129" t="b">
@@ -14024,7 +14096,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -14032,12 +14104,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sorrow</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14050,16 +14122,16 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D130" t="b">
@@ -14075,12 +14147,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>西川貴教</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14093,16 +14165,16 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D131" t="b">
@@ -14110,7 +14182,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -14118,12 +14190,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>ひなたぼっこ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>REIRIE</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14136,16 +14208,16 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D132" t="b">
@@ -14153,7 +14225,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -14161,34 +14233,48 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+          <t>藍月なくる&amp;棗いつき</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9-RVzXLF53U</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>78910</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Itsuki Natsume / 棗いつき</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:35:08</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D133" t="b">
@@ -14196,7 +14282,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -14204,31 +14290,380 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-PX7FqZ55tE</t>
-        </is>
-      </c>
-      <c r="J133" t="n">
-        <v>105042</v>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>TVアニメ「魔法少女育成計画restart」公式チャンネル</t>
-        </is>
-      </c>
+          <t>ゆきむら。</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr">
+      <c r="O133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ワールド イズ ダンシング</t>
+        </is>
+      </c>
+      <c r="D134" t="b">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>終宵</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>262519</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
+        </is>
+      </c>
+      <c r="M134" t="n">
+        <v>262519</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:35:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>5806</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026夏アニメ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ONE PIECE HEROINES</t>
+        </is>
+      </c>
+      <c r="D135" t="b">
+        <v>0</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>主題歌</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>ONE PIECE（モノクロ版）</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>電子書籍（コミック）</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6hRjsvdINgg</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>17920416</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>ONE PIECE Official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YFbno_aPm0w</t>
+        </is>
+      </c>
+      <c r="M135" t="n">
+        <v>27924515</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>ONE PIECE Official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:35:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>帰還者の魔法は特別です 第2期</t>
+        </is>
+      </c>
+      <c r="D136" t="b">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Sorrow</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>獣王武神ダンデヴァイン</t>
+        </is>
+      </c>
+      <c r="D137" t="b">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>曲名未発表</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>西川貴教</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D138" t="b">
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Flare of Soul</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
+        </is>
+      </c>
+      <c r="D139" t="b">
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D140" t="b">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-PX7FqZ55tE</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>105042</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>TVアニメ「魔法少女育成計画restart」公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
         <is>
           <t>2026-06-21T18:36:51</t>
         </is>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -4238,7 +4238,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026年7月4日（土）～ TOKYO MX・BS11にて</t>
+          <t>2026年7月4日（土）～ TOKYO MX・BS11ほか</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026年10月〜</t>
+          <t>2026年10月1日（木）〜 テレビ神奈川・CBCテレビにて</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -11652,13 +11652,37 @@
           <t>QWER</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>16839</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>16839</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:05:01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11695,13 +11719,37 @@
           <t>QWER</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>16839</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>16839</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:05:10</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -12374,13 +12422,27 @@
           <t>Omoinotake</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s1bZEnGAX8I</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>3841595</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:06:54</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12417,13 +12479,27 @@
           <t>Omoinotake</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s1bZEnGAX8I</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>3841595</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:07:22</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -2732,8 +2732,16 @@
           <t>原因は自分にある。</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>泣いた悪魔</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>えむにみに</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=27260</t>
@@ -3468,10 +3476,26 @@
           <t>ライデンフィルム</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ハイメンテナンスガール</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>オーイシマサヨシ</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ベリーグッド・エンカウント</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>内田真礼</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=26828</t>
@@ -7793,7 +7817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O147"/>
+  <dimension ref="A1:O150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11375,7 +11399,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -11391,45 +11415,21 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>泣いた悪魔</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>KI_EN</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>140125</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
-        <v>140125</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:23:55</t>
-        </is>
-      </c>
+          <t>えむにみに</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -11458,21 +11458,45 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+          <t>KI_EN</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>140125</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>140125</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:23:55</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -11493,7 +11517,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -11501,12 +11525,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tilt</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>harmoe</t>
+          <t>DIALOGUE+</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -11528,7 +11552,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -11536,7 +11560,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -11544,35 +11568,21 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>Tilt</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=qpFcQ1Bek08</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>69452</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>VAP Official</t>
-        </is>
-      </c>
+          <t>harmoe</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:24:32</t>
-        </is>
-      </c>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11585,7 +11595,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -11601,21 +11611,35 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+          <t>七海ひろき</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qpFcQ1Bek08</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>69452</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>VAP Official</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:24:32</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11628,7 +11652,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -11644,45 +11668,21 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>QWER</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>16839</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>16839</v>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>2026-06-25T09:05:01</t>
-        </is>
-      </c>
+          <t>SEKAI NO OWARI</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>To Be Continued</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-06-25T09:05:10</t>
+          <t>2026-06-25T09:05:01</t>
         </is>
       </c>
     </row>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -11778,21 +11778,45 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ひとひら</t>
+          <t>To Be Continued</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>秦基博</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+          <t>QWER</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>16839</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>16839</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:05:10</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11813,7 +11837,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -11821,12 +11845,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>ひとひら</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
+          <t>秦基博</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11848,7 +11872,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>トミカとトム</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -11856,7 +11880,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -11864,12 +11888,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>きみのたからもの</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>May J.</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -11891,7 +11915,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>トミカとトム</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -11899,7 +11923,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -11907,12 +11931,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>きみのたからもの</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>May J.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11942,7 +11966,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -11950,45 +11974,21 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Soarin’</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Ginger Root</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>3207</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Lantis Channel</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
-        </is>
-      </c>
-      <c r="M82" t="n">
-        <v>3207</v>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Lantis Channel</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:26:16</t>
-        </is>
-      </c>
+          <t>五阿弥ルナ</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>猫と竜</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -12017,21 +12017,45 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>猫日</t>
+          <t>Soarin’</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>suis from ヨルシカ</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
+          <t>Ginger Root</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>3207</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Lantis Channel</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>3207</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Lantis Channel</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:26:16</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12052,7 +12076,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -12060,21 +12084,35 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ただいまの場所</t>
+          <t>猫日</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>shallm</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+          <t>suis from ヨルシカ</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5Of2HNJa_gs</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>5618588</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>ヨルシカ / n-buna Official</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2026-06-26T09:06:03</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12087,7 +12125,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>猫と竜</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -12095,7 +12133,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -12103,12 +12141,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>ただいまの場所</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>安保心結</t>
+          <t>shallm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -12130,7 +12168,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -12138,7 +12176,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -12146,45 +12184,21 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>WANIMA</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>402991</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>TMSアニメ公式チャンネル</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
-        <v>402991</v>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>TMSアニメ公式チャンネル</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:26:31</t>
-        </is>
-      </c>
+          <t>安保心結</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12209,25 +12223,25 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Chevon</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
+          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>174316</v>
+        <v>402991</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -12236,11 +12250,11 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
+          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>174316</v>
+        <v>402991</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -12249,7 +12263,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-06-21T18:26:42</t>
+          <t>2026-06-21T18:26:31</t>
         </is>
       </c>
     </row>
@@ -12272,29 +12286,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
+          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>294329</v>
+        <v>174316</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -12303,11 +12317,11 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
+          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>294329</v>
+        <v>174316</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -12316,7 +12330,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-06-21T18:26:53</t>
+          <t>2026-06-21T18:26:42</t>
         </is>
       </c>
     </row>
@@ -12343,25 +12357,25 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>Novel Core</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>25824</v>
+        <v>294329</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -12370,11 +12384,11 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>25824</v>
+        <v>294329</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -12383,7 +12397,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-06-21T18:27:05</t>
+          <t>2026-06-21T18:26:53</t>
         </is>
       </c>
     </row>
@@ -12398,7 +12412,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D90" t="b">
@@ -12406,41 +12420,51 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
+          <t>三代目 J SOUL BROTHERS</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s1bZEnGAX8I</t>
+          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>3841595</v>
+        <v>25824</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>25824</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-06-25T09:06:54</t>
+          <t>2026-06-21T18:27:05</t>
         </is>
       </c>
     </row>
@@ -12455,7 +12479,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>花織さんは転生しても喧嘩がしたい</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -12463,7 +12487,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -12471,35 +12495,21 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>ハイメンテナンスガール</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=s1bZEnGAX8I</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>3841595</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
+          <t>オーイシマサヨシ</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>2026-06-25T09:07:22</t>
-        </is>
-      </c>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12512,7 +12522,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>バンドリ！ ゆめ∞みた</t>
+          <t>花織さんは転生しても喧嘩がしたい</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -12520,7 +12530,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -12528,45 +12538,21 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>これはぼくたちの生存のあらすじ</t>
+          <t>ベリーグッド・エンカウント</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>夢限大みゅーたいぷ</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Ech7Tj8ga0Y</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>124089</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>BanG Dream Channel☆</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Ech7Tj8ga0Y</t>
-        </is>
-      </c>
-      <c r="M92" t="n">
-        <v>124089</v>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>BanG Dream Channel☆</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>2026-06-24T09:06:31</t>
-        </is>
-      </c>
+          <t>内田真礼</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12579,7 +12565,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -12595,21 +12581,35 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+          <t>Omoinotake</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s1bZEnGAX8I</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>3841595</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:06:54</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D94" t="b">
@@ -12638,21 +12638,35 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+          <t>Omoinotake</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s1bZEnGAX8I</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>3841595</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:07:22</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12665,7 +12679,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>バンドリ！ ゆめ∞みた</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -12681,33 +12695,43 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>これはぼくたちの生存のあらすじ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>小倉唯</t>
+          <t>夢限大みゅーたいぷ</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=LFS_qg2JrPI</t>
+          <t>https://www.youtube.com/watch?v=Ech7Tj8ga0Y</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>11323</v>
+        <v>124089</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Yui Ogura YouTube OFFICIAL CHANNEL</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>BanG Dream Channel☆</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ech7Tj8ga0Y</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>124089</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>BanG Dream Channel☆</t>
+        </is>
+      </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-06-21T18:27:45</t>
+          <t>2026-06-24T09:06:31</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12746,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -12730,7 +12754,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -12738,35 +12762,21 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=MzjYjMBpQ6g</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>4603</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>大西亜玖璃 - Aguri Onishi</t>
-        </is>
-      </c>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:27:58</t>
-        </is>
-      </c>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12779,7 +12789,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -12787,7 +12797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -12795,35 +12805,21 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>milet</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nR_vqhD2rGM</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>451401</v>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>TOHO animation</t>
-        </is>
-      </c>
+          <t>仲村宗悟</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:28:12</t>
-        </is>
-      </c>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12836,7 +12832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -12852,21 +12848,35 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FREEZE ME UP</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>SiM</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+          <t>小倉唯</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LFS_qg2JrPI</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>11323</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Yui Ogura YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:27:45</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12879,7 +12889,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -12895,21 +12905,35 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Groooovy</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>I Don't Like Mondays.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+          <t>大西亜玖璃</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MzjYjMBpQ6g</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>4603</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>大西亜玖璃 - Aguri Onishi</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:27:58</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12922,7 +12946,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -12930,7 +12954,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -12938,21 +12962,35 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+          <t>milet</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nR_vqhD2rGM</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>451401</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:28:12</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12965,7 +13003,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BLEACH 千年血戦篇-禍進譚-</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -12981,12 +13019,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I-BULL</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>jo0ji</t>
+          <t>SiM</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -13008,7 +13046,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BLEACH 千年血戦篇-禍進譚-</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -13024,12 +13062,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>螺旋</t>
+          <t>Groooovy</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>9Lana</t>
+          <t>I Don't Like Mondays.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13051,7 +13089,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>文豪ストレイドッグス わん！２</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -13059,7 +13097,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -13067,12 +13105,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>僕ら～芥川龍之介Ver.～</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>芥川龍之介（CV.小野賢章）</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13094,7 +13132,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="D104" t="b">
@@ -13110,12 +13148,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>○✕△□</t>
+          <t>I-BULL</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>浪漫派マシュマロ</t>
+          <t>jo0ji</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13137,7 +13175,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -13153,12 +13191,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Firetail</t>
+          <t>螺旋</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>チョーキューメイ</t>
+          <t>9Lana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13180,7 +13218,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>文豪ストレイドッグス わん！２</t>
         </is>
       </c>
       <c r="D106" t="b">
@@ -13188,7 +13226,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -13196,12 +13234,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Blacker Co., Ltd.</t>
+          <t>僕ら～芥川龍之介Ver.～</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>イツカ▶</t>
+          <t>芥川龍之介（CV.小野賢章）</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13223,7 +13261,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -13231,7 +13269,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -13239,12 +13277,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Elegy of the Enemies</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>The Canbellz</t>
+          <t>浪漫派マシュマロ</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13266,7 +13304,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D108" t="b">
@@ -13278,16 +13316,16 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>白い蝶が飛んだら</t>
+          <t>Firetail</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
+          <t>チョーキューメイ</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13309,7 +13347,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -13325,12 +13363,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>Blacker Co., Ltd.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>イツカ▶</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13352,7 +13390,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D110" t="b">
@@ -13368,12 +13406,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>Elegy of the Enemies</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>The Canbellz</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13395,7 +13433,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D111" t="b">
@@ -13403,43 +13441,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>白い蝶が飛んだら</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>590624</v>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
-        </is>
-      </c>
+          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:29:37</t>
-        </is>
-      </c>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13452,7 +13476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D112" t="b">
@@ -13460,7 +13484,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -13468,35 +13492,21 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>590624</v>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
-        </is>
-      </c>
+          <t>ももいろクローバーZ</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:29:56</t>
-        </is>
-      </c>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13509,7 +13519,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D113" t="b">
@@ -13525,12 +13535,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>とけて煌る</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>neNna</t>
+          <t>i☆Ris</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13552,7 +13562,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D114" t="b">
@@ -13568,21 +13578,35 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+          <t>水樹奈々</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>590624</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:29:37</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13595,7 +13619,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D115" t="b">
@@ -13611,21 +13635,35 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+          <t>青木陽菜</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>590624</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:29:56</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13638,7 +13676,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
         </is>
       </c>
       <c r="D116" t="b">
@@ -13646,7 +13684,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -13654,45 +13692,21 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>とけて煌る</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=hZ6TnKvB2rc</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>12105753</v>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>大原ゆい子Official YouTube</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=PINgF6rCuME</t>
-        </is>
-      </c>
-      <c r="M116" t="n">
-        <v>2457533</v>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>TOHO animation</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:30:35</t>
-        </is>
-      </c>
+          <t>neNna</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13705,7 +13719,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D117" t="b">
@@ -13713,7 +13727,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -13721,35 +13735,21 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ODxfIvSgWuo</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>1140774</v>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>TOHO animation</t>
-        </is>
-      </c>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:31:08</t>
-        </is>
-      </c>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D118" t="b">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -13778,45 +13778,21 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>家入レオ</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=vJzWWkigrU8</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>32222</v>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>家入レオ</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5QGZX_Kky4I</t>
-        </is>
-      </c>
-      <c r="M118" t="n">
-        <v>27576</v>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>leafstamp</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:31:32</t>
-        </is>
-      </c>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13829,7 +13805,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D119" t="b">
@@ -13837,7 +13813,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -13845,21 +13821,45 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
+          <t>大原ゆい子</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hZ6TnKvB2rc</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>12105753</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>大原ゆい子Official YouTube</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PINgF6rCuME</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>2457533</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:30:35</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D120" t="b">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -13888,25 +13888,25 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>中島美嘉</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
+          <t>https://www.youtube.com/watch?v=ODxfIvSgWuo</t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>480871</v>
+        <v>1140774</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
+          <t>TOHO animation</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -13914,7 +13914,7 @@
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-06-21T18:32:14</t>
+          <t>2026-06-21T18:31:08</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D121" t="b">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -13945,33 +13945,43 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>煙とブルー</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ネクライトーキー</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
+          <t>https://www.youtube.com/watch?v=vJzWWkigrU8</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>480871</v>
+        <v>32222</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+          <t>家入レオ</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5QGZX_Kky4I</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
+        <v>27576</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>leafstamp</t>
+        </is>
+      </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-06-21T18:32:32</t>
+          <t>2026-06-21T18:31:32</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13996,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>闇芝居 十七期</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D122" t="b">
@@ -14002,12 +14012,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>闇芝居のブルース</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>風輪（徳間ジャパンコミュニケーションズ）</t>
+          <t>冨岡愛</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14029,7 +14039,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D123" t="b">
@@ -14045,25 +14055,25 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Why? RED induction</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>忘れらんねえよ</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RMaOR0Pyfts</t>
+          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>50838</v>
+        <v>480871</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID Official Channel</t>
+          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -14071,7 +14081,7 @@
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
-          <t>2026-06-21T18:33:01</t>
+          <t>2026-06-21T18:32:14</t>
         </is>
       </c>
     </row>
@@ -14086,7 +14096,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D124" t="b">
@@ -14102,21 +14112,35 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Weiter! Weiter!</t>
+          <t>煙とブルー</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+          <t>ネクライトーキー</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>480871</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:32:32</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14129,7 +14153,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>闇芝居 十七期</t>
         </is>
       </c>
       <c r="D125" t="b">
@@ -14137,7 +14161,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -14145,45 +14169,21 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>闇芝居のブルース</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>blank paper</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>603666</v>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
-        </is>
-      </c>
-      <c r="M125" t="n">
-        <v>603666</v>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:33:22</t>
-        </is>
-      </c>
+          <t>風輪（徳間ジャパンコミュニケーションズ）</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D126" t="b">
@@ -14208,29 +14208,29 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Dannie May</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
+          <t>https://www.youtube.com/watch?v=RMaOR0Pyfts</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>66350</v>
+        <v>50838</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+          <t>MYTH &amp; ROID Official Channel</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -14238,7 +14238,7 @@
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-06-21T18:33:34</t>
+          <t>2026-06-21T18:33:01</t>
         </is>
       </c>
     </row>
@@ -14253,7 +14253,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D127" t="b">
@@ -14269,45 +14269,21 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=aw45Q_mr0_M</t>
-        </is>
-      </c>
-      <c r="J127" t="n">
-        <v>9441868</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>ONE OR EIGHT</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=VJflo-z7e7A</t>
-        </is>
-      </c>
-      <c r="M127" t="n">
-        <v>151043</v>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:33:47</t>
-        </is>
-      </c>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14328,41 +14304,51 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
+          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>66350</v>
+        <v>603666</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
           <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
+        </is>
+      </c>
+      <c r="M128" t="n">
+        <v>603666</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-06-21T18:34:00</t>
+          <t>2026-06-21T18:33:22</t>
         </is>
       </c>
     </row>
@@ -14377,7 +14363,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D129" t="b">
@@ -14389,25 +14375,39 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+          <t>Dannie May</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>66350</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:34</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D130" t="b">
@@ -14436,21 +14436,45 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>TrySail</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
+          <t>ONE OR EIGHT</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aw45Q_mr0_M</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>9441868</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>ONE OR EIGHT</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VJflo-z7e7A</t>
+        </is>
+      </c>
+      <c r="M130" t="n">
+        <v>151043</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:47</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14463,37 +14487,51 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>虹色Passions！</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>虹ヶ咲学園スクールアイドル同好会</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
+          <t>カラノア</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>66350</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:34:00</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14506,15 +14544,15 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -14522,12 +14560,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>NEO SKY, NEO MAP!</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>虹ヶ咲学園スクールアイドル同好会</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14549,7 +14587,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D133" t="b">
@@ -14557,7 +14595,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -14565,12 +14603,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14592,15 +14630,15 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="D134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -14608,12 +14646,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>虹色Passions！</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14635,15 +14673,15 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="D135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -14651,12 +14689,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>NEO SKY, NEO MAP!</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14678,7 +14716,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D136" t="b">
@@ -14686,7 +14724,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -14694,12 +14732,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>REIRIE</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14721,7 +14759,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D137" t="b">
@@ -14729,7 +14767,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -14737,35 +14775,21 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9-RVzXLF53U</t>
-        </is>
-      </c>
-      <c r="J137" t="n">
-        <v>78910</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Itsuki Natsume / 棗いつき</t>
-        </is>
-      </c>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:35:08</t>
-        </is>
-      </c>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14778,7 +14802,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D138" t="b">
@@ -14786,7 +14810,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -14794,12 +14818,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ゆきむら。</t>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14821,7 +14845,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D139" t="b">
@@ -14829,7 +14853,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -14837,45 +14861,21 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>ひなたぼっこ</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
-        </is>
-      </c>
-      <c r="J139" t="n">
-        <v>262519</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>SHOCHIKU anime Channel</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
-        </is>
-      </c>
-      <c r="M139" t="n">
-        <v>262519</v>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>SHOCHIKU anime Channel</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:35:26</t>
-        </is>
-      </c>
+          <t>REIRIE</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ONE PIECE HEROINES</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D140" t="b">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -14904,58 +14904,48 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ONE PIECE（モノクロ版）</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>電子書籍（コミック）</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6hRjsvdINgg</t>
+          <t>https://www.youtube.com/watch?v=9-RVzXLF53U</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>17920416</v>
+        <v>78910</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>ONE PIECE Official YouTube Channel</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=YFbno_aPm0w</t>
-        </is>
-      </c>
-      <c r="M140" t="n">
-        <v>27924515</v>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>ONE PIECE Official YouTube Channel</t>
-        </is>
-      </c>
+          <t>Itsuki Natsume / 棗いつき</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-06-21T18:35:55</t>
+          <t>2026-06-21T18:35:08</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D141" t="b">
@@ -14963,7 +14953,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -14971,12 +14961,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sorrow</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>ゆきむら。</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14989,16 +14979,16 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="D142" t="b">
@@ -15014,34 +15004,58 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>終宵</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>西川貴教</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>262519</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
+        </is>
+      </c>
+      <c r="M142" t="n">
+        <v>262519</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:35:26</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>ONE PIECE HEROINES</t>
         </is>
       </c>
       <c r="D143" t="b">
@@ -15049,7 +15063,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -15057,21 +15071,45 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>ONE PIECE（モノクロ版）</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
+          <t>電子書籍（コミック）</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6hRjsvdINgg</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>17920416</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>ONE PIECE Official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YFbno_aPm0w</t>
+        </is>
+      </c>
+      <c r="M143" t="n">
+        <v>27924515</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>ONE PIECE Official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:35:55</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15084,7 +15122,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>帰還者の魔法は特別です 第2期</t>
         </is>
       </c>
       <c r="D144" t="b">
@@ -15092,7 +15130,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -15100,12 +15138,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>Sorrow</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15127,7 +15165,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>獣王武神ダンデヴァイン</t>
         </is>
       </c>
       <c r="D145" t="b">
@@ -15143,35 +15181,21 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>曲名未発表</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-PX7FqZ55tE</t>
-        </is>
-      </c>
-      <c r="J145" t="n">
-        <v>105042</v>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>TVアニメ「魔法少女育成計画restart」公式チャンネル</t>
-        </is>
-      </c>
+          <t>西川貴教</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:36:51</t>
-        </is>
-      </c>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15184,7 +15208,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>魔法の姉妹ルルットリリィ 第2クール</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="D146" t="b">
@@ -15200,45 +15224,21 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bubee</t>
+          <t>Flare of Soul</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>ILLIT</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=sNIntrw0m-g</t>
-        </is>
-      </c>
-      <c r="J146" t="n">
-        <v>66633</v>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Bandai Namco Filmworks Channel</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=sNIntrw0m-g</t>
-        </is>
-      </c>
-      <c r="M146" t="n">
-        <v>66633</v>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>Bandai Namco Filmworks Channel</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>2026-06-24T09:09:26</t>
-        </is>
-      </c>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>魔法の姉妹ルルットリリィ 第2クール</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="D147" t="b">
@@ -15267,41 +15267,208 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
+          <t>STELLAR</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>魔法少女育成計画restart</t>
+        </is>
+      </c>
+      <c r="D148" t="b">
+        <v>0</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-PX7FqZ55tE</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>105042</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>TVアニメ「魔法少女育成計画restart」公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:36:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>魔法の姉妹ルルットリリィ 第2クール</t>
+        </is>
+      </c>
+      <c r="D149" t="b">
+        <v>0</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Bubee</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>ILLIT</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sNIntrw0m-g</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>66633</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Bandai Namco Filmworks Channel</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sNIntrw0m-g</t>
+        </is>
+      </c>
+      <c r="M149" t="n">
+        <v>66633</v>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Bandai Namco Filmworks Channel</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>2026-06-24T09:09:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>魔法の姉妹ルルットリリィ 第2クール</t>
+        </is>
+      </c>
+      <c r="D150" t="b">
+        <v>0</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
           <t>Calling</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>ルルットリリィ（こんぺとリリィ（CV.橘めい）、ましゅールル（CV.小鹿なお））</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7oNuxIfJqiI</t>
         </is>
       </c>
-      <c r="J147" t="n">
+      <c r="J150" t="n">
         <v>195116</v>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="K150" t="inlineStr">
         <is>
           <t>Bandai Namco Filmworks Channel</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7oNuxIfJqiI</t>
         </is>
       </c>
-      <c r="M147" t="n">
+      <c r="M150" t="n">
         <v>195116</v>
       </c>
-      <c r="N147" t="inlineStr">
+      <c r="N150" t="inlineStr">
         <is>
           <t>Bandai Namco Filmworks Channel</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr">
+      <c r="O150" t="inlineStr">
         <is>
           <t>2026-06-24T09:09:35</t>
         </is>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -2105,8 +2105,16 @@
           <t>杏子</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>クライマル</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>スキマスイッチ</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>https://www.animatetimes.com/tag/details.php?id=26463</t>
@@ -3317,7 +3325,7 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026年7月～ tvk（テレビ神奈川）にて</t>
+          <t>2026年7月8日（水）～ tvk（テレビ神奈川）にて</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7817,7 +7825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O150"/>
+  <dimension ref="A1:O152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10395,7 +10403,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>サイボーグ009 ネメシス</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -10403,7 +10411,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -10411,45 +10419,21 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>さよならララ</t>
+          <t>クライマル</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>いきものがかり</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=c4-6PwVRRj8</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>305568</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=c4-6PwVRRj8</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
-        <v>305568</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:21:38</t>
-        </is>
-      </c>
+          <t>スキマスイッチ</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -10470,7 +10454,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -10478,21 +10462,45 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hearts Glow</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Hana Hope</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+          <t>いきものがかり</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c4-6PwVRRj8</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>305568</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c4-6PwVRRj8</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>305568</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:21:38</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -10505,7 +10513,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>サンダー３</t>
+          <t>さよならララ</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -10521,12 +10529,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>しゅるれりら</t>
+          <t>Hearts Glow</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>音羽-otoha-</t>
+          <t>Hana Hope</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -10548,7 +10556,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>スーパーの裏でヤニ吸うふたり</t>
+          <t>サンダー３</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -10556,7 +10564,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -10564,45 +10572,21 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>イチジク煙</t>
+          <t>しゅるれりら</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ずっと真夜中でいいのに。</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ut889MZ9yNo</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>6309471</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>ずっと真夜中でいいのに。 ZUTOMAYO</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=OUmtsSroxns</t>
-        </is>
-      </c>
-      <c r="M54" t="n">
-        <v>594902</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Asmik Ace</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:21:56</t>
-        </is>
-      </c>
+          <t>音羽-otoha-</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -10623,7 +10607,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -10631,43 +10615,43 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>イチジク煙</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>ずっと真夜中でいいのに。</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9eo3M7-wAtU</t>
+          <t>https://www.youtube.com/watch?v=ut889MZ9yNo</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>867945</v>
+        <v>6309471</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t>ずっと真夜中でいいのに。 ZUTOMAYO</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OUmtsSroxns</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>594902</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
           <t>Asmik Ace</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9eo3M7-wAtU</t>
-        </is>
-      </c>
-      <c r="M55" t="n">
-        <v>867945</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Asmik Ace</t>
-        </is>
-      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-06-21T18:22:09</t>
+          <t>2026-06-21T18:21:56</t>
         </is>
       </c>
     </row>
@@ -10682,7 +10666,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
+          <t>スーパーの裏でヤニ吸うふたり</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -10690,7 +10674,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -10698,21 +10682,45 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>INUWASI</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+          <t>imase</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9eo3M7-wAtU</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>867945</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Asmik Ace</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9eo3M7-wAtU</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>867945</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Asmik Ace</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:09</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -10733,7 +10741,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -10741,12 +10749,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Holy Sweet Home</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>音感れもねゐど</t>
+          <t>INUWASI</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -10768,15 +10776,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
+          <t>捨てられ聖女の異世界ごはん旅 隠れスキルでキャンピングカーを召喚しました</t>
         </is>
       </c>
       <c r="D58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -10784,12 +10792,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>スノウドロップ</t>
+          <t>Holy Sweet Home</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Conton Candy</t>
+          <t>音感れもねゐど</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -10819,7 +10827,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -10827,12 +10835,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>水平線は僕の古傷</t>
+          <t>スノウドロップ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+          <t>Conton Candy</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -10854,15 +10862,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>正反対な君と僕 第2期</t>
+          <t>青春ブタ野郎はサンタクロースの夢を見ない</t>
         </is>
       </c>
       <c r="D60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -10870,45 +10878,21 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>メガネを外して</t>
+          <t>水平線は僕の古傷</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>乃紫</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=XOKQluw_YLU</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>3803168</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>乃紫</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
-        </is>
-      </c>
-      <c r="M60" t="n">
-        <v>1711081</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>SHOCHIKU anime Channel</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:22:34</t>
-        </is>
-      </c>
+          <t>広川卯月、赤城郁実、姫路紗良、霧島透子</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -10933,29 +10917,29 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>猫じゃらし</t>
+          <t>メガネを外して</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>7co</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
+          <t>https://www.youtube.com/watch?v=XOKQluw_YLU</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1711081</v>
+        <v>3803168</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>SHOCHIKU anime Channel</t>
+          <t>乃紫</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -10973,7 +10957,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-06-21T18:22:43</t>
+          <t>2026-06-21T18:22:34</t>
         </is>
       </c>
     </row>
@@ -10996,29 +10980,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ピュア feat. 橋本絵莉子</t>
+          <t>猫じゃらし</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>PAS TASTA</t>
+          <t>7co</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A6aH9jPW8ZY</t>
+          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>273328</v>
+        <v>1711081</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -11027,11 +11011,11 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A6aH9jPW8ZY</t>
+          <t>https://www.youtube.com/watch?v=JIn6WqZ_Fs4</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>273328</v>
+        <v>1711081</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -11040,7 +11024,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-06-21T18:22:55</t>
+          <t>2026-06-21T18:22:43</t>
         </is>
       </c>
     </row>
@@ -11067,25 +11051,49 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>運命の君</t>
+          <t>ピュア feat. 橋本絵莉子</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Mega Shinnosuke</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+          <t>PAS TASTA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A6aH9jPW8ZY</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>273328</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A6aH9jPW8ZY</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>273328</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:22:55</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -11098,7 +11106,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
+          <t>正反対な君と僕 第2期</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -11106,20 +11114,20 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>license</t>
+          <t>運命の君</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Redhair Rosy</t>
+          <t>Mega Shinnosuke</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -11149,7 +11157,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -11157,12 +11165,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>終わらない夜の守り方</t>
+          <t>license</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>インナージャーニー</t>
+          <t>Redhair Rosy</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -11184,7 +11192,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
+          <t>世界最強の後衛 ～迷宮国の新人探索者～</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -11192,7 +11200,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -11200,12 +11208,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>命短し対する乙女よ</t>
+          <t>終わらない夜の守り方</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>花冷え。</t>
+          <t>インナージャーニー</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -11235,7 +11243,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -11243,12 +11251,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>NEW GAME</t>
+          <t>命短し対する乙女よ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>halca</t>
+          <t>花冷え。</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -11270,7 +11278,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>対ありでした。～お嬢さまは格闘ゲームなんてしない～</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -11278,7 +11286,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -11286,12 +11294,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>NEW GAME</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SPYAIR</t>
+          <t>halca</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -11313,7 +11321,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>追放された転生重騎士はゲーム知識で無双する</t>
+          <t>地球大好き！きっくん</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -11321,7 +11329,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -11329,12 +11337,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lv.1 職業：⼈間</t>
+          <t>防衛ライン（だいたい平和です）</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ReoNa</t>
+          <t>まめぞう合唱団（えだまめ CV：新田恵海、そらまめ CV：田所あずさ）</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -11356,7 +11364,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -11372,12 +11380,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>火宴</t>
+          <t>Awake</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>原因は自分にある。</t>
+          <t>SPYAIR</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -11399,7 +11407,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>鉄鍋のジャン！</t>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -11415,12 +11423,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>泣いた悪魔</t>
+          <t>Lv.1 職業：⼈間</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>えむにみに</t>
+          <t>ReoNa</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -11442,7 +11450,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>手札が多めのビクトリア</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -11450,7 +11458,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -11458,45 +11466,21 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>縁のつき</t>
+          <t>火宴</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>KI_EN</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>140125</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
-        </is>
-      </c>
-      <c r="M72" t="n">
-        <v>140125</v>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:23:55</t>
-        </is>
-      </c>
+          <t>原因は自分にある。</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -11509,7 +11493,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>鉄鍋のジャン！</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -11517,7 +11501,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -11525,12 +11509,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>夏に重ねて</t>
+          <t>泣いた悪魔</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>DIALOGUE+</t>
+          <t>えむにみに</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -11552,7 +11536,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
+          <t>手札が多めのビクトリア</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -11568,21 +11552,45 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tilt</t>
+          <t>縁のつき</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>harmoe</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+          <t>KI_EN</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>140125</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-HNOXWE2wVU</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>140125</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:23:55</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11595,7 +11603,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>天は赤い河のほとり</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -11611,35 +11619,21 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>暁の空</t>
+          <t>夏に重ねて</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>七海ひろき</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=qpFcQ1Bek08</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>69452</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>VAP Official</t>
-        </is>
-      </c>
+          <t>DIALOGUE+</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:24:32</t>
-        </is>
-      </c>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11652,7 +11646,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>天幕のジャードゥーガル</t>
+          <t>転校先の清楚可憐な美少女が、昔男子と思って一緒に遊んだ幼馴染だった件</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -11660,7 +11654,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -11668,21 +11662,35 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>Tilt</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SEKAI NO OWARI</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+          <t>harmoe</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=d4TzLZZaeac</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>2770</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>harmoeオフィシャルYouTubeチャンネル</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-06-27T09:04:53</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11695,7 +11703,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天は赤い河のほとり</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -11711,43 +11719,33 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SHOW DOWN</t>
+          <t>暁の空</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>QWER</t>
+          <t>七海ひろき</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+          <t>https://www.youtube.com/watch?v=qpFcQ1Bek08</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>16839</v>
+        <v>69452</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
-        </is>
-      </c>
-      <c r="M77" t="n">
-        <v>16839</v>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
+          <t>VAP Official</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-06-25T09:05:01</t>
+          <t>2026-06-21T18:24:32</t>
         </is>
       </c>
     </row>
@@ -11762,7 +11760,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>盗掘王</t>
+          <t>天幕のジャードゥーガル</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -11770,7 +11768,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -11778,45 +11776,21 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>To Be Continued</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>QWER</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>16839</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
-        </is>
-      </c>
-      <c r="M78" t="n">
-        <v>16839</v>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>KADOKAWAanime</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>2026-06-25T09:05:10</t>
-        </is>
-      </c>
+          <t>SEKAI NO OWARI</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11829,7 +11803,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -11845,21 +11819,45 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ひとひら</t>
+          <t>SHOW DOWN</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>秦基博</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+          <t>QWER</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>16839</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>16839</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:05:01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11872,7 +11870,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
+          <t>盗掘王</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -11888,21 +11886,45 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>To Be Continued</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>櫻井優衣</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
+          <t>QWER</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>16839</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PVN8Pj_Ykyo</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>16839</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:05:10</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11915,7 +11937,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>トミカとトム</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -11923,7 +11945,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -11931,12 +11953,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>きみのたからもの</t>
+          <t>ひとひら</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>May J.</t>
+          <t>秦基博</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11958,7 +11980,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>透明な夜に駆ける君と、目に見えない恋をした。</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -11966,7 +11988,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -11974,12 +11996,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ユーレカ・エヴリカ</t>
+          <t>光</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>五阿弥ルナ</t>
+          <t>櫻井優衣</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -12001,7 +12023,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
+          <t>トミカとトム</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -12009,7 +12031,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -12017,45 +12039,21 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Soarin’</t>
+          <t>きみのたからもの</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Ginger Root</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>3207</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Lantis Channel</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
-        </is>
-      </c>
-      <c r="M83" t="n">
-        <v>3207</v>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>Lantis Channel</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:26:16</t>
-        </is>
-      </c>
+          <t>May J.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12068,7 +12066,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>猫と竜</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D84" t="b">
@@ -12084,35 +12082,21 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>猫日</t>
+          <t>ユーレカ・エヴリカ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>suis from ヨルシカ</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5Of2HNJa_gs</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>5618588</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>ヨルシカ / n-buna Official</t>
-        </is>
-      </c>
+          <t>五阿弥ルナ</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:06:03</t>
-        </is>
-      </c>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12125,7 +12109,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>猫と竜</t>
+          <t>二十世紀電氣目録-ユーレカ・エヴリカ-</t>
         </is>
       </c>
       <c r="D85" t="b">
@@ -12141,21 +12125,45 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ただいまの場所</t>
+          <t>Soarin’</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>shallm</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
+          <t>Ginger Root</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>3207</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Lantis Channel</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5rQWh9aIflw</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>3207</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Lantis Channel</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:26:16</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12168,7 +12176,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>パイの実 おしの森へようこそ！</t>
+          <t>猫と竜</t>
         </is>
       </c>
       <c r="D86" t="b">
@@ -12176,7 +12184,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -12184,21 +12192,35 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>パイしか勝たん！推しの森活</t>
+          <t>猫日</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>安保心結</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+          <t>suis from ヨルシカ</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5Of2HNJa_gs</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>5618588</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>ヨルシカ / n-buna Official</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>2026-06-26T09:06:03</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12211,7 +12233,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>猫と竜</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -12219,7 +12241,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -12227,45 +12249,21 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>フルボコ</t>
+          <t>ただいまの場所</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>WANIMA</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>402991</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>TMSアニメ公式チャンネル</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
-        </is>
-      </c>
-      <c r="M87" t="n">
-        <v>402991</v>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>TMSアニメ公式チャンネル</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:26:31</t>
-        </is>
-      </c>
+          <t>shallm</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12278,7 +12276,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>刃牙道 第2クール</t>
+          <t>パイの実 おしの森へようこそ！</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -12286,53 +12284,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>六ノ輪</t>
+          <t>パイしか勝たん！推しの森活</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Chevon</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>174316</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>TMSアニメ公式チャンネル</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
-        </is>
-      </c>
-      <c r="M88" t="n">
-        <v>174316</v>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>TMSアニメ公式チャンネル</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:26:42</t>
-        </is>
-      </c>
+          <t>安保心結</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12353,7 +12327,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -12361,21 +12335,21 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Mountain Top</t>
+          <t>フルボコ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Novel Core</t>
+          <t>WANIMA</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
+          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>294329</v>
+        <v>402991</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -12384,11 +12358,11 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
+          <t>https://www.youtube.com/watch?v=3KIPGQJh4vI</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>294329</v>
+        <v>402991</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -12397,7 +12371,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-06-21T18:26:53</t>
+          <t>2026-06-21T18:26:31</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12394,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -12428,21 +12402,21 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>KATANA</t>
+          <t>六ノ輪</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>三代目 J SOUL BROTHERS</t>
+          <t>Chevon</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>25824</v>
+        <v>174316</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -12451,11 +12425,11 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+          <t>https://www.youtube.com/watch?v=x0ygvWo5e3k</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>25824</v>
+        <v>174316</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -12464,7 +12438,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-06-21T18:27:05</t>
+          <t>2026-06-21T18:26:42</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12453,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>花織さんは転生しても喧嘩がしたい</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D91" t="b">
@@ -12487,7 +12461,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -12495,21 +12469,45 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ハイメンテナンスガール</t>
+          <t>Mountain Top</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>オーイシマサヨシ</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
+          <t>Novel Core</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>294329</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KKOr3xF2iOM</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>294329</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:26:53</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12522,7 +12520,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>花織さんは転生しても喧嘩がしたい</t>
+          <t>刃牙道 第2クール</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -12534,25 +12532,49 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ベリーグッド・エンカウント</t>
+          <t>KATANA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>内田真礼</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+          <t>三代目 J SOUL BROTHERS</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>25824</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1LBv6-z-0ok</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>25824</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>TMSアニメ公式チャンネル</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:27:05</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12565,7 +12587,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>花織さんは転生しても喧嘩がしたい</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -12581,35 +12603,21 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FLASHBULB</t>
+          <t>ハイメンテナンスガール</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=s1bZEnGAX8I</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>3841595</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
+          <t>オーイシマサヨシ</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>2026-06-25T09:06:54</t>
-        </is>
-      </c>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12622,7 +12630,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>花ざかりの君たちへ 第2期</t>
+          <t>花織さんは転生しても喧嘩がしたい</t>
         </is>
       </c>
       <c r="D94" t="b">
@@ -12638,35 +12646,21 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>花束</t>
+          <t>ベリーグッド・エンカウント</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=s1bZEnGAX8I</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>3841595</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Omoinotake</t>
-        </is>
-      </c>
+          <t>内田真礼</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>2026-06-25T09:07:22</t>
-        </is>
-      </c>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12679,7 +12673,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>バンドリ！ ゆめ∞みた</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -12695,43 +12689,33 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>これはぼくたちの生存のあらすじ</t>
+          <t>FLASHBULB</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>夢限大みゅーたいぷ</t>
+          <t>Omoinotake</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Ech7Tj8ga0Y</t>
+          <t>https://www.youtube.com/watch?v=s1bZEnGAX8I</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>124089</v>
+        <v>3841595</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>BanG Dream Channel☆</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Ech7Tj8ga0Y</t>
-        </is>
-      </c>
-      <c r="M95" t="n">
-        <v>124089</v>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>BanG Dream Channel☆</t>
-        </is>
-      </c>
+          <t>Omoinotake</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-06-24T09:06:31</t>
+          <t>2026-06-25T09:06:54</t>
         </is>
       </c>
     </row>
@@ -12746,7 +12730,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>花ざかりの君たちへ 第2期</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -12754,7 +12738,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -12762,21 +12746,35 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>マデュアル↔ハート</t>
+          <t>花束</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+          <t>Omoinotake</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s1bZEnGAX8I</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>3841595</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Omoinotake</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:07:22</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12789,7 +12787,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
+          <t>バンドリ！ ゆめ∞みた</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -12797,7 +12795,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -12805,21 +12803,45 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ハンドメイド</t>
+          <t>これはぼくたちの生存のあらすじ</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>仲村宗悟</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
+          <t>夢限大みゅーたいぷ</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ech7Tj8ga0Y</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>124089</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>BanG Dream Channel☆</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ech7Tj8ga0Y</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>124089</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>BanG Dream Channel☆</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>2026-06-24T09:06:31</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12832,7 +12854,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -12848,35 +12870,21 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Q.E.D.</t>
+          <t>マデュアル↔ハート</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>小倉唯</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=LFS_qg2JrPI</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>11323</v>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Yui Ogura YouTube OFFICIAL CHANNEL</t>
-        </is>
-      </c>
+          <t>メロディ・ウェーブ(CV：宮本侑芽) ルシアナ・ルトルバーグ(CV：大久保瑠美)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:27:45</t>
-        </is>
-      </c>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12889,7 +12897,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
+          <t>ヒロイン？聖女？いいえ、オールワークスメイドです（誇）！</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -12905,35 +12913,21 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>グッバイ・ララバイ</t>
+          <t>ハンドメイド</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>大西亜玖璃</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=MzjYjMBpQ6g</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
-        <v>4603</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>大西亜玖璃 - Aguri Onishi</t>
-        </is>
-      </c>
+          <t>仲村宗悟</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:27:58</t>
-        </is>
-      </c>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12946,7 +12940,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -12962,25 +12956,25 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Q.E.D.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>milet</t>
+          <t>小倉唯</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nR_vqhD2rGM</t>
+          <t>https://www.youtube.com/watch?v=LFS_qg2JrPI</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>451401</v>
+        <v>11323</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>TOHO animation</t>
+          <t>Yui Ogura YouTube OFFICIAL CHANNEL</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -12988,7 +12982,7 @@
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-06-21T18:28:12</t>
+          <t>2026-06-21T18:27:45</t>
         </is>
       </c>
     </row>
@@ -13003,7 +12997,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ブチ切れ令嬢は報復を誓いました。 ～魔導書の力で祖国を叩き潰します～</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -13011,7 +13005,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -13019,21 +13013,35 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>FREEZE ME UP</t>
+          <t>グッバイ・ララバイ</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>SiM</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+          <t>大西亜玖璃</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MzjYjMBpQ6g</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>4603</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>大西亜玖璃 - Aguri Onishi</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:27:58</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -13046,7 +13054,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BLACK TORCH</t>
+          <t>ふつつかな悪女ではございますが～雛宮蝶鼠とりかえ伝～</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -13054,7 +13062,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -13062,21 +13070,35 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Groooovy</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>I Don't Like Mondays.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+          <t>milet</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nR_vqhD2rGM</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>451401</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:28:12</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13089,7 +13111,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>プラノサウルス ガチコセイブツ部</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D103" t="b">
@@ -13097,7 +13119,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -13105,21 +13127,45 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ガチde古生</t>
+          <t>FREEZE ME UP</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>リンクルプラネット</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
+          <t>SiM</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2FjRzlo5zHI</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>25222</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>ShoProアニメチャンネル</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2FjRzlo5zHI</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>25222</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ShoProアニメチャンネル</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>2026-06-27T09:06:42</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13132,7 +13178,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BLEACH 千年血戦篇-禍進譚-</t>
+          <t>BLACK TORCH</t>
         </is>
       </c>
       <c r="D104" t="b">
@@ -13140,7 +13186,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -13148,12 +13194,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I-BULL</t>
+          <t>Groooovy</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>jo0ji</t>
+          <t>I Don't Like Mondays.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -13175,7 +13221,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BLEACH 千年血戦篇-禍進譚-</t>
+          <t>プラノサウルス ガチコセイブツ部</t>
         </is>
       </c>
       <c r="D105" t="b">
@@ -13183,7 +13229,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -13191,12 +13237,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>螺旋</t>
+          <t>ガチde古生</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9Lana</t>
+          <t>リンクルプラネット</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13218,7 +13264,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>文豪ストレイドッグス わん！２</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="D106" t="b">
@@ -13226,7 +13272,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -13234,12 +13280,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>僕ら～芥川龍之介Ver.～</t>
+          <t>I-BULL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>芥川龍之介（CV.小野賢章）</t>
+          <t>jo0ji</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13261,7 +13307,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>BLEACH 千年血戦篇-禍進譚-</t>
         </is>
       </c>
       <c r="D107" t="b">
@@ -13269,7 +13315,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -13277,12 +13323,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>○✕△□</t>
+          <t>螺旋</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>浪漫派マシュマロ</t>
+          <t>9Lana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13304,7 +13350,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
+          <t>文豪ストレイドッグス わん！２</t>
         </is>
       </c>
       <c r="D108" t="b">
@@ -13320,12 +13366,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Firetail</t>
+          <t>僕ら～芥川龍之介Ver.～</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>チョーキューメイ</t>
+          <t>芥川龍之介（CV.小野賢章）</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13347,7 +13393,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D109" t="b">
@@ -13363,12 +13409,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Blacker Co., Ltd.</t>
+          <t>○✕△□</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>イツカ▶</t>
+          <t>浪漫派マシュマロ</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13390,7 +13436,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
+          <t>ヘルモード ～やり込み好きのゲーマーは廃設定の異世界で無双する～ 2nd Season</t>
         </is>
       </c>
       <c r="D110" t="b">
@@ -13406,12 +13452,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Elegy of the Enemies</t>
+          <t>Firetail</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>The Canbellz</t>
+          <t>チョーキューメイ</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13441,20 +13487,20 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>白い蝶が飛んだら</t>
+          <t>Blacker Co., Ltd.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
+          <t>イツカ▶</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13476,7 +13522,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D112" t="b">
@@ -13484,7 +13530,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -13492,12 +13538,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>会心の一劇</t>
+          <t>Elegy of the Enemies</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ももいろクローバーZ</t>
+          <t>The Canbellz</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13519,7 +13565,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>炎の闘球女 ドッジ弾子</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌 第2クール</t>
         </is>
       </c>
       <c r="D113" t="b">
@@ -13531,16 +13577,16 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Welcome to あざとさワールド</t>
+          <t>白い蝶が飛んだら</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>i☆Ris</t>
+          <t>イツカ▶ feat. Dr. Washington | Special Guest Guitar:Tsuyoshi Ujiki</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13562,7 +13608,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D114" t="b">
@@ -13578,35 +13624,21 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CRIMSON BULLET</t>
+          <t>会心の一劇</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>水樹奈々</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>590624</v>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
-        </is>
-      </c>
+          <t>ももいろクローバーZ</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:29:37</t>
-        </is>
-      </c>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13619,7 +13651,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
+          <t>炎の闘球女 ドッジ弾子</t>
         </is>
       </c>
       <c r="D115" t="b">
@@ -13635,35 +13667,21 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ephemeral</t>
+          <t>Welcome to あざとさワールド</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>青木陽菜</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>590624</v>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
-        </is>
-      </c>
+          <t>i☆Ris</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:29:56</t>
-        </is>
-      </c>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13676,7 +13694,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D116" t="b">
@@ -13684,7 +13702,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -13692,21 +13710,35 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>とけて煌る</t>
+          <t>CRIMSON BULLET</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>neNna</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+          <t>水樹奈々</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>590624</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:29:37</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13719,7 +13751,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>魔法少女リリカルなのは EXCEEDS Gun Blaze Vengeance</t>
         </is>
       </c>
       <c r="D117" t="b">
@@ -13727,7 +13759,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -13735,21 +13767,35 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Windmaker</t>
+          <t>Ephemeral</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>花耶</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+          <t>青木陽菜</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TzvGIjaMbYE</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>590624</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>魔法少女リリカルなのは YouTube OFFICIAL CHANNEL</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:29:56</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13762,7 +13808,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
+          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした</t>
         </is>
       </c>
       <c r="D118" t="b">
@@ -13778,12 +13824,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>アンノウンミー</t>
+          <t>とけて煌る</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+          <t>neNna</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13805,7 +13851,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D119" t="b">
@@ -13821,45 +13867,21 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>決意の唄</t>
+          <t>Windmaker</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>大原ゆい子</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=hZ6TnKvB2rc</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>12105753</v>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>大原ゆい子Official YouTube</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=PINgF6rCuME</t>
-        </is>
-      </c>
-      <c r="M119" t="n">
-        <v>2457533</v>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>TOHO animation</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:30:35</t>
-        </is>
-      </c>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13872,7 +13894,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
+          <t>無自覚聖女は今日も無意識に力を垂れ流す</t>
         </is>
       </c>
       <c r="D120" t="b">
@@ -13888,35 +13910,21 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>祈り、終われば</t>
+          <t>アンノウンミー</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>中島美嘉</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ODxfIvSgWuo</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>1140774</v>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>TOHO animation</t>
-        </is>
-      </c>
+          <t>ウタヒメドリーム オールスターズ【夢咲いぶき（CV:山﨑玲奈） 桜木舞華（CV:鈴木杏奈） 真白清美（CV:其原有沙） HiREN（CV:花耶） 水月ひかり（CV:礒部花凜） 高木凛（CV:鷲見友美ジェナ） 萩原ひまわり（CV:倉知玲鳳） SAKURAKO（CV:竹内夢）】</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:31:08</t>
-        </is>
-      </c>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13929,7 +13937,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D121" t="b">
@@ -13945,43 +13953,43 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>メビウス</t>
+          <t>決意の唄</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>大原ゆい子</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vJzWWkigrU8</t>
+          <t>https://www.youtube.com/watch?v=hZ6TnKvB2rc</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>32222</v>
+        <v>12105753</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>家入レオ</t>
+          <t>大原ゆい子Official YouTube</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5QGZX_Kky4I</t>
+          <t>https://www.youtube.com/watch?v=PINgF6rCuME</t>
         </is>
       </c>
       <c r="M121" t="n">
-        <v>27576</v>
+        <v>2457533</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>leafstamp</t>
+          <t>TOHO animation</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-06-21T18:31:32</t>
+          <t>2026-06-21T18:30:35</t>
         </is>
       </c>
     </row>
@@ -13996,7 +14004,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>メビウス・ダスト</t>
+          <t>無職転生Ⅲ ～異世界行ったら本気だす～</t>
         </is>
       </c>
       <c r="D122" t="b">
@@ -14012,21 +14020,35 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ジレンマ</t>
+          <t>祈り、終われば</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>冨岡愛</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+          <t>中島美嘉</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ODxfIvSgWuo</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>1140774</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>TOHO animation</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:31:08</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14039,7 +14061,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D123" t="b">
@@ -14055,33 +14077,43 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>なんもねえ</t>
+          <t>メビウス</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>忘れらんねえよ</t>
+          <t>家入レオ</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
+          <t>https://www.youtube.com/watch?v=vJzWWkigrU8</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>480871</v>
+        <v>32222</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>家入レオ</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5QGZX_Kky4I</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>27576</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>leafstamp</t>
+        </is>
+      </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>2026-06-21T18:32:14</t>
+          <t>2026-06-21T18:31:32</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14128,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ヤニねこ</t>
+          <t>メビウス・ダスト</t>
         </is>
       </c>
       <c r="D124" t="b">
@@ -14112,35 +14144,21 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>煙とブルー</t>
+          <t>ジレンマ</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ネクライトーキー</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>480871</v>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
-        </is>
-      </c>
+          <t>冨岡愛</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:32:32</t>
-        </is>
-      </c>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14153,7 +14171,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>闇芝居 十七期</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D125" t="b">
@@ -14161,7 +14179,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -14169,21 +14187,35 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>闇芝居のブルース</t>
+          <t>なんもねえ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>風輪（徳間ジャパンコミュニケーションズ）</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
+          <t>忘れらんねえよ</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>480871</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:32:14</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14196,7 +14228,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>ヤニねこ</t>
         </is>
       </c>
       <c r="D126" t="b">
@@ -14204,7 +14236,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -14212,25 +14244,25 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Why? RED induction</t>
+          <t>煙とブルー</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID</t>
+          <t>ネクライトーキー</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RMaOR0Pyfts</t>
+          <t>https://www.youtube.com/watch?v=ydK2WdTAOgU</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>50838</v>
+        <v>480871</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>MYTH &amp; ROID Official Channel</t>
+          <t>TVアニメ『ヤニねこ』公式【ハメちゃんねる】</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -14238,7 +14270,7 @@
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-06-21T18:33:01</t>
+          <t>2026-06-21T18:32:32</t>
         </is>
       </c>
     </row>
@@ -14253,7 +14285,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>幼女戦記Ⅱ</t>
+          <t>闇芝居 十七期</t>
         </is>
       </c>
       <c r="D127" t="b">
@@ -14269,12 +14301,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Weiter! Weiter!</t>
+          <t>闇芝居のブルース</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
+          <t>風輪（徳間ジャパンコミュニケーションズ）</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14296,7 +14328,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D128" t="b">
@@ -14312,43 +14344,33 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>YOAKE</t>
+          <t>Why? RED induction</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>blank paper</t>
+          <t>MYTH &amp; ROID</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
+          <t>https://www.youtube.com/watch?v=RMaOR0Pyfts</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>603666</v>
+        <v>50838</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
-        </is>
-      </c>
-      <c r="M128" t="n">
-        <v>603666</v>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
-        </is>
-      </c>
+          <t>MYTH &amp; ROID Official Channel</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-06-21T18:33:22</t>
+          <t>2026-06-21T18:33:01</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14385,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>鎧真伝サムライトルーパー 第2クール</t>
+          <t>幼女戦記Ⅱ</t>
         </is>
       </c>
       <c r="D129" t="b">
@@ -14371,43 +14393,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>BAD遺伝子</t>
+          <t>Weiter! Weiter!</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Dannie May</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
-        </is>
-      </c>
-      <c r="J129" t="n">
-        <v>66350</v>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
-        </is>
-      </c>
+          <t>ターニャ・デグレチャフ（CV：悠木碧）</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:33:34</t>
-        </is>
-      </c>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14428,7 +14436,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -14436,34 +14444,34 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>YOAKE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>blank paper</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aw45Q_mr0_M</t>
+          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>9441868</v>
+        <v>603666</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>ONE OR EIGHT</t>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VJflo-z7e7A</t>
+          <t>https://www.youtube.com/watch?v=kHUPdA8H6qk</t>
         </is>
       </c>
       <c r="M130" t="n">
-        <v>151043</v>
+        <v>603666</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -14472,7 +14480,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2026-06-21T18:33:47</t>
+          <t>2026-06-21T18:33:22</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14503,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -14503,12 +14511,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ばけもん</t>
+          <t>BAD遺伝子</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>カラノア</t>
+          <t>Dannie May</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -14529,7 +14537,7 @@
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-06-21T18:34:00</t>
+          <t>2026-06-21T18:33:34</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14552,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D132" t="b">
@@ -14552,7 +14560,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -14560,21 +14568,45 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>＋ENCOUNT</t>
+          <t>POWER</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+          <t>ONE OR EIGHT</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aw45Q_mr0_M</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>9441868</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>ONE OR EIGHT</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VJflo-z7e7A</t>
+        </is>
+      </c>
+      <c r="M132" t="n">
+        <v>151043</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:33:47</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14587,7 +14619,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
+          <t>鎧真伝サムライトルーパー 第2クール</t>
         </is>
       </c>
       <c r="D133" t="b">
@@ -14599,25 +14631,39 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>憧憬</t>
+          <t>ばけもん</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>TrySail</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+          <t>カラノア</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OKEoQo3cGVg</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>66350</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>TVアニメ『鎧真伝サムライトルーパー』公式</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:34:00</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14630,11 +14676,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -14646,12 +14692,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>虹色Passions！</t>
+          <t>＋ENCOUNT</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>虹ヶ咲学園スクールアイドル同好会</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14673,11 +14719,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
+          <t>落第賢者の学院無双～二度目の転生、Sランクチート魔術師冒険録～</t>
         </is>
       </c>
       <c r="D135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -14689,12 +14735,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>NEO SKY, NEO MAP!</t>
+          <t>憧憬</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>虹ヶ咲学園スクールアイドル同好会</t>
+          <t>TrySail</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14716,11 +14762,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="D136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -14732,12 +14778,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Wonder</t>
+          <t>虹色Passions！</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>CROWN HEAD</t>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14759,11 +14805,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>領民0人スタートの辺境領主様</t>
+          <t>ラブライブ！虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="D137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -14775,12 +14821,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>星降る夜の約束</t>
+          <t>NEO SKY, NEO MAP!</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>虹ヶ咲学園スクールアイドル同好会</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14802,7 +14848,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D138" t="b">
@@ -14818,12 +14864,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>ダラダラ♡ダンシング</t>
+          <t>Wonder</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+          <t>CROWN HEAD</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14845,7 +14891,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>令和のダラさん</t>
+          <t>領民0人スタートの辺境領主様</t>
         </is>
       </c>
       <c r="D139" t="b">
@@ -14861,12 +14907,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>ひなたぼっこ</t>
+          <t>星降る夜の約束</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>REIRIE</t>
+          <t>花耶</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14888,7 +14934,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D140" t="b">
@@ -14904,35 +14950,21 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Not a Hero</t>
+          <t>ダラダラ♡ダンシング</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>藍月なくる&amp;棗いつき</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9-RVzXLF53U</t>
-        </is>
-      </c>
-      <c r="J140" t="n">
-        <v>78910</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>Itsuki Natsume / 棗いつき</t>
-        </is>
-      </c>
+          <t>ダラさん（CV：田村睦心） 三⼗⽊⾕⽇向（CV：津田美波） 三⼗⽊⾕薫（CV：寺澤百花） ナレーション（CV：てらそままさき）</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:35:08</t>
-        </is>
-      </c>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14945,7 +14977,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LV999の村人</t>
+          <t>令和のダラさん</t>
         </is>
       </c>
       <c r="D141" t="b">
@@ -14961,21 +14993,45 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ひなたぼっこ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>ゆきむら。</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
+          <t>REIRIE</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HjtjOaJz-_U</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>15548</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HjtjOaJz-_U</t>
+        </is>
+      </c>
+      <c r="M141" t="n">
+        <v>15548</v>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>KADOKAWAanime</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>2026-06-27T09:08:38</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14988,7 +15044,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ワールド イズ ダンシング</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D142" t="b">
@@ -15004,43 +15060,33 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>終宵</t>
+          <t>Not a Hero</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>マカロニえんぴつ</t>
+          <t>藍月なくる&amp;棗いつき</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
+          <t>https://www.youtube.com/watch?v=9-RVzXLF53U</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>262519</v>
+        <v>78910</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>SHOCHIKU anime Channel</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
-        </is>
-      </c>
-      <c r="M142" t="n">
-        <v>262519</v>
-      </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>SHOCHIKU anime Channel</t>
-        </is>
-      </c>
+          <t>Itsuki Natsume / 棗いつき</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-06-21T18:35:26</t>
+          <t>2026-06-21T18:35:08</t>
         </is>
       </c>
     </row>
@@ -15055,7 +15101,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ONE PIECE HEROINES</t>
+          <t>LV999の村人</t>
         </is>
       </c>
       <c r="D143" t="b">
@@ -15063,7 +15109,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>主題歌</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -15071,58 +15117,34 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>ONE PIECE（モノクロ版）</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>電子書籍（コミック）</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=6hRjsvdINgg</t>
-        </is>
-      </c>
-      <c r="J143" t="n">
-        <v>17920416</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>ONE PIECE Official YouTube Channel</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=YFbno_aPm0w</t>
-        </is>
-      </c>
-      <c r="M143" t="n">
-        <v>27924515</v>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>ONE PIECE Official YouTube Channel</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:35:55</t>
-        </is>
-      </c>
+          <t>ゆきむら。</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>帰還者の魔法は特別です 第2期</t>
+          <t>ワールド イズ ダンシング</t>
         </is>
       </c>
       <c r="D144" t="b">
@@ -15138,34 +15160,58 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sorrow</t>
+          <t>終宵</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
+          <t>マカロニえんぴつ</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>262519</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zu45LJG7Chs</t>
+        </is>
+      </c>
+      <c r="M144" t="n">
+        <v>262519</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>SHOCHIKU anime Channel</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:35:26</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>5947</v>
+        <v>5806</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026秋アニメ</t>
+          <t>2026夏アニメ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>獣王武神ダンデヴァイン</t>
+          <t>ONE PIECE HEROINES</t>
         </is>
       </c>
       <c r="D145" t="b">
@@ -15173,7 +15219,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>主題歌</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -15181,21 +15227,45 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>曲名未発表</t>
+          <t>ONE PIECE（モノクロ版）</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>西川貴教</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
+          <t>電子書籍（コミック）</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6hRjsvdINgg</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>17920416</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>ONE PIECE Official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YFbno_aPm0w</t>
+        </is>
+      </c>
+      <c r="M145" t="n">
+        <v>27924515</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>ONE PIECE Official YouTube Channel</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:35:55</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15208,7 +15278,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>帰還者の魔法は特別です 第2期</t>
         </is>
       </c>
       <c r="D146" t="b">
@@ -15224,12 +15294,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Flare of Soul</t>
+          <t>Sorrow</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>花耶</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15251,7 +15321,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>転生した大聖女は、聖女であることをひた隠す</t>
+          <t>獣王武神ダンデヴァイン</t>
         </is>
       </c>
       <c r="D147" t="b">
@@ -15259,7 +15329,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -15267,12 +15337,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>STELLAR</t>
+          <t>曲名未発表</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>ウタヒメドリーム オールスターズ</t>
+          <t>西川貴教</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15294,7 +15364,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>魔法少女育成計画restart</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="D148" t="b">
@@ -15310,35 +15380,21 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>No tears here</t>
+          <t>Flare of Soul</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>茅原実里</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-PX7FqZ55tE</t>
-        </is>
-      </c>
-      <c r="J148" t="n">
-        <v>105042</v>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>TVアニメ「魔法少女育成計画restart」公式チャンネル</t>
-        </is>
-      </c>
+          <t>花耶</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:36:51</t>
-        </is>
-      </c>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15351,7 +15407,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>魔法の姉妹ルルットリリィ 第2クール</t>
+          <t>転生した大聖女は、聖女であることをひた隠す</t>
         </is>
       </c>
       <c r="D149" t="b">
@@ -15359,7 +15415,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -15367,45 +15423,21 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bubee</t>
+          <t>STELLAR</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>ILLIT</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=sNIntrw0m-g</t>
-        </is>
-      </c>
-      <c r="J149" t="n">
-        <v>66633</v>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Bandai Namco Filmworks Channel</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=sNIntrw0m-g</t>
-        </is>
-      </c>
-      <c r="M149" t="n">
-        <v>66633</v>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>Bandai Namco Filmworks Channel</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>2026-06-24T09:09:26</t>
-        </is>
-      </c>
+          <t>ウタヒメドリーム オールスターズ</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15418,7 +15450,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>魔法の姉妹ルルットリリィ 第2クール</t>
+          <t>魔法少女育成計画restart</t>
         </is>
       </c>
       <c r="D150" t="b">
@@ -15426,7 +15458,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -15434,41 +15466,165 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
+          <t>No tears here</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>茅原実里</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-PX7FqZ55tE</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>105042</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>TVアニメ「魔法少女育成計画restart」公式チャンネル</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>2026-06-21T18:36:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>魔法の姉妹ルルットリリィ 第2クール</t>
+        </is>
+      </c>
+      <c r="D151" t="b">
+        <v>0</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Bubee</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>ILLIT</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sNIntrw0m-g</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>66633</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Bandai Namco Filmworks Channel</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sNIntrw0m-g</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
+        <v>66633</v>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Bandai Namco Filmworks Channel</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>2026-06-24T09:09:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>5947</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026秋アニメ</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>魔法の姉妹ルルットリリィ 第2クール</t>
+        </is>
+      </c>
+      <c r="D152" t="b">
+        <v>0</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
           <t>Calling</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="H152" t="inlineStr">
         <is>
           <t>ルルットリリィ（こんぺとリリィ（CV.橘めい）、ましゅールル（CV.小鹿なお））</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7oNuxIfJqiI</t>
         </is>
       </c>
-      <c r="J150" t="n">
+      <c r="J152" t="n">
         <v>195116</v>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="K152" t="inlineStr">
         <is>
           <t>Bandai Namco Filmworks Channel</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7oNuxIfJqiI</t>
         </is>
       </c>
-      <c r="M150" t="n">
+      <c r="M152" t="n">
         <v>195116</v>
       </c>
-      <c r="N150" t="inlineStr">
+      <c r="N152" t="inlineStr">
         <is>
           <t>Bandai Namco Filmworks Channel</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr">
+      <c r="O152" t="inlineStr">
         <is>
           <t>2026-06-24T09:09:35</t>
         </is>

--- a/data/anime_list.xlsx
+++ b/data/anime_list.xlsx
@@ -7946,29 +7946,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>52344</v>
+        <v>53914</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>アズールレーン</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bFCBwBCTCBU</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>26101</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>SHOCHIKU anime Channel</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-06-21T18:13:31</t>
+          <t>2026-06-29T09:00:17</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8275,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>22060</v>
+        <v>24042</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8298,7 +8288,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>22060</v>
+        <v>24042</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8307,7 +8297,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-06-21T18:14:06</t>
+          <t>2026-06-29T09:00:48</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8342,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>20903</v>
+        <v>22520</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -8365,7 +8355,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>20903</v>
+        <v>22520</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -8374,7 +8364,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-06-21T18:14:12</t>
+          <t>2026-06-29T09:00:53</t>
         </is>
       </c>
     </row>
@@ -8415,11 +8405,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8So8zgJAYMI</t>
+          <t>https://www.youtube.com/watch?v=X_knFby9AJc</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6811</v>
+        <v>35315</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8428,11 +8418,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8So8zgJAYMI</t>
+          <t>https://www.youtube.com/watch?v=X_knFby9AJc</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>6811</v>
+        <v>35315</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8441,7 +8431,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-06-21T18:14:24</t>
+          <t>2026-06-29T09:01:02</t>
         </is>
       </c>
     </row>
@@ -8480,37 +8470,13 @@
           <t>汐れいら</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=6fUdDUk-FZQ</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>3487</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>アニプレックス チャンネル</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=6fUdDUk-FZQ</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>3487</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>アニプレックス チャンネル</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2026-06-21T18:14:33</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8940,7 +8906,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>362547</v>
+        <v>365426</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -8952,7 +8918,7 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-06-21T18:16:17</t>
+          <t>2026-06-29T09:02:33</t>
         </is>
       </c>
     </row>
@@ -8991,13 +8957,37 @@
           <t>ユニコーン</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7BDs9fUOFu8</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>9248</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NBCUniversal Anime/Music</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7BDs9fUOFu8</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>9248</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>NBCUniversal Anime/Music</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-06-29T09:02:42</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9034,13 +9024,37 @@
           <t>BLUE ENCOUNT</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1Q1Kgixu70g</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>899</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NBCUniversal Anime/Music</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1Q1Kgixu70g</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>899</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>NBCUniversal Anime/Music</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-06-29T09:02:51</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -9083,7 +9097,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13154</v>
+        <v>19123</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -9095,7 +9109,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-06-21T18:16:54</t>
+          <t>2026-06-29T09:03:02</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9154,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>16610711</v>
+        <v>16727541</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -9153,7 +9167,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>223037</v>
+        <v>224181</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -9162,7 +9176,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-06-21T18:17:17</t>
+          <t>2026-06-29T09:03:21</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9350,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1851</v>
+        <v>2093</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -9348,7 +9362,7 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-06-21T18:17:42</t>
+          <t>2026-06-29T09:03:43</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9536,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>466412</v>
+        <v>470198</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -9535,7 +9549,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>466412</v>
+        <v>470198</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -9544,7 +9558,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-06-21T18:18:12</t>
+          <t>2026-06-29T09:04:09</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9689,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>11744</v>
+        <v>13244</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -9688,7 +9702,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>11744</v>
+        <v>13244</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -9697,7 +9711,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-06-21T18:18:28</t>
+          <t>2026-06-29T09:04:26</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9756,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>13489</v>
+        <v>14672</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -9755,7 +9769,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>13489</v>
+        <v>14672</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -9764,7 +9778,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-06-21T18:18:33</t>
+          <t>2026-06-29T09:04:30</t>
         </is>
       </c>
     </row>
@@ -9805,11 +9819,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fuXZMQAD9vU</t>
+          <t>https://www.youtube.com/watch?v=R3V4sAXUJ-g</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>12852008</v>
+        <v>66192472</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -9821,7 +9835,7 @@
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-06-21T18:19:08</t>
+          <t>2026-06-29T09:04:58</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9880,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>295392</v>
+        <v>296633</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -9878,7 +9892,7 @@
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-06-21T18:19:26</t>
+          <t>2026-06-29T09:05:13</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9937,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>295392</v>
+        <v>296633</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -9935,7 +9949,7 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-06-21T18:19:43</t>
+          <t>2026-06-29T09:05:27</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10080,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>6682341</v>
+        <v>6747037</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -10078,7 +10092,7 @@
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-06-21T18:20:22</t>
+          <t>2026-06-29T09:06:00</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10137,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>42562</v>
+        <v>53817</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -10136,7 +10150,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -10145,7 +10159,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-06-21T18:20:33</t>
+          <t>2026-06-29T09:06:09</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10333,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>4032</v>
+        <v>4309</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -10331,7 +10345,7 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-06-21T18:21:04</t>
+          <t>2026-06-29T09:06:39</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10390,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>13236</v>
+        <v>19444</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -10388,7 +10402,7 @@
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-06-21T18:21:26</t>
+          <t>2026-06-29T09:06:57</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10490,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>305568</v>
+        <v>310640</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -10489,7 +10503,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>305568</v>
+        <v>310640</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -10498,7 +10512,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-06-21T18:21:38</t>
+          <t>2026-06-29T09:07:13</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10643,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>6309471</v>
+        <v>6358421</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -10642,7 +10656,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>594902</v>
+        <v>631848</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -10651,7 +10665,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-06-21T18:21:56</t>
+          <t>2026-06-29T09:07:37</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10710,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>867945</v>
+        <v>993597</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -10709,7 +10723,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>867945</v>
+        <v>993597</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -10718,7 +10732,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-06-21T18:22:09</t>
+          <t>2026-06-29T09:07:46</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10949,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>3803168</v>
+        <v>3923215</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -10948,7 +10962,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>1711081</v>
+        <v>1763982</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -10957,7 +10971,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-06-21T18:22:34</t>
+          <t>2026-06-29T09:08:11</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11016,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>1711081</v>
+        <v>1763982</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -11015,7 +11029,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>1711081</v>
+        <v>1763982</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -11024,7 +11038,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-06-21T18:22:43</t>
+          <t>2026-06-29T09:08:20</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11083,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>273328</v>
+        <v>278831</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -11082,7 +11096,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>273328</v>
+        <v>278831</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -11091,7 +11105,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-06-21T18:22:55</t>
+          <t>2026-06-29T09:08:30</t>
         </is>
       </c>
     </row>
@@ -11566,7 +11580,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>140125</v>
+        <v>154655</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -11579,7 +11593,7 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>140125</v>
+        <v>154655</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -11588,7 +11602,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-06-21T18:23:55</t>
+          <t>2026-06-29T09:09:43</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11747,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>69452</v>
+        <v>152288</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -11745,7 +11759,7 @@
       <c r